--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O309"/>
+  <dimension ref="A1:O310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19429,7 +19429,6 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19460,8 +19459,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
-      <c r="L307" t="inlineStr"/>
       <c r="M307" t="inlineStr">
         <is>
           <t>review</t>
@@ -19494,7 +19491,6 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19525,8 +19521,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
-      <c r="L308" t="inlineStr"/>
       <c r="M308" t="inlineStr">
         <is>
           <t>review</t>
@@ -19559,7 +19553,6 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19590,8 +19583,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
-      <c r="L309" t="inlineStr"/>
       <c r="M309" t="inlineStr">
         <is>
           <t>review</t>
@@ -19603,6 +19594,71 @@
         </is>
       </c>
       <c r="O309" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>auto-845442d2f0b8</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Jericoacoara wird dritter Fraport-Flughafen in Brasilien</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Fraport expandiert in Südamerika. Der Frankfurter Flughafenbetreiber übernimmt den Betrieb eines dritten Flughafens ins Brasilien - unter dem Dach einer bestehenden Konzession für den Flughafen Fortaleza betreibt Fraport jetzt auch den Airport in Jericoacoara. Die Konzession läuft bis 2047.</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53542/Jericoacoara-wird-dritter-Fraport-Flughafen-in-Brasilien.html</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O310"/>
+  <dimension ref="A1:O324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19615,7 +19615,6 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19646,8 +19645,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
-      <c r="L310" t="inlineStr"/>
       <c r="M310" t="inlineStr">
         <is>
           <t>review</t>
@@ -19659,6 +19656,916 @@
         </is>
       </c>
       <c r="O310" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>auto-7fe26f918c22</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Amazon Air setzt Zusammenarbeit mit 21 Air nach tödlichem Unfall in Miami aus</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Amazon Air hat die Zusammenarbeit mit der Frachtfluggesellschaft 21 Air nach dem tödlichen Unfall einer Boeing 767 in Miami vorerst ausgesetzt. Das Flugzeug war am 6. September als Flug 7598 mit Amazon-Paketen an Bord bei der Landung über das Ende der Piste hinausgerollt. Es kam rund 396 Meter hinter der Landebahn mit einem Fahrzeug eines Flugzeugreinigungsunternehmens zusammen.</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/amazon-air-setzt-zusammenarbeit-mit-21-air-nach-toedlichem-unfall-in-miami-aus/lymhrmx</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr"/>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>auto-81dccab86981</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Luftfahrt Symposium 2026</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Bei dem Symposium werden Expertinnen und Experten aus Luftfahrt, Politik und Wirtschaft über die Zukunft der österreichischen Luftfahrt sprechen. Im Fokus stehen die Auswirkungen globaler Krisen und steigender Kosten sowie die Frage, wie Österreich seinen Luftfahrtstandort stärken und Wettbewerbsfähig halten kann.</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ads/luftfahrt-symposium-2026/p95q41m</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>auto-9ddbce2dae65</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Air Montenegro einziger Bieter für sechs subventionierte Strecken - darunter auch die nach Frankfurt</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Air Montenegro ist laut dem Portal See News der einzige Bieter für sechs staatlich subventionierte internationale Strecken ab Podgorica. Die Ausschreibung hat einen Wert von 4,79 Millionen Euro und umfasst Verbindungen nach Brüssel, Paris, Amsterdam, Zagreb, Frankfurt und Bari. Sie gilt für den Zeitraum von Juni 2026 bis Mai 2030.</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/air-montenegro-einziger-bieter-fuer-sechs-subventionierte-strecken-darunter-auch-die/594ldt5</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>auto-ce2ab488f3df</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Nach Übernahme von Nippon Cargo: Neue Frachtairline heißt ANA Nippon Cargo</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Titel:</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/nach-uebernahme-von-nippon-cargo-neue-frachtairline-heisst-ana-nippon-cargo/bzdjjky</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>auto-e3c1f75764ee</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Flughafen München: Auslastung auf arabischen Strecken erholt sich auf 80 Prozent</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Der Iran-Konflikt belastete im ersten Halbjahr die Verbindungen zwischen München und dem Nahen Osten. Inzwischen hat sich die Nachfrage deutlich erholt. Gleichzeitig investiert der Flughafen mit dem neuen Pier am Terminal 1 gezielt in Passagiere aus der arabischen Welt.</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flughaefen/flughafen-muenchen-auslastung-auf-arabischen-strecken-erholt-sich-auf-80-prozent/17b4s7y</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr"/>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>auto-908dd8596c01</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Easyjet-Pilotinnen und Piloten in Frankreich setzen Streik aus</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Die Pilotinnen und Piloten von Easyjet in Frankreich haben ihren für den 13. und 14. September geplanten Streik ausgesetzt. Grund ist die Wiederaufnahme der Verhandlungen zwischen der Gewerkschaft SNPL und der Airline. Der Arbeitskampf ist damit jedoch nicht endgültig vom Tisch und könnte Ende September stattfinden.</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/easyjet-pilotinnen-und-piloten-in-frankreich-setzen-streik-aus/8d4djks</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>auto-51cf91e623c5</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Condor vergibt neue Flugnummern für City-Strecken</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Condor ordnet zum Beginn des Winterflugplans 2026/27 die Flugnummern ihres City-Netzes ab Frankfurt neu, wie das Portal Aero Routes berichtet. Ab dem 25. Oktober erhalten die Verbindungen nach Berlin, Hamburg, London-Gatwick, Mailand-Malpensa, München, Paris, Prag, Wien und Zürich neue Nummernbereiche.</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/condor-vergibt-neue-flugnummern-fuer-city-strecken/4tv43cb</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>auto-0cf51c83f353</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Harte Landung beschädigt Boeing 767 F von Amerijet</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Eine Boeing 767-300 BDSF von Amerijet ist nach einer harten Landung in Guatemala-Stadt außer Betrieb. Der Frachter mit dem Kennzeichen N373CM landete am Sonntag (6. September) auf Piste 02. Dabei entstanden sichtbare Verformungen im oberen Bereich des vorderen Rumpfes.</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/harte-landung-beschaedigt-boeing-767-f-von-amerijet/lc0g5kn</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>auto-6d4704df79ee</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Piloten von Condor sahen die Piste von Frankfurt schon – und durften trotzdem nicht landen</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Nach technischen Problemen startete ein Flug von Condor mit mehr als zwei Stunden Verspätung auf Sardinien. Die Crew holte kräftig Zeit auf und erreichte Frankfurt um Mitternacht. Doch obwohl nur noch wenig bis ans Ziel fehlte, gab es keine Landeerlaubnis. Der Airbus A320 musste nach Köln/Bonn weiterfliegen.</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/sicherheit/condor-flug-verpasst-frankfurt-landung-um-sekunden-umleitung-nach-koeln/bb088hs</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>auto-8c9bbb8269ff</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Flughafen Caracas will größte Erdbebenschäden bis 2027 beheben</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Venezuela will einen Teil der Erdbebenschäden am Flughafen Caracas-Maiquetía im ersten Halbjahr 2027 beheben. Nach Angaben von Verkehrsminister Francisco Garcês sind umfangreiche Bauarbeiten nötig, weshalb der Flughafen 2026 nicht einmal teilweise wieder regulär in Betrieb gehen soll. Eine schwer beschädigte Start- und Landebahn sei inzwischen vollständig repariert.</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flughafen-caracas-will-groesste-erdbebenschaeden-bis-2027-beheben/qhhlhgy</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>auto-a4b2156954e6</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Amazon setzt Zusammenarbeit mit 21 Air aus</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>MIAMI - Eine Boeing 767-300F mit Amazon-Logo schießt rund 400 Meter über die Landebahn hinaus. Der Unfall im Miami reißt fünf Menschen in den Tod. Amazon Air Cargo will den Betreiber der Unglücksmaschine nun vorerst nicht länger in die eigene Luftfrachtlogistik einspannen.</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53620/Amazon-setzt-Zusammenarbeit-mit-21-Air-aus.html</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>auto-75a4a0b813b2</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Leasingfirma fordert hohen Millionenbetrag von Easyjet</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>LONDON - Easyjet ist vor der Übernahme durch den US-Investor Apollo mit einer Millionenklage konfrontiert. In dem Verfahren geht es um Russlandsanktionen, sechs Airbus A320 - und die Frage, unter welchen Voraussetzungen europäische Airlines nach Ausbruch des Ukraine-Kriegs Leasingverträge mit russischen Firmen beenden durften.</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53619/Leasingfirma-fordert-hohen-Millionenbetrag-von-Easyjet.html</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>auto-5b1589b1732d</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>"Die Mediation ist eine verkappte MTV-Verhandlung"</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Schlichtung und Mediation: Lufthansa und Vereinigung Cockpit setzen die zuletzt angespannten Tarifbeziehungen in zweigleisigen Verhandlungen und mit externer Hilfe neu auf. In der Schlichtung geht es vor allem ums Geld. Die Mediation zieht laut Konzernkreisen MTV-Verhandlungen vor.</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53613/Die-Mediation-ist-eine-verkappte-MTV-Verhandlung.html</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>auto-ef8dcaa20418</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Frankfurt Cargo Services: Pharma Center quadruples temperature-controlled cargo space - TRANSPORT - die Zeitung für den Güterverkehr</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMizAFBVV95cUxQejAwYlpER09JeDFiZl91VUpGcTZjWlJmcnVkbEFMc3loZy1GRmh2SkYtNzFJVGw3c3BIQTRybnpZQm4yd19rbXBLd2l3LWo5OWw4cDBFTXNuUS1wLUpYajJBMHB1akx4SGxPTGJETWFaNVpmZEptdFYzZU91eGk2eEN6dDlRQnBxRUJxOE1iQ2hqa2Z0Ty1fdXdwVkQ5RVI1Ykw1VjdkQUJ4cGNIZHhweEVyc2Q5b0dpYTNfQUZGQlZGVVJnNFY0MnJFMHA?oc=5" target="_blank"&gt;Frankfurt Cargo Services: Pharma Center quadruples temperature-controlled cargo space&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;TRANSPORT - die Zeitung für den Güterverkehr&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQejAwYlpER09JeDFiZl91VUpGcTZjWlJmcnVkbEFMc3loZy1GRmh2SkYtNzFJVGw3c3BIQTRybnpZQm4yd19rbXBLd2l3LWo5OWw4cDBFTXNuUS1wLUpYajJBMHB1akx4SGxPTGJETWFaNVpmZEptdFYzZU91eGk2eEN6dDlRQnBxRUJxOE1iQ2hqa2Z0Ty1fdXdwVkQ5RVI1Ykw1VjdkQUJ4cGNIZHhweEVyc2Q5b0dpYTNfQUZGQlZGVVJnNFY0MnJFMHA?oc=5</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O324"/>
+  <dimension ref="A1:O325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19677,7 +19677,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19708,8 +19707,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
-      <c r="L311" t="inlineStr"/>
       <c r="M311" t="inlineStr">
         <is>
           <t>review</t>
@@ -19742,7 +19739,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19773,8 +19769,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr"/>
       <c r="M312" t="inlineStr">
         <is>
           <t>review</t>
@@ -19807,7 +19801,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19838,8 +19831,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
-      <c r="L313" t="inlineStr"/>
       <c r="M313" t="inlineStr">
         <is>
           <t>review</t>
@@ -19872,7 +19863,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19903,8 +19893,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
-      <c r="L314" t="inlineStr"/>
       <c r="M314" t="inlineStr">
         <is>
           <t>review</t>
@@ -19937,7 +19925,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19968,8 +19955,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
-      <c r="L315" t="inlineStr"/>
       <c r="M315" t="inlineStr">
         <is>
           <t>review</t>
@@ -20002,7 +19987,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20033,8 +20017,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
-      <c r="L316" t="inlineStr"/>
       <c r="M316" t="inlineStr">
         <is>
           <t>review</t>
@@ -20067,7 +20049,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20098,8 +20079,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
-      <c r="L317" t="inlineStr"/>
       <c r="M317" t="inlineStr">
         <is>
           <t>review</t>
@@ -20132,7 +20111,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20163,8 +20141,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
-      <c r="L318" t="inlineStr"/>
       <c r="M318" t="inlineStr">
         <is>
           <t>review</t>
@@ -20197,7 +20173,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20228,8 +20203,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
-      <c r="L319" t="inlineStr"/>
       <c r="M319" t="inlineStr">
         <is>
           <t>review</t>
@@ -20262,7 +20235,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20293,8 +20265,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
-      <c r="L320" t="inlineStr"/>
       <c r="M320" t="inlineStr">
         <is>
           <t>review</t>
@@ -20327,7 +20297,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20358,8 +20327,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
-      <c r="L321" t="inlineStr"/>
       <c r="M321" t="inlineStr">
         <is>
           <t>review</t>
@@ -20392,7 +20359,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20423,8 +20389,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
-      <c r="L322" t="inlineStr"/>
       <c r="M322" t="inlineStr">
         <is>
           <t>review</t>
@@ -20457,7 +20421,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20488,8 +20451,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
-      <c r="L323" t="inlineStr"/>
       <c r="M323" t="inlineStr">
         <is>
           <t>review</t>
@@ -20522,7 +20483,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20553,8 +20513,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
-      <c r="L324" t="inlineStr"/>
       <c r="M324" t="inlineStr">
         <is>
           <t>review</t>
@@ -20566,6 +20524,71 @@
         </is>
       </c>
       <c r="O324" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>auto-62857c7ebf70</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Aus ANA Cargo und NCA wird "ANA Nippon Cargo"</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>TOKIO - All Nippon Airways (ANA) zieht 2027 drei Frachtbetriebe in einer neuen Airline zusammen.</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53624/Aus-ANA-Cargo-und-NCA-wird-ANA-Nippon-Cargo.html</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O325"/>
+  <dimension ref="A1:O335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20545,7 +20545,6 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20576,8 +20575,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
-      <c r="L325" t="inlineStr"/>
       <c r="M325" t="inlineStr">
         <is>
           <t>review</t>
@@ -20589,6 +20586,656 @@
         </is>
       </c>
       <c r="O325" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>auto-3255a8127765</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Kühne und Nagel eröffnet neues Pharma-Logistikzentrum am Flughafen Frankfurt</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Kühne+Nagel hat am Flughafen Frankfurt ein neues Logistikzentrum für Pharma- und Gesundheitsprodukte eröffnet. Die 3505 Quadratmeter große Anlage befindet sich in der Cargo City Süd und ist auf temperaturempfindliche Sendungen spezialisiert. Rund 2500 Quadratmeter stehen für Produkte bei 15 bis 25 Grad Celsius zur Verfügung, mehr als 500 Quadratmeter für Kühltransporte bei zwei bis acht Grad. Hinzu kommen Tiefkühler für Temperaturen bis minus 70 Grad.</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/kuehne-und-nagel-eroeffnet-neues-pharma-logistikzentrum-am-flughafen-frankfurt/sv13zvy</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>auto-ac2ca21faa18</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>OE-LPI: Austrian Airlines erhält heute ihre vierte Boeing 787</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Austrian Airlines erwartet am Mittwoch (16. September) ihren viertenDreamliner in Wien. Die Boeing 787 mit der österreichischen Registrierung OE-LPI soll um 16 Uhr in Frankfurt starten und als Flug OS1472 um 17:25 Uhr in Wien landen. Zuvor flog die Boeing 787 bei Lufthansa als D-ABPA.</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/oe-lpi-austrian-airlines-erhaelt-heute-ihre-vierte-boeing-787/2jhedk3</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>auto-4737b4a036f9</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Transavia France bekommt 2027 erste Airbus A321 Neo</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>ransavia France wird ab 2027 auch Airbus A321 Neo einsetzen. Das erste Exemplar soll Ende des ersten Quartals in Dienst gehen. Zum Höhepunkt des Sommerflugplans 2027 sollen bereits fünf A321 Neo für die französische Billigfluggesellschaft fliegen, berichtet das Portal &lt;a href="https://www.journal-aviation.com/actualites-transport-aerien/compagnies-aeriennes/transavia-france-integrera-des-airbus-a321neo-a-partir-de-2027-20260915.html?utm_source=mailpoet&amp;utm_medium=email&amp;utm_source_platform=mailpoet&amp;utm_campaign=le-journal-de-laviation-votre-newsletter-quotidienne-6" id="49870e29-e06e-4563-b33e-60f32a479715" data-link-role-code="target_blank"&gt;Journal de L'Aviation&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/transavia-france-bekommt-2027-erste-airbus-a321-neo/z1tgz6w</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>auto-8b90aad91da6</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Air France stockt Flüge zwischen Guadeloupe und Miami auf</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Air France baut im Winterflugplan 2026/27 die Verbindung zwischen Pointe-à-Pitre auf Guadeloupe und Miami aus. Ab dem 11. Dezember bietet die Fluggesellschaft vier statt der bisher vorgesehenen drei wöchentlichen Flüge an. Zum Einsatz kommen Airbus A320.</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/air-france-stockt-fluege-zwischen-guadeloupe-und-miami-auf/76mjxmf</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>auto-45b81bbedffc</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Gesundheitsamt weitet "Mückenmonitoring" aus</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Wieder sind Menschen in Frankfurt an Malaria erkrankt. Das Gesundheitsamt vermutet einen Zusammenhang mit einer Mücke beim Flughafen. Es schaltet eine Hotline frei. Wie oft klingelt dieses Telefon?</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53654/Gesundheitsamt-weitet-Mueckenmonitoring-aus.html</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>auto-38710f220030</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>"Die A350F ist weder eine A350-1000 noch eine A350-900"</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>TOULOUSE - Neun Monate, zwei Flugzeuge, ein Ziel: Airbus nimmt die Flugerprobung der A350F in Angriff. Nach 400 Flugteststunden soll der neue Frachter 2027 die EASA-Zulassung erhalten. Testpiloten und -ingenieure trainieren bereits im Simulator - denn die A350F wird sich nicht (ganz) wie eine A350-900 oder A350-1000 fliegen.</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53651/Die-A350F-ist-weder-eine-A350-1000-noch-eine-A350-900.html</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>auto-5b6c447f093f</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Lufthansa gibt Firmenkunden mehr Zeit für Buchungen</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa räumt Firmenkunden ein größeres Zeitfenster für verbindliche Flugbuchungen ein - über die NDC-Schnittstelle ausgegebene Ticketpreise gelten für 24 Stunden. Doch es gibt Ausnahmen.</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53647/Lufthansa-gibt-Firmenkunden-mehr-Zeit-fuer-Buchungen.html</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr"/>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>auto-c58826704943</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Diskussion über neue Flugroute "Cindy-S"</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Die neue Route entlastet manche Orte vom Fluglärm. In anderen Ecken ist es seitdem lauter geworden. Was das aktuelle Monitoring bisher ergeben hat, soll nun vorgestellt werden.</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53644/Diskussion-ueber-neue-Flugroute-Cindy-S.html</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr"/>
+      <c r="L333" t="inlineStr"/>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>auto-8dc98ff33c5f</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Viele Betreiber kritischer Infrastruktur ohne Drohnenschutz</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>FRANKFURT - "Lücke zwischen Risikowahrnehmung und Vorbereitung": Trotz wachsender Gefahren durch unerlaubte Drohnenüberflüge fehlen vielerorts in Deutschland Schutzmaßnahmen. Rund die Hälfte der Betreiber kritischer Infrastruktur kann Drohnen weder detektieren noch abwehren.</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53642/Kritis-Drohnenschutz.html</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr"/>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>auto-b0a40e91d0fe</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Weitere Malaria-Fälle in Frankfurt</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Nach mehreren Malaria-Fällen bei Mitarbeitern des Frankfurter Flughafens sind zwei Bewohner eines nahegelegenen Stadtteils an der Infektionskrankheit erkrankt.</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53641/Weitere-Malaria-Faelle-in-Frankfurt.html</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O335"/>
+  <dimension ref="A1:O344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20607,7 +20607,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20638,8 +20637,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
-      <c r="L326" t="inlineStr"/>
       <c r="M326" t="inlineStr">
         <is>
           <t>review</t>
@@ -20672,7 +20669,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20703,8 +20699,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
-      <c r="L327" t="inlineStr"/>
       <c r="M327" t="inlineStr">
         <is>
           <t>review</t>
@@ -20737,7 +20731,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20768,8 +20761,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
-      <c r="L328" t="inlineStr"/>
       <c r="M328" t="inlineStr">
         <is>
           <t>review</t>
@@ -20802,7 +20793,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20833,8 +20823,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
-      <c r="L329" t="inlineStr"/>
       <c r="M329" t="inlineStr">
         <is>
           <t>review</t>
@@ -20867,7 +20855,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20898,8 +20885,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
-      <c r="L330" t="inlineStr"/>
       <c r="M330" t="inlineStr">
         <is>
           <t>review</t>
@@ -20932,7 +20917,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -20963,8 +20947,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
-      <c r="L331" t="inlineStr"/>
       <c r="M331" t="inlineStr">
         <is>
           <t>review</t>
@@ -20997,7 +20979,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21028,8 +21009,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
-      <c r="L332" t="inlineStr"/>
       <c r="M332" t="inlineStr">
         <is>
           <t>review</t>
@@ -21062,7 +21041,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21093,8 +21071,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
-      <c r="L333" t="inlineStr"/>
       <c r="M333" t="inlineStr">
         <is>
           <t>review</t>
@@ -21127,7 +21103,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21158,8 +21133,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
-      <c r="L334" t="inlineStr"/>
       <c r="M334" t="inlineStr">
         <is>
           <t>review</t>
@@ -21192,7 +21165,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21223,8 +21195,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
-      <c r="L335" t="inlineStr"/>
       <c r="M335" t="inlineStr">
         <is>
           <t>review</t>
@@ -21236,6 +21206,591 @@
         </is>
       </c>
       <c r="O335" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>auto-47885694a64b</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Drei Tote bei Absturz einer Cirrus SR22 in den Schweizer Alpen</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Beim Absturz eines Kleinflugzeugs bei Leukerbad im Kanton Wallis sind am Dienstag (15. September) drei Menschen ums Leben gekommen. Die Cirrus SR22T war in Lugano gestartet und nach einer Zwischenlandung in Sionn auf dem Weg zum Flugplatz Buochs. Kurz nach 16 Uhr kollidierte sie aus bislang ungeklärter Ursache mit dem nördlichen Hang im Gebiet Fluhalp.</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/drei-tote-bei-absturz-einer-cirrus-sr22-in-den-schweizer-alpen/blx764g</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>auto-bb8d0042aa36</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>French Bee fliegt im Winter bis zu vier Mal wöchentlich nach Montreal</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>French Bee baut im Winterflugplan 2026/27 ihr Angebot ab Paris-Orly aus. Zwischen dem 24. Oktober und 27. März fliegt die französische Billigfluggesellschaft bis zu vier Mal pro Woche nach Montreal, bis zu 14 Mal nach La Réunion und bis zu drei Mal nach Papeete.</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/french-bee-fliegt-im-winter-bis-zu-vier-mal-woechentlich-nach-montreal/75q3y57</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>auto-f5284929a044</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>ITA Airways, Lufthansa, Qatar Airways und Co.: Die Luftfahrtbranche kommt in Frankfurt zusammen</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Von künstlicher Intelligenz und nachhaltigen Treibstoffen bis zu Flottenfinanzierung und Geopolitik: Ende September diskutiert die Luftfahrtbranche in Frankfurt über ihre wichtigsten Zukunftsthemen. Auch zahlreiche Airline- und Flughafenchefs sind dabei - und aeroTELEGRAPH.</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ita-chef-eberhart-eroeffnet-global-aviation-conference-frankfurt-2026/v3f9837</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>auto-5ad7e17a4887</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>So häufig infizieren sich Menschen mit "Flughafen-Malaria"</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Erneut erkranken Menschen in Frankfurt an Malaria. Fachleute gehen davon aus, dass dies mit dem Flughafen zusammen hängt. Eigentlich kommen solche Fälle extrem selten vor. Das Gesundheitsamt rät zu Mückenschutz. Wie oft infizieren sich Menschen in Europa mit dem Malaria-Erreger?</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53662/So-haeufig-infizieren-sich-Menschen-mit-Flughafen-Malaria.html</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>auto-839c663559b8</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Condor-Flug scheitert knapp an Nachtflugverbot</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Kurz vor der geplanten Landung am Frankfurter Flughafen hat ein Flugzeug wegen des dort geltenden Nachtflugverbots wieder abdrehen müssen.</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53660/Condor-Flug-scheitert-knapp-an-Nachtflugverbot.html</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr"/>
+      <c r="L340" t="inlineStr"/>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>auto-6852cf19f42e</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Weitere Messwerte zu neuer Flugroute "Cindy-S" vorgelegt</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Zur neuen Flugroute "Cindy-S" des Frankfurter Flughafens sind weitere Messergebnisse vorgestellt worden. Die neue Route wird nach Angaben der Fluglärmkommission (FLK) demnach überwiegend eingehalten, auch die Flughöhen änderten sich im Vergleich zur vorangegangenen Route nicht signifikant.</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53658/Weitere-Messwerte-zu-neuer-Flugroute-Cindy-S-vorgelegt.html</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>auto-1db8b7f916d5</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Malaria: Authority advises mosquito protection near Frankfurt Airport - Logistik Heute</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitAFBVV95cUxQM0kxR1J5UHp6NkJ5c20zM25oeUV1ZHFsN1gtajJETGNicTlxZG5uRTRZaFJhSFd2U2RwNlNidmljSWN3N2hyc1Z2STVLV3hoYlNDcEFEZ2gtam9uRkR1bzNiXzRzaHJHbU9ZdmZTYW1kQnpHSjZiM2ZXSHBHaDRySkxmOEZ1RzliYkdlYlBvUlc1OUJkUUE5TXdCMHZTdFpuZU11WjFJOHdGUjhZb0xLWDdQZjA?oc=5" target="_blank"&gt;Malaria: Authority advises mosquito protection near Frankfurt Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Logistik Heute&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQM0kxR1J5UHp6NkJ5c20zM25oeUV1ZHFsN1gtajJETGNicTlxZG5uRTRZaFJhSFd2U2RwNlNidmljSWN3N2hyc1Z2STVLV3hoYlNDcEFEZ2gtam9uRkR1bzNiXzRzaHJHbU9ZdmZTYW1kQnpHSjZiM2ZXSHBHaDRySkxmOEZ1RzliYkdlYlBvUlc1OUJkUUE5TXdCMHZTdFpuZU11WjFJOHdGUjhZb0xLWDdQZjA?oc=5</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr"/>
+      <c r="L342" t="inlineStr"/>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>auto-847606d339a2</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Malaria: Two residents near Frankfurt Airport fall ill - Logistik Heute</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMioAFBVV95cUxQSDNDZXU0RlVmLVJ3dktfUmhNTUI3TWdGVzJyd0NiQnpkZ2pNbEZ4R293U1V5Y2s5eW9yLTNPajAzODFoZjlOUzhKdmNOb2hOQVRoUTZlTmY0dFl2WGEyOTdUakFxVVNjRmNuRjM0YWhrNXJOclF4T3ZhRUljLXctdDB5RHdCYnlnMWVSVUp6R2ViQzJTZVcyeTIzQ2ZVX3M3?oc=5" target="_blank"&gt;Malaria: Two residents near Frankfurt Airport fall ill&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Logistik Heute&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQSDNDZXU0RlVmLVJ3dktfUmhNTUI3TWdGVzJyd0NiQnpkZ2pNbEZ4R293U1V5Y2s5eW9yLTNPajAzODFoZjlOUzhKdmNOb2hOQVRoUTZlTmY0dFl2WGEyOTdUakFxVVNjRmNuRjM0YWhrNXJOclF4T3ZhRUljLXctdDB5RHdCYnlnMWVSVUp6R2ViQzJTZVcyeTIzQ2ZVX3M3?oc=5</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr"/>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>auto-b75aa08c621d</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Aviation Lounge by Steigenberger in Frankfurt - Business-Travel.de</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiiwFBVV95cUxOd0laY1RnQTc2SDhiTW5DUE9NWS1EN3BVdzhzVXdJMTlLRlZkeU1taUNRM3ZGZnRYMVI3QWFRLVdHYi1UM013S0UtdlFwa2ZKZTZ2RWZGMnRWcm1FRjRDdjEtUTRJUGxKdkp3SHVXUzFKei10X3dweGpwcDNTUkhfc2xkM3pOU3FCOU1R?oc=5" target="_blank"&gt;Aviation Lounge by Steigenberger in Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Business-Travel.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOd0laY1RnQTc2SDhiTW5DUE9NWS1EN3BVdzhzVXdJMTlLRlZkeU1taUNRM3ZGZnRYMVI3QWFRLVdHYi1UM013S0UtdlFwa2ZKZTZ2RWZGMnRWcm1FRjRDdjEtUTRJUGxKdkp3SHVXUzFKei10X3dweGpwcDNTUkhfc2xkM3pOU3FCOU1R?oc=5</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O344"/>
+  <dimension ref="A1:O350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21227,7 +21227,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -21258,8 +21257,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
-      <c r="L336" t="inlineStr"/>
       <c r="M336" t="inlineStr">
         <is>
           <t>review</t>
@@ -21292,7 +21289,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21323,8 +21319,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
-      <c r="L337" t="inlineStr"/>
       <c r="M337" t="inlineStr">
         <is>
           <t>review</t>
@@ -21357,7 +21351,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21388,8 +21381,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
-      <c r="L338" t="inlineStr"/>
       <c r="M338" t="inlineStr">
         <is>
           <t>review</t>
@@ -21422,7 +21413,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21453,8 +21443,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
-      <c r="L339" t="inlineStr"/>
       <c r="M339" t="inlineStr">
         <is>
           <t>review</t>
@@ -21487,7 +21475,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21518,8 +21505,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
-      <c r="L340" t="inlineStr"/>
       <c r="M340" t="inlineStr">
         <is>
           <t>review</t>
@@ -21552,7 +21537,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21583,8 +21567,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
-      <c r="L341" t="inlineStr"/>
       <c r="M341" t="inlineStr">
         <is>
           <t>review</t>
@@ -21617,7 +21599,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21648,8 +21629,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
-      <c r="L342" t="inlineStr"/>
       <c r="M342" t="inlineStr">
         <is>
           <t>review</t>
@@ -21682,7 +21661,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21713,8 +21691,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
-      <c r="L343" t="inlineStr"/>
       <c r="M343" t="inlineStr">
         <is>
           <t>review</t>
@@ -21747,7 +21723,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21778,8 +21753,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
-      <c r="L344" t="inlineStr"/>
       <c r="M344" t="inlineStr">
         <is>
           <t>review</t>
@@ -21791,6 +21764,396 @@
         </is>
       </c>
       <c r="O344" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>auto-80ca53f7ec36</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Nach Bruchlandung von Amazon Air: Miami öffnet dritte Start- und Landebahn wieder</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Der Flughafen Miami kann nach dem tödlichen Unfall eines Amazon-Frachtflugzeugs wieder drei seiner vier Start- und Landebahnen vollständig nutzen. Das Wrack der Boeing 767-300 F wurde am Dienstag (15. September) von der Unfallstelle entfernt, anschließend hob der Flughafen die Einschränkungen für die dritte Piste auf. Die vierte bleibt für weitere Inspektionen und Reparaturen geschlossen.</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/nach-bruchlandung-von-amazon-air-miami-oeffnet-dritte-start-und-landebahn-wieder/sprrkes</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr"/>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>auto-210724b256e3</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Air Tahiti Nui darf Hubschraubersparte verkaufen</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Air Tahiti Nui hat von der Wettbewerbsbehörde Französisch-Polynesiens die Genehmigung zum Verkauf ihrer Beteiligung an Tahiti Nui Helicopters erhalten. Käufer ist Tavake SAS. Die Fluggesellschaft hofft, die Transaktion bis Ende Oktober abzuschließen. Sie hatte sich nach einer strategischen Überprüfung für den Ausstieg entschieden, um sich auf ihr Kerngeschäft mit Langstreckenflügen zu konzentrieren, berichtet Radio 1 Tahiti.</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/air-tahiti-nui-darf-hubschraubersparte-verkaufen/5vlmg7t</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr"/>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>auto-aeb0f6a24824</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Lufthansa ersetzt ältere Airbus A320 durch Boeing 737 MAX 10</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Eurowings erhält zwischen 2027 und 2032 40 Boeing 737 MAX 8. Dabei belässt es Lufthansa nicht - der Aufsichtsrat hat am Donnerstag einem Ausbau des 737-MAX-Auftrags auf 60 Festbestellungen zugestimmt. Lufthansa plant jetzt auch mit dem Topmodell der Serie. Lieferstart: Anfang der 2030er Jahre.</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53672/Lufthansa-ersetzt-aeltere-Airbus-A320-durch-Boeing-737-MAX-10.html</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>auto-eb3914aaac11</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Weiterer Malaria-Patient in Frankfurt gestorben</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>FRANKFURT - In Frankfurt gibt es nun drei Malaria-Tote. Ein Anwohner der Gegend um den Flughafen starb an der Infektion, wie die Stadt mitteilte. Er soll sich durch eine eingeschleppte Mücke infiziert haben.</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53669/Weiterer-Malaria-Patient-in-Frankfurt-gestorben.html</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr"/>
+      <c r="L348" t="inlineStr"/>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>auto-ea8cec89e121</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Discover Airlines übernimmt erneut eine Langstrecke von Lufthansa - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMimAFBVV95cUxPdk1faF92bFRqeGRWMTJXOC1mSWRvNzJpeE9mamF6OFQzV21XSnVUTVhhYW1SejJ3eUpsLV9LOHl5aE5vblZ2WC1fblZoRXRlY0VjQndaN3ZTRVFOTGM2UlRCZXdvVUxkejlQNXFGWmNpS1dRMW9lRkllcFVPRDJ3Qms4V3kzejVBcDRVcmdKV3JNVWFSSDV5TQ?oc=5" target="_blank"&gt;Discover Airlines übernimmt erneut eine Langstrecke von Lufthansa&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPdk1faF92bFRqeGRWMTJXOC1mSWRvNzJpeE9mamF6OFQzV21XSnVUTVhhYW1SejJ3eUpsLV9LOHl5aE5vblZ2WC1fblZoRXRlY0VjQndaN3ZTRVFOTGM2UlRCZXdvVUxkejlQNXFGWmNpS1dRMW9lRkllcFVPRDJ3Qms4V3kzejVBcDRVcmdKV3JNVWFSSDV5TQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>auto-5cf91ad4392c</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>TAP Air Portugal Flight TP1329 just made an emergency return to London Gatwick - airlive</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMivAFBVV95cUxNeTlWNHFaQWVGOWVKcjI0dTNFN0E5c2RRd1hGWUp2b0NHLWVGS0c2VTdMNG9qeExSbDZfWmQ2NU4tXzd3SVNmazJYSTM3cjhVbW44RlZjOVE4TVV0Snc3czR0U1pnNWNiTUZvSW1GU3l6bWtEaC0zSDJRbXY3bFI1RWMxdUpXVUUxN2RESHg1akpSSVlYbm52UWRkaWh4UnYwNUtSUGZSQ3FrN0k3OWpvTXh6MS10RllfTndTLQ?oc=5" target="_blank"&gt;TAP Air Portugal Flight TP1329 just made an emergency return to London Gatwick&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNeTlWNHFaQWVGOWVKcjI0dTNFN0E5c2RRd1hGWUp2b0NHLWVGS0c2VTdMNG9qeExSbDZfWmQ2NU4tXzd3SVNmazJYSTM3cjhVbW44RlZjOVE4TVV0Snc3czR0U1pnNWNiTUZvSW1GU3l6bWtEaC0zSDJRbXY3bFI1RWMxdUpXVUUxN2RESHg1akpSSVlYbm52UWRkaWh4UnYwNUtSUGZSQ3FrN0k3OWpvTXh6MS10RllfTndTLQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O350"/>
+  <dimension ref="A1:O355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21785,7 +21785,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21816,8 +21815,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
-      <c r="L345" t="inlineStr"/>
       <c r="M345" t="inlineStr">
         <is>
           <t>review</t>
@@ -21850,7 +21847,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21881,8 +21877,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
-      <c r="L346" t="inlineStr"/>
       <c r="M346" t="inlineStr">
         <is>
           <t>review</t>
@@ -21915,7 +21909,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -21946,8 +21939,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
-      <c r="L347" t="inlineStr"/>
       <c r="M347" t="inlineStr">
         <is>
           <t>review</t>
@@ -21980,7 +21971,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22011,8 +22001,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
-      <c r="L348" t="inlineStr"/>
       <c r="M348" t="inlineStr">
         <is>
           <t>review</t>
@@ -22045,7 +22033,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22076,8 +22063,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
-      <c r="L349" t="inlineStr"/>
       <c r="M349" t="inlineStr">
         <is>
           <t>review</t>
@@ -22110,7 +22095,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -22141,8 +22125,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
-      <c r="L350" t="inlineStr"/>
       <c r="M350" t="inlineStr">
         <is>
           <t>review</t>
@@ -22154,6 +22136,331 @@
         </is>
       </c>
       <c r="O350" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>auto-882cd313e7de</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Air France-KLM baut Angebot in Portugal deutlich aus</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Air France-KLM erhöht im Winter 2026/27 die Kapazität in Portugal gemessen an Sitzplatzkilometern um zwölf Prozent. Air France, KLM und Transavia bieten insgesamt 24 Strecken und bis zu 238 wöchentliche Flüge ab Lissabon, Porto, Faro, Funchal und Ponta Delgada nach Frankreich, in die Niederlande und nach Belgien an, berichtetd as Portal Kiosque de Aviação.</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/air-france-klm-baut-angebot-in-portugal-deutlich-aus/cv09zyq</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>auto-5ba7c40d1dea</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Boeing darf 777 F drei Jahre länger bauen</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Boeing darf den Frachter 777 F drei Jahre länger produzieren als bislang vorgesehen. Die US-Luftfahrtbehörde FAA hat eine Ausnahmegenehmigung für bis zu 35 neu gebaute Exemplare erteilt, die zwischen Anfang 2028 und Ende 2030 erstmals ein Lufttüchtigkeitszeugnis erhalten. Der 777 F erfüllt neue Vorgaben zu Treibstoffeffizienz und CO₂-Emissionen nicht, die ab 2028 gelten.</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/boeing-darf-777-f-drei-jahre-laenger-bauen/v8wkc1k</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>auto-34fde26e28c1</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Demokratische Republik Kongo: Fahrwerk von Boeing 737 von Serve Air knickt beim Start ein</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Bei einer Boeing 737-300 F von Serve Air ist am Donnerstag (17. September) beim Start in Kindu in der Demokratischen Republik Kongo das rechte Hauptfahrwerk eingebrochen. Der Frachter mit der Registrierung 9S-AAI sollte von Kindu nach Kinshasa fliegen und befand sich auf der Startbahn 36, als das Fahrwerk nachgab und das Flugzeug nach rechts ausbrach.</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/demokratische-republik-kongo-fahrwerk-von-boeing-737-von-serve-air-knickt-beim-start/be1eyn7</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>auto-4dc1e6043e34</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Test von Air France ergab: Kleine Umwege helfen gegen klimaschädliche Kondensstreifen</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Air France hat auf fast 4300 Transatlantikflügen untersucht, ob sich besonders klimaschädliche Kondensstreifen durch angepasste Flugrouten vermeiden lassen. Zwischen Februar und April wurden 245 Flüge mit potenziell hoher Klimawirkung identifiziert, 130 davon tatsächlich umgeleitet.</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/test-von-air-france-ergab-kleine-umwege-helfen-gegen-klimaschaedliche-kondensstreifen/tlt9q42</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>auto-60c993f5f917</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Attestor tritt bei Condor auf die Kostenbremse</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Attestor verlangt von Condor mehr Ausgabendisziplin. Im Wandel von einer Ferien- zu einer Netzgesellschaft muss Condor in den kommenden zwei Geschäftsjahren jeweils 100 Millionen Euro einsparen. Nur wie? Die Airline fordert nach Gewerkschaftsangaben Zugeständnisse des Personals.</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53683/Attestor-drueckt-bei-Condor-auf-die-Kostenbremse.html</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O355"/>
+  <dimension ref="A1:O357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22157,7 +22157,6 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22188,8 +22187,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
-      <c r="L351" t="inlineStr"/>
       <c r="M351" t="inlineStr">
         <is>
           <t>review</t>
@@ -22222,7 +22219,6 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22253,8 +22249,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
-      <c r="L352" t="inlineStr"/>
       <c r="M352" t="inlineStr">
         <is>
           <t>review</t>
@@ -22287,7 +22281,6 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22318,8 +22311,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
-      <c r="L353" t="inlineStr"/>
       <c r="M353" t="inlineStr">
         <is>
           <t>review</t>
@@ -22352,7 +22343,6 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22383,8 +22373,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
-      <c r="L354" t="inlineStr"/>
       <c r="M354" t="inlineStr">
         <is>
           <t>review</t>
@@ -22417,7 +22405,6 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22448,8 +22435,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
-      <c r="L355" t="inlineStr"/>
       <c r="M355" t="inlineStr">
         <is>
           <t>review</t>
@@ -22461,6 +22446,136 @@
         </is>
       </c>
       <c r="O355" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>auto-cf27a4515491</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Angeschlagener Flughafen Bremen denkt über private Investoren nach - und will im Sommer wieder Frankfurt-Flüge</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Im Kampf gegen sein Defizit erwägt der norddeutsche Airport, sich für private Investoren zu öffnen. Außerdem will der Flughafen Bremen Lufthansa zur Wiederaufnahme der Frankfurt-Flüge bewegen - und lockt dabei auch mit möglichen Rabatten bei den Entgelten.</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flughafen-bremen-denkt-ueber-private-investoren-nach-und-will-lufthansa-fluege-nach/rvl13f1</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>auto-1712749c67df</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Singapore Airlines gewinnt - so bewertet Skytrax die Airlines</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Singapore Airlines ist bei den World Airline Awards 2026 von Skytrax als beste Fluggesellschaft der Welt ausgezeichnet worden. Die Airline erhielt den Titel zum sechsten Mal und gewann zudem die Kategorien Economy Class und Economy-Catering. Die Auszeichnungen wurden am 18. September in London vergeben. Grundlage ist eine internationale Passagierbefragung, an der Reisende aus mehr als 100 Ländern teilnahmen.</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/singapore-airlines-gewinnt-so-bewertet-skytrax-die-airlines/86c6ffk</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O357"/>
+  <dimension ref="A1:O364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22467,7 +22467,6 @@
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22498,8 +22497,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
-      <c r="L356" t="inlineStr"/>
       <c r="M356" t="inlineStr">
         <is>
           <t>review</t>
@@ -22532,7 +22529,6 @@
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22563,8 +22559,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
-      <c r="L357" t="inlineStr"/>
       <c r="M357" t="inlineStr">
         <is>
           <t>review</t>
@@ -22576,6 +22570,461 @@
         </is>
       </c>
       <c r="O357" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>auto-1435cf5e9f0e</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Swissport expandiert nach Kolumbien und übernimmt Mehrheit an GHI</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Swissport erschließt einen weiteren Markt in Lateinamerika. Der Schweizer Bodenabfertigungskonzern hat eine verbindliche Vereinbarung zur Übernahme einer Mehrheitsbeteiligung am kolumbianischen Anbieter Giraldo Hermanos International (GHI) unterzeichnet. GHI ist derzeit in Bogotá und Medellín tätig und besitzt die Zulassung für Bodenabfertigungsdienste an allen wichtigen Flughäfen des Landes. Zum Angebot gehören Passagier- und Frachtabfertigung sowie die Betreuung von Reisenden mit eingeschränkter Mobilität. Zu den Kunden zählen unter anderem Copa Airlines, Air Europa, Turpial Airlines, Solar Cargo und FedEx. Für Swissport ist es der Markteintritt in Kolumbien. In Lateinamerika ist das Unternehmen bislang an 85 Flughäfen in 15 Ländern vertreten. Der Abschluss der Transaktion steht noch unter dem Vorbehalt der üblichen Bedingungen und behördlichen Genehmigungen.</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/swissport-expandiert-nach-kolumbien-und-uebernimmt-mehrheit-an-ghi/kh0yxls</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>auto-cd252751469f</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Tarmac Aerosave darf indische Airbus A320 in Frankreich warten</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Tarmac Aerosave erhält Zugang zum indischen Markt. Die indische Luftfahrtbehörde DGCA hat dem französischen Unternehmen eine Zulassung für die gesamte Airbus-A320-Familie erteilt. Sie gilt unabhängig von der Triebwerksvariante – sowohl für CFM International CFM56 und Leap-1A als auch für IAE V2500 und Pratt &amp;amp; Whitney PW1100G.</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/tarmac-aerosave-darf-indische-airbus-a320-in-frankreich-warten/pz6vcx1</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>auto-757d83bd4f9b</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Air France baut La-Première-Angebot in die USA weiter aus</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Air France will ihre First Class La Première in den kommenden 18 Monaten auf weiteren Strecken in die USA anbieten. Konzernchef Ben Smith nannte gegenüber der Nachrichtenagentur Bloomberg Boston als eine der neuen Destinationen. Gleichzeitig soll das Angebot auf bestehenden Strecken wachsen.</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/air-france-baut-la-premiere-angebot-in-die-usa-weiter-aus/3zjn728</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>auto-718931941c78</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Hawaiian Airlines setzt Boeing 737 erstmals zwischen den Inseln ein</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Hawaiian Airlines und Alaska Airlines setzen ab dem 3. Oktober zusätzlich Boeing 737-800 auf Verbindungen innerhalb Hawaiis ein. Geplant sind täglich drei Hin- und Rückflüge zwischen Honolulu und Kahului auf Maui. Die Flugzeuge fliegen unter der Marke Alaska Airlines und sollen zusätzliche Passagier- und Frachtkapazität schaffen.</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/hawaiian-airlines-setzt-boeing-737-erstmals-zwischen-den-inseln-ein/jxsyn7r</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>auto-d61015f7474c</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Muscat and Beyond: Mit Oman Air den Oman und die Welt entdecken</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Oman ist ein Land für Entdecker. Nur wenige Flugstunden von Zürich, München oder Frankfurt entfernt treffen spektakuläre Bergwelten auf goldene Wüsten, türkisfarbene Wadis und eine fast 3.000 Kilometer lange Küste. Oman Air bringt Reisende mitten hinein - und von Muscat aus weiter zu mehr als 40 Zielen in Asien und darüber hinaus.</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/oman-air-via-muscat-business-class-streckennetz-und-stopover/7htss1b</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>auto-d9d9f0ceab50</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Flughafen Bremen hofft auf Rückkehr der Frankfurt-Linie</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>BREMEN - "Sehr intensive Gespräche": Bremen will Lufthansa zur Wiederaufnahme der eingestellten Zubringerflüge an das Drehkreuz Frankfurt bewegen. Eine Entscheidung für den Sommerflugplan 2027 muss in den nächsten Wochen fallen. Konnektivität ist derzeit nicht die einzige Sorge der Bremer.</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53691/Flughafen-Bremen-hofft-auf-Rueckkehr-der-Frankfurt-Linie.html</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>auto-75c963a9320e</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Manchester-bound flight carrying 230 people makes emergency landing in Russia - Metro.co.uk</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitgFBVV95cUxQVDFrVG1EcHJfSVNmdjdaa2N3dmxFYm90cmFIR09OWncwQTFTY1p1bFFPSGlXS3RWUl9JZ0taOGNKZWV5NmpkRmFoZW5Pd09pc1RuZEJ6blhhZ29uQU5zeUgxRHg1QVRBaVRjNWZaR0h2bEpnZ2RtMnlwcGQ0cnpsMktYZXZuQTR2emxVQUpXN2xFMmM1NWRPYlNhdkxwQ0NUWk9SaU10R0RpMEp2aHI2blJjY1V3dw?oc=5" target="_blank"&gt;Manchester-bound flight carrying 230 people makes emergency landing in Russia&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Metro.co.uk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQVDFrVG1EcHJfSVNmdjdaa2N3dmxFYm90cmFIR09OWncwQTFTY1p1bFFPSGlXS3RWUl9JZ0taOGNKZWV5NmpkRmFoZW5Pd09pc1RuZEJ6blhhZ29uQU5zeUgxRHg1QVRBaVRjNWZaR0h2bEpnZ2RtMnlwcGQ0cnpsMktYZXZuQTR2emxVQUpXN2xFMmM1NWRPYlNhdkxwQ0NUWk9SaU10R0RpMEp2aHI2blJjY1V3dw?oc=5</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O364"/>
+  <dimension ref="A1:O371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22591,7 +22591,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22622,8 +22621,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
-      <c r="L358" t="inlineStr"/>
       <c r="M358" t="inlineStr">
         <is>
           <t>review</t>
@@ -22656,7 +22653,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22687,8 +22683,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
-      <c r="L359" t="inlineStr"/>
       <c r="M359" t="inlineStr">
         <is>
           <t>review</t>
@@ -22721,7 +22715,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22752,8 +22745,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
-      <c r="L360" t="inlineStr"/>
       <c r="M360" t="inlineStr">
         <is>
           <t>review</t>
@@ -22786,7 +22777,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22817,8 +22807,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
-      <c r="L361" t="inlineStr"/>
       <c r="M361" t="inlineStr">
         <is>
           <t>review</t>
@@ -22851,7 +22839,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22882,8 +22869,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
-      <c r="L362" t="inlineStr"/>
       <c r="M362" t="inlineStr">
         <is>
           <t>review</t>
@@ -22916,7 +22901,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -22947,8 +22931,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
-      <c r="L363" t="inlineStr"/>
       <c r="M363" t="inlineStr">
         <is>
           <t>review</t>
@@ -22981,7 +22963,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -23012,8 +22993,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
-      <c r="L364" t="inlineStr"/>
       <c r="M364" t="inlineStr">
         <is>
           <t>review</t>
@@ -23025,6 +23004,461 @@
         </is>
       </c>
       <c r="O364" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>auto-71650c0e2b85</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Flugpersonal in Frankreich kündigt fünftägigen Streik im Oktober an</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Reisenden in Frankreich drohen zu Beginn der Herbstferien Flugausfälle und Verspätungen. Sechs Gewerkschaften des Kabinen- und Cockpitpersonals haben für den 17. bis 21. Oktober 2026 einen fünftägigen Streik angekündigt. Sie protestieren gegen eine Reform der Regeln für die Weiterbeschäftigung im Ruhestand, die Anfang 2027 in Kraft treten soll.</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flugpersonal-in-frankreich-kuendigt-fuenftaegigen-streik-im-oktober-an/mm0b36z</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>auto-9c9c11af0a7b</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>South African Airways muss unrechtmäßige Flugzeug-Leasingverlängerung rückabwickeln</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Ein südafrikanisches Sondergericht hat die Verlängerung eines Leasingvertrags zwischen South African Airways und Flyfofa Airways für rechtswidrig erklärt. SAA hatte 2019 den Vertrag für ein Frachtflugzeug um drei Jahre verlängert, ohne ein Vergabeverfahren durchzuführen oder die erforderliche Genehmigung des Finanzministeriums einzuholen. Das Flugzeug war bei Vertragsabschluss außer Betrieb. South African Airways zahlte dennoch weiter, während es am Boden blieb.</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/south-african-airways-muss-unrechtmaessige-flugzeug-leasingverlaengerung/vlmtr18</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>auto-1c8babc37c52</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>CV Sky verstärkt Flotte mit zusätzlicher ATR 72</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Die kapverdische Fluggesellschaft CV Sky LACV hat ihre Kapazitäten mit einer geleasten ATR 72-200 von Global Aviation verstärkt. Das Flugzeug mit der Registrierung 5T-ZMS ist seit dem 12. September im Einsatz. Mit der zusätzlichen ATR will CVsky auf die gestiegene Nachfrage reagieren und insbesondere die Frequenzen auf Verbindungen über Praia und São Filipe erhöhen, so das Portal News Aero.</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/cv-sky-verstaerkt-flotte-mit-zusaetzlicher-atr-72/lrv8vlb</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>auto-84c44e335a46</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>DHL Express startet neue Frachtroute zwischen Bahrain und Johannesburg</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>DHL Express hat eine neue Direktverbindung zwischen Bahrain und Johannesburg aufgenommen. Eine Boeing 767 F bedient die Strecke künftig ein Mal wöchentlich. Der erste Flug ist bereits am Flughafen Johannesburg-OR Tambo eingetroffen.</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/dhl-express-startet-neue-frachtroute-zwischen-bahrain-und-johannesburg/61ydcvg</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>auto-8476f75a136c</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Großbritannien betankt saudische Kampfjets in der Luft</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>LONDON - Die britische Regierung reagiert auf eine Anfrage Saudi-Arabiens und liefert militärische Hilfe. An Angriffen auf die Huthi-Rebellen soll Großbritannien aber nicht beteiligt sein.</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53707/Grossbritannien-betankt-saudische-Kampfjets-in-der-Luft.html</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>auto-0e09ca584559</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Rechenzentren: Amazon setzt auf Logistiker Kühne+Nagel</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>HAMBURG - Der Wettstreit der KI-Giganten wird auch über Logistik entschieden - der Aufbau neuer Rechenzentren beschert der Luftfrachtbranche Milliardenumsätze. Amazon setzt auf Kühne+Nagel. Der US-Konzern sichert Verträge mit Optionen auf eine Unternehmensbeteiligung ab.</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53705/Rechenzentren-Amazon-setzt-auf-Logistiker-KuehneNagel.html</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr"/>
+      <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>auto-4c758dd5e4de</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>BEA vertieft Untersuchung zu Beinahekatastrophe in Nizza</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>NIZZA - 358 Menschen entgehen am 21. September 2025 knapp einer Katastrophe: Ein Airbus A320 fliegt in Nizza die falsche Landebahn an - und verfehlt einen startbereiten Easyjet-Airbus um wenige Meter. Die französische Flugunfallbehörde BEA arbeitet den Vorfall akribisch auf, der Flughafen zieht Konsequenzen.</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53703/BEA-vertieft-Untersuchung-zu-Beinahekatastrophe-in-Nizza.html</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O371"/>
+  <dimension ref="A1:O381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23025,7 +23025,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23056,8 +23055,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
-      <c r="L365" t="inlineStr"/>
       <c r="M365" t="inlineStr">
         <is>
           <t>review</t>
@@ -23090,7 +23087,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23121,8 +23117,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
-      <c r="L366" t="inlineStr"/>
       <c r="M366" t="inlineStr">
         <is>
           <t>review</t>
@@ -23155,7 +23149,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23186,8 +23179,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
-      <c r="L367" t="inlineStr"/>
       <c r="M367" t="inlineStr">
         <is>
           <t>review</t>
@@ -23220,7 +23211,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23251,8 +23241,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
-      <c r="L368" t="inlineStr"/>
       <c r="M368" t="inlineStr">
         <is>
           <t>review</t>
@@ -23285,7 +23273,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23316,8 +23303,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
-      <c r="L369" t="inlineStr"/>
       <c r="M369" t="inlineStr">
         <is>
           <t>review</t>
@@ -23350,7 +23335,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23381,8 +23365,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
-      <c r="L370" t="inlineStr"/>
       <c r="M370" t="inlineStr">
         <is>
           <t>review</t>
@@ -23415,7 +23397,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23446,8 +23427,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
-      <c r="L371" t="inlineStr"/>
       <c r="M371" t="inlineStr">
         <is>
           <t>review</t>
@@ -23459,6 +23438,656 @@
         </is>
       </c>
       <c r="O371" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>auto-c3fbcadd3bd8</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Airbus erhält 25-Jahres-Vertrag für Cybersicherheit in Frankreich</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Die französische Rüstungsbeschaffungsbehörde DGA hat Airbus über die Tochter Airbus Cybersecurity einen 25-Jahres-Vertrag für Cybersicherheits-Gateways erteilt. Die Systeme sollen in den Netzwerken des französischen Verteidigungsministeriums und seiner Direktionen und Abteilungen zum Einsatz kommen, wie Airbus am Mittwoch (23. September) mitteilt. Der Vertrag umfasst Entwicklung, Produktion und langfristige Wartung.</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker-verteidigung/airbus-erhaelt-25-jahres-vertrag-fuer-cybersicherheit-in-frankreich/cd8hlz5</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>auto-269720ff30df</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Jupiter Jet least zwei Boeing 757 F</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Der US-amerikanische Flugzeughändler Aer Sale hat einen umgebauten Boeing 757-200PCF an die kasachische Fluggesellschaft Jupiter Jet geliefert. Die Übergabe erfolgte Anfang September. Damit hat AerSale inzwischen drei zentralasiatische Frachtfluggesellschaften mit umgebauten Boeing 757 beliefert.</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/jupiter-jet-least-zwei-boeing-757-f/b19j6cf</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr"/>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>auto-97b0d68cfc41</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Flughafen Dresden und EFW Elbe Flugzeugwerke planen weitere Entwicklung</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Die Mitteldeutsche Flughafen AG will die Wachstumspläne der Elbe Flugzeugwerke EFW am Standort Dresden unterstützen. Beide Unternehmen haben vereinbart, den künftigen Infrastrukturbedarf gemeinsam zu ermitteln und bei möglichen Veränderungen am Flughafen frühzeitig zu berücksichtigen.</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flughafen-dresden-und-efw-elbe-flugzeugwerke-planen-weitere-entwicklung/22wy5p5</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>auto-5721b69ee00a</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Safran beteiligt sich an französischem Antriebsspezialisten Akira</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Safran hat über seine Beteiligungsgesellschaft Safran Corporate Ventures eine Minderheitsbeteiligung am französischen Unternehmen Akira erworben. Der Spezialist für die Entwicklung und Erprobung von Antriebssystemen will mit dem neuen Kapital seine Produktions- und Testkapazitäten ausbauen und künftig auch kleinere und mittlere Serien fertigen. Angaben zur Höhe der Investition machte Safran nicht.</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/safran-beteiligt-sich-an-franzoesischem-antriebsspezialisten-akira/z7sf1jb</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>auto-61631e18a5ae</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Lufthansa bringt Subventionen für Zubringerlinien ins Spiel</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa rechnet ihr Zubringersystem nach. Wegbrechende Frequenzen und Strecken im innerdeutschen Netz schränken Hubanbindungen ganzer Regionen ein. Lufthansa fordert konkrete Entlastungen - und reißt zum ersten Mal auch die Möglichkeit direkter Subventionen einzelner Flugstrecken an.</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53723/Lufthansa-bringt-Subventionen-von-Zubringerlinien-ins-Spiel.html</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>auto-fe89caeef0e7</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Kein Sozialplan für Cityline-Piloten?</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa sperrt sich nach Darstellung der Pilotengewerkschaft Vereinigung Cockpit gegen einen Sozialplan bei Cityline. Lufthansa will das so nicht stehenlassen.</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53721/Kein-Sozialplan-fuer-Cityline-Piloten.html</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>auto-1d9b8f68f745</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Condor baut Zubringernetz 2027 weiter aus</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Condor baut ihr Zubringer- und Städtenetz rund um das Drehkreuz Frankfurt im Sommer 2027 auf 16 Ziele aus. Diese Ziele sind neu.</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53720/Condor-baut-Zubringernetz-2027-weiter-aus.html</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr"/>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>auto-c2a3576b6685</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Bericht: Air France-KLM bietet Portugal Beteiligung an</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>LISSABON - Portugal will im Bieterrennen um TAP Air Portugal Mitte Oktober über den Zuschlag entscheiden. Beteiligungsangebote von Lufthansa und Air France-KLM liegen effektiv nahe beieinander - unterscheiden sich nach einem Medienbericht aber in einem Detail klar: Air France-KLM wedelt mit eigenen Aktien, Lufthansa mit Geld.</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53695/Bericht-Air-France-KLM-bietet-Portugal-Beteiligung-an.html</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>auto-33447c1809e4</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Dubai-Flüge: Emirates verdrängt Condor aus Berlin</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Condor nimmt ihre täglichen Verbindungen von Berlin und Stuttgart nach Dubai zum Winterflugplan aus dem Programm. Die Airline spielt in einer Mitteilung auf die kürzlich erfolgte Freigabe von Emirates-Flügen in Berlin an. Condor muss sich laut Kreisen zudem einem Spardiktat ihres Hauptinvestors unterwerfen.</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53710/Dubai-Fluege-Emirates-verdraengt-Condor-aus-Berlin.html</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr"/>
+      <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>auto-5f2fb9717458</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Delta flight DL147 Airbus A350 from Atlanta to Santiago declared an emergency and diverted - airlive</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMizAFBVV95cUxNUWJrUS1aMjFSVWNISWxyVWoxWE9PTXNEcVVIbzJLeWZSdV9FU1luLW5MTlBvWk5IYkprZEF4THk0aHNfMDUtRDF2bEF1NDU2bXpUU24xWTNFUWFGUkdpSkxlQktSQ3Fqc2p0aGlnd3o2ZEprd1lrNFU4Y0JiRDJ5bG56NmVVTjY1enNSUWw2TEhlNVZiUVFoTkducDJGYjlOUEdiVk1BdkIwQXl6NkE0cG9NU3ZlRUdGOG04bUoxa2lKQ1c1eGNuWXVuUkg?oc=5" target="_blank"&gt;Delta flight DL147 Airbus A350 from Atlanta to Santiago declared an emergency and diverted&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNUWJrUS1aMjFSVWNISWxyVWoxWE9PTXNEcVVIbzJLeWZSdV9FU1luLW5MTlBvWk5IYkprZEF4THk0aHNfMDUtRDF2bEF1NDU2bXpUU24xWTNFUWFGUkdpSkxlQktSQ3Fqc2p0aGlnd3o2ZEprd1lrNFU4Y0JiRDJ5bG56NmVVTjY1enNSUWw2TEhlNVZiUVFoTkducDJGYjlOUEdiVk1BdkIwQXl6NkE0cG9NU3ZlRUdGOG04bUoxa2lKQ1c1eGNuWXVuUkg?oc=5</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr"/>
+      <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O381"/>
+  <dimension ref="A1:O391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23459,7 +23459,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23490,8 +23489,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
-      <c r="L372" t="inlineStr"/>
       <c r="M372" t="inlineStr">
         <is>
           <t>review</t>
@@ -23524,7 +23521,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23555,8 +23551,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
-      <c r="L373" t="inlineStr"/>
       <c r="M373" t="inlineStr">
         <is>
           <t>review</t>
@@ -23589,7 +23583,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23620,8 +23613,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
-      <c r="L374" t="inlineStr"/>
       <c r="M374" t="inlineStr">
         <is>
           <t>review</t>
@@ -23654,7 +23645,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23685,8 +23675,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
-      <c r="L375" t="inlineStr"/>
       <c r="M375" t="inlineStr">
         <is>
           <t>review</t>
@@ -23719,7 +23707,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23750,8 +23737,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
-      <c r="L376" t="inlineStr"/>
       <c r="M376" t="inlineStr">
         <is>
           <t>review</t>
@@ -23784,7 +23769,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23815,8 +23799,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
-      <c r="L377" t="inlineStr"/>
       <c r="M377" t="inlineStr">
         <is>
           <t>review</t>
@@ -23849,7 +23831,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23880,8 +23861,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
-      <c r="L378" t="inlineStr"/>
       <c r="M378" t="inlineStr">
         <is>
           <t>review</t>
@@ -23914,7 +23893,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -23945,8 +23923,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
-      <c r="L379" t="inlineStr"/>
       <c r="M379" t="inlineStr">
         <is>
           <t>review</t>
@@ -23979,7 +23955,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24010,8 +23985,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
-      <c r="L380" t="inlineStr"/>
       <c r="M380" t="inlineStr">
         <is>
           <t>review</t>
@@ -24044,7 +24017,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -24075,8 +24047,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
-      <c r="L381" t="inlineStr"/>
       <c r="M381" t="inlineStr">
         <is>
           <t>review</t>
@@ -24088,6 +24058,656 @@
         </is>
       </c>
       <c r="O381" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>auto-9b823f2207c0</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>DAT-Fluggäste aus Linz können in Frankfurt nun auch auf Qatar Airways umsteigen</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Seit Ende März 2026 fliegt DAT mit einer ATR 72 auf der staatlich subventionierten Strecke zwischen Linz und Frankfurt. &lt;a href="https://www.aerotelegraph.com/flughaefen/fluege-zwischen-linz-und-frankfurt-bleiben-ziemlich-leer/ymv4c00" id="74068d22-cf68-44df-a775-a8b545aff8c9"&gt;Doch die Auslastung blieb zunächst bescheiden: Im April lag sie bei rund 27 Prozent, im Mai bei 30 Prozent, im Juni 35 Prozent und im Juli bei 30 Prozent&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/dat-fluggaeste-aus-linz-koennen-in-frankfurt-nun-auch-auf-qatar-airways-umsteigen/b9j17r1</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr"/>
+      <c r="L382" t="inlineStr"/>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>auto-bd5fb72d0984</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Singapore Airlines betreibt weiterhin fünf Boeing 777 F für DHL</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>DHL Express und Singapore Airlines haben ihre Zusammenarbeit beim Betrieb von fünf Boeing 777 F verlängert. Die in Singapur stationierten Frachtflugzeuge werden weiterhin von Piloten der Singapore Airlines geflogen. Die Fluggesellschaft übernimmt zudem die Wartung.</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/singapore-airlines-betreibt-weiterhin-fuenf-boeing-777-f-fuer-dhl/tr72f28</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr"/>
+      <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>auto-0492cb2b26fa</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>ST Engineering wartet Triebwerke von Hebei Airlines' Boeing 737</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>ST Engineering übernimmt für zwei Jahre exklusiv die Wartung von CFM56-7B-Triebwerken der chinesischen Hebei Airlines. Die Vereinbarung umfasst sogenannte «Performance Restoration Shop Visits» für 14 Triebwerke, die an Boeing 737-800 der Airline eingesetzt werden. Die Arbeiten beginnen im September 2026 und werden im ST-Engineering-Werk im chinesischen Xiamen durchgeführt. Dort verfügt das Unternehmen über Kapazitäten für CFM56-7B und CFM56-5B. ST Engineering verweist auf die weiterhin hohe Nachfrage nach Wartungsleistungen für CFM56-Triebwerke, da Fluggesellschaften ihre Schmalrumpfflotten angesichts hoher Auslastung länger betreiben. Parallel baut das Unternehmen seine Kapazitäten für die nächste Triebwerksgeneration Leap aus.</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/st-engineering-wartet-triebwerke-von-hebei-airlines-boeing-737/rj0dcj5</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>auto-ede7355fe863</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Airbus-Crew übt Vollbremsungen mit A350F</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>TOULOUSE - Airbus will nächste Woche die Flugtests mit der A350F aufnehmen. Nach 400 Flugteststunden soll der neue Frachter 2027 die EASA-Zulassung erhalten. In Toulouse führte der Prototyp am Donnerstag Startabbruchtests durch - ein klares Indiz für einen in Kürze bevorstehenden Erstflug.</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53741/Airbus-Crew-uebt-Vollbremsung-mit-A350F.html</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr"/>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>auto-ddffe5177bc2</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Teyssen: Lufthansa verliert den Anschluss</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Johannes Teyssen ist im neuen Job angekommen. Seit einigen Monaten wacht der ehemalige E.ON-Chef von der Spitze des Aufsichtsrats über den verzweigten Lufthansa-Konzern - und erwartet im Lufthansa-Kernbereich Handlungsbedarf über einen laufenden Transformationsplan hinaus.</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53736/Teyssen-Lufthansa-verliert-den-Anschluss.html</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr"/>
+      <c r="L386" t="inlineStr"/>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>auto-dd6c130873f3</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Lufthansa verlängert mit drei Konzernvorständen</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa hatte 2024 ihren Konzernvorstand radikal umgebaut. Nun hat Lufthansa erste Verträge verlängert.</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53735/Lufthansa-verlaengert-mit-drei-Konzernvorstaenden.html</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr"/>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>auto-3b5d5509ec57</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Air Corsica zieht fast alle ATR 72-600 aus dem Verkehr</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>AJACCIO - "Ungewöhnliche Gerüche" in Cockpits und Kabinen: Air Corsica zieht fünf ihrer sieben ATR 72-600 für einen gründlichen Technikcheck aus dem Verkehr. Der Ausfall von fünf ATR-72-600 stellt die französische Regionalfluggesellschaft vor erhebliche operative Herausforderungen.</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53730/Air-Corsica-zieht-fast-alle-ATR-72-600-aus-dem-Verkehr.html</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>auto-8ddde135d0d5</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Lufthansa prüft zentralere Steuerung von Lufthansa Airlines</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa krempelt ihren Kernbereich seit 2024 um: "Turnaround" zeigt im größten Teilkonzern Lufthansa Airlines Wirkung. Nach einem Medienbericht prüft Lufthansa im laufenden Programm eine weitere Maßnahme. Das Teilprojekt "Nexus" ist intern allerdings umstritten.</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53719/Lufthansa-prueft-zentralere-Steuerung-von-Lufthansa-Airlines.html</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>auto-e0ec0732518c</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Wizz Air fliegt von Frankfurt nach Sofia und Budapest - aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMipAFBVV95cUxQNVhtQzRtdDRST1BpT3VaUmpScURsNjZWdlJvXzdPLS1nTGwtSXJwSEhLUHFFLTZLckEwd19peF83YUI5OEE4UEhuTHFBY01hSXotamdzQllIYm1FQUZnb0RkdWQ4VElGRk9seXY5Nm94b0VYRVphbDZwbGxOR2JVTUp2U2p5aUtNRGFIaXNDSU5RaTdFTVNGdXJHRGJoeWYwN281Tw?oc=5" target="_blank"&gt;Wizz Air fliegt von Frankfurt nach Sofia und Budapest&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;aeroTELEGRAPH&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNVhtQzRtdDRST1BpT3VaUmpScURsNjZWdlJvXzdPLS1nTGwtSXJwSEhLUHFFLTZLckEwd19peF83YUI5OEE4UEhuTHFBY01hSXotamdzQllIYm1FQUZnb0RkdWQ4VElGRk9seXY5Nm94b0VYRVphbDZwbGxOR2JVTUp2U2p5aUtNRGFIaXNDSU5RaTdFTVNGdXJHRGJoeWYwN281Tw?oc=5</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr"/>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>auto-9e2efadfcf10</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>easyJet flight U28105 declared an emergency over France following technical issue with the aircraft - airlive</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi2AFBVV95cUxPdlZ6T3ViUDFFWHpGSy1DYl9oZDROZWx5cnZqTVR4LWlncHM0OUp5WURMRlFQeHUwR3JReGJ2NlZWbVpuYzZabjRlSHlpbjhqOVF2NUk0VS1JZGpaXzUzTUQzeGtRbmZkSWw2aTliVXgwY205Tm1FaVpBUk9FWk9IcHdrUEVyWDd5a2JQVnpMc04ycm81bkRNNW9hZlpHT3lxUzBLRm81ZTc1ZGRkUHZ2cS11NHdkQ2E3OUprRWtTd2RacEhNN2J5b29scl9Ra2tDVXYtMTRqSDc?oc=5" target="_blank"&gt;easyJet flight U28105 declared an emergency over France following technical issue with the aircraft&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPdlZ6T3ViUDFFWHpGSy1DYl9oZDROZWx5cnZqTVR4LWlncHM0OUp5WURMRlFQeHUwR3JReGJ2NlZWbVpuYzZabjRlSHlpbjhqOVF2NUk0VS1JZGpaXzUzTUQzeGtRbmZkSWw2aTliVXgwY205Tm1FaVpBUk9FWk9IcHdrUEVyWDd5a2JQVnpMc04ycm81bkRNNW9hZlpHT3lxUzBLRm81ZTc1ZGRkUHZ2cS11NHdkQ2E3OUprRWtTd2RacEhNN2J5b29scl9Ra2tDVXYtMTRqSDc?oc=5</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr"/>
+      <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O391"/>
+  <dimension ref="A1:O394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24079,7 +24079,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24110,8 +24109,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
-      <c r="L382" t="inlineStr"/>
       <c r="M382" t="inlineStr">
         <is>
           <t>review</t>
@@ -24144,7 +24141,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24175,8 +24171,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
-      <c r="L383" t="inlineStr"/>
       <c r="M383" t="inlineStr">
         <is>
           <t>review</t>
@@ -24209,7 +24203,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24240,8 +24233,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
-      <c r="L384" t="inlineStr"/>
       <c r="M384" t="inlineStr">
         <is>
           <t>review</t>
@@ -24274,7 +24265,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24305,8 +24295,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
-      <c r="L385" t="inlineStr"/>
       <c r="M385" t="inlineStr">
         <is>
           <t>review</t>
@@ -24339,7 +24327,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24370,8 +24357,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
-      <c r="L386" t="inlineStr"/>
       <c r="M386" t="inlineStr">
         <is>
           <t>review</t>
@@ -24404,7 +24389,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24435,8 +24419,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
-      <c r="L387" t="inlineStr"/>
       <c r="M387" t="inlineStr">
         <is>
           <t>review</t>
@@ -24469,7 +24451,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24500,8 +24481,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
-      <c r="L388" t="inlineStr"/>
       <c r="M388" t="inlineStr">
         <is>
           <t>review</t>
@@ -24534,7 +24513,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24565,8 +24543,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
-      <c r="L389" t="inlineStr"/>
       <c r="M389" t="inlineStr">
         <is>
           <t>review</t>
@@ -24599,7 +24575,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24630,8 +24605,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
-      <c r="L390" t="inlineStr"/>
       <c r="M390" t="inlineStr">
         <is>
           <t>review</t>
@@ -24664,7 +24637,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24695,8 +24667,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
-      <c r="L391" t="inlineStr"/>
       <c r="M391" t="inlineStr">
         <is>
           <t>review</t>
@@ -24708,6 +24678,201 @@
         </is>
       </c>
       <c r="O391" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>auto-3fb5159c39dd</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Azul baut Flotte um drei Flieger aus - Airbus A321 P2F, A330 und Cessna Sky Courier eingeflottet</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Die brasilianische Fluggesellschaft Azul hat ihre Flotte um zwei Flugzeuge erweitert. Am 18. September traf der Airbus A321 P2F PS-AJF in Belo Horizonte ein. Er ist das dritte von insgesamt sechs geplanten Frachtflugzeugen dieses Typs für Azul Logística. Einen Tag später folgte der Airbus A330 PR-AHF, der künftig auf internationalen Langstrecken nach Europa und in die USA eingesetzt werden soll. Beide Flugzeuge kamen aus China.</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/azul-baut-flotte-um-drei-flieger-aus-airbus-a321-p2f-a330-und-cessna-sky-courier/509rwlb</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr"/>
+      <c r="L392" t="inlineStr"/>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>auto-39e06b7c898c</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>KM Malta Airlines kombiniert Flüge mit TGV-Verbindungen</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>KM Malta Airlines und die französische Bahngesellschaft SNCF Voyageurs starten eine Train+Air-Partnerschaft. Reisende können damit Flüge der maltesischen Airline und anschließende Bahnfahrten durch Frankreich sowie nach Brüssel gemeinsam buchen. Als Umsteigepunkte dienen die Flughäfen Paris-Charles-de-Gaulle und Lyon-Saint-Exupéry.</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/km-malta-airlines-kombiniert-fluege-mit-tgv-verbindungen/hh2j27f</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr"/>
+      <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>auto-4033e252c366</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Attestor übernimmt Condor 2027 ganz</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Attestor übt eine Option auf noch vom Staat gehaltene Condor-Anteile aus. Die Komplettübernahme werde am 31. August 2027 vollzogen, teilte Condor am Freitag in Frankfurt mit. Condor hatte zuvor die Voraussetzungen für einen Ausstieg von Bund und Hessen geschaffen.</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53748/Attestor-uebernimmt-Condor-2027-ganz.html</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O394"/>
+  <dimension ref="A1:O398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24699,7 +24699,6 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24730,8 +24729,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
-      <c r="L392" t="inlineStr"/>
       <c r="M392" t="inlineStr">
         <is>
           <t>review</t>
@@ -24764,7 +24761,6 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24795,8 +24791,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
-      <c r="L393" t="inlineStr"/>
       <c r="M393" t="inlineStr">
         <is>
           <t>review</t>
@@ -24829,7 +24823,6 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24860,8 +24853,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
-      <c r="L394" t="inlineStr"/>
       <c r="M394" t="inlineStr">
         <is>
           <t>review</t>
@@ -24873,6 +24864,266 @@
         </is>
       </c>
       <c r="O394" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>auto-3a4f4658c298</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Lufthansa nimmt Flüge zwischen Bremen und Frankfurt wieder auf</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Bremens Beharrlichkeit zahlt sich aus: Lufthansa wird die Hansestadt im kommenden Sommerflugplan wieder mit Frankfurt verbinden. Allerdings mit einer deutlich niedrigeren Frequenz.</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flughaefen/lufthansa-verbindet-bremen-wieder-mit-frankfurt/swdl4kc</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>auto-cbf8e9025410</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Qatar Airways, IAG und Malaysia Airlines starten gemeinsames Frachtgeschäft</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Die Frachtsparten von Qatar Airways, IAG und Malaysia Airlines stehen kurz vor dem Start ihres gemeinsamen Cargo-Geschäfts. Qatar Airways Cargo, IAG Cargo und MAS kargo wollen die Kooperation in den kommenden Wochen kommerziell lancieren – rund ein Jahr später als ursprünglich geplant.</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/qatar-airways-iag-und-malaysia-airlines-starten-gemeinsames-frachtgeschaeft/e9mn93l</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>auto-8665f0dee6af</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Lufthansa nimmt Bremen-Frankfurt wieder auf</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>BREMEN - Für Passagiere aus Bremen und Umgebung wird die Reise zu vielen internationalen Zielen einfacher: Ab dem Sommer soll täglich wieder ein Flugzeug nach Frankfurt starten, wie die Bremer Senatskanzlei mitteilte.</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53756/Lufthansa-nimmt-Bremen-Frankfurt-wieder-auf.html</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr"/>
+      <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>auto-0f7534d1679a</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Bundesregierung stellt Milliardenbetrag für eSAF-Nutzung bereit</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>BERLIN - Deutschland, Österreich und Luxemburg wollen gemeinsam den Markthochlauf von erneuerbarem strombasiertem Kerosin (eSAF) in Europa beschleunigen. Dafür greifen die Initiatoren auf ein spezielles Auktionsmodell zurück, bei dem der Staat die Preislücke zwischen Angebot und Nachfrage schließt.</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53754/Deutschland-foerdert-eSAF-mit-Milliardensumme.html</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr"/>
+      <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O398"/>
+  <dimension ref="A1:O401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24885,7 +24885,6 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24916,8 +24915,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
-      <c r="L395" t="inlineStr"/>
       <c r="M395" t="inlineStr">
         <is>
           <t>review</t>
@@ -24950,7 +24947,6 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -24981,8 +24977,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
-      <c r="L396" t="inlineStr"/>
       <c r="M396" t="inlineStr">
         <is>
           <t>review</t>
@@ -25015,7 +25009,6 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -25046,8 +25039,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr"/>
       <c r="M397" t="inlineStr">
         <is>
           <t>review</t>
@@ -25080,7 +25071,6 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -25111,8 +25101,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
-      <c r="L398" t="inlineStr"/>
       <c r="M398" t="inlineStr">
         <is>
           <t>review</t>
@@ -25124,6 +25112,201 @@
         </is>
       </c>
       <c r="O398" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>auto-824b44c4d10c</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Boeing 747-400 von Lufthansa bricht Flug ab</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Ein Lufthansa-Flug von Frankfurt nach Toronto mit 371 Passagieren an Bord ist aus Sicherheitsgründen über Schottland umgekehrt und in Manchester gelandet.</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53761/Boeing-747-400-von-Lufthansa-bricht-Flug-ab.html</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr"/>
+      <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>auto-7c96161b913d</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Lufthansa LH470 to Toronto declared an emergency and diverted to Manchester - airlive</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr"/>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiuAFBVV95cUxOMUNtX0diMHhvYzJLMjNPT3Jmd0lvWEg4RnpXcVAxU3lUcVRJVnRNUFYxOXVPZWp4UkZHTFp4RmhIaFJKSEhSbENabGJ3aHFyRGtsTzJKYU5pMGVnand2T1NKUzUxZkFGM2JQV1Jod2d2clFTeUd6NWJZWEZWZ0tncGJIWXJ2WXM1QXRiTE5XVV95MjI3cGhLSk5aY2JGUnFvdTNESzVzZVJ2UzJ3czMyWms2cHlKSUN4?oc=5" target="_blank"&gt;Lufthansa LH470 to Toronto declared an emergency and diverted to Manchester&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOMUNtX0diMHhvYzJLMjNPT3Jmd0lvWEg4RnpXcVAxU3lUcVRJVnRNUFYxOXVPZWp4UkZHTFp4RmhIaFJKSEhSbENabGJ3aHFyRGtsTzJKYU5pMGVnand2T1NKUzUxZkFGM2JQV1Jod2d2clFTeUd6NWJZWEZWZ0tncGJIWXJ2WXM1QXRiTE5XVV95MjI3cGhLSk5aY2JGUnFvdTNESzVzZVJ2UzJ3czMyWms2cHlKSUN4?oc=5</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>auto-4f2ea915b8cb</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Lucknow emergency landing for Dubai–Kathmandu flight: 154 passengers onboard; diverted due to bad weather, ... - bhaskarenglish.in</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr"/>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiwwFBVV95cUxQM2s2bGpfako2dXNOdjBCcG0yeHdoTDNjSmNJd01EQXNDTTdxcUM5R0RJRXAtN0toV0kwWG9UOUUtODVjcmVzQ0RaQllMSlJTWHl4Zk5JTmc3Uk1oMzRmUTNHazl6QVRwa1g2bTFxMWIzS3ZQM0ZacDcydWlCN2lGYTgycmhQNk5IcU9jdk45bWZuRzFBbjJXdTVyOXBndkdtREpLNlVEMlJqNXE2TVotS0I4QktqVE5hdWNCazFnODBSemvSAcgBQVVfeXFMT2I3MkNaX1ZsZTAxclpMaHF5Wjl0ZEcycnhRZVdPb2JuY3cwZzBJVkxRLWxLUGdKTDBNcVZYbHJ4YlZFakNlR0p3NWtIeXpoQmFaenJlVlFNRzVkZHN3NGczV2F2QWdwdWRBYzBjODl5c2tfcWNHVVFCZWExTU80OXdFMTJSNUNJdkhwSGttV1pneTBxUTkwN1U4ME8ydWJGcVJyUlQ4Q3N2UFNvMktpS2lQZll6MHR5X2REOGxYYmJjVmQzSnZvZW0?oc=5" target="_blank"&gt;Lucknow emergency landing for Dubai–Kathmandu flight: 154 passengers onboard; diverted due to bad weather, ...&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;bhaskarenglish.in&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQM2s2bGpfako2dXNOdjBCcG0yeHdoTDNjSmNJd01EQXNDTTdxcUM5R0RJRXAtN0toV0kwWG9UOUUtODVjcmVzQ0RaQllMSlJTWHl4Zk5JTmc3Uk1oMzRmUTNHazl6QVRwa1g2bTFxMWIzS3ZQM0ZacDcydWlCN2lGYTgycmhQNk5IcU9jdk45bWZuRzFBbjJXdTVyOXBndkdtREpLNlVEMlJqNXE2TVotS0I4QktqVE5hdWNCazFnODBSemvSAcgBQVVfeXFMT2I3MkNaX1ZsZTAxclpMaHF5Wjl0ZEcycnhRZVdPb2JuY3cwZzBJVkxRLWxLUGdKTDBNcVZYbHJ4YlZFakNlR0p3NWtIeXpoQmFaenJlVlFNRzVkZHN3NGczV2F2QWdwdWRBYzBjODl5c2tfcWNHVVFCZWExTU80OXdFMTJSNUNJdkhwSGttV1pneTBxUTkwN1U4ME8ydWJGcVJyUlQ4Q3N2UFNvMktpS2lQZll6MHR5X2REOGxYYmJjVmQzSnZvZW0?oc=5</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O401"/>
+  <dimension ref="A1:O405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25133,7 +25133,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -25164,8 +25163,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
-      <c r="L399" t="inlineStr"/>
       <c r="M399" t="inlineStr">
         <is>
           <t>review</t>
@@ -25198,7 +25195,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -25229,8 +25225,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
-      <c r="L400" t="inlineStr"/>
       <c r="M400" t="inlineStr">
         <is>
           <t>review</t>
@@ -25263,7 +25257,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -25294,8 +25287,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
-      <c r="L401" t="inlineStr"/>
       <c r="M401" t="inlineStr">
         <is>
           <t>review</t>
@@ -25307,6 +25298,266 @@
         </is>
       </c>
       <c r="O401" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>auto-b45dcb20b038</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Fünf Ziele: Vini nimmt Frankfurt-Egelsbach ins Angebot auf</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Vini erweitert seine Plattform für regionale Flugverbindungen auf Frankfurt-Egelsbach. Reisende und Unternehmen können dort ab sofort ihren Bedarf für Flüge nach Sylt, Antwerpen, Hamburg, Bremen und Berlin-Schönhagen hinterlegen und entsprechende Verbindungen anfragen. Vini bündelt damit die Nachfrage für mögliche regionale Flugverbindungen. Zuvor hatte das Unternehmen bereits Testwochen und erste Verbindungen rund um Bern, München, Mannheim, Berlin und Karlsruhe durchgeführt.</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/fuenf-ziele-vini-nimmt-frankfurt-egelsbach-ins-angebot-auf/pnyjvdd</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>auto-afb83bd3d875</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Warum Treibstoff der größte Risikofaktor für Airlines bleibt</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Fluggesellschaften legen den Sommerflugplan 2027 fest. Kerosinkosten sind dabei die große Variable. Für kleinere Fluganbieter wird die Planungsunsicherheit nach Einschätzung von Ryanair-Chef Michael O'Leary 2027 existenzentscheidend. Und auch Analysten warnen vor Turbulenzen.</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53751/Warum-Treibstoff-der-groesste-Risikofaktor-fuer-Europas-Airlines-bleibt.html</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>auto-8209677fc386</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Emergency: Delta flight DL251 to Boston turned around over Atlantic and diverted to Porto - airlive</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiygFBVV95cUxOMGo0U3NvUjA3TlVfdTcxdTlBclhTZndxWEVMSV9wdjZHTVl6Qzh1d0ZRb2djcThUUXhqb0d6ZzBVRDctdlJkRkxuVXdKZHBlMnZaZzdzdmc4QU9FazF1WUpaRW9EenBPcjIzRlFUTEFWMnFRelEtYVJDYVplT2VudUkwYVNxOFVSZmdSeC1KMjB6eDJQM2VKZnJDMmVFSkZZRjR0a3o5cHZpeDNhRGZFVlJCbFdEYmZoMHFfRGZyYWQwNWFrNXBvRl9B?oc=5" target="_blank"&gt;Emergency: Delta flight DL251 to Boston turned around over Atlantic and diverted to Porto&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMGo0U3NvUjA3TlVfdTcxdTlBclhTZndxWEVMSV9wdjZHTVl6Qzh1d0ZRb2djcThUUXhqb0d6ZzBVRDctdlJkRkxuVXdKZHBlMnZaZzdzdmc4QU9FazF1WUpaRW9EenBPcjIzRlFUTEFWMnFRelEtYVJDYVplT2VudUkwYVNxOFVSZmdSeC1KMjB6eDJQM2VKZnJDMmVFSkZZRjR0a3o5cHZpeDNhRGZFVlJCbFdEYmZoMHFfRGZyYWQwNWFrNXBvRl9B?oc=5</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>auto-550b9342854b</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>United Airlines Boeing 787 to San Francisco dumped fuel following emergency call - airlive</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMivwFBVV95cUxNUUx0aGtGX1JvdzFiTTdXZVVjamFPLVJtUDRLdWZqdlYyZmlEYmVsSjgyNDEyQThibmJpSGZDTUloaTdXRnp6WEZaR1hHSTRwRHVUaUlIcUhWY0Z0ajVMRWhLc2xhODJxYWNBUkFyQlZkMnRLSzBYLWhGUWUtV1B4amZhRXMzZ3M0TkVRaG0wc0Q4NDBzVWVDajJSQ0pEZzN6OUMzRVlQOWhjbkg1bU1DbW4zY0FKUUZoVnNROVJFWQ?oc=5" target="_blank"&gt;United Airlines Boeing 787 to San Francisco dumped fuel following emergency call&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNUUx0aGtGX1JvdzFiTTdXZVVjamFPLVJtUDRLdWZqdlYyZmlEYmVsSjgyNDEyQThibmJpSGZDTUloaTdXRnp6WEZaR1hHSTRwRHVUaUlIcUhWY0Z0ajVMRWhLc2xhODJxYWNBUkFyQlZkMnRLSzBYLWhGUWUtV1B4amZhRXMzZ3M0TkVRaG0wc0Q4NDBzVWVDajJSQ0pEZzN6OUMzRVlQOWhjbkg1bU1DbW4zY0FKUUZoVnNROVJFWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O405"/>
+  <dimension ref="A1:O414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25319,7 +25319,6 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -25350,8 +25349,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
-      <c r="L402" t="inlineStr"/>
       <c r="M402" t="inlineStr">
         <is>
           <t>review</t>
@@ -25384,7 +25381,6 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -25415,8 +25411,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
-      <c r="L403" t="inlineStr"/>
       <c r="M403" t="inlineStr">
         <is>
           <t>review</t>
@@ -25449,7 +25443,6 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -25480,8 +25473,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
-      <c r="L404" t="inlineStr"/>
       <c r="M404" t="inlineStr">
         <is>
           <t>review</t>
@@ -25514,7 +25505,6 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -25545,8 +25535,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
-      <c r="L405" t="inlineStr"/>
       <c r="M405" t="inlineStr">
         <is>
           <t>review</t>
@@ -25558,6 +25546,591 @@
         </is>
       </c>
       <c r="O405" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>auto-bf2166290141</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Eine dieser beiden Airlines wird zuerst mit dem Airbus A350 F fliegen</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Am Dienstag ist der Airbus-A350-Frachter zum ersten Mal abgehoben. Ende 2027 will der Flugzeugbauer den ersten A350 F aus der Serienproduktion ausliefern. Zwei Kunden kommen für die Premiere infrage.</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugzeuge/eine-dieser-beiden-airlines-wird-zuerst-mit-dem-airbus-a350-f-fliegen/yswdnmw</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr"/>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>auto-5aa6510a15ba</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Herbstferien: Flughafen Frankfurt erwartet 3,5 Millionen Fluggäste - und warnt vor Wartezeiten</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Mit Beginn der Herbstferien in Hessen und anderen Bundesländern steigt das Passagieraufkommen am Flughafen Frankfurt. Zwischen dem 2. und 18. Oktober erwartet Flughafenbetreiberin Fraport rund 3,5 Millionen Reisende. Bereits für das erste Ferienwochenende vom 2. bis 4. Oktober rechnet Fraport mit etwa 650.000 Fluggästen.</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/herbstferien-flughafen-frankfurt-erwartet-35-millionen-fluggaeste-und-warnt-vor/dlxkhvy</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr"/>
+      <c r="L407" t="inlineStr"/>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>auto-8e96567dc47e</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Oman Air und Lufthansa erweitern Codeshare-Kooperation um Flüge nach Polen</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Oman Air und Lufthansa habe ihre Codeshare-Zusammenarbeit ausgebaut, wie das Portal &lt;a href="https://www.aeroroutes.com/eng/260924-wylhcodeshare" id="4ae770bc-1d7b-488e-8288-d42c09a0b456"&gt;Aero Routes&lt;/a&gt; berichtet. So platziert die omanische Fluggesellschaft seit dem 25. September ihren Code auf vier zusätzlichen Lufthansa-Strecken: Frankfurt - Danzig, Frankfurt - Posen, Frankfurt - Wrocław sowie München- Wrocław. Für Reisende bedeutet das, dass die Verbindungen nun auch unter Oman-Air-Flugnummern buchbar sind. Die neuen Codeshare-Flüge ergänzen die bereits bestehende Kooperation der beiden Fluggesellschaften.</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/oman-air-und-lufthansa-erweitern-codeshare-kooperation-um-fluege-nach-polen/mj46rj2</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr"/>
+      <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>auto-148906203bbb</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Airbus nimmt Flugerprobung der A350F auf</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>TOULOUSE - Airbus schickt die A350F in die Flugerprobung - der neue Frachter ist am Dienstag in Toulouse zu einem ersten Testflug gestartet. Die Piloten müssen "aerodynamische Eigenschaften" des Frachters kennenlernen, die sich von denen der Passagierversionen A350-900 und A350-1000 unterscheiden.</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53785/Airbus-nimmt-Flugerprobung-der-A350F-auf.html</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr"/>
+      <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>auto-cbe1e8775680</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt: 6,3 Millionen Passagiere im August</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Die Passagierzahlen am Frankfurter Flughafen stagnieren. Bei Luftfracht läuft es besser.</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53784/Flughafen-Frankfurt-63-Millionen-Passagiere-im-August.html</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>auto-860b2ac2aa10</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Lufthansa-Chef erwartet noch höhere Kerosin-Kosten</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Nicht nur den Autofahrern machen die gestiegenen Ölpreise an den Tankstellen zu schaffen. Auch die Lufthansa muss mehr Geld für Kerosin aufwenden. Das spüren die Passagiere.</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53783/Lufthansa-Chef-erwartet-noch-hoehere-Kerosin-Kosten.html</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>auto-65f0c3387d98</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Lufthansa rechnet bei Auslieferungen weiter mit Gegenwind</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>FRANKFURT - "Unwägbarkeiten auf der Flottenseite": Lufthansa-Chef Carsten Spohr sieht "große Fragezeichen" hinter Lieferterminen der Boeing 777-9. Lufthansa plant den Flugsommer 2027 in Frankfurt zunächst ohne das Flugzeug. In München macht sich Lufthansa auf spätere A350-1000-Auslieferungen gefasst.</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53782/Lufthansa-rechnet-bei-Auslieferungen-weiter-mit-Gegenwind.html</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>auto-c4b15ab2a7e2</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>United flight UA2123 to SFO declared an emergency then diverted to Salt Lake City - airlive.net</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiwAFBVV95cUxPd2NBUU1adXRCTnB4YWhxUVZsNmw0SzZXZ3ZSZWU0Sy1wcTM4azYwQk84eDdjUUFqQU82LTBCeV9YZlQ3QzRSMzJvdDNkblhpakpyVEdaRlFWUWxKTGRDd2FtYzE0Sm5LVGNJQ205dS1JWlBEMGVyREh6WEFuQ3A3a0M4LV9aSWU3MWlMUFRsSzBFcG1kbVloSlg4Z2huUzcyWWQ0S3FBY2M2N1VVc1paUkpac0ZOUUZ6NHozaFEyS00?oc=5" target="_blank"&gt;United flight UA2123 to SFO declared an emergency then diverted to Salt Lake City&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive.net&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPd2NBUU1adXRCTnB4YWhxUVZsNmw0SzZXZ3ZSZWU0Sy1wcTM4azYwQk84eDdjUUFqQU82LTBCeV9YZlQ3QzRSMzJvdDNkblhpakpyVEdaRlFWUWxKTGRDd2FtYzE0Sm5LVGNJQ205dS1JWlBEMGVyREh6WEFuQ3A3a0M4LV9aSWU3MWlMUFRsSzBFcG1kbVloSlg4Z2huUzcyWWQ0S3FBY2M2N1VVc1paUkpac0ZOUUZ6NHozaFEyS00?oc=5</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>auto-e2dc139ccf03</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Flight makes emergency landing in Italy after pilot forced to cut engine - CBS News</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiggFBVV95cUxQcm4wN2JSdWtGM25FZzFVY3RvR1RVelNQY0NGcGsySTlUOTFady1jb3F5Q3BJRnFCNFFmWEhXdXpBNHZ4T3U1bml2cFRGM3BaUkRqTGVRTFJGa3gxV2VGaEtBZ1YtbmRlTFlzT1Z1T25NdDVILVBCSGgxVnNFaXI4eVp3?oc=5" target="_blank"&gt;Flight makes emergency landing in Italy after pilot forced to cut engine&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;CBS News&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQcm4wN2JSdWtGM25FZzFVY3RvR1RVelNQY0NGcGsySTlUOTFady1jb3F5Q3BJRnFCNFFmWEhXdXpBNHZ4T3U1bml2cFRGM3BaUkRqTGVRTFJGa3gxV2VGaEtBZ1YtbmRlTFlzT1Z1T25NdDVILVBCSGgxVnNFaXI4eVp3?oc=5</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O414"/>
+  <dimension ref="A1:O422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25567,7 +25567,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -25598,8 +25597,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
-      <c r="L406" t="inlineStr"/>
       <c r="M406" t="inlineStr">
         <is>
           <t>review</t>
@@ -25632,7 +25629,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -25663,8 +25659,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
-      <c r="L407" t="inlineStr"/>
       <c r="M407" t="inlineStr">
         <is>
           <t>review</t>
@@ -25697,7 +25691,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -25728,8 +25721,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
-      <c r="L408" t="inlineStr"/>
       <c r="M408" t="inlineStr">
         <is>
           <t>review</t>
@@ -25762,7 +25753,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -25793,8 +25783,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
-      <c r="L409" t="inlineStr"/>
       <c r="M409" t="inlineStr">
         <is>
           <t>review</t>
@@ -25827,7 +25815,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -25858,8 +25845,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
-      <c r="L410" t="inlineStr"/>
       <c r="M410" t="inlineStr">
         <is>
           <t>review</t>
@@ -25892,7 +25877,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -25923,8 +25907,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
-      <c r="L411" t="inlineStr"/>
       <c r="M411" t="inlineStr">
         <is>
           <t>review</t>
@@ -25957,7 +25939,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -25988,8 +25969,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
       <c r="M412" t="inlineStr">
         <is>
           <t>review</t>
@@ -26022,7 +26001,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -26053,8 +26031,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
       <c r="M413" t="inlineStr">
         <is>
           <t>review</t>
@@ -26087,7 +26063,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -26118,8 +26093,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
       <c r="M414" t="inlineStr">
         <is>
           <t>review</t>
@@ -26131,6 +26104,526 @@
         </is>
       </c>
       <c r="O414" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>auto-2e225218f9c6</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Swissport eröffnet neuen Frachtbetrieb im französischen Teil des Flughafens Basel/Mulhouse</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Swissport hat am französischen Teil des Euro Airport Basel/Mulhouse/Freiburg einen neuen Frachtbetrieb eröffnet. Das Unternehmen hat dafür ein 3000 Quadratmeter großes Lager in Betrieb genommen. Davon entfallen 1000 Quadratmeter auf einen französischen Zollbereich und 2000 Quadratmeter auf die internationale Frachtabfertigung. Zunächst konzentriert sich Swissport auf die Abfertigung von Airline-Fracht. Der Betrieb ist eigenständig, soll aber eng mit der bestehenden Frachtabfertigung im Schweizer Teil des Flughafens zusammenarbeiten.</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/swissport-eroeffnet-neuen-frachtbetrieb-im-franzoesischen-teil-des-flughafens/2hjjpcv</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>auto-d7a6094be0a3</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Lufthansa Group soll durch ITA Airways um zehn Prozent wachsen</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Lufthansa Group soll durch die vollständige Integration von ITA Airways im kommenden Jahr um rund zehn Prozent wachsen. Das sagte Konzernchef Carsten Spohr am Montagabend (28. September) bei einer Veranstaltung vor Journalistinnen und Journalisten in Frankfurt. Der Zuwachs beziehe sich auf Flotte, Umsatz und angebotene Sitzplatzkilometer. Lufthansa hält derzeit 41 Prozent an ITA und will im ersten Quartal 2027 auf 90 Prozent aufstocken.</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lufthansa-group-soll-durch-ita-airways-um-zehn-prozent-wachsen/v3fe213</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>auto-d38f9612f113</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Wie Condor mit dem Projekt «Da Vinci» den Umzug ins Terminal 3 vorbereitet</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Im April 2027 will Condor an ihrem Heimatflughafen Frankfurt ins neue Terminal 3 umziehen. Ein internes Schreiben zeigt, mit welchen Vorbereitungen die Fluglinie gerade beschäftigt ist. Dabei geht es unter anderem um ein spezielles Tel-Aviv-Gate und um Walk Boarding.</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flughaefen/condors-umzug-ins-t3-am-flughafen-frankfurt-so-laufen-die-vorbereitungen-im-projekt/menh26w</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>auto-994246a6c088</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Minister: Entscheidung über TAP-Gebote Mitte Oktober</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>LISSABON - Das Bieterrennen um TAP Air Portugal zwischen Lufthansa und Air France-KLM geht in die heiße Phase: Portugal will nachgebesserte Angebote zügig prüfen.</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53795/Minister-Entscheidung-ueber-TAP-Gebote-Mitte-Oktober.html</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr"/>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>auto-40815a2e83d1</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Mehr meldepflichtige Drohnen-Vorfälle</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>SCHWERIN - Ob militärische Anlagen, Einrichtungen zur Energieversorgung oder andere kritische Infrastruktur - für bestimmte Bereiche werden Drohnensichtungen speziell erfasst. Zuletzt gab es mehr Fälle in MV.</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53789/Mehr-meldepflichtige-Drohnen-Vorfaelle.html</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>auto-b557db7edb09</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Bundeswehr will 16 Airbus A400M nachbestellen</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>BREMEN - Airbus brauchte dringend Folgeaufträge, Deutschland : Die Bundeswehr will 16 weitere Transportflugzeuge vom Typ A400M bestellen. Das sagte Bundesverteidigungsminister Boris Pistorius (SPD) bei einer Pressekonferenz in Bremen nach einem Besuch des dortigen Airbus-Werks.</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53787/Bundeswehr-will-16-Airbus-A400M-nachbestellen.html</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>auto-d38ba48c15a3</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>🔴LIVE Night Planespotting Frankfurt Airport ✈️LH506 Retro Queen YT🛫 Leeds Elections 2026 (ByoeKQcuJ9) - Unisba Media</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMihAFBVV95cUxOdDlpU2ZxTHNiN0JHTGJWckNXZHhHWlVYX3pBdDV4ZWplcHpTUXA3V096czhmWm82elFaTjhzSHJTV1M2X19ReUcwTzIydVBmQklQY056Q2JYUjRfMFZyRVFqRDN1QUpvOHo0UG5ZaXBPNHh3VEVzREVaVHdFbTVUTUwxZHU?oc=5" target="_blank"&gt;🔴LIVE Night Planespotting Frankfurt Airport ✈️LH506 Retro Queen YT🛫 Leeds Elections 2026 (ByoeKQcuJ9)&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Unisba Media&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOdDlpU2ZxTHNiN0JHTGJWckNXZHhHWlVYX3pBdDV4ZWplcHpTUXA3V096czhmWm82elFaTjhzSHJTV1M2X19ReUcwTzIydVBmQklQY056Q2JYUjRfMFZyRVFqRDN1QUpvOHo0UG5ZaXBPNHh3VEVzREVaVHdFbTVUTUwxZHU?oc=5</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>auto-4028d5682e87</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>An Air France Boeing 777 made an emergency landing in Munich early this morning following engine issue - airlive</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi3AFBVV95cUxNRzhzQlp3bzVleTRSNWRmeUtDN2F5WXU1SWJiOUNjOTZFY1lsTjlRUUVtVS1mR3lpMjh1cmw3cGhpZjRhUWNrLXVxeWw1Nko5cE1jSlhCWFltcmYtOFhUbXQ5NjRDSnBpZXUwOWgwX05PUkhQTTFqaFFuNDVMSnM0RnNyaFlWbm1OTkJmalc5VGdpWGJ3SmNBcDRMbGRHX19UaEFuc2JlMTE2T3VvVlpuaC1NVmxFZzU2eGFZNklkV0I0OTBmYVhwcHBGSVdiS1hqTFUwMDZkNWdNN0Zy?oc=5" target="_blank"&gt;An Air France Boeing 777 made an emergency landing in Munich early this morning following engine issue&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNRzhzQlp3bzVleTRSNWRmeUtDN2F5WXU1SWJiOUNjOTZFY1lsTjlRUUVtVS1mR3lpMjh1cmw3cGhpZjRhUWNrLXVxeWw1Nko5cE1jSlhCWFltcmYtOFhUbXQ5NjRDSnBpZXUwOWgwX05PUkhQTTFqaFFuNDVMSnM0RnNyaFlWbm1OTkJmalc5VGdpWGJ3SmNBcDRMbGRHX19UaEFuc2JlMTE2T3VvVlpuaC1NVmxFZzU2eGFZNklkV0I0OTBmYVhwcHBGSVdiS1hqTFUwMDZkNWdNN0Zy?oc=5</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O422"/>
+  <dimension ref="A1:O430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26125,7 +26125,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -26156,8 +26155,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
       <c r="M415" t="inlineStr">
         <is>
           <t>review</t>
@@ -26190,7 +26187,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -26221,8 +26217,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
-      <c r="L416" t="inlineStr"/>
       <c r="M416" t="inlineStr">
         <is>
           <t>review</t>
@@ -26255,7 +26249,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -26286,8 +26279,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
-      <c r="L417" t="inlineStr"/>
       <c r="M417" t="inlineStr">
         <is>
           <t>review</t>
@@ -26320,7 +26311,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -26351,8 +26341,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
-      <c r="L418" t="inlineStr"/>
       <c r="M418" t="inlineStr">
         <is>
           <t>review</t>
@@ -26385,7 +26373,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -26416,8 +26403,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
-      <c r="L419" t="inlineStr"/>
       <c r="M419" t="inlineStr">
         <is>
           <t>review</t>
@@ -26450,7 +26435,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -26481,8 +26465,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
-      <c r="L420" t="inlineStr"/>
       <c r="M420" t="inlineStr">
         <is>
           <t>review</t>
@@ -26515,7 +26497,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -26546,8 +26527,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
-      <c r="L421" t="inlineStr"/>
       <c r="M421" t="inlineStr">
         <is>
           <t>review</t>
@@ -26580,7 +26559,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -26611,8 +26589,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
-      <c r="L422" t="inlineStr"/>
       <c r="M422" t="inlineStr">
         <is>
           <t>review</t>
@@ -26624,6 +26600,526 @@
         </is>
       </c>
       <c r="O422" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>auto-9608b80c303b</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Condor weitet Fly-Pink-Kampagne mit Eintracht Frankfurt aus</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Condor baut ihre Fly-Pink-Kampagne im Brustkrebsmonat Oktober gemeinsam mit Eintracht Frankfurt und Brustkrebs Deutschland aus. Ein Schwerpunkt ist das Bundesliga-Spiel der Eintracht gegen den 1. FC Köln am 16. Oktober 2026. Dabei werden der Videowürfel und weitere Flächen im Stadion pink beleuchtet, zudem gibt es Informationen zu Vorsorge und Früherkennung.</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/condor-weitet-fly-pink-kampagne-mit-eintracht-frankfurt-aus/x0dqfyy</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>auto-1c056368751e</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Lufthansa und Austrian Airlines wollen Jordanien-Flüge wie geplant starten</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Die verschärfte Sicherheitsempfehlung der Europäischen Agentur für Flugsicherheit Easa für Jordanien könnte Auswirkungen auf die geplante Wiederaufnahme der Flüge von Lufthansa Group nach Amman haben. Die Easa empfiehlt inzwischen, den jordanischen Luftraum in sämtlichen Höhen zu meiden. Zuvor hatte sie lediglich zu erhöhter Vorsicht geraten.</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lufthansa-und-austrian-airlines-wollen-jordanien-fluege-wie-geplant-starten/jm4dc26</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr"/>
+      <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>auto-265c59ad42a8</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Croatia Airlines plant mit Airbus A319 nur bis Ende Oktober</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Die kroatischen Fluglinie hat ihre Flugpläne für den Airbus A319 im Oktober 2026 angepasst. Nach den derzeit veröffentlichten Daten soll das Flugzeugmodell auf mehreren Strecken nur noch bis Anfang beziehungsweise Mitte Oktober eingesetzt werden, wie das Portal &lt;a href="https://www.aeroroutes.com/eng/260929-ouoct26319" id="8b69dfe4-e5fa-4cb1-92b6-275c417e43d2"&gt;Aero Routes&lt;/a&gt; berichtet. Dazu gehören unter anderem Zagreb - Frankfurt bis 7. Oktober, Zagreb - München bis 2. Oktober, Zagreb - Berlin bis 4. Oktober und Zagreb - Zürich bis 3. Oktober. Auf der Strecke Zagreb - Split - Rom soll der A319 noch bis 23. Oktober fliegen.</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/croatia-airlines-plant-mit-airbus-a319-nur-bis-ende-oktober/d4r56kc</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr"/>
+      <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>auto-b70546ff52ff</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Air France-KLM und Lufthansa haben verbesserte Angebote für Tap eingereicht</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Air France-KLM und Lufthansa haben am 30. September 2026 ihre endgültigen und verbesserten Angebote für einen Einstieg bei Tap eingereicht. Damit endet die Verhandlungsphase im portugiesischen Privatisierungsverfahren. Beide Konzerne sind die verbliebenen Interessenten.</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/air-france-klm-und-lufthansa-haben-verbesserte-angebote-fuer-tap-eingereicht/zem687k</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>auto-dabc7af24f92</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Qanot Sharq pausiert Frankfurt-Flüge für drei Wochen</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Qanot Sharq setzt ihre Verbindung zwischen Tashkent und Frankfurt zu Beginn des Winterflugplans 2026/27 vorübergehend aus. Vom 27. Oktober bis einschließlich 13. November 2026 finden auf der Strecke keine Flüge statt, so das Portal Aero Routes. Am 17. November nimmt die usbekische Fluggesellschaft die Verbindung wieder auf.</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/qanot-sharq-pausiert-frankfurt-fluege-fuer-drei-wochen/g9llr8p</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>auto-9f42194fa868</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Flughafen in Süditalien will mit Flügen nach Rom und Mailand groß rauskommen</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Bislang steht in Taranto vor allem Fracht im Fokus. Doch der Flughafen im süditalienischen Apulien will auch im Passagierverkehr eine größere Rolle spielen. Dafür sollen regelmäßige Flüge nach Rom und Mailand-Linate sorgen.</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flughaefen/flughafen-in-sueditalien-will-mit-fluegen-nach-rom-und-mailand-gross-rauskommen/f5lmn0b</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>auto-16a81b5f40f3</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>"Es sind schon große Schritte, die wir gehen"</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa übernimmt 2027 die Kontrolle über ITA Airways. Konzernchef Carsten Spohr sieht die laufende Integration auf Kurs - und rechnet 2027 mit einem deutlichen ITA-Effekt im Lufthansa-System. Die neue Tochtergesellschaft soll ihre Stärken auch im Joint Venture mit United Airlines ausspielen.</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53813/Es-sind-schon-grosse-Schritte-die-wir-gehen.html</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr"/>
+      <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>auto-2a1afc83c735</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines bestellt acht Boeing 777-8F</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>SEATTLE - Boeing gewinnt einen weiteren Kunden für sein neues Frachtermodell: Ethiopian Airlines bestellt acht 777-8F.</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53812/Ethiopian-Airlines-bestellt-acht-Boeing-777-8F.html</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr"/>
+      <c r="L430" t="inlineStr"/>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O430"/>
+  <dimension ref="A1:O443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26621,7 +26621,6 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -26652,8 +26651,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
-      <c r="L423" t="inlineStr"/>
       <c r="M423" t="inlineStr">
         <is>
           <t>review</t>
@@ -26686,7 +26683,6 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -26717,8 +26713,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
-      <c r="L424" t="inlineStr"/>
       <c r="M424" t="inlineStr">
         <is>
           <t>review</t>
@@ -26751,7 +26745,6 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -26782,8 +26775,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
-      <c r="L425" t="inlineStr"/>
       <c r="M425" t="inlineStr">
         <is>
           <t>review</t>
@@ -26816,7 +26807,6 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -26847,8 +26837,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
-      <c r="L426" t="inlineStr"/>
       <c r="M426" t="inlineStr">
         <is>
           <t>review</t>
@@ -26881,7 +26869,6 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -26912,8 +26899,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
-      <c r="L427" t="inlineStr"/>
       <c r="M427" t="inlineStr">
         <is>
           <t>review</t>
@@ -26946,7 +26931,6 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -26977,8 +26961,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
-      <c r="L428" t="inlineStr"/>
       <c r="M428" t="inlineStr">
         <is>
           <t>review</t>
@@ -27011,7 +26993,6 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27042,8 +27023,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
-      <c r="L429" t="inlineStr"/>
       <c r="M429" t="inlineStr">
         <is>
           <t>review</t>
@@ -27076,7 +27055,6 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27107,8 +27085,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
-      <c r="L430" t="inlineStr"/>
       <c r="M430" t="inlineStr">
         <is>
           <t>review</t>
@@ -27120,6 +27096,851 @@
         </is>
       </c>
       <c r="O430" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>auto-a052490eba16</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Thai Airways entlässt Chef nach Flug- und Gepäckchaos</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Thai Airways hat ihren Vorstandschef Chai Eamsiri mit sofortiger Wirkung entlassen. Der Verwaltungsrat begründete die Entscheidung laut der Zeitung Bangkok Post mit anhaltenden operativen Problemen nach schweren Überschwemmungen seit dem 25. September. Zahlreiche Flüge waren verspätet, zudem stauten sich mehr als 10.000 Gepäckstücke und Frachtsendungen. Für den 1. und 2. Oktober strich die Fluggesellschaft insgesamt 24 Flüge.</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/thai-airways-entlaesst-chef-nach-flug-und-gepaeckchaos/6tp707t</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr"/>
+      <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>auto-27d8a371d5a3</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Auch Flüge nach Frankfurt, Genf, München und Wien betroffen: Animawings stoppt Betrieb</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr"/>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Die rumänische Fluggesellschaft AnimaWings hat einen Tag nach ihrem Antrag auf Eröffnung eines Gläubigerschutz alle regulären Flüge vorübergehend eingestellt. Nach Angaben des Portals Boarding Pass wurden bereits die für Donnerstag geplanten Linienflüge gestrichen und der Ticketverkauf auf zahlreichen Strecken ausgesetzt. Einige Verbindungen sind bis zum 25. Oktober nicht mehr buchbar, andere auf unbestimmte Zeit.</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/auch-fluege-nach-frankfurt-genf-muenchen-und-wien-betroffen-animawings-stoppt-betrieb/nex3x2r</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr"/>
+      <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>auto-226a5594c2b6</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Lufthansa Group führt Basic-Tarif auf allen Europastrecken ein</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Die Lufthansa Group weitet ihren Economy-Basic-Tarif ab dem 6. Oktober 2026 auf alle Europastrecken aus. Das berichtet Travel-Dealz unter Berufung auf eine Mitteilung an Vertriebspartner. Betroffen sind Lufthansa, Lufthansa City Airlines, Austrian Airlines, Swiss, Brussels Airlines, Air Dolomiti und Discover Airlines. Bislang wurde der im April eingeführte Tarif nur auf ausgewählten Strecken angeboten, wie das Portal Travel Dealz berichtet.</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lufthansa-group-fuehrt-basic-tarif-auf-allen-europastrecken-ein/vkq1vdd</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr"/>
+      <c r="L433" t="inlineStr"/>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>auto-e88f02822c0a</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Mit diesen Strecken startet Lufthansa City Airlines in die Airbus-A220-Ära</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Noch ist der erste Airbus A220-300 von Lufthansa City Airlines nicht ausgeliefert. Doch der Flugplan verrät bereits, wann und wo das neue Flugzeugmodell erstmals eingesetzt werden soll. Im Janaur startet es der Linienbetrieb ab Frankfurt.</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugzeuge/airbus-a220-von-lufthansa-city-airlines-fliegt-zuerst-nach-bruessel/lj0ffp1</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr"/>
+      <c r="L434" t="inlineStr"/>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>auto-b68daccdf1e4</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Abu-Dhabi-Investor erwägt Übernahme von Atlas Air</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Die Investmentgesellschaft L’imad Holding aus Abu Dhabi erwägt einem Bericht der Nahrichtenagentur Bloomberg zufolge ein Angebot für Atlas Air Worldwide Holdings. Bloomberg hatte am 17. September 2026 unter Berufung auf mit der Angelegenheit vertraute Personen über das Interesse berichtet. Der Luftfrachtkonzern könnte dabei mit rund zehn Milliarden US-Dollar bewertet werden.</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/abu-dhabi-investor-erwaegt-uebernahme-von-atlas-air/fv5d9ez</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr"/>
+      <c r="L435" t="inlineStr"/>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>auto-133dee3abd66</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Wie Virgin Atlantic an die Frau von Gründer Richard Branson erinnert</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr"/>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Virgin Atlantic gestaltet einen neuen Airbus A330 Neo mit Erinnerungsstücken an Joan Branson, die 2025 verstorbene Frau von Gründer Richard Branson. Es ist nicht das erste Mal, dass die Airline ein Mitglied der Familie ehrt.</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/airlines/airbus-a330-900-von-virgin-atlantic-erinnert-an-joan-branson/z3b6fk7</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr"/>
+      <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>auto-57a76047f69d</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>21 Festnahmen wegen Drogenschmuggels über Flughafen Brüssel</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Belgische und französische Behörden haben 21 Personen festgenommen, die einem internationalen Drogennetzwerk angehört haben sollen. Dieses soll den Flughafen Brüssel für den Schmuggel von Kokain und Cannabis genutzt haben. Die Ermittlungen begannen im Februar 2025 nach dem Fund von rund 30 Kilogramm Kokain aus Cancún, berichten belgische Medien.</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/21-festnahmen-wegen-drogenschmuggels-ueber-flughafen-bruessel/2g469p2</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr"/>
+      <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>auto-f4083638f0d3</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>US-Ermittler legen Zwischenbericht zu Landeunfall in Miami vor</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr"/>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>MIAMI - Ein instabiler Anflug endet in einem Desaster. Die US-Flugunfallbehörde NTSB hat zu dem schweren Landeunfall einer Boeing 767-300ER in Miami einen ersten Zwischenbericht vorgelegt. Am Ende der Landebahn war der Frachter im Auftrag von Amazon immer noch extrem schnell unterwegs.</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53828/NTSB-erster-Zwischenbericht-Amazon-Prime-Air-Miami-Boeing-767.html</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr"/>
+      <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>auto-efff36b97bab</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>"Wir hatten zu viel Kurzstreckenkapazität"</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa will im "wachsenden Langstreckengeschäft" mit weniger Zubringung auskommen. Die "Verbindungsqualität" der sechs Lufthansa-Interkontdrehkreuze werde darunter nicht leiden, stellte Lufthansa-Chef Carsten Spohr jetzt in Frankfurt klar - im Gegenteil.</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53814/Wir-hatten-zu-viel-Kurzstreckenkapazitaet.html</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr"/>
+      <c r="L439" t="inlineStr"/>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>auto-60d65c6e41cc</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Bundeswehr bekommt Drohnenregiment</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>BERGEN - Für den Kampf mit unbemannten Systemen stellt die Bundeswehr ein eigenes Drohnenregiment auf. Der Verband werde aus bis zu 600 Männern und Frauen bestehen und Reichweiten bis zu 500 Kilometer abdecken, sagte Verteidigungsminister Boris Pistorius auf dem niedersächsischen Truppenübungsplatz Bergen.</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53822/Bundeswehr-bekommt-Drohnenregiment.html</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr"/>
+      <c r="L440" t="inlineStr"/>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>auto-3d9e9ca71f5e</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Lufthansa übernimmt für LOT gebaute Boeing 787-9</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>WARSCHAU - Boeing hat zwei ursprünglich für LOT Polish Airlines gebaute 787-9 umgebucht. Das Dreamliner-Duo wird in naher Zukunft die Lufthansa-Flotte in Frankfurt verstärken - Lufthansa lässt Allegris-Kabinen einbauen. LOT Polish Airlines greift stattdessen bei gebrauchten 787 zu.</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53771/Lufthansa-uebernimmt-fuer-LOT-Polish-Airlines-gebaute-Boeing-787-9.html</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr"/>
+      <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>auto-8b26bddfdf38</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Netanjahu sieht islamistisches Tatmotiv</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>TEL AVIV - Der Flug von Dubai nach Tel Aviv ist offenbar nur knapp einer Katastrophe entgangen - viele Fragen sind noch offen. Doch Israels Ministerpräsident Netanjahu sieht beim Motiv eine klare Tendenz.</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53819/Netanjahu-sieht-islamistisches-Tatmotiv.html</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>auto-0641ff661c82</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Emirates A380 declares emergency over Europe, diverts to Frankfurt mid-flight - Zee News</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirAFBVV95cUxNMGFPWmYwUF9ER1hpcDE0d3JnNmVVdURma0Vjc1ppQmNlQkpqSlRrUWxKempEbzVlb3hzRU40NFFQYWE1dWxwVHVpQTY4UmcwU3pwQXlBa3oySDVGZFRYdUliang0eHlQMDEwTGFJUjJGMld5NEd5ZW5hTUpnNHBnX04yc001QlBHU3hLTlZESjBLWEh3ZFE2SFlfWXF0dUJicDFQZExGU2dJbEFp0gGyAUFVX3lxTE5KMzkyRUgzMFZkc2ltMldwcEVkbnRPVGpVdm5FX1hSTnc1NnJMNFpMWDNjaUJUX0hkZ3pXeHlSYVhXbnFDbTVMbkhPY2dVblFGZ3Bla3lSS3U4Y3JJRFFuLW9ySUcyRzJndVo0RXFrbzJEdEw3RC01UWNZUEdTNEpManlmZm9DYnNJVV9RRG5VY1pRVTRRb3BoOExRVXl1bnFqV1J1bkl4SGZBSjNHX0MyREE?oc=5" target="_blank"&gt;Emirates A380 declares emergency over Europe, diverts to Frankfurt mid-flight&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Zee News&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNMGFPWmYwUF9ER1hpcDE0d3JnNmVVdURma0Vjc1ppQmNlQkpqSlRrUWxKempEbzVlb3hzRU40NFFQYWE1dWxwVHVpQTY4UmcwU3pwQXlBa3oySDVGZFRYdUliang0eHlQMDEwTGFJUjJGMld5NEd5ZW5hTUpnNHBnX04yc001QlBHU3hLTlZESjBLWEh3ZFE2SFlfWXF0dUJicDFQZExGU2dJbEFp0gGyAUFVX3lxTE5KMzkyRUgzMFZkc2ltMldwcEVkbnRPVGpVdm5FX1hSTnc1NnJMNFpMWDNjaUJUX0hkZ3pXeHlSYVhXbnFDbTVMbkhPY2dVblFGZ3Bla3lSS3U4Y3JJRFFuLW9ySUcyRzJndVo0RXFrbzJEdEw3RC01UWNZUEdTNEpManlmZm9DYnNJVV9RRG5VY1pRVTRRb3BoOExRVXl1bnFqV1J1bkl4SGZBSjNHX0MyREE?oc=5</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr"/>
+      <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O443"/>
+  <dimension ref="A1:O447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27117,7 +27117,6 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27148,8 +27147,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
-      <c r="L431" t="inlineStr"/>
       <c r="M431" t="inlineStr">
         <is>
           <t>review</t>
@@ -27182,7 +27179,6 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27213,8 +27209,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
-      <c r="L432" t="inlineStr"/>
       <c r="M432" t="inlineStr">
         <is>
           <t>review</t>
@@ -27247,7 +27241,6 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27278,8 +27271,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
-      <c r="L433" t="inlineStr"/>
       <c r="M433" t="inlineStr">
         <is>
           <t>review</t>
@@ -27312,7 +27303,6 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27343,8 +27333,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
-      <c r="L434" t="inlineStr"/>
       <c r="M434" t="inlineStr">
         <is>
           <t>review</t>
@@ -27377,7 +27365,6 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27408,8 +27395,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
-      <c r="L435" t="inlineStr"/>
       <c r="M435" t="inlineStr">
         <is>
           <t>review</t>
@@ -27442,7 +27427,6 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27473,8 +27457,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
-      <c r="L436" t="inlineStr"/>
       <c r="M436" t="inlineStr">
         <is>
           <t>review</t>
@@ -27507,7 +27489,6 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27538,8 +27519,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
-      <c r="L437" t="inlineStr"/>
       <c r="M437" t="inlineStr">
         <is>
           <t>review</t>
@@ -27572,7 +27551,6 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
       <c r="E438" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27603,8 +27581,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
-      <c r="L438" t="inlineStr"/>
       <c r="M438" t="inlineStr">
         <is>
           <t>review</t>
@@ -27637,7 +27613,6 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
       <c r="E439" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27668,8 +27643,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
-      <c r="L439" t="inlineStr"/>
       <c r="M439" t="inlineStr">
         <is>
           <t>review</t>
@@ -27702,7 +27675,6 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
       <c r="E440" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27733,8 +27705,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
-      <c r="L440" t="inlineStr"/>
       <c r="M440" t="inlineStr">
         <is>
           <t>review</t>
@@ -27767,7 +27737,6 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
       <c r="E441" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -27798,8 +27767,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
-      <c r="L441" t="inlineStr"/>
       <c r="M441" t="inlineStr">
         <is>
           <t>review</t>
@@ -27832,7 +27799,6 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
       <c r="E442" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27863,8 +27829,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
-      <c r="L442" t="inlineStr"/>
       <c r="M442" t="inlineStr">
         <is>
           <t>review</t>
@@ -27897,7 +27861,6 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
       <c r="E443" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27928,8 +27891,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
-      <c r="L443" t="inlineStr"/>
       <c r="M443" t="inlineStr">
         <is>
           <t>review</t>
@@ -27941,6 +27902,266 @@
         </is>
       </c>
       <c r="O443" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>auto-b70a83c0317b</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Swiss fordert von der Schweiz eine halbe Million für Hotelkosten</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Die Schweizer Lufthansa-Tochter fordert vom Schweizer Bund rund 510.000 Franken (knapp 530.000 Euro) für Hotelübernachtungen von Sicherheitsbeauftragten im Luftverkehr. Wie die Zeitung &lt;a href="https://www.tagesanzeiger.ch/swiss-fordert-510000-franken-vom-bund-fuer-hotelnaechte-923392520743" id="105857a2-2371-4ca4-ace0-4f2ab387aba2"&gt;Tages-Anzeiger&lt;/a&gt; berichtet, hatte Swiss die Kosten von 2016 bis 2024 wegen eines internen Abrechnungsfehlers nicht vollständig in Rechnung gestellt.</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/swiss-fordert-von-der-schweiz-eine-halbe-million-fuer-hotelkosten/5t50b0b</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>auto-3498143605b1</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Twin Jet nimmt Straßburg - Marseille wieder auf</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Twin Jet nimmt am 3. November die Verbindung zwischen Straßburg und Marseille wieder auf. Die französische Fluggesellschaft hatte die Strecke bereits früher bedient, unter anderem ab September 2024. Geflogen wird dienstags bis freitags. Dienstags und mittwochs gibt es jeweils zwei Verbindungen pro Richtung, donnerstags und freitags jeweils eine.</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/twin-jet-nimmt-strassburg-marseille-wieder-auf/gry8f1l</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>auto-0287b51171c9</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Eurofighter-Manöver am Flughafen Nürnberg</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr"/>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>NÜRNBERG - Die Bundeswehr übt den Verteidigungsfall. Dazu wird auch zivile Infrastruktur genutzt. Von Montag an ist der Flughafen Nürnberg an der Reihe.</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53836/Eurofighter-Manoever-am-Flughafen-Nuernberg.html</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr"/>
+      <c r="L446" t="inlineStr"/>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>auto-7ed71bf74499</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Lufthansa und Air France-KLM greifen tiefer in die Tasche</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>LISSABON - Portugal will einen Minderheitsanteil seiner staatlichen Fluggesellschaft TAP Air Portugal verkaufen: Lufthansa und Air France-KLM warten auf eine Entscheidung aus Lissabon. Neue Gebote der Flugkonzerne liegen nach einem Medienbericht über der Milliardenschwelle.</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53833/Lufthansa-und-Air-France-KLM-erhoehen-Angebote.html</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr"/>
+      <c r="L447" t="inlineStr"/>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O447"/>
+  <dimension ref="A1:O448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27923,7 +27923,6 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
       <c r="E444" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -27954,8 +27953,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
-      <c r="L444" t="inlineStr"/>
       <c r="M444" t="inlineStr">
         <is>
           <t>review</t>
@@ -27988,7 +27985,6 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
       <c r="E445" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28019,8 +28015,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
-      <c r="L445" t="inlineStr"/>
       <c r="M445" t="inlineStr">
         <is>
           <t>review</t>
@@ -28053,7 +28047,6 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28084,8 +28077,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
-      <c r="L446" t="inlineStr"/>
       <c r="M446" t="inlineStr">
         <is>
           <t>review</t>
@@ -28118,7 +28109,6 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28149,8 +28139,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
-      <c r="L447" t="inlineStr"/>
       <c r="M447" t="inlineStr">
         <is>
           <t>review</t>
@@ -28162,6 +28150,71 @@
         </is>
       </c>
       <c r="O447" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>auto-d8687b1f6b66</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Transavia stationiert erstmals Airbus in Rotterdam</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr"/>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Transavia hat erstmals einen Airbus-Jet fest in Rotterdam stationiert. Der Airbus A320 Neo mit der Registrierung PH-YHR landete am Mittwochabend als Flug HV010 am Flughafen Rotterdam / Den Haag. Damit besteht die dortige Flotte nun aus einem A320 Neo und sechs Boeing 737. In den kommenden Jahren sollen die Boeing 737 schrittweise durch Airbus-Flugzeuge ersetzt werden. Die Air-France-KLM-Tochter betreibt seit dem Jahr 2000 eine Basis in Rotterdam und fliegt von dort 31 Ziele an.</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/transavia-stationiert-erstmals-airbus-in-rotterdam/cg20r17</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O448"/>
+  <dimension ref="A1:O454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28171,7 +28171,6 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28202,8 +28201,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
-      <c r="L448" t="inlineStr"/>
       <c r="M448" t="inlineStr">
         <is>
           <t>review</t>
@@ -28215,6 +28212,396 @@
         </is>
       </c>
       <c r="O448" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>auto-4da366b18671</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Vier von fünf dünnen Europa-Strecken haben nur eine Airline</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Fast jede zweite innereuropäische Kurzstrecke gehört zu den sogenannten dünnen Strecken, also Verbindungen mit vergleichsweise wenig Nachfrage. 42 Prozent bieten weniger als 50.000 Sitze pro Jahr, machen aber nur sechs Prozent der angebotenen Kapazität aus. Das zeigt der «Annual Pulse 2026» der European Regions Airline Association (ERAA), die 58 Regionalairlines und mehr als 150 weitere Unternehmen der europäischen Luftfahrt vertritt.</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/vier-von-fuenf-duennen-europa-strecken-haben-nur-eine-airline/q5rnrqw</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr"/>
+      <c r="L449" t="inlineStr"/>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>auto-16e2873315c3</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>BDL und DLR: Luftverkehrsstandort Deutschland verliert an Anbindung</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr"/>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Der Luftverkehrsstandort Deutschland hat nach der Corona-Pandemie bei der internationalen Anbindung an Boden verloren. Das zeigt ein gemeinsamer Wirtschaftsreport des Deutschen Zentrums für Luft- und Raumfahrt (DLR) und des Bundesverbands der Deutschen Luftverkehrswirtschaft (BDL). Frankfurt erreichte 2024 bei den direkt erreichbaren Zielen wieder annähernd das Vorkrisenniveau. Andere große deutsche Flughäfen lagen dagegen bis zu 18 Prozent darunter. Auch Flugfrequenzen und Verbindungen zu Randzeiten gingen vielerorts zurück.</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/bdl-und-dlr-luftverkehrsstandort-deutschland-verliert-an-anbindung/sf9nlgl</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>auto-45d7a8932689</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>«Je mehr Unruhe auf der Welt, desto besser für Lufthansa Cargo»</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Krisen verändern Frachtströme. Und Lufthansa Cargo profitiert davon. Konzernchef Carsten Spohr spricht ungewöhnlich offen darüber, warum geopolitische Unruhe der Frachtsparte Geschäft bringen kann. Und er erwartet, dass Lufthansa Cargo in den kommenden Jahren stärker wächst als die Passagierairlines.</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/fracht/lufthansa-chef-carsten-spohr-je-mehr-unruhe-auf-der-welt-desto-besser-fuer-cargo/wq2gc39</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr"/>
+      <c r="L451" t="inlineStr"/>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>auto-6a3bfde7bc81</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Air Astana schaut sich weitere Ziele in Europa an</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr"/>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Air Astana prüft den Ausbau ihres Streckennetzes in Europa. Bisher bedient sie Frankfurt und London. Wie Chef Ibrahim Canliel im Gespräch mit aeroTELEGRAPH sagt, hat die kasachische Fluggesellschaft mehrere weitere Städte in Mittel- und Westeuropa im Blick.</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/air-astana-schaut-sich-weitere-ziele-in-europa-an/79m6612</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr"/>
+      <c r="L452" t="inlineStr"/>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>auto-e5e95ca80036</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Israel lag Crew-Liste vor Flydubai-Flug FZ1073 vor - doch Fragen zur Überprüfung sind offen</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr"/>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>Den israelischen Behörden lag die Liste der Besatzung des Flydubai-Fluges vor, auf dem der Kopilot den Kapitän angriff und offenbar den Jet zum Absturz bringen wollte. Doch Fragen zur Sicherheitsüberprüfung bleiben offen. Das Verkehrsministerium gerät immer stärker in die Kritik.</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/sicherheit/israel-lag-crew-liste-vor-flydubai-flug-fz1073-vor-doch-fragen-zur-ueberpruefung-sind/zk8ej7d</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr"/>
+      <c r="L453" t="inlineStr"/>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>auto-b998ccc20e3f</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt: 79 Airlines und 243 Ziele stehen im Winterflugplan 2024/2025 - airportzentrale.de</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr"/>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiugFBVV95cUxQYWdpU3VQTXAxbVpGZUowY282RU1WMm10RWRvdm9aVFR0a3lSVEdvek54WU53SEtpMFlTb0dpZnFxcHJSMElfZzlZQTB2UFFpRlBNLS0zdEhwN1VCYkNQN2R2ZFFQY2NzV1BHeGRDc0xXd3NtQ1k4elBhVWZrYnZfeExfUFZGY19OeW9vUWlPZW95R2dWYmFNRFVjRktJLWViNXB4YVE2V0FVeUdRWlVQWXhIWnNudmM1WGc?oc=5" target="_blank"&gt;Flughafen Frankfurt: 79 Airlines und 243 Ziele stehen im Winterflugplan 2024/2025&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airportzentrale.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYWdpU3VQTXAxbVpGZUowY282RU1WMm10RWRvdm9aVFR0a3lSVEdvek54WU53SEtpMFlTb0dpZnFxcHJSMElfZzlZQTB2UFFpRlBNLS0zdEhwN1VCYkNQN2R2ZFFQY2NzV1BHeGRDc0xXd3NtQ1k4elBhVWZrYnZfeExfUFZGY19OeW9vUWlPZW95R2dWYmFNRFVjRktJLWViNXB4YVE2V0FVeUdRWlVQWXhIWnNudmM1WGc?oc=5</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr"/>
+      <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O454"/>
+  <dimension ref="A1:O457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28233,7 +28233,6 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28264,8 +28263,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
-      <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr">
         <is>
           <t>review</t>
@@ -28298,7 +28295,6 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28329,8 +28325,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
-      <c r="L450" t="inlineStr"/>
       <c r="M450" t="inlineStr">
         <is>
           <t>review</t>
@@ -28363,7 +28357,6 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28394,8 +28387,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
-      <c r="L451" t="inlineStr"/>
       <c r="M451" t="inlineStr">
         <is>
           <t>review</t>
@@ -28428,7 +28419,6 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28459,8 +28449,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
-      <c r="L452" t="inlineStr"/>
       <c r="M452" t="inlineStr">
         <is>
           <t>review</t>
@@ -28493,7 +28481,6 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28524,8 +28511,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
-      <c r="L453" t="inlineStr"/>
       <c r="M453" t="inlineStr">
         <is>
           <t>review</t>
@@ -28558,7 +28543,6 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28589,8 +28573,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
-      <c r="L454" t="inlineStr"/>
       <c r="M454" t="inlineStr">
         <is>
           <t>review</t>
@@ -28602,6 +28584,201 @@
         </is>
       </c>
       <c r="O454" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>auto-271ac6d7a745</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>PAL-V plant weltweites Trainingsnetz für Flugautos</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr"/>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Der niederländische Flugauto-Hersteller PAL-V will gemeinsam mit dem Trainingsspezialisten Avion und dem Fly-Drive-Dienstleister Flyve eine weltweite Ausbildungsinfrastruktur aufbauen. Dazu haben die drei Unternehmen eine Absichtserklärung unterzeichnet.</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/pal-v-plant-weltweites-trainingsnetz-fuer-flugautos/5b61bcp</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr"/>
+      <c r="L455" t="inlineStr"/>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>auto-e591ab0e9a4d</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>BDF: Regionen sollen innerdeutsche Flüge subventionieren</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr"/>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>BERLIN / FRANKFURT - Inlandsflüge sind in Deutschland nach Corona teuer und deutlich seltener geworden. Die Branche ruft nach staatlichem Geld, um einzelne Regionen weiterhin anzubinden.</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53857/BDF-Regionen-sollen-innerdeutsche-Fluege-subventionieren.html</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr"/>
+      <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>auto-a255825697a9</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Air France AF711 to Paris is declaring an emergency and turning around Morocco - airlive</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr"/>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMivAFBVV95cUxPOU9QRDlUNTJ5cG9NVV9pRWZuRjZiSTB5Z1BieU9HUlpPbmJVdDZCLTNUQndUbGJRbVZEaDNwRlJnb3pkQ3lvTmctN3Z3Z0t4Um9SVkdkdnFKOGtaSFVoTE5iOTlfanRHdUttMDh6SGl2ajE4cVd0STAzem9DYzRhbTdYc0FVTEdZNEtRdW5rWTIzSDBBaHp5bnE5aFdXZWwzSU1uZ3Zhb3l0NEI3d0tHc2VrVXJjNGZJWkZRMA?oc=5" target="_blank"&gt;Air France AF711 to Paris is declaring an emergency and turning around Morocco&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPOU9QRDlUNTJ5cG9NVV9pRWZuRjZiSTB5Z1BieU9HUlpPbmJVdDZCLTNUQndUbGJRbVZEaDNwRlJnb3pkQ3lvTmctN3Z3Z0t4Um9SVkdkdnFKOGtaSFVoTE5iOTlfanRHdUttMDh6SGl2ajE4cVd0STAzem9DYzRhbTdYc0FVTEdZNEtRdW5rWTIzSDBBaHp5bnE5aFdXZWwzSU1uZ3Zhb3l0NEI3d0tHc2VrVXJjNGZJWkZRMA?oc=5</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr"/>
+      <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O457"/>
+  <dimension ref="A1:O465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28605,7 +28605,6 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28636,8 +28635,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
-      <c r="L455" t="inlineStr"/>
       <c r="M455" t="inlineStr">
         <is>
           <t>review</t>
@@ -28670,7 +28667,6 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28701,8 +28697,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
-      <c r="L456" t="inlineStr"/>
       <c r="M456" t="inlineStr">
         <is>
           <t>review</t>
@@ -28735,7 +28729,6 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28766,8 +28759,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
-      <c r="L457" t="inlineStr"/>
       <c r="M457" t="inlineStr">
         <is>
           <t>review</t>
@@ -28779,6 +28770,526 @@
         </is>
       </c>
       <c r="O457" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>auto-112618eca846</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Lufthansa Group senkt Altersversorgung von Vorständen</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr"/>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Kürzlich hat der Lufthansa-Group-Aufsichtsrat &lt;a href="https://www.aerotelegraph.com/ticker/lufthansa-verlaengert-vertraege-von-drei-vorstandsmitgliedern/p02h1qq" id="ce1d08cd-2ed9-42c0-9d83-ba33df442657"&gt;die Verträge der Vorstandsmitglieder Grazia Vittadini, Till Streichert und Dieter Vranckx verlängert&lt;/a&gt;. Nun berichtet das Portal &lt;a href="https://www.aero.de/news-53801/Lufthansa-IR-Altersversorgung-Vorstaende.html" id="b490a2d8-9161-4477-8efe-b0895a1cdecc" data-link-role-code="target_blank"&gt;Aero&lt;/a&gt;, dass dabei die Beiträge zur betrieblichen Altersversorgung gekürzt wurden. «Wir können bestätigen, dass bei der Wiederbestellung von Grazia Vittadini, Till Streichert und Dieter Vranckx die Beitragshöhe zur betrieblichen Altersversorgung auf 30 Prozent der Grundvergütung abgesenkt wurde», so eine Lufthansa-Sprecherin. Damit reagiert der Konzern auch auf Kritik von Aktionären an vergleichsweise üppigen Versorgungsleistungen.</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lufthansa-group-senkt-altersversorgung-von-vorstaenden/c8dhtcg</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr"/>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>auto-f81069d74987</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Ryanair zieht aus Bremen ab - Flughafen stellt Sanierungsgeschäftsführer ein</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr"/>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Gerade erst hat Bremen mit großen Mühen Lufthansa zur Wiederaufnahme der Frankfurt-Route bewegt. Jetzt teilt Ryanair dem norddeutschen Flughafen mit, dass sie im kommenden Sommer nicht mehr von dort aus fliegen wird. Der angeschlagene Airport muss nun den Sparkurs verschärfen und will einen Sanierungsgeschäftsführer einstellen.</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flughaefen/flughafen-bremen-verliert-ryanair-und-holt-sanierer/k0h8pl4</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr"/>
+      <c r="L459" t="inlineStr"/>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>auto-17da6b9062d7</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Lufthansa tauft Konferenzzentrum Seeheim um</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr"/>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Lufthansa gibt ihrem Konferenzhotel in Seeheim einen neuen Namen und Markenauftritt. Aus Lufthansa Seeheim wird das Lufthansa Group Hotel &amp;amp; Campus Seeheim. Gleichzeitig erhält das Haus ein neues Logo und Erscheinungsbild.</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lufthansa-tauft-konferenzzentrum-seeheim-um/zv5hf52</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr"/>
+      <c r="L460" t="inlineStr"/>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>auto-b48a5ec2c1b2</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Usbekistan: My Freighter hat ihre zehnte Boeing 767 F</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr"/>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Die usbekische Frachtfluggesellschaft My Freighter hat ihre zehnte Boeing 767-300 übernommen. Das 33 Jahre alte, zum Frachter umgebaute Flugzeug traf am 4. Oktober aus den USA in Taschkent ein. Es trägt nun die usbekische Registrierung UK67023 und wurde nach dem mittelasiatischen Herrscher und Feldherrn Zahir-al-Din Muhammad Babur benannt.</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/usbekistan-my-freighter-hat-ihre-zehnte-boeing-767-f/8e8v2cb</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr"/>
+      <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>auto-b36c82ff33f9</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>25 Schlauchboote für Schleuser am Flughafen East Midlands beschlagnahmt</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr"/>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Britische Ermittler haben am Flughafen East Midlands 25 aufblasbare Boote beschlagnahmt, die für Schleuser im Ärmelkanal bestimmt gewesen sein sollen. Die rund neun Meter langen Boote waren Teil einer Luftfrachtsendung von der Türkei in die Niederlande und wurden am 2. Oktober bei einem Zwischenstopp am Frachtzentrum des Flughafens entdeckt, wie die britische Kriminalpolizei NCA (National Crime Agency) am Dienstag (6. Oktober) mitteilte.</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/25-schlauchboote-fuer-schleuser-am-flughafen-east-midlands-beschlagnahmt/43kp119</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr"/>
+      <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>auto-7c98596dd1b8</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Lufthansa kürzt Altersversorgung von Vorständen</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr"/>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa zieht mit drei Vertragsverlängerungen alle Konzernvorstände in ein einheitliches Vergütungssystem mit geringeren Beiträgen zur betrieblichen Altersversorgung. Der Konzern reagiert damit auch auf Kritik von Aktionären, die auf vergleichsweise üppige Versorgungsleistungen hingewiesen hatten.</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53801/Lufthansa-IR-Altersversorgung-Vorstaende.html</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr"/>
+      <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>auto-3ea8aafb6475</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Lufthansa lenkt mehr Kapazität nach Japan</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr"/>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Der Lufthansa-Konzern weitet das gruppenweite Flugangebot nach Japan im Sommer 2027 deutlich aus. Lufthansa nimmt die Verbindung von Frankfurt nach Nagoya wieder auf - und fliegt künftig täglich von Frankfurt nach Tokio-Narita.</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53860/Lufthansa-lenkt-mehr-Kapazitaet-nach-Japan.html</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr"/>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>auto-4dc01dc648b3</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Passagier randaliert auf Lufthansa-Flug</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr"/>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Ein 33-Jähriger fällt während eines Fluges mit aggressivem Verhalten auf. Das Bordpersonal und Passagiere greifen ein.</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53859/Passagier-randaliert-auf-Lufthansa-Flug.html</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr"/>
+      <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O465"/>
+  <dimension ref="A1:O471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28791,7 +28791,6 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28822,8 +28821,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
-      <c r="L458" t="inlineStr"/>
       <c r="M458" t="inlineStr">
         <is>
           <t>review</t>
@@ -28856,7 +28853,6 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28887,8 +28883,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
-      <c r="L459" t="inlineStr"/>
       <c r="M459" t="inlineStr">
         <is>
           <t>review</t>
@@ -28921,7 +28915,6 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -28952,8 +28945,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
-      <c r="L460" t="inlineStr"/>
       <c r="M460" t="inlineStr">
         <is>
           <t>review</t>
@@ -28986,7 +28977,6 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29017,8 +29007,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
-      <c r="L461" t="inlineStr"/>
       <c r="M461" t="inlineStr">
         <is>
           <t>review</t>
@@ -29051,7 +29039,6 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29082,8 +29069,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
-      <c r="L462" t="inlineStr"/>
       <c r="M462" t="inlineStr">
         <is>
           <t>review</t>
@@ -29116,7 +29101,6 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29147,8 +29131,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
-      <c r="L463" t="inlineStr"/>
       <c r="M463" t="inlineStr">
         <is>
           <t>review</t>
@@ -29181,7 +29163,6 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29212,8 +29193,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
-      <c r="L464" t="inlineStr"/>
       <c r="M464" t="inlineStr">
         <is>
           <t>review</t>
@@ -29246,7 +29225,6 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29277,8 +29255,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
-      <c r="L465" t="inlineStr"/>
       <c r="M465" t="inlineStr">
         <is>
           <t>review</t>
@@ -29290,6 +29266,396 @@
         </is>
       </c>
       <c r="O465" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>auto-c112128e3fde</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Tödlicher Unfall: Verunglückte Elixir verlor Landeklappe</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr"/>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Beim &lt;a href="https://www.aerotelegraph.com/general-aviation/flugverbot-fuer-elixir-aircraft-nach-toedlichem-absturz/kmnndmv" id="3c6b73a8-9d4d-44cd-8849-3570fa638176"&gt;Absturz einer Elixir starben am 1. Oktober die zwei Firmenpiloten an Bord&lt;/a&gt;. Elixir Aircraft und die europäische Behörde Easa beorderten am nächsten Tag alle Flugzeuge des Herstellers zu Boden. Nun hat die französische Untersuchungsbehörde BEA eine erste kurze Schilderung des Unfallhergangs veröffentlicht. «Nach zwei Platzrunden auf dem Flugplatz Rochefort meldet einer der Piloten eine Platzrunde in geringer Höhe an», heißt es darin. «Im letzten Kurvenflug auf die Piste 12 löst sich die linke Landeklappe vom Flugzeug. Der Pilot verliert die Kontrolle über das Luftfahrzeug. Der Rettungsfallschirm des Flugzeugs wird in geringer Höhe ausgelöst. Das Flugzeug kollidiert mit dem Boden.»</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/toedlicher-unfall-verunglueckte-elixir-verlor-landeklappe/bep70h7</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr"/>
+      <c r="L466" t="inlineStr"/>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>auto-e2caf5f82bfd</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Pegasus setzt auf KI für den Kundenservice</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr"/>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>Pegasus Airlines investiert in das Technologieunternehmen Zingly.ai und arbeitet mit ihm bei einem KI-gestützten Sprachassistenten für den Kundenservice zusammen. Die Technologie soll Anfragen von Passagieren telefonisch in natürlicher Sprache bearbeiten und möglichst direkt lösen, statt sie lediglich zur späteren Bearbeitung aufzunehmen.</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/pegasus-setzt-auf-ki-fuer-den-kundenservice/g8n2f78</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr"/>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>auto-3946b27cfa74</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Drei Tote bei Angriffen auf saudische Flughäfen</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr"/>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Bei Angriffen auf die Flughäfen Abha und Riyadh sind in Saudi-Arabien drei Menschen getötet und 36 verletzt worden. Das teilte laut der Nachrichtenagentur Reuters die saudische Zivilluftfahrtbehörde GACA mit. In Abha kamen zwei Frauen aus Marokko und Algerien ums Leben, 28 Menschen wurden verletzt. Beim Angriff auf den Flughafen Riyadh wurde ein Sudanese getötet, acht weitere Menschen wurden verletzt. Die Huthi-Miliz bekannte sich zu den Angriffen.</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/drei-tote-bei-angriffen-auf-saudische-flughaefen/l0285my</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr"/>
+      <c r="L468" t="inlineStr"/>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>auto-756f9681b98f</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>D-AIFF: Lufthansa hat weiteren Airbus A340-300 nach Teruel gebracht</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr"/>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>Lufthansa hat sich von einem weiteren Airbus A340-300 verabschiedet*. Das knapp 25 Jahre alte Flugzeug mit dem Kennzeichen D-AIFF und dem Taufnamen Delmenhorst absolvierte seinen letzten Linienflug am 19. September von San Jose nach Frankfurt (LH519).</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/d-aiff-lufthansa-hat-weiteren-airbus-a340-300-nach-teruel-gebracht/sp5v4vt</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr"/>
+      <c r="L469" t="inlineStr"/>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>auto-a2186a8c0642</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Mister Air: Neue Frachtfluglinie startet mit Boeing 757</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr"/>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Die rumänische Frachtfluggesellschaft Mister Air startet mit einem Boeing 757-200 PCF ihren Flugbetrieb. Der Leasinggeber Aer Sale, von dem Mister Air den Umbaufrachter mietet, teilt mir, dass das Flugzeug noch im Oktober in den kommerziellen Einsatz gehen soll.</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/mister-air-neue-frachtfluglinie-startet-mit-boeing-757/413gjn0</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr"/>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>auto-f859bb10999b</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Leipzig/Halle und Dresden bieten mehr Flüge als im Sommer</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr"/>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>LEIPZIG - Mit dem Beginn der Herbstferien nimmt der Reiseverkehr an den Flughäfen Leipzig/Halle und Dresden zu. Besonders gefragt sind Ziele am Mittelmeer und in Ägypten.</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53871/LeipzigHalle-und-Dresden-bieten-mehr-Fluege-als-im-Sommer.html</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr"/>
+      <c r="L471" t="inlineStr"/>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O471"/>
+  <dimension ref="A1:O475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29287,7 +29287,6 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29318,8 +29317,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
-      <c r="L466" t="inlineStr"/>
       <c r="M466" t="inlineStr">
         <is>
           <t>review</t>
@@ -29352,7 +29349,6 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29383,8 +29379,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
-      <c r="L467" t="inlineStr"/>
       <c r="M467" t="inlineStr">
         <is>
           <t>review</t>
@@ -29417,7 +29411,6 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29448,8 +29441,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
-      <c r="L468" t="inlineStr"/>
       <c r="M468" t="inlineStr">
         <is>
           <t>review</t>
@@ -29482,7 +29473,6 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
       <c r="E469" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29513,8 +29503,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
-      <c r="L469" t="inlineStr"/>
       <c r="M469" t="inlineStr">
         <is>
           <t>review</t>
@@ -29547,7 +29535,6 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29578,8 +29565,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
-      <c r="L470" t="inlineStr"/>
       <c r="M470" t="inlineStr">
         <is>
           <t>review</t>
@@ -29612,7 +29597,6 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
       <c r="E471" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29643,8 +29627,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
-      <c r="L471" t="inlineStr"/>
       <c r="M471" t="inlineStr">
         <is>
           <t>review</t>
@@ -29656,6 +29638,266 @@
         </is>
       </c>
       <c r="O471" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>auto-536cdc70fe37</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Etihad Airways rückt ins Zentrum des Man-City-Skandals</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr"/>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Im Finanzskandal um Manchester City geht es um die Frage, woher das Sponsoringgeld von Etihad Airways wirklich kam. Eine alte Stellungnahme der Airline im Subventionsstreit mit US-Airlines wird dabei zum Problem - für den Klub und für Etihad selbst.</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/airlines/etihad-airways-rueckt-ins-zentrum-des-skandals-um-manchester-city/1qt5phj</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr"/>
+      <c r="L472" t="inlineStr"/>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>auto-70c21d77573e</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Pilotenstreik und Flottenstress setzen Air Corsica unter Druck</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr"/>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>AJACCIO - In den ATR-Ausfall platzt ein Pilotenstreik - für Air Corsica kommt es gerade knüppeldick. Die französische Fluggesellschaft stellt sich für die nächsten Tage auf "erhebliche Einschränkungen" im Programm ein. Air Corsica will über den Wetlease-Markt Ersatzkapazitäten organisieren - doch das ist nicht so einfach.</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53883/Pilotenstreik-und-Flottenstress-setzen-Air-Corsica-unter-Druck.html</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr"/>
+      <c r="L473" t="inlineStr"/>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>auto-4cd91accabd2</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Lufthansa stoppt alle Flüge nach Riad</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr"/>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Nach Angriffen auf den Flughafen in Riad streicht die Lufthansa alle Verbindungen dorthin. Die Huthi-Miliz droht mit weiteren Attacken auf saudische Ziele.</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53878/Lufthansa-stoppt-alle-Fluege-nach-Riad.html</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr"/>
+      <c r="L474" t="inlineStr"/>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>auto-8007714706c4</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt: Trio mit Kokain festgenommen</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr"/>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Der Zugriff am Frankfurter Flughafen ist Teil eines größeren Ermittlungsverfahrens. Nach Behördenangaben wird einer Gruppierung Schmuggel und Handel mit mindestens 590 Kilogramm Kokain vorgeworfen.</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53876/Flughafen-Frankfurt-Trio-mit-Kokain-festgenommen.html</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr"/>
+      <c r="L475" t="inlineStr"/>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O475"/>
+  <dimension ref="A1:O480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29659,7 +29659,6 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29690,8 +29689,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
-      <c r="L472" t="inlineStr"/>
       <c r="M472" t="inlineStr">
         <is>
           <t>review</t>
@@ -29724,7 +29721,6 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29755,8 +29751,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
-      <c r="L473" t="inlineStr"/>
       <c r="M473" t="inlineStr">
         <is>
           <t>review</t>
@@ -29789,7 +29783,6 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29820,8 +29813,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
-      <c r="L474" t="inlineStr"/>
       <c r="M474" t="inlineStr">
         <is>
           <t>review</t>
@@ -29854,7 +29845,6 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29885,8 +29875,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
-      <c r="L475" t="inlineStr"/>
       <c r="M475" t="inlineStr">
         <is>
           <t>review</t>
@@ -29898,6 +29886,331 @@
         </is>
       </c>
       <c r="O475" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>auto-344f35bdf5f5</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Air France mit zwei neuen Zielen in den USA - und Dolly-Parton-Flugnummer</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr"/>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Air France nimmt im Sommerflugplan 2027 zwei neue Ziele in den USA auf. Ab dem 3. Mai fliegt die französische Airline drei Mal pro Woche von Paris-Charles de Gaulle nach San Diego in Kalifornien. Am 14. Mai folgt Nashville in Tennessee, ebenfalls mit drei wöchentlichen Flügen. Auf beiden Strecken setzt Air France Airbus A350-900 ein.</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/air-france-mit-zwei-neuen-zielen-in-den-usa-und-dolly-parton-flugnummer/d5t468e</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr"/>
+      <c r="L476" t="inlineStr"/>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>auto-0540c6665ac8</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Kalitta Air soll hinter Bestellung von Airbus A350 F stecken</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr"/>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Ende August &lt;a href="https://www.aerotelegraph.com/flugzeuge/anonymer-kunde-bestellt-acht-airbus-a350-f/s7ss3dq" id="8edda402-65ee-41da-b766-3e6560d01780"&gt;tauchte im Airbus-Orderbuch eine Bestellung über acht A350 F auf - allerdings anonym, ohne Nennung des Kunden&lt;/a&gt;. Nun berichtet Reuters, dass die amerikanische Frachtairline Kalitta Air hinter dem Auftrag stecken soll. Die Nachrichtenagentur beruft sich auf drei mit dem Vorgang vertraute Personen. Kalitta Air erklärte Reuters zufolge, sie prüfe den neuen Frachtflugzeugtyp, habe jedoch keine Bestellung bekanntzugeben.</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/kalitta-air-soll-hinter-bestellung-von-airbus-a350-f-stecken/21etqny</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr"/>
+      <c r="L477" t="inlineStr"/>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>auto-de2c7acc4559</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Fraport will Kleinstflughäfen in Griechenland übernehmen</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr"/>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Griechenland schreibt eine Konzession für 22 Regionalflughäfen aus - Fraport ist die Sache einen genaueren Blick wert. Der Frankfurter Flughafenkonzern ist bereits seit einigen Jahren in Griechenland erfolgreich. Das aktuelle Konzessionspaket hat allerdings einen Haken.</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53872/Fraport-will-fuer-weiteres-Flughafenpaket-in-Griechenland-bietet.html</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr"/>
+      <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>auto-a9184d2e3182</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Lufthansa und Air France-KLM klagen gegen irische Aufsicht</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr"/>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>DUBLIN - Lufthansa und Air France-KLM gehen gegen die irische Luftfahrtbehörde IAA vor. In der Klage, geführt über den Branchenverband ENAA, geht es um nicht weniger als die EU-Flugrechte von Ryanair. Die Betriebslizenz hängt an der Eigentümerstruktur - hier bietet Ryanair seit dem Brexit eine offene Flanke.</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53886/Lufthansa-und-Air-France-KLM-klagen-gegen-irische-Aufsicht.html</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr"/>
+      <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>auto-f239f8ea8912</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>LOT feiert 60 Jahre Warschau – Frankfurt - airportzentrale.de</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr"/>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiggFBVV95cUxOUEdpeTVkZ2hNZmVNSzgyM3IzRGhXRkRoT00zbVBVUXVNb3RZcEZ3S25IS3ZqN0hDTnFJRm9UVDhobmdxcnRHcVRVQUFGcVVQem16aGYtT1BWc3k0cDRmQjhxVDN1MFFQNVRsMVEwSERSS2JJdmJOWlNrLWk1cmJSeGFR?oc=5" target="_blank"&gt;LOT feiert 60 Jahre Warschau – Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airportzentrale.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOUEdpeTVkZ2hNZmVNSzgyM3IzRGhXRkRoT00zbVBVUXVNb3RZcEZ3S25IS3ZqN0hDTnFJRm9UVDhobmdxcnRHcVRVQUFGcVVQem16aGYtT1BWc3k0cDRmQjhxVDN1MFFQNVRsMVEwSERSS2JJdmJOWlNrLWk1cmJSeGFR?oc=5</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr"/>
+      <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O480"/>
+  <dimension ref="A1:O481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29907,7 +29907,6 @@
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -29938,8 +29937,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
-      <c r="L476" t="inlineStr"/>
       <c r="M476" t="inlineStr">
         <is>
           <t>review</t>
@@ -29972,7 +29969,6 @@
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30003,8 +29999,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
-      <c r="L477" t="inlineStr"/>
       <c r="M477" t="inlineStr">
         <is>
           <t>review</t>
@@ -30037,7 +30031,6 @@
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30068,8 +30061,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
-      <c r="L478" t="inlineStr"/>
       <c r="M478" t="inlineStr">
         <is>
           <t>review</t>
@@ -30102,7 +30093,6 @@
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30133,8 +30123,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
-      <c r="L479" t="inlineStr"/>
       <c r="M479" t="inlineStr">
         <is>
           <t>review</t>
@@ -30167,7 +30155,6 @@
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30198,8 +30185,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
-      <c r="L480" t="inlineStr"/>
       <c r="M480" t="inlineStr">
         <is>
           <t>review</t>
@@ -30211,6 +30196,71 @@
         </is>
       </c>
       <c r="O480" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>auto-c335155f668e</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Air France flight AF652 returned to Paris after pilots declared an emergency - airlive</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr"/>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiugFBVV95cUxPeFRrb1lDM0NTR3kzRGhaVjIyS1BublkxQ3VUMGpzdlBZQ1g1T0J0RnhsSXgxdW5RSi1CTFVmVXhfek5BdHdTQWh0bm9wcVllSGdtd2dZN2d5Zm9fd3ozZU1DUExwcHd3OFdVNFFIWDFqVGF5MnU1TklQcnVnTjhWM05pc2ZyMl9DV1BnbGY1aGRrZW5VWHp1S1lyQzEwU0J5WUJTQmZORDg0c1NRRGprdVJsX2dLckpnY3c?oc=5" target="_blank"&gt;Air France flight AF652 returned to Paris after pilots declared an emergency&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPeFRrb1lDM0NTR3kzRGhaVjIyS1BublkxQ3VUMGpzdlBZQ1g1T0J0RnhsSXgxdW5RSi1CTFVmVXhfek5BdHdTQWh0bm9wcVllSGdtd2dZN2d5Zm9fd3ozZU1DUExwcHd3OFdVNFFIWDFqVGF5MnU1TklQcnVnTjhWM05pc2ZyMl9DV1BnbGY1aGRrZW5VWHp1S1lyQzEwU0J5WUJTQmZORDg0c1NRRGprdVJsX2dLckpnY3c?oc=5</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr"/>
+      <c r="L481" t="inlineStr"/>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O481"/>
+  <dimension ref="A1:O487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30217,7 +30217,6 @@
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30248,8 +30247,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
-      <c r="L481" t="inlineStr"/>
       <c r="M481" t="inlineStr">
         <is>
           <t>review</t>
@@ -30261,6 +30258,396 @@
         </is>
       </c>
       <c r="O481" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>auto-a7e9f883f06b</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Hylight: Französisches Start-up sammelt 13 Millionen Euro für wasserstoffbetriebene Luftschiffe ein</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr"/>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Das französische Start-up Hylight hat in einer Finanzierungsrunde 13 Millionen Euro eingesammelt. Mit dem Geld will das 2022 gegründete Unternehmen die Produktion seiner autonomen, wasserstoffbetriebenen Luftschiffe ausbauen. Bis 2027 sollen 15 statt bisher vier Hylighter gleichzeitig im Einsatz sein.</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/hylight-franzoesisches-start-up-sammelt-13-millionen-euro-fuer-wasserstoffbetriebene/rznxsne</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>auto-d38921f08c1b</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>DHL erweitert Kühlkettennetz um sechs Luftfrachtverbindungen nach Asien</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr"/>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>DHL Global Forwarding baut sein Luftfrachtnetz für temperaturempfindliche Pharma- und Gesundheitsprodukte aus. Sechs neue Frachtkorridore verbinden Europa und Nordamerika mit wichtigen Pharmastandorten in Asien.</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/dhl-erweitert-kuehlkettennetz-um-sechs-luftfrachtverbindungen-nach-asien/91k9cpk</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr"/>
+      <c r="L483" t="inlineStr"/>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>auto-59319177fe51</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Lufthansa Cargo verlegt Frachtflüge in Mumbai an neuen Flughafen</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr"/>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Lufthansa Cargo erweitert im Winterflugplan 2026/2027 ihr Frachternetz auf 88 wöchentliche Verbindungen zu 40 Zielen. Ab dem 12. Oktober verlagert die Fluggesellschaft ihre Frachterflüge in Mumbai vom bisherigen Flughafen zum neuen Navi Mumbai International Airport. Zudem wird Singapur in einen Frachterumlauf über Taipeh aufgenommen.</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lufthansa-cargo-verlegt-frachtfluege-in-mumbai-an-neuen-flughafen/6s4bz7d</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr"/>
+      <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>auto-73b300a11838</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Lufthansa Group übergibt Wartung von CFM56-Triebwerken an FL Technics</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr"/>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>FL Technics Engine Services hat mit der Group Engine Management GmbH der Lufthansa Group einen Vertrag über die Wartung und Reparatur von Triebwerken der CFM56-Familie geschlossen. Die Vereinbarung umfasst entsprechende Instandhaltungsarbeiten am Triebwerksstandort von FL Technics.</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lufthansa-group-uebergibt-wartung-von-cfm56-triebwerken-an-fl-technics/ztb33rp</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>auto-91740f7e0c85</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Flughafen London-Heathrow wirbt für dritte Startbahn: 40 Fluggesellschaften wollen neu kommen</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr"/>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Der Flughafen London-Heathrow hat im September knapp 7,2 Millionen Passagiere abgefertigt, darunter rund 1,4 Millionen Umsteiger. Das Frachtaufkommen stieg gegenüber dem Vorjahresmonat um fünf Prozent. Nach Angaben des Flughafens bemühen sich derzeit mehr als 40 Fluggesellschaften um Zugang zu London-Heathrow, dessen Kapazitäten weitgehend ausgeschöpft sind.</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flughafen-london-heathrow-wirbt-fuer-dritte-startbahn-40-fluggesellschaften-wollen/5v8rkj8</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>auto-c37800c56b30</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Emergency Landing: Turkish Airlines Flight Diverted to Barcelona - Global Banking &amp; Finance Review</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr"/>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMinwFBVV95cUxQdzFYYVN2UkdscTNHSklLM01Ud2tvVnNJTS11MWVKWDVFWlF4RGg1RFBqQ1FMNGFKNkpLWWJUenFib3VxSmdKTFg0aC1rajQyTFVMRXdTSE9aMnhEUTNIZFhjUW9nNGNnRXVRQmdWakM1TDNqa2RDdGNwNVhwOXRUR0ZCS016TUtZWk8ySGtfNmUzS0NmeEVUUUxBN3FBYmc?oc=5" target="_blank"&gt;Emergency Landing: Turkish Airlines Flight Diverted to Barcelona&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Global Banking &amp; Finance Review&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQdzFYYVN2UkdscTNHSklLM01Ud2tvVnNJTS11MWVKWDVFWlF4RGg1RFBqQ1FMNGFKNkpLWWJUenFib3VxSmdKTFg0aC1rajQyTFVMRXdTSE9aMnhEUTNIZFhjUW9nNGNnRXVRQmdWakM1TDNqa2RDdGNwNVhwOXRUR0ZCS016TUtZWk8ySGtfNmUzS0NmeEVUUUxBN3FBYmc?oc=5</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr"/>
+      <c r="L487" t="inlineStr"/>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O487"/>
+  <dimension ref="A1:O491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30279,7 +30279,6 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30310,8 +30309,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
-      <c r="L482" t="inlineStr"/>
       <c r="M482" t="inlineStr">
         <is>
           <t>review</t>
@@ -30344,7 +30341,6 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30375,8 +30371,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
-      <c r="L483" t="inlineStr"/>
       <c r="M483" t="inlineStr">
         <is>
           <t>review</t>
@@ -30409,7 +30403,6 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30440,8 +30433,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
-      <c r="L484" t="inlineStr"/>
       <c r="M484" t="inlineStr">
         <is>
           <t>review</t>
@@ -30474,7 +30465,6 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30505,8 +30495,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
-      <c r="L485" t="inlineStr"/>
       <c r="M485" t="inlineStr">
         <is>
           <t>review</t>
@@ -30539,7 +30527,6 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30570,8 +30557,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
-      <c r="L486" t="inlineStr"/>
       <c r="M486" t="inlineStr">
         <is>
           <t>review</t>
@@ -30604,7 +30589,6 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -30635,8 +30619,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
-      <c r="L487" t="inlineStr"/>
       <c r="M487" t="inlineStr">
         <is>
           <t>review</t>
@@ -30648,6 +30630,266 @@
         </is>
       </c>
       <c r="O487" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>auto-def971f47a96</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Israel macht ernst und schickt Frachter von Ethiopian Airlines zurück</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr"/>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Eine Boeing 737 F von Ethiopian Cargo musste auf dem Weg nach Tel Aviv umkehren. Der Grund: Im Cockpit saß eine Person mit indonesischem Pass. Die Crewliste war erst nach dem Start in Israel eingegangen.</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugzeuge/ethiopian-cargo-muss-flug-nach-tel-aviv-wegen-crew-mitglied-umkehren/se5k0sm</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr"/>
+      <c r="L488" t="inlineStr"/>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>auto-f8db42cbba0b</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>In Endrunde: Flughafen Zürich und Fraport bewerben sich um Betrieb des Flughafens Hurghada</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr"/>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Ägypten hat sieben internationale Unternehmen und Konsortien für die nächste Runde der Ausschreibung zum Betrieb und zur Entwicklung des Flughafens Hurghada zugelassen. Darunter befinden sich mit dem Flughafen Zürich und Fraport auch zwei Flughafenbetreiber aus dem deutschsprachigen Raum.</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/in-endrunde-flughafen-zuerich-und-fraport-bewerben-sich-um-betrieb-des-flughafens/fvxsxrk</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr"/>
+      <c r="L489" t="inlineStr"/>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>auto-c82e8f9e6a90</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Wie das Drehkreuz Frankfurt Streiks und Weltkrisen trotzt</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr"/>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Iran-Krieg, Lufthansa-Streiks, Kurzstrecken-Erosion: 2026 startete für den Frankfurter Flughafen mit einem perfekten Sturm. Nach einem starken Sommer schließt das größte deutsche Luftfahrtdrehkreuz immerhin wieder zu Vorjahreswerten auf. Betreiber Fraport zieht eine Zwischenbilanz.</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53912/Wie-das-Drehkreuz-Frankfurt-Streiks-und-Krisen-trotzt.html</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr"/>
+      <c r="L490" t="inlineStr"/>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>auto-cbf84b8e58b7</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Thai Airways Boeing 777 flight TG921 to Bangkok declared an emergency and just returned to Frankfurt - airlive</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr"/>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi2gFBVV95cUxQdWtvbUg3MVo1MWJqX2VBbW0xTmxrVXU3VzVRaXBzWDJ3Qllza2hkZVdGOFl5ZGVGSk4wbktmdlF1U3lmZTBKZUNaS3BDTGtRR1QyZXk0aC1feEZnZkE1Vk9sdnJvNjVlb1BzdGpGeXU4RXhUeWIzakJYeHg5Z3dkSGV2WDVQYkRZVUx6Z3BOcGh4ampuTDhTNUhNUFpJUzVjSS16N1A0dER6WFlOaWtPQ0FQbEdxSDVXOGcwZ3ExMmcxaF9ubk52ZTFyc0NTa25PQ1VQRVNwT183Z9IB4gFBVV95cUxNd243cVNRWHY1bzhJeXZXSzNEWGg1bEJhVThsNjFTUnEyVGdFTldqY180cGhOMFZVLU8wZlRXVGpjampkVmJJVzVQaUx2d293RjU3a3FuY0JyVlh5dXM4RWNzQS13X0V6SGl5aHhVUlpKbm5DanBRZzEtZTdpRjJKTGJvY0NYZ3k5SUdYSllfYjlqZzBGWE1nNlNZbktmLTZ4VjBFcWEyVVJnNHRhZTdFdnF2UlA5amp3WkZRYjFsN01qQWJVMHoxbEdHQWp4QTdFR09TdWlmSHdBSE9wbVZZbkx3?oc=5" target="_blank"&gt;Thai Airways Boeing 777 flight TG921 to Bangkok declared an emergency and just returned to Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQdWtvbUg3MVo1MWJqX2VBbW0xTmxrVXU3VzVRaXBzWDJ3Qllza2hkZVdGOFl5ZGVGSk4wbktmdlF1U3lmZTBKZUNaS3BDTGtRR1QyZXk0aC1feEZnZkE1Vk9sdnJvNjVlb1BzdGpGeXU4RXhUeWIzakJYeHg5Z3dkSGV2WDVQYkRZVUx6Z3BOcGh4ampuTDhTNUhNUFpJUzVjSS16N1A0dER6WFlOaWtPQ0FQbEdxSDVXOGcwZ3ExMmcxaF9ubk52ZTFyc0NTa25PQ1VQRVNwT183Z9IB4gFBVV95cUxNd243cVNRWHY1bzhJeXZXSzNEWGg1bEJhVThsNjFTUnEyVGdFTldqY180cGhOMFZVLU8wZlRXVGpjampkVmJJVzVQaUx2d293RjU3a3FuY0JyVlh5dXM4RWNzQS13X0V6SGl5aHhVUlpKbm5DanBRZzEtZTdpRjJKTGJvY0NYZ3k5SUdYSllfYjlqZzBGWE1nNlNZbktmLTZ4VjBFcWEyVVJnNHRhZTdFdnF2UlA5amp3WkZRYjFsN01qQWJVMHoxbEdHQWp4QTdFR09TdWlmSHdBSE9wbVZZbkx3?oc=5</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr"/>
+      <c r="L491" t="inlineStr"/>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O491"/>
+  <dimension ref="A1:O504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30651,7 +30651,6 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -30682,8 +30681,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
-      <c r="L488" t="inlineStr"/>
       <c r="M488" t="inlineStr">
         <is>
           <t>review</t>
@@ -30716,7 +30713,6 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30747,8 +30743,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
-      <c r="L489" t="inlineStr"/>
       <c r="M489" t="inlineStr">
         <is>
           <t>review</t>
@@ -30781,7 +30775,6 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30812,8 +30805,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
-      <c r="L490" t="inlineStr"/>
       <c r="M490" t="inlineStr">
         <is>
           <t>review</t>
@@ -30846,7 +30837,6 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30877,8 +30867,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
-      <c r="L491" t="inlineStr"/>
       <c r="M491" t="inlineStr">
         <is>
           <t>review</t>
@@ -30890,6 +30878,851 @@
         </is>
       </c>
       <c r="O491" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>auto-80277486ae66</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Miles &amp; More ermöglicht wieder nachträglichen CO₂-Ausgleich gegen Statuspunkte</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr"/>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>Nach mehrmonatiger Unterbrechung hat Miles &amp;amp; More die Möglichkeit zur nachträglichen Buchung von CO₂-Einsparpaketen wieder freigeschaltet. Seit dieser Woche können Mitglieder des Vielfliegerprogramms von Lufthansa Group bereits absolvierte Flüge wieder nachträglich mit entsprechenden Paketen ergänzen und dafür zusätzliche Meilen sowie Points und Qualifying Points erhalten.</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/miles-und-more-ermoeglicht-wieder-nachtraeglichen-co-ausgleich-gegen-statuspunkte/hp49xkk</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr"/>
+      <c r="L492" t="inlineStr"/>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>auto-849099ebb6fa</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Japan Airlines entscheidet sich gegen Airbus A220 und für Embraer E2</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr"/>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>Airbus A220 oder Embraer E2? Japan Airlines JAL hat sich bei der Erneuerung ihrer Regionalflotte entschieden. Für ihre Tochter J-Air bestellt sie bis zu 26 Embraer E190-E2. Ausschlaggebend sind unter anderem niedrigere Betriebs- und Wartungskosten sowie die veränderte Nachfrage auf Japans Inlandstrecken.</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugzeuge/japan-airlines-entscheidet-sich-gegen-airbus-a220-und-fuer-embraer-e2/pwvz26f</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr"/>
+      <c r="L493" t="inlineStr"/>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>auto-a8f5197b8252</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Trinity Airways setzt Frankfurt-Flüge im Winter aus</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr"/>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>Die südkoreanische Fluggesellschaft Trinity Airways, ehemals T'way Air, stellt ihre Verbindung zwischen Seoul-Incheon und Frankfurt im Winterflugplan 2026/27 vorerst ein. Mit Stand vom 13. Oktober sind für die gesamte Wintersaison keine Flüge auf der Strecke mehr buchbar, so das Portal Aero Routes.</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/trinity-airways-setzt-frankfurt-fluege-im-winter-aus/en2redp</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr"/>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>auto-2799f689f3ed</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Medien: Lufthansa wird Zuschlag für TAP Air Portugal erhalten</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr"/>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>LISSABON - Lufthansa steht vor einem Zuschlag für einen Einstieg bei TAP Air Portugal. Nach portugiesischen Medienberichten wird sich der Konzern im Bieterwettstreit mit Air France-KLM mit einem reinen Barangebot durchsetzen. Das Regierungskabinett kommt am Mittwoch zu einer Sondersitzung zusammen.</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53924/Medien-Lufthansa-wird-Zuschlag-fuer-TAP-Air-Portugal-erhalten.html</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr"/>
+      <c r="L495" t="inlineStr"/>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>auto-9c8fa284f2eb</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>A United 35-year-old Boeing 767 to Amsterdam is declaring an emergency and diverting to Canada - airlive</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr"/>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi0gFBVV95cUxOQllleldEbUFyR21pelZXeTJSbFpMQWMycW1BTjJYTjVsb1pFQjFMOEdxbUc2bFhfcVNTWHhlLW9tSlRrbkMzOXZOQWlMLVp0REZBVTZCT3d6SU1ESzBVS2xWRUtGVDZILUpYSk9WQ2UxZElMc3hIcTlVRkROYXpXSjNkcnNieWVYLW9MS3JycklYM3g5bGJPenZPUnM3ZGVJdG5UREJxMHppVVNvdDliMHJ5aVZGNnBpTnVkR1pybkJSZHdJcGtQbmFfamdmM0JfTVHSAdoBQVVfeXFMTWZNY1dRUmlCN3pZWUx2ZTV4SlF0b0NQQkNTRXc1OTRGaHl1ZTBIUzlLeFMzNmhPTGxNOE5ZUWgwTF91Q3VjYzlfZFV6XzlxZm9hNmtKcXptWlRXVFRaVUgwMXRFSUQ3RUZfM3JhaGxDQ0V6WDZTanRpb3g2YUh4ZmloQWN4NzNZNW1OaDlBbVJldE00NDlQU1lDSTFQZVBaUEVzcW45cGFWaDFBTUMwUlRERG8xRFZPZTM0cUw1aGVMbEdQSll6RlpXbXlnMEpyUk9QUEV4UDI3VEE?oc=5" target="_blank"&gt;A United 35-year-old Boeing 767 to Amsterdam is declaring an emergency and diverting to Canada&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOQllleldEbUFyR21pelZXeTJSbFpMQWMycW1BTjJYTjVsb1pFQjFMOEdxbUc2bFhfcVNTWHhlLW9tSlRrbkMzOXZOQWlMLVp0REZBVTZCT3d6SU1ESzBVS2xWRUtGVDZILUpYSk9WQ2UxZElMc3hIcTlVRkROYXpXSjNkcnNieWVYLW9MS3JycklYM3g5bGJPenZPUnM3ZGVJdG5UREJxMHppVVNvdDliMHJ5aVZGNnBpTnVkR1pybkJSZHdJcGtQbmFfamdmM0JfTVHSAdoBQVVfeXFMTWZNY1dRUmlCN3pZWUx2ZTV4SlF0b0NQQkNTRXc1OTRGaHl1ZTBIUzlLeFMzNmhPTGxNOE5ZUWgwTF91Q3VjYzlfZFV6XzlxZm9hNmtKcXptWlRXVFRaVUgwMXRFSUQ3RUZfM3JhaGxDQ0V6WDZTanRpb3g2YUh4ZmloQWN4NzNZNW1OaDlBbVJldE00NDlQU1lDSTFQZVBaUEVzcW45cGFWaDFBTUMwUlRERG8xRFZPZTM0cUw1aGVMbEdQSll6RlpXbXlnMEpyUk9QUEV4UDI3VEE?oc=5</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr"/>
+      <c r="L496" t="inlineStr"/>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>auto-8197ece580f2</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Emergency: United Boeing 767 to Newark dumped fuel before diversion to London Heathrow - airlive</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr"/>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMixgFBVV95cUxOM1hyNTFBTFZnb0laYUVwNDhpZnFaemtDZHRERldQQlFfOGN4Vjk3ejRrc3lDcDhNZGFXUktJbW1Jamh4OENTR2VyYllKeTA3eXVfNVJWcEdBNFQ4TmVYMUtwZkpVYWotQ1dxNndhSTF6ZnRnSmxkZi03UjZzUFBrNndydUZWM18zOEJzTC1jd3dPSnRsZ19lVTV6cUVjUHctbHRIMmt2N0tSSkdXRHpER005ZTNxSEIwUVUzV3huYVNUNWNOUHfSAc4BQVVfeXFMUG82TDc1M19GTlRyT3FISy1Nbmp1ZXkyT3BueDE3cldia0N4ZDc2ZURwaUV6b1R2R3Yyd1dlUVNCYlRSQ0V5WjlaTnZKajZaYmJoa0hyT3RQeUNhUnFULWIxaFJyYWtPcjZ5a0FQNGFmUW1Qb3U5MGhKLVFCNXd4NG9mYkt6TzdCa0ljLXA3dXJrbVBrbDltUTc5bUN0X05YVVN2Umd3SW12bjVhbmNrTVR6OUFRRlVuRmltQ19IaFFyclJOMEVMVTRKY1lGZHc?oc=5" target="_blank"&gt;Emergency: United Boeing 767 to Newark dumped fuel before diversion to London Heathrow&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOM1hyNTFBTFZnb0laYUVwNDhpZnFaemtDZHRERldQQlFfOGN4Vjk3ejRrc3lDcDhNZGFXUktJbW1Jamh4OENTR2VyYllKeTA3eXVfNVJWcEdBNFQ4TmVYMUtwZkpVYWotQ1dxNndhSTF6ZnRnSmxkZi03UjZzUFBrNndydUZWM18zOEJzTC1jd3dPSnRsZ19lVTV6cUVjUHctbHRIMmt2N0tSSkdXRHpER005ZTNxSEIwUVUzV3huYVNUNWNOUHfSAc4BQVVfeXFMUG82TDc1M19GTlRyT3FISy1Nbmp1ZXkyT3BueDE3cldia0N4ZDc2ZURwaUV6b1R2R3Yyd1dlUVNCYlRSQ0V5WjlaTnZKajZaYmJoa0hyT3RQeUNhUnFULWIxaFJyYWtPcjZ5a0FQNGFmUW1Qb3U5MGhKLVFCNXd4NG9mYkt6TzdCa0ljLXA3dXJrbVBrbDltUTc5bUN0X05YVVN2Umd3SW12bjVhbmNrTVR6OUFRRlVuRmltQ19IaFFyclJOMEVMVTRKY1lGZHc?oc=5</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr"/>
+      <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>auto-5695a290fda2</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Alaska Airlines Boeing 787-9 is declaring an emergency off France coast, after U-turn over UK - airlive</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr"/>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMizwFBVV95cUxPaTY1ZTFSYXZOWmVQajY0OHJtaDJpNUpxWm50V1hRaEJKZ2gtMFZySG4tT0ZxNUlrTTN3YjMyWExVOVVybFBudmhXMjRqSlRwN3NGVW5KbDFReDVwbVBlZFUyQlRTTm15c1FRRnN1Qmtxam5fS3ExSm9OUEJ0ZVNvMDBmajhLYjNwUFV6bUI0cnZlMkxxX1lINkdBYlU2SEVkLU9HQ3VEUDNrWWRraHhudFFmS0JsNXhLLVhiUG1tTU9LWllUX01ubXZJeGpMMjjSAdcBQVVfeXFMTTRjY2lhZkY5VDJMWS1OMm5WZklIa0h5QXNKM0ZBWjVmM2tlOVRYMUstSjhYQ0VSZ0k5Vjh1OHNXNkZ4MHdhUzBfeVZicEtoQzgtTjhLTU83LWxrVW4zdWlYaG56VXRkU0E3ay1WM0N5eEIza3BtSzhTUXhwQ2gxSnBsNFJOMjh4aFZocmxpZEFsSTBvZTN6cWR3ZVd4aGdqdEN0aHpyNGh6bzNJMkpFVFhTNnVLeC1GTzhwblZFeHNNUURSbXdCYXNQcXg2SkJGNThkNEI0NzA?oc=5" target="_blank"&gt;Alaska Airlines Boeing 787-9 is declaring an emergency off France coast, after U-turn over UK&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPaTY1ZTFSYXZOWmVQajY0OHJtaDJpNUpxWm50V1hRaEJKZ2gtMFZySG4tT0ZxNUlrTTN3YjMyWExVOVVybFBudmhXMjRqSlRwN3NGVW5KbDFReDVwbVBlZFUyQlRTTm15c1FRRnN1Qmtxam5fS3ExSm9OUEJ0ZVNvMDBmajhLYjNwUFV6bUI0cnZlMkxxX1lINkdBYlU2SEVkLU9HQ3VEUDNrWWRraHhudFFmS0JsNXhLLVhiUG1tTU9LWllUX01ubXZJeGpMMjjSAdcBQVVfeXFMTTRjY2lhZkY5VDJMWS1OMm5WZklIa0h5QXNKM0ZBWjVmM2tlOVRYMUstSjhYQ0VSZ0k5Vjh1OHNXNkZ4MHdhUzBfeVZicEtoQzgtTjhLTU83LWxrVW4zdWlYaG56VXRkU0E3ay1WM0N5eEIza3BtSzhTUXhwQ2gxSnBsNFJOMjh4aFZocmxpZEFsSTBvZTN6cWR3ZVd4aGdqdEN0aHpyNGh6bzNJMkpFVFhTNnVLeC1GTzhwblZFeHNNUURSbXdCYXNQcXg2SkJGNThkNEI0NzA?oc=5</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr"/>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>auto-07070d5c4d30</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>United 25-year-old Boeing 767 diverted to Dublin after sudden loss of autopilot over Atlantic - airlive</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr"/>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMizwFBVV95cUxPOGMyUFRJUVM3dkVTZmVsVEVYbDFhYmw1Z053NW9fMEliNDhtaXZIZzJHRFBwNW1nb3hBRDN2ZFhyVnpnZ1JoNVhBMllXbzhBTS1hZ3B0bkVadTlwUW1ZdmFKc0J0LWlUM0FsdDMwd3B0U3l2YzdKSXhTdUpYcnZVazJlTWJScWYyMHFZMVl5MTdLNEg0TXBXM2RtR09qM2lWcl9MSTRycmNUc0xjTnF0eUZkOExJV09KNGVKMTdESHdTakdNVkducmRvY2VvdmPSAdcBQVVfeXFMUFE0NmJpSF9JNDlCQURuUmRabWFLTWlkVVd2WVFDOWFueXB0dGloVXlrTVlwc09oU210N1BFeWJKcGg2bmkwSk1qLXlrN0k5eDdJSUlCRnZnZzFSdENwanV3UkJpYWd4ZHRoa0xUcnN2UVdPOEZEai0yd09DNm9MbkdUMDRzTGRUWGpMX3VVYnhrMF9fZmZzSWNDNjNWRjloeUk2S2pnVFdfVmx2SmpHV1M4aHBGQVdYM3VrOUVZT1NDSUt1WXdKTS1xUWw1aUZaMTVkUHNENGc?oc=5" target="_blank"&gt;United 25-year-old Boeing 767 diverted to Dublin after sudden loss of autopilot over Atlantic&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPOGMyUFRJUVM3dkVTZmVsVEVYbDFhYmw1Z053NW9fMEliNDhtaXZIZzJHRFBwNW1nb3hBRDN2ZFhyVnpnZ1JoNVhBMllXbzhBTS1hZ3B0bkVadTlwUW1ZdmFKc0J0LWlUM0FsdDMwd3B0U3l2YzdKSXhTdUpYcnZVazJlTWJScWYyMHFZMVl5MTdLNEg0TXBXM2RtR09qM2lWcl9MSTRycmNUc0xjTnF0eUZkOExJV09KNGVKMTdESHdTakdNVkducmRvY2VvdmPSAdcBQVVfeXFMUFE0NmJpSF9JNDlCQURuUmRabWFLTWlkVVd2WVFDOWFueXB0dGloVXlrTVlwc09oU210N1BFeWJKcGg2bmkwSk1qLXlrN0k5eDdJSUlCRnZnZzFSdENwanV3UkJpYWd4ZHRoa0xUcnN2UVdPOEZEai0yd09DNm9MbkdUMDRzTGRUWGpMX3VVYnhrMF9fZmZzSWNDNjNWRjloeUk2S2pnVFdfVmx2SmpHV1M4aHBGQVdYM3VrOUVZT1NDSUt1WXdKTS1xUWw1aUZaMTVkUHNENGc?oc=5</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr"/>
+      <c r="L499" t="inlineStr"/>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>auto-4c8c53449a2d</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>One of Delta’s oldest active passenger aircraft finally landed in Portugal after initial planned diversion to Iceland - airlive</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr"/>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi7gFBVV95cUxPZGpVbGRxb2FOY25paFNJVzU5cF82N1FTUDBKeUFNVnJBZjg2YzN1eUVvN0I5a0I0aVpnYUp4cUJ4bzc2OFp6UVZWcnF0a0hNdEFFTWlxc25QdVZvME5xYWo4QWFpNU9RMFdoOHA3U2dvUl9XWHMza1I1ZUstS1ZyMTBBb1ZBSEFTcFV4QXNDbjFLOVJhYlJ2TXdRMGZER2JEN2owOVdGTUd3eXEzUUI2Ynk1X0VmdU0zN01GUHJnQ0liODJMWmt1Vy1fSHRrME03VWIyOWwyYkRxdDJncVg3VlNzajQ0SkljRjR3b3pn0gH2AUFVX3lxTE1aNnN1emdvRUR3TDNsUVp4NkZFRWhobjQwUk0wMWswc2Q4SXNGYWVEYzUxb29ILVFrNkl4NDNsVTJKSmlzY1dYRlNsdEtYTXg0WkgyTU04NFB6RXVyUFo0RnVqS2stVXRBUW9SRktNV2p4MmVZeENqNlprOXJwYzBWSVhUbGpueU9mM2o4MDhFVENmenA2T0sxMkxRVWdJOGxEbWVkQVF5UW1iOE5RdEFjMlVEeHlvRkpHOGR6Y2swUmIyalZBd1RRbTl0QVk1NHBvbjd1WG5QMERiNkhxZC04QWR3cTlNRkh4ZjF1YloxMnEtcEVtZw?oc=5" target="_blank"&gt;One of Delta’s oldest active passenger aircraft finally landed in Portugal after initial planned diversion to Iceland&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPZGpVbGRxb2FOY25paFNJVzU5cF82N1FTUDBKeUFNVnJBZjg2YzN1eUVvN0I5a0I0aVpnYUp4cUJ4bzc2OFp6UVZWcnF0a0hNdEFFTWlxc25QdVZvME5xYWo4QWFpNU9RMFdoOHA3U2dvUl9XWHMza1I1ZUstS1ZyMTBBb1ZBSEFTcFV4QXNDbjFLOVJhYlJ2TXdRMGZER2JEN2owOVdGTUd3eXEzUUI2Ynk1X0VmdU0zN01GUHJnQ0liODJMWmt1Vy1fSHRrME03VWIyOWwyYkRxdDJncVg3VlNzajQ0SkljRjR3b3pn0gH2AUFVX3lxTE1aNnN1emdvRUR3TDNsUVp4NkZFRWhobjQwUk0wMWswc2Q4SXNGYWVEYzUxb29ILVFrNkl4NDNsVTJKSmlzY1dYRlNsdEtYTXg0WkgyTU04NFB6RXVyUFo0RnVqS2stVXRBUW9SRktNV2p4MmVZeENqNlprOXJwYzBWSVhUbGpueU9mM2o4MDhFVENmenA2T0sxMkxRVWdJOGxEbWVkQVF5UW1iOE5RdEFjMlVEeHlvRkpHOGR6Y2swUmIyalZBd1RRbTl0QVk1NHBvbjd1WG5QMERiNkhxZC04QWR3cTlNRkh4ZjF1YloxMnEtcEVtZw?oc=5</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr"/>
+      <c r="L500" t="inlineStr"/>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>auto-c13b98ad16e1</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Swiss flight LX52 to Boston declared Mayday mid-Atlantic reporting onboard smoke - airlive</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr"/>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMivgFBVV95cUxNczRNQVZZNXZHWk1IVFRQVHduclloQzkwR0taNk0wTGtUc0szX2J6elZJS2M0ZjdTOEtuYi1xTS1Ob2hzTmZCNktRYTFZa2ZLSUVrZjR6Z29qSjk2OXRCcklOS0oyWTk5Q2JsdENjSURDeUYwOGZEb0thNVNPamUyTEFuMHg2U25mU0Zsam1Eb080cnVkVUhfNkNUUFBSNlk3aktvdzkxNU90RE9WT0RxbzFlei1ZcTdfS1JZT1Z30gHGAUFVX3lxTE56eDBwMW04VmYzYnh5WGs2ZldhVEFoVXl2bmlWLUpyTC1fY1UtLTlmNzRFLVB4UTRqbmxKaHVCbDBiUktfeTRYeWtYY2hUV0dPZkNTLURNLTZjYUlaSTJyZHhIMnJNWDRCN29XeWJ6V0RrcWtVNkg2QzdERjZSeC1qRWt4Q1VpcVp5ZWtXNDFjdVZkMmtqOHJUbG95VFhSZDJjMG5IMGlrQW8tLWVVUHk3RGs0Q1JncEp4eXE2TWp2dkRmaHNaQQ?oc=5" target="_blank"&gt;Swiss flight LX52 to Boston declared Mayday mid-Atlantic reporting onboard smoke&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNczRNQVZZNXZHWk1IVFRQVHduclloQzkwR0taNk0wTGtUc0szX2J6elZJS2M0ZjdTOEtuYi1xTS1Ob2hzTmZCNktRYTFZa2ZLSUVrZjR6Z29qSjk2OXRCcklOS0oyWTk5Q2JsdENjSURDeUYwOGZEb0thNVNPamUyTEFuMHg2U25mU0Zsam1Eb080cnVkVUhfNkNUUFBSNlk3aktvdzkxNU90RE9WT0RxbzFlei1ZcTdfS1JZT1Z30gHGAUFVX3lxTE56eDBwMW04VmYzYnh5WGs2ZldhVEFoVXl2bmlWLUpyTC1fY1UtLTlmNzRFLVB4UTRqbmxKaHVCbDBiUktfeTRYeWtYY2hUV0dPZkNTLURNLTZjYUlaSTJyZHhIMnJNWDRCN29XeWJ6V0RrcWtVNkg2QzdERjZSeC1qRWt4Q1VpcVp5ZWtXNDFjdVZkMmtqOHJUbG95VFhSZDJjMG5IMGlrQW8tLWVVUHk3RGs0Q1JncEp4eXE2TWp2dkRmaHNaQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr"/>
+      <c r="L501" t="inlineStr"/>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>auto-ee89ab30b583</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>American Airlines flight AA705 to Charlotte diverted to Heathrow after crew declared an emergency - airlive</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr"/>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi1gFBVV95cUxNRUhCcFdLVTREeUhpQUlBWWRpdXVFUzdDZ3FfS3F0bV95VEVNT3g3Sng2NXltOWlxdFpLLW9PdEJFSm5MaDZmS0huUHRuRUVTbHMwdHB4WWlrOWd3ZXlOdWRWM0hKSVJYSW14anJucHgtYmZMOFBOMWo2c3dXQWFrRkFtbFVrUU9zZ05aNlNCbG9nbXMxTEhhWG5BeVZlWHMwdFJVMTRucTNSRlc5YklLNW54VXVsNXFIYm9pZ1JmMFBMOTUxQkdmUUtXNHI2RFhtODRSRnVB0gHeAUFVX3lxTE83bGNsQVJEUGJLWEQtRmFYOEhnVkR4LWVoX09mbWN0OEg2bjh1azlDdDNtbVJ6MzVLNG9KNkZvR0NjWHN5bDhOb1l3MU9MNHBFWUxtX1R5S3FsX1ltdWgxc3VhNldySVY5SlNYc3JEazBuUURHTmlqRjJpOWcwRk1fU1JBMW5COEhCNGQtZHNQdVRmYzUtRmZGUlpGT1NYWm9teEZRQkhtTmxJbW1zckRfcHhHejN1YzZ5R3BEZFQ1dHctU0VxajVpQlQ1STFkaWNDQVd2Ukt4RUdfd2FxUQ?oc=5" target="_blank"&gt;American Airlines flight AA705 to Charlotte diverted to Heathrow after crew declared an emergency&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNRUhCcFdLVTREeUhpQUlBWWRpdXVFUzdDZ3FfS3F0bV95VEVNT3g3Sng2NXltOWlxdFpLLW9PdEJFSm5MaDZmS0huUHRuRUVTbHMwdHB4WWlrOWd3ZXlOdWRWM0hKSVJYSW14anJucHgtYmZMOFBOMWo2c3dXQWFrRkFtbFVrUU9zZ05aNlNCbG9nbXMxTEhhWG5BeVZlWHMwdFJVMTRucTNSRlc5YklLNW54VXVsNXFIYm9pZ1JmMFBMOTUxQkdmUUtXNHI2RFhtODRSRnVB0gHeAUFVX3lxTE83bGNsQVJEUGJLWEQtRmFYOEhnVkR4LWVoX09mbWN0OEg2bjh1azlDdDNtbVJ6MzVLNG9KNkZvR0NjWHN5bDhOb1l3MU9MNHBFWUxtX1R5S3FsX1ltdWgxc3VhNldySVY5SlNYc3JEazBuUURHTmlqRjJpOWcwRk1fU1JBMW5COEhCNGQtZHNQdVRmYzUtRmZGUlpGT1NYWm9teEZRQkhtTmxJbW1zckRfcHhHejN1YzZ5R3BEZFQ1dHctU0VxajVpQlQ1STFkaWNDQVd2Ukt4RUdfd2FxUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr"/>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>auto-fa3012f6f62c</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Jet2 flight LS1473 made a U-turn over France after pilots declared an emergency - airlive</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr"/>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMivgFBVV95cUxQREZDdER4STdyY2dSZk5IZ0NEeVJXelcxSjF1ZXJoYW52ZWx6UWxLYTN0cW5NUkIydHNHZGZUTFpCb0k1SGlWVU1LV0RaUk5pSnJsZWNnbmR4ekQ4YlV1UjdsVUh4SXhXcmxRNl95MUEzVUNZTUhsWWdXdms2aXlBVWMwLTZPTzNudVpxZkZGLUpaM1FoXzBXdF9FSXZyd0hwUS1jUkNlOW5FdXZZTTM3cEFfTzZDdXU2eTZvekZB0gHGAUFVX3lxTE45M0hiYTNoYUk2T1o0VGxacTJIOTRNcy14cmNWNUFEVzNBZzZTQnI5b3Jhci1iV3I5TzdqVE04WkxPVE5TOXJpM2JGdHRQcG1OdFZ4aUp5dWd0Vl80VHNKZWV2aE1jQkpraG41ZHhheTd6V3BISnloYXlzRFd1cWJxWU92b055dXVsYzNOZkxJalBYbFo2bkFJaTFjMVMzRlA3VzFyUmF6UlloSU1ZOFFXMjM0V1pQbEx3VlZwcll4c3hCV0hfdw?oc=5" target="_blank"&gt;Jet2 flight LS1473 made a U-turn over France after pilots declared an emergency&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQREZDdER4STdyY2dSZk5IZ0NEeVJXelcxSjF1ZXJoYW52ZWx6UWxLYTN0cW5NUkIydHNHZGZUTFpCb0k1SGlWVU1LV0RaUk5pSnJsZWNnbmR4ekQ4YlV1UjdsVUh4SXhXcmxRNl95MUEzVUNZTUhsWWdXdms2aXlBVWMwLTZPTzNudVpxZkZGLUpaM1FoXzBXdF9FSXZyd0hwUS1jUkNlOW5FdXZZTTM3cEFfTzZDdXU2eTZvekZB0gHGAUFVX3lxTE45M0hiYTNoYUk2T1o0VGxacTJIOTRNcy14cmNWNUFEVzNBZzZTQnI5b3Jhci1iV3I5TzdqVE04WkxPVE5TOXJpM2JGdHRQcG1OdFZ4aUp5dWd0Vl80VHNKZWV2aE1jQkpraG41ZHhheTd6V3BISnloYXlzRFd1cWJxWU92b055dXVsYzNOZkxJalBYbFo2bkFJaTFjMVMzRlA3VzFyUmF6UlloSU1ZOFFXMjM0V1pQbEx3VlZwcll4c3hCV0hfdw?oc=5</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr"/>
+      <c r="L503" t="inlineStr"/>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>auto-2b060b1f3806</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>TUI flight BY7614 just declared an emergency over France, now diverting to Gatwick - airlive</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr"/>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirwFBVV95cUxQUHFQZWVnQUxzaGM5elBRbVFXMm1Vb093UXkwaERMTlZHcEpJN2RPQXU5NVdSUkE4NkF4Y18yaTVkM3dlTk5ZQ2MyOTZoaUlTelI5U0lKWFZVa254RlRWbGN3UVlFaFp2bUp6YVNXdHN5bklDcFlFLXYyUGdVVU1seGltN2RRYjM2bVVFVV9hcHplcHlINVpvbW9TUFM2QzhmbW1wYjVlbHZLR1pBdW4w0gG3AUFVX3lxTFB5OE5EUHhFR2ZDOFQta3pNZTUzcXFfN014NFdPbkxjb0JhM2t2REk2QjBMQ3dBekJKUFl4MVZfWldMZmJYelVjZ21URTVjNDFESmNFeHByOHd3SUg2Z1FiaWNTM0dUeTRvWmV3dXRoSVFUU2x6UnFCMXZCT3ZyRXJ4N1locTRFaGk3UFpPdE5yYWVzZGRXR3pYbVpUMlBPbzFqS1ZRV0pJclRQbmRycEQyS3VFTGxaMA?oc=5" target="_blank"&gt;TUI flight BY7614 just declared an emergency over France, now diverting to Gatwick&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQUHFQZWVnQUxzaGM5elBRbVFXMm1Vb093UXkwaERMTlZHcEpJN2RPQXU5NVdSUkE4NkF4Y18yaTVkM3dlTk5ZQ2MyOTZoaUlTelI5U0lKWFZVa254RlRWbGN3UVlFaFp2bUp6YVNXdHN5bklDcFlFLXYyUGdVVU1seGltN2RRYjM2bVVFVV9hcHplcHlINVpvbW9TUFM2QzhmbW1wYjVlbHZLR1pBdW4w0gG3AUFVX3lxTFB5OE5EUHhFR2ZDOFQta3pNZTUzcXFfN014NFdPbkxjb0JhM2t2REk2QjBMQ3dBekJKUFl4MVZfWldMZmJYelVjZ21URTVjNDFESmNFeHByOHd3SUg2Z1FiaWNTM0dUeTRvWmV3dXRoSVFUU2x6UnFCMXZCT3ZyRXJ4N1locTRFaGk3UFpPdE5yYWVzZGRXR3pYbVpUMlBPbzFqS1ZRV0pJclRQbmRycEQyS3VFTGxaMA?oc=5</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr"/>
+      <c r="L504" t="inlineStr"/>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O504"/>
+  <dimension ref="A1:O520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30899,7 +30899,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30930,8 +30929,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
-      <c r="L492" t="inlineStr"/>
       <c r="M492" t="inlineStr">
         <is>
           <t>review</t>
@@ -30964,7 +30961,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -30995,8 +30991,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
-      <c r="L493" t="inlineStr"/>
       <c r="M493" t="inlineStr">
         <is>
           <t>review</t>
@@ -31029,7 +31023,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -31060,8 +31053,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
-      <c r="L494" t="inlineStr"/>
       <c r="M494" t="inlineStr">
         <is>
           <t>review</t>
@@ -31094,7 +31085,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -31125,8 +31115,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
-      <c r="L495" t="inlineStr"/>
       <c r="M495" t="inlineStr">
         <is>
           <t>review</t>
@@ -31159,7 +31147,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -31190,8 +31177,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
-      <c r="L496" t="inlineStr"/>
       <c r="M496" t="inlineStr">
         <is>
           <t>review</t>
@@ -31224,7 +31209,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -31255,8 +31239,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
-      <c r="L497" t="inlineStr"/>
       <c r="M497" t="inlineStr">
         <is>
           <t>review</t>
@@ -31289,7 +31271,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -31320,8 +31301,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
-      <c r="L498" t="inlineStr"/>
       <c r="M498" t="inlineStr">
         <is>
           <t>review</t>
@@ -31354,7 +31333,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -31385,8 +31363,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
-      <c r="L499" t="inlineStr"/>
       <c r="M499" t="inlineStr">
         <is>
           <t>review</t>
@@ -31419,7 +31395,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -31450,8 +31425,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
-      <c r="L500" t="inlineStr"/>
       <c r="M500" t="inlineStr">
         <is>
           <t>review</t>
@@ -31484,7 +31457,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -31515,8 +31487,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
-      <c r="L501" t="inlineStr"/>
       <c r="M501" t="inlineStr">
         <is>
           <t>review</t>
@@ -31549,7 +31519,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -31580,8 +31549,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
-      <c r="L502" t="inlineStr"/>
       <c r="M502" t="inlineStr">
         <is>
           <t>review</t>
@@ -31614,7 +31581,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -31645,8 +31611,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
-      <c r="L503" t="inlineStr"/>
       <c r="M503" t="inlineStr">
         <is>
           <t>review</t>
@@ -31679,7 +31643,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -31710,8 +31673,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
-      <c r="L504" t="inlineStr"/>
       <c r="M504" t="inlineStr">
         <is>
           <t>review</t>
@@ -31723,6 +31684,1046 @@
         </is>
       </c>
       <c r="O504" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>auto-ea9e7d38cd37</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>HON Circle: Lufthansa Group streicht weitere Sitzplatzprivilegien für beste Vielfliegende</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr"/>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>Die Lufthansa-Gruppe schränkt die Vorteile für ihre Vielfliegenden mit HON-Circle-Status weiter ein. Ab dem 27. Oktober müssen auch sie bei Buchungen im Economy-Light-Tarif auf interkontinentalen Flügen für eine Sitzplatzreservierung bezahlen. Bislang war diese für HON Circle Member kostenlos.</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/hon-circle-lufthansa-group-streicht-weitere-sitzplatzprivilegien-fuer-beste/1qb31m7</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr"/>
+      <c r="L505" t="inlineStr"/>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>auto-69b7dc1accc8</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Condor sieht trotz Kerosinengpass in Frankfurt keine Einschränkungen</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr"/>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>Die angespannte Kerosinversorgung am Flughafen Frankfurt hat nach Angaben von Condor derzeit keine Auswirkungen auf den Flugbetrieb der Fluggesellschaft. «Condor ist aktuell nicht von der bestehenden Limitierung bei der Kerosinversorgung am Flughafen Frankfurt betroffen», erklärt das Unternehmen. Alle Flüge fänden wie geplant statt, Einschränkungen für Passagiere gebe es nicht.</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/condor-sieht-trotz-kerosinengpass-in-frankfurt-keine-einschraenkungen/4h955l8</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr"/>
+      <c r="L506" t="inlineStr"/>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>auto-5700177224bb</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Nach wiederholten Pannen mit Airbus A330 Neo bei Aircalin wird unabhängige Untersuchung gefordert</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr"/>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>Nach zahlreichen technischen Problemen und Flugausfällen bei Aircalin fordert die neukaledonische Verbraucherschutzorganisation Que choisir ensemble eine unabhängige Untersuchung der Fluggesellschaft. In einem Schreiben vom 13. Oktober verlangt sie ein Treffen mit der Regierung Neukaledoniens, berichtet das Portal France Info.</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/nach-wiederholten-pannen-mit-airbus-a330-neo-bei-aircalin-wird-unabhaengige/j18j8j1</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr"/>
+      <c r="L507" t="inlineStr"/>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>auto-519544c466a9</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Keine Flugstreichungen bei Lufthansa und Condor</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr"/>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Weder Lufthansa noch Condor erwarten Flugstreichungen infolge eines möglichen Kerosinmangels am Drehkreuz Frankfurt.</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53942/Keine-Flugstreichungen-bei-Lufthansa-und-Condor.html</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr"/>
+      <c r="L508" t="inlineStr"/>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>auto-ce6236f05752</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>So erklärt Lufthansa die Logik hinter dem TAP-Deal</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr"/>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Die Lufthansa verspricht sich vom Einstieg bei Portugals Staatsfluglinie TAP Air Portugal deutliche Vorteile. Die jährlichen Synergien dürften sich auf bis zu 450 Millionen Euro belaufen, erklärten Lufthansa-Chef Carsten Spohr und Finanzvorstand Till Streichert am Donnerstag in einer Online-Konferenz mit Analysten.</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53941/So-erklaert-Lufthansa-die-Logik-hinter-dem-TAP-Deal.html</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr"/>
+      <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>auto-68a3cbb10879</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Polen baut Militärbereich am Flughafen Breslau aus</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr"/>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>WARSCHAU - Polen baut die militärlogistische Infrastruktur für US-Streitkräfte am Flughafen Breslau-Strachowice aus.</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53939/Polen-baut-Militaerbereich-am-Flughafen-Breslau-aus.html</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr"/>
+      <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>auto-63ccab0db463</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Airbus sieht Nachfrage für "längere" A350</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr"/>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>TOULOUSE - Airbus taktet die A350-Linie 2028 auf zwölf Flugzeuge pro Monat hoch. Über weitere Ausbaustufen will Airbus "eher früher als später" entscheiden. Der Konzern befasst sich parallel mit einem neuen Topmodell: Airbus erkennt im Markt "Nachfrage" für eine zweifach gestreckte A350-Version.</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53937/Airbus-sieht-Nachfrage-fuer-gestreckte-A350.html</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr"/>
+      <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>auto-212248eda4aa</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Kerosinmangel am Flughafen Frankfurt</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr"/>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa ist am Frankfurter Flughafen mit Kerosinmangel konfrontiert. Piloten sollen jetzt an anderen Flughäfen zusätzlichen Treibstoff tanken und so die Kerosinreserven am Drehkreuz schonen.</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53936/Kerosinmangel-am-Flughafen-Frankfurt.html</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr"/>
+      <c r="L512" t="inlineStr"/>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>auto-f73678452105</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Das haben Lufthansa und Portugal vereinbart</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr"/>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa ist dem Einstieg bei TAP Air Portugal einen entscheidenden Schritt näher. Jetzt werden erste Details bekannt. Lufthansa hat Air France-KLM mit einem 16 Prozent höheren Gebot und Investitionszusagen ausgestochen. Die wichtigsten Fragen und Antworten zum TAP-Deal im Überblick.</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53934/Das-haben-Lufthansa-und-Portugal-vereinbart.html</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr"/>
+      <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>auto-f9125ac957b9</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Lufthansa macht bei TAP Air Portugal das Rennen</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr"/>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>LISSABON - Die portugiesische Regierung treibt die Teilprivatisierung der Staatsairline TAP Air Portugal voran. Im Kampf um knapp die Hälfte der Anteile setzt sich die Lufthansa mit einm Milliardengebot gegen Air France-KLM durch: Lissabon wird zum siebten Konzerndrehkreuz im Lufthansa-System.</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53931/Lufthansa-macht-bei-TAP-Air-Portugal-das-Rennen.html</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr"/>
+      <c r="L514" t="inlineStr"/>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>auto-401f64912339</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Hellenic Air Force F-16 Makes Emergency Landing at Zakynthos Airport After Technical Fault: how 11 outlets framed it - NewsCord</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr"/>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi6gFBVV95cUxNeE9TdkRPZXNSSVZKZXAzYzJmNVZPdUtmNDZpc0dEMDRTTVdnMXljc0hLV1YwenZMWHI0NFFsbmFUSW9leXROamhUWHU4S3gtdUxXdjFLTjVSb0djenAyTzl2dm9UVXRZMkVlajgxWmI0SE9sU2ZkeHVEZUg2dkdIUDU1ck1GS0JoYlJmQ1pJMDl1NGhpRTFMdmpVZGhuZjJmYjh3X3R6UWhuaDBGX1VrOWg4R2hkUm0xallsQjBiNGs2ZXlZUTNUMlFKdE9xdXBhekViMU0zODJFbDNGM2dyMlBXaTBSNlpSNUE?oc=5" target="_blank"&gt;Hellenic Air Force F-16 Makes Emergency Landing at Zakynthos Airport After Technical Fault: how 11 outlets framed it&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;NewsCord&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNeE9TdkRPZXNSSVZKZXAzYzJmNVZPdUtmNDZpc0dEMDRTTVdnMXljc0hLV1YwenZMWHI0NFFsbmFUSW9leXROamhUWHU4S3gtdUxXdjFLTjVSb0djenAyTzl2dm9UVXRZMkVlajgxWmI0SE9sU2ZkeHVEZUg2dkdIUDU1ck1GS0JoYlJmQ1pJMDl1NGhpRTFMdmpVZGhuZjJmYjh3X3R6UWhuaDBGX1VrOWg4R2hkUm0xallsQjBiNGs2ZXlZUTNUMlFKdE9xdXBhekViMU0zODJFbDNGM2dyMlBXaTBSNlpSNUE?oc=5</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr"/>
+      <c r="L515" t="inlineStr"/>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>auto-8b8d3adbc152</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Air France flight AF158 to DFW turned around over Atlantic, crew declaring an emergency - airlive</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr"/>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiywFBVV95cUxPM0Z5UTBBY0lZTnNoNWhnbjQ5ZVZpOXExeFNIQXVCUi1YNGNDakUzYzAySzR3NW91d0VDSjRQM2RBRGUyRGVWTWlTa0pucVg4d04zZmdzSkpUbjJ3QTRZOXUzOE5Tb0NuU3RrWHN4QUhyTnpjdHBidHoxNDJETkpZUVBEaDlvckh3SDZ5bF9SbVVLbW12T1JuUVBlY0g1VXAwUWxwRVp0SS1Tc0lnTlBZa0VfTVBnWU1uaWdsZElRaXhsck9raEhxV0dDSdIB0wFBVV95cUxOUDBQdDlGa1FobjFXUVktaTVhTEwxMHBvdXYzU3huR3NNTVFZbUpKU0w1M1A2YzNvd0NZZURYY09BRUtaWVB6X0VZMHNwMHllOUNlU3BnQnFqZVd3NWRYdDJWVlJHajJyWDNvdUs4UXhneHhGaG5mOHlMTVlWZjkwQ3RyT3o5MVdsQm5YZVc4UkN3NzRpcFRPUkhTVWxLeVVMYlE0Mmw0Q0pRYW5zaEhaS1NXRFhHNHItcDRvb2UzQmp4bWs5Ykh2bjJkRjRGY1Z3YWY0?oc=5" target="_blank"&gt;Air France flight AF158 to DFW turned around over Atlantic, crew declaring an emergency&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPM0Z5UTBBY0lZTnNoNWhnbjQ5ZVZpOXExeFNIQXVCUi1YNGNDakUzYzAySzR3NW91d0VDSjRQM2RBRGUyRGVWTWlTa0pucVg4d04zZmdzSkpUbjJ3QTRZOXUzOE5Tb0NuU3RrWHN4QUhyTnpjdHBidHoxNDJETkpZUVBEaDlvckh3SDZ5bF9SbVVLbW12T1JuUVBlY0g1VXAwUWxwRVp0SS1Tc0lnTlBZa0VfTVBnWU1uaWdsZElRaXhsck9raEhxV0dDSdIB0wFBVV95cUxOUDBQdDlGa1FobjFXUVktaTVhTEwxMHBvdXYzU3huR3NNTVFZbUpKU0w1M1A2YzNvd0NZZURYY09BRUtaWVB6X0VZMHNwMHllOUNlU3BnQnFqZVd3NWRYdDJWVlJHajJyWDNvdUs4UXhneHhGaG5mOHlMTVlWZjkwQ3RyT3o5MVdsQm5YZVc4UkN3NzRpcFRPUkhTVWxLeVVMYlE0Mmw0Q0pRYW5zaEhaS1NXRFhHNHItcDRvb2UzQmp4bWs5Ykh2bjJkRjRGY1Z3YWY0?oc=5</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr"/>
+      <c r="L516" t="inlineStr"/>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>auto-a9bc8f47a0e1</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Delta flight from Copenhagen to JFK diverted to Paris and declared emergency for priority landing - airlive</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr"/>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi3AFBVV95cUxOLU5pbkx3Qmx3QTBHSFZDaDVkU1daVG90VGdBMkRwdklKT2VxRFJnNUtYcDBIaF83Qk1Rbmt4MjU3Z0hlM2ZVdlNuRkJWeXhZZktSVGFJRmJobjE0WjZTSW5yeEFPWVo3anRjUlJBcG42Nlp2REJOVFZnS3JtdDliVWQzbWo1c3VLUWdzN2JDeUNlSzZkNzF2Sk16SkpuLTB4QWRFOHNGNW10WjcyeEFraUNPcTBLQTVhbDhFN0YyZzROM2JFeEdLTTFCTVExbnNUR1B0YlEwaDdHdHZD0gHkAUFVX3lxTE92QTFMU0JvbjdPU0VZeEtYcTMweVltWFQ2TGdYelNST2c0ZVozb0d1VWxnRnZtQ041T0FxRENmWWhINmFwR0QxekgwbHVreXBwWHFfVk95MW5FazFXOVBfOXBDOFhWcnQ3Ml91T0NvckZmV0ZNeTNVNktpb1RLeTZ1YnFfanBIOXQyUlRmSjRWUG5pS3JaNVpFd0ZaWGUwNmZYRFhHUW9KSW1fY3BEOVBOU0hkMWlONFI3NlV3R3NBUVlvYlBhTVJ1b01qS0ZlT3lWWFVHNk1BeDdnTi16ZVJMZU1TTw?oc=5" target="_blank"&gt;Delta flight from Copenhagen to JFK diverted to Paris and declared emergency for priority landing&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOLU5pbkx3Qmx3QTBHSFZDaDVkU1daVG90VGdBMkRwdklKT2VxRFJnNUtYcDBIaF83Qk1Rbmt4MjU3Z0hlM2ZVdlNuRkJWeXhZZktSVGFJRmJobjE0WjZTSW5yeEFPWVo3anRjUlJBcG42Nlp2REJOVFZnS3JtdDliVWQzbWo1c3VLUWdzN2JDeUNlSzZkNzF2Sk16SkpuLTB4QWRFOHNGNW10WjcyeEFraUNPcTBLQTVhbDhFN0YyZzROM2JFeEdLTTFCTVExbnNUR1B0YlEwaDdHdHZD0gHkAUFVX3lxTE92QTFMU0JvbjdPU0VZeEtYcTMweVltWFQ2TGdYelNST2c0ZVozb0d1VWxnRnZtQ041T0FxRENmWWhINmFwR0QxekgwbHVreXBwWHFfVk95MW5FazFXOVBfOXBDOFhWcnQ3Ml91T0NvckZmV0ZNeTNVNktpb1RLeTZ1YnFfanBIOXQyUlRmSjRWUG5pS3JaNVpFd0ZaWGUwNmZYRFhHUW9KSW1fY3BEOVBOU0hkMWlONFI3NlV3R3NBUVlvYlBhTVJ1b01qS0ZlT3lWWFVHNk1BeDdnTi16ZVJMZU1TTw?oc=5</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr"/>
+      <c r="L517" t="inlineStr"/>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>auto-9058ba663373</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Air France flight AF1750 to Copenhagen declared an emergency and just diverted to Amsterdam - airlive</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr"/>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMizgFBVV95cUxPeXN3RFJBMFJKQmxNMGptc1ZzT3VLOVF5SU1zb1RjVXExb203MTFldHN6RmhXdlhhd0pPb08tN3pFdkJiSnhtMG91TE1aR25sSGRzT0t6RU80LXZaTmNmdFZDMWVybE9hcjRQZnFsT3NLVExLZ0NYUEVuSENvSUZEckhjQ1VmajFuLWY2am8xVXYzSmJiNzFYVjVrNF9TZlkzRFNTSjZKMTRlR0pzZUtva2xPMUIxVDEyT3ZiTTJ4WkUyajNKalR4RDl6aVRMUdIB1gFBVV95cUxQNzhISFE4UWlWX0JjejN5MWk1SXRxQjN5cTJNZnItZ1VkbFNVUDJUaGYzSVZXUVRWU19FcWw3djV1U2VHNTg2d3lSYkFXQzJiWkpuZWNWMk9pbTk4S1BhRVM0XzdEZC1abVFPak1ENTRzR1YybnY3dW5kVGdmeTItQm9fUktHaGRNZ1hlYjJmM3B2WTlWSDhLOUtvekZZS04zR0IzWjNIVlFMZEliUXNNYk5RdTI5Y2h4Rmg3S2JueWxheWI1Q0VOakZIWTludHAxYWp3ZzB3?oc=5" target="_blank"&gt;Air France flight AF1750 to Copenhagen declared an emergency and just diverted to Amsterdam&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPeXN3RFJBMFJKQmxNMGptc1ZzT3VLOVF5SU1zb1RjVXExb203MTFldHN6RmhXdlhhd0pPb08tN3pFdkJiSnhtMG91TE1aR25sSGRzT0t6RU80LXZaTmNmdFZDMWVybE9hcjRQZnFsT3NLVExLZ0NYUEVuSENvSUZEckhjQ1VmajFuLWY2am8xVXYzSmJiNzFYVjVrNF9TZlkzRFNTSjZKMTRlR0pzZUtva2xPMUIxVDEyT3ZiTTJ4WkUyajNKalR4RDl6aVRMUdIB1gFBVV95cUxQNzhISFE4UWlWX0JjejN5MWk1SXRxQjN5cTJNZnItZ1VkbFNVUDJUaGYzSVZXUVRWU19FcWw3djV1U2VHNTg2d3lSYkFXQzJiWkpuZWNWMk9pbTk4S1BhRVM0XzdEZC1abVFPak1ENTRzR1YybnY3dW5kVGdmeTItQm9fUktHaGRNZ1hlYjJmM3B2WTlWSDhLOUtvekZZS04zR0IzWjNIVlFMZEliUXNNYk5RdTI5Y2h4Rmg3S2JueWxheWI1Q0VOakZIWTludHAxYWp3ZzB3?oc=5</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr"/>
+      <c r="L518" t="inlineStr"/>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>auto-5ea4843141eb</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Delta A330 engine fire forces emergency landing - Airline Ratings</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr"/>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMikAFBVV95cUxOd19fS0pFN0tpTGx4Y1AxTEpLTkNFbWdzYnhfT2Jkb1g0NWdrUVR3ZDVNcXhGcWtUZzdoTTRjQmNyaDY1U1dWay11dkRCNS1qTG5xSVFXWnVnWjRDc29tWjY1QUhLN21hYXhmbEtoZkZiZzRSZ2NGeEw3QklVX1JBOHdNVnF3b2dWbDNWWWdKLUk?oc=5" target="_blank"&gt;Delta A330 engine fire forces emergency landing&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Airline Ratings&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOd19fS0pFN0tpTGx4Y1AxTEpLTkNFbWdzYnhfT2Jkb1g0NWdrUVR3ZDVNcXhGcWtUZzdoTTRjQmNyaDY1U1dWay11dkRCNS1qTG5xSVFXWnVnWjRDc29tWjY1QUhLN21hYXhmbEtoZkZiZzRSZ2NGeEw3QklVX1JBOHdNVnF3b2dWbDNWWWdKLUk?oc=5</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr"/>
+      <c r="L519" t="inlineStr"/>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>auto-6b9e19c8a359</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>SAS flight SK1684 to Copenhagen made an emergency landing in Zurich - airlive</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr"/>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirAFBVV95cUxOamRwcktDeDdzbFFuSE44dTFZZzZRZDBfcWNDdXFrX3NLQ3pyWGNRYXBvX0JHamZQQkVyaVhfUHM1anVSY1RTalRKeDJhbEhyTF9qTU04ODNSZEVjNjFseFFtMThVaGliOUxaMUtKMFB5d2xaa3hrMzJrZHNkM253NTFzWTJJdlh4WUdyUzlVc25qTVBvSkUyek9kU1VJcTJUTU5kLXRxTU1TbndX0gG0AUFVX3lxTFBydUdScVBtOWNzblp1bUw1aU4zckdndnprSllubUEyOVd0TmhSSU91TC1IVnBrMWRCRERtVnJTTGpvcDBwZzdRWkc2NXVuV1pmak5aYXdTM2V6NDVuRkc4N25DYV9qWl9Ec1pNMmRlUURycThGVnY2UEhFTExkUkJBRnFaSndvckszRGU3MGdhNmp1eVEtQk15bC1oTFdYRGEzZmtyeExrZ3VFaFRjaHhiV1VTQw?oc=5" target="_blank"&gt;SAS flight SK1684 to Copenhagen made an emergency landing in Zurich&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOamRwcktDeDdzbFFuSE44dTFZZzZRZDBfcWNDdXFrX3NLQ3pyWGNRYXBvX0JHamZQQkVyaVhfUHM1anVSY1RTalRKeDJhbEhyTF9qTU04ODNSZEVjNjFseFFtMThVaGliOUxaMUtKMFB5d2xaa3hrMzJrZHNkM253NTFzWTJJdlh4WUdyUzlVc25qTVBvSkUyek9kU1VJcTJUTU5kLXRxTU1TbndX0gG0AUFVX3lxTFBydUdScVBtOWNzblp1bUw1aU4zckdndnprSllubUEyOVd0TmhSSU91TC1IVnBrMWRCRERtVnJTTGpvcDBwZzdRWkc2NXVuV1pmak5aYXdTM2V6NDVuRkc4N25DYV9qWl9Ec1pNMmRlUURycThGVnY2UEhFTExkUkJBRnFaSndvckszRGU3MGdhNmp1eVEtQk15bC1oTFdYRGEzZmtyeExrZ3VFaFRjaHhiV1VTQw?oc=5</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr"/>
+      <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O520"/>
+  <dimension ref="A1:O525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31705,7 +31705,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -31736,8 +31735,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
-      <c r="L505" t="inlineStr"/>
       <c r="M505" t="inlineStr">
         <is>
           <t>review</t>
@@ -31770,7 +31767,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -31801,8 +31797,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
-      <c r="L506" t="inlineStr"/>
       <c r="M506" t="inlineStr">
         <is>
           <t>review</t>
@@ -31835,7 +31829,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -31866,8 +31859,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
-      <c r="L507" t="inlineStr"/>
       <c r="M507" t="inlineStr">
         <is>
           <t>review</t>
@@ -31900,7 +31891,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -31931,8 +31921,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
-      <c r="L508" t="inlineStr"/>
       <c r="M508" t="inlineStr">
         <is>
           <t>review</t>
@@ -31965,7 +31953,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -31996,8 +31983,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
-      <c r="L509" t="inlineStr"/>
       <c r="M509" t="inlineStr">
         <is>
           <t>review</t>
@@ -32030,7 +32015,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -32061,8 +32045,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
-      <c r="L510" t="inlineStr"/>
       <c r="M510" t="inlineStr">
         <is>
           <t>review</t>
@@ -32095,7 +32077,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -32126,8 +32107,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
-      <c r="L511" t="inlineStr"/>
       <c r="M511" t="inlineStr">
         <is>
           <t>review</t>
@@ -32160,7 +32139,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
       <c r="E512" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -32191,8 +32169,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
-      <c r="L512" t="inlineStr"/>
       <c r="M512" t="inlineStr">
         <is>
           <t>review</t>
@@ -32225,7 +32201,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -32256,8 +32231,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
-      <c r="L513" t="inlineStr"/>
       <c r="M513" t="inlineStr">
         <is>
           <t>review</t>
@@ -32290,7 +32263,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr"/>
       <c r="E514" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -32321,8 +32293,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
-      <c r="L514" t="inlineStr"/>
       <c r="M514" t="inlineStr">
         <is>
           <t>review</t>
@@ -32355,7 +32325,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
       <c r="E515" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -32386,8 +32355,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
-      <c r="L515" t="inlineStr"/>
       <c r="M515" t="inlineStr">
         <is>
           <t>review</t>
@@ -32420,7 +32387,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr"/>
       <c r="E516" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -32451,8 +32417,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
-      <c r="L516" t="inlineStr"/>
       <c r="M516" t="inlineStr">
         <is>
           <t>review</t>
@@ -32485,7 +32449,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr"/>
       <c r="E517" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -32516,8 +32479,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
-      <c r="L517" t="inlineStr"/>
       <c r="M517" t="inlineStr">
         <is>
           <t>review</t>
@@ -32550,7 +32511,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D518" t="inlineStr"/>
       <c r="E518" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -32581,8 +32541,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
-      <c r="L518" t="inlineStr"/>
       <c r="M518" t="inlineStr">
         <is>
           <t>review</t>
@@ -32615,7 +32573,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
       <c r="E519" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -32646,8 +32603,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
-      <c r="L519" t="inlineStr"/>
       <c r="M519" t="inlineStr">
         <is>
           <t>review</t>
@@ -32680,7 +32635,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -32711,8 +32665,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
-      <c r="L520" t="inlineStr"/>
       <c r="M520" t="inlineStr">
         <is>
           <t>review</t>
@@ -32724,6 +32676,331 @@
         </is>
       </c>
       <c r="O520" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>auto-16016bd0dfac</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Lot-Mutterkonzern PGL plant eigene Flotte von Frachtflugzeugen</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr"/>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>Die polnische Luftfahrtgruppe Polska Grupa Lotnicza PGL)hat eine neue Strategie für die Jahre 2026 bis 2032 mit einem Ausblick bis 2035 verabschiedet. Der Mutterkonzern von Lot Polish Airlines will seine sechs Tochtergesellschaften enger miteinander verzahnen und neue Geschäftsfelder erschließen.</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lot-mutterkonzern-pgl-plant-eigene-flotte-von-frachtflugzeugen/tyrdw8p</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr"/>
+      <c r="L521" t="inlineStr"/>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>auto-ca45bf1d8391</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Swiss schickt Flugzeuge mit volleren Tanks nach Frankfurt</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr"/>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Dem Flughafen Frankfurt steht weniger Kerosin zur Verfügung als sonst. Lufthansa-Crews tanken vorübergehend an anderen Flughäfen mehr. Nach Informationen von aero.de wendet auch Swiss "Tankering"-Strategien auf Frankfurt-Linien an, um die dortigen Reserven zu schonen.</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53950/Swiss-schickt-Flugzeuge-mit-volleren-Tanks-nach-Frankfurt.html</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr"/>
+      <c r="L522" t="inlineStr"/>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>auto-ea99489c790a</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Schweiz zapft Kerosinreserven an</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr"/>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>ZÜRICH - Nach Versorgungsengpässen Frankfurt stockt auch am Flughafen Zürich der Kerosinnachschub. Die Schweiz öffnet nun die Lager.</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53945/Schweiz-zapft-Kerosinreserven-an.html</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr"/>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>auto-d4047d344de1</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Lufthansa Cargo bedient Europaziele weiter mit Boeing 777F</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr"/>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Schwerpunkt Asien: Lufthansa Cargo fliegt im Winter 2026/2027 öfter nach Fernost. Im Europanetz plant Lufthansa Cargo weiter ohne die seit einem halben Jahr stillgelegten A321F. Der zunächst provisorische 777F-Einsatz auf drei Europalinien verfestigt sich im Winter 2026/2027 zu einem "Regelflugplan".</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53913/Lufthansa-Cargo-bedient-Europaziele-weiter-mit-Boeing-777F.html</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>auto-340db25e8072</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Keine Einschränkung bei Kerosinversorung</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr"/>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>MÜNCHEN - Pipelines und Pegelstände: Lufthansa plagen in Frankfurt Kerosinsorgen - in der Herbstferienzeit muss das Drehkreuz mit seinen Spritreserven haushalten. Der Konzern reagiert, Piloten bringen jetzt Spirt von anderen Flughäfen mit nach Frankfurt. Wie sieht die Lage in München aus?</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53940/Flughafen-Muenchen-Kerosinversorgung.html</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr"/>
+      <c r="L525" t="inlineStr"/>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O525"/>
+  <dimension ref="A1:O530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32697,7 +32697,6 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr"/>
       <c r="E521" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -32728,8 +32727,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
-      <c r="L521" t="inlineStr"/>
       <c r="M521" t="inlineStr">
         <is>
           <t>review</t>
@@ -32762,7 +32759,6 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr"/>
       <c r="E522" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -32793,8 +32789,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
-      <c r="L522" t="inlineStr"/>
       <c r="M522" t="inlineStr">
         <is>
           <t>review</t>
@@ -32827,7 +32821,6 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr"/>
       <c r="E523" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -32858,8 +32851,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
-      <c r="L523" t="inlineStr"/>
       <c r="M523" t="inlineStr">
         <is>
           <t>review</t>
@@ -32892,7 +32883,6 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr"/>
       <c r="E524" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -32923,8 +32913,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
-      <c r="L524" t="inlineStr"/>
       <c r="M524" t="inlineStr">
         <is>
           <t>review</t>
@@ -32957,7 +32945,6 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
       <c r="E525" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -32988,8 +32975,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
-      <c r="L525" t="inlineStr"/>
       <c r="M525" t="inlineStr">
         <is>
           <t>review</t>
@@ -33001,6 +32986,331 @@
         </is>
       </c>
       <c r="O525" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>auto-8ced8a2732e6</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt erhält 8,7 Millionen Euro für emissionsfreie Bodenversorgung</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr"/>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>Der Flughafen Frankfurt erhält vom Bundesverkehrsministerium rund 8,7 Millionen Euro Fördermittel für die Modernisierung seiner Bodenversorgung. Bis 2030 sollen alle 252 Flugzeugparkpositionen entweder über einen festen Stromanschluss oder batterieelektrische Bodenstromaggregate verfügen. Damit sollen dieselbetriebene Aggregate ersetzt werden.</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flughafen-frankfurt-erhaelt-87-millionen-euro-fuer-emissionsfreie-bodenversorgung/ygtgz8f</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr"/>
+      <c r="L526" t="inlineStr"/>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>auto-256e8236e6e5</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Lufthansa schickt Airbus A340-600 auf letzten Linienflug</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr"/>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Rekordbrecher, Klimaforscher, Star-Alliance-Botschafter, Fanflieger: Der Airbus A340-600 zählt zu den schillernsten Lufthansa-Interkontflugzeugen. Nun beendet der "Lange" mit einem letzten Transatlantik-Umlauf seine Zeit beim Kranich. Die kürzere A340-300 braucht Lufthansa auch 2027 noch in Frankfurt.</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53927/Lufthansa-schickt-Airbus-A340-600-auf-letzten-Linienflug.html</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr"/>
+      <c r="L527" t="inlineStr"/>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>auto-c4b8c43f4945</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Lufthansa erwägt Verkauf von Software-Geschäftsteilen</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr"/>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Die Lufthansa prüft einem Pressebericht zufolge den Verkauf eines Teils ihres Software-Geschäfts. Eine Transaktion könne ein Volumen von nahezu einer Milliarde Euro haben, berichtet die "Financial Times" (FT) am Freitag unter Berufung auf mit der Situation vertraute Personen.</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53954/Lufthansa-erwaegt-Verkauf-von-Software-Geschaeftsteilen.html</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr"/>
+      <c r="L528" t="inlineStr"/>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>auto-223c3461a54b</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Who are the mystery pilots who successfully landed endangered Flydubai flight 1073? - France 24</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr"/>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiywFBVV95cUxPQjRjTzZob3RzSWFfTFY0MkY5ZEJEdmExM3YyWVRhS2dESU5lTEhyU3VWcnV2TTFyb1k4Rm9nY05WcjBHejU2MERjT2ZxSk5VUVZiZzVKNk5jWDJYMG9JYl9wMmZpNFJZTUlyc2NXa1MxN1MxTEUyT0E5Um5Nc2hpOFE3TGZ1ZlI1c2tTM0RZbkI0UmJ2Yk9ZYWZtMUlibDdwcm5UOTFETTA2bEpCdktWM1c1eHhiZDZXWmZzYXVtNE5ucnF4UWhUMDJJZw?oc=5" target="_blank"&gt;Who are the mystery pilots who successfully landed endangered Flydubai flight 1073?&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;France 24&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPQjRjTzZob3RzSWFfTFY0MkY5ZEJEdmExM3YyWVRhS2dESU5lTEhyU3VWcnV2TTFyb1k4Rm9nY05WcjBHejU2MERjT2ZxSk5VUVZiZzVKNk5jWDJYMG9JYl9wMmZpNFJZTUlyc2NXa1MxN1MxTEUyT0E5Um5Nc2hpOFE3TGZ1ZlI1c2tTM0RZbkI0UmJ2Yk9ZYWZtMUlibDdwcm5UOTFETTA2bEpCdktWM1c1eHhiZDZXWmZzYXVtNE5ucnF4UWhUMDJJZw?oc=5</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr"/>
+      <c r="L529" t="inlineStr"/>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>auto-93d7468b34a9</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>United flight UA957 is declaring an emergency and returning to Geneva - airlive</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr"/>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMisAFBVV95cUxPcUlBYzZFbktodkhMWlo2b3NxMUFNNEJXazhSVkdLbmtfSjl4Znh6X2NQeTV4R3UtZEpYb2pUdVVqVWhSYjFBa01TSEYtVU5FUC03VTNKOEI0cjF2cDlJUjJER01wYWVWNEpFSllNMWZTdExHNUtFYTIydGxOY2RoOVRVcTljaDZfQlFCZ2hieWZIMUlwZmsyQWxScFN4UEJoVWxsS01TNkI2cnBjZGhtLdIBuAFBVV95cUxOVTk5akkxM2pybm5WU0dNQmx4VTdWOUpNTGdmcnhkTTNBUmROd09FczgyOUQ3Uk1zWEpuTXg5cTlYSVdQWWVKVDVkWlVFV05zaDFiWUtOZEphRmxZV1ZIbnBMSW9Mc2RPbHh1bDlxekFqamFMYzVGTm5FZEo1dmhES3JrNU9mRmVsZjgyR0dXc3k1NzY3LUxRRkRNZWZZTHpzdlhqZm9fNVNXUXdybFRaUzR0ODExYTRU?oc=5" target="_blank"&gt;United flight UA957 is declaring an emergency and returning to Geneva&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPcUlBYzZFbktodkhMWlo2b3NxMUFNNEJXazhSVkdLbmtfSjl4Znh6X2NQeTV4R3UtZEpYb2pUdVVqVWhSYjFBa01TSEYtVU5FUC03VTNKOEI0cjF2cDlJUjJER01wYWVWNEpFSllNMWZTdExHNUtFYTIydGxOY2RoOVRVcTljaDZfQlFCZ2hieWZIMUlwZmsyQWxScFN4UEJoVWxsS01TNkI2cnBjZGhtLdIBuAFBVV95cUxOVTk5akkxM2pybm5WU0dNQmx4VTdWOUpNTGdmcnhkTTNBUmROd09FczgyOUQ3Uk1zWEpuTXg5cTlYSVdQWWVKVDVkWlVFV05zaDFiWUtOZEphRmxZV1ZIbnBMSW9Mc2RPbHh1bDlxekFqamFMYzVGTm5FZEo1dmhES3JrNU9mRmVsZjgyR0dXc3k1NzY3LUxRRkRNZWZZTHpzdlhqZm9fNVNXUXdybFRaUzR0ODExYTRU?oc=5</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr"/>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O530"/>
+  <dimension ref="A1:O533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33007,7 +33007,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr"/>
       <c r="E526" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -33038,8 +33037,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
-      <c r="L526" t="inlineStr"/>
       <c r="M526" t="inlineStr">
         <is>
           <t>review</t>
@@ -33072,7 +33069,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -33103,8 +33099,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
-      <c r="L527" t="inlineStr"/>
       <c r="M527" t="inlineStr">
         <is>
           <t>review</t>
@@ -33137,7 +33131,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -33168,8 +33161,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
-      <c r="L528" t="inlineStr"/>
       <c r="M528" t="inlineStr">
         <is>
           <t>review</t>
@@ -33202,7 +33193,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -33233,8 +33223,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
-      <c r="L529" t="inlineStr"/>
       <c r="M529" t="inlineStr">
         <is>
           <t>review</t>
@@ -33267,7 +33255,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -33298,8 +33285,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
-      <c r="L530" t="inlineStr"/>
       <c r="M530" t="inlineStr">
         <is>
           <t>review</t>
@@ -33311,6 +33296,201 @@
         </is>
       </c>
       <c r="O530" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>auto-593240fcbbbb</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Fünf Airlines operieren A380 nach FRA - Austrian Wings</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr"/>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMihAFBVV95cUxOLW5nd05NdWxiVF8tYkFKZ3FXQkdzaG1zaWtTYzRqN0owT2Nad0dIdkExaldBYlhjNWR0VGkyeDFiSWxYV204anNfcWpvSElBbjRHYjBtbVF6c1Y0RWJoOHNNNGVyTlpoUFJXdXh3SXFGT0QzeHh3TEw3TEJZbmhudlBPbHQ?oc=5" target="_blank"&gt;Fünf Airlines operieren A380 nach FRA&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Austrian Wings&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOLW5nd05NdWxiVF8tYkFKZ3FXQkdzaG1zaWtTYzRqN0owT2Nad0dIdkExaldBYlhjNWR0VGkyeDFiSWxYV204anNfcWpvSElBbjRHYjBtbVF6c1Y0RWJoOHNNNGVyTlpoUFJXdXh3SXFGT0QzeHh3TEw3TEJZbmhudlBPbHQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr"/>
+      <c r="L531" t="inlineStr"/>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>auto-1ac050bf8438</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Emergency: Delta flight DL251 to Boston turned around over Atlantic and diverted to Porto - airlive</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr"/>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiygFBVV95cUxOMGo0U3NvUjA3TlVfdTcxdTlBclhTZndxWEVMSV9wdjZHTVl6Qzh1d0ZRb2djcThUUXhqb0d6ZzBVRDctdlJkRkxuVXdKZHBlMnZaZzdzdmc4QU9FazF1WUpaRW9EenBPcjIzRlFUTEFWMnFRelEtYVJDYVplT2VudUkwYVNxOFVSZmdSeC1KMjB6eDJQM2VKZnJDMmVFSkZZRjR0a3o5cHZpeDNhRGZFVlJCbFdEYmZoMHFfRGZyYWQwNWFrNXBvRl9B0gHSAUFVX3lxTE00eDViOEpzMjBmR3Z1TnJLYkNVMjNnTU9HU2ZLRE9MTFBJdnJNbGl6UkprbkpIcGp0UjBTaEd2OG1xT0lJT1lScTlWVnNOYXplckI2ZVduNDJqU0pEREFjcmZudG8xc0tmdk5LS05YQUVSQXpfTUs3aFZnUHN1ZkRXb09lLXFEeU9zcGtNREZHYU1pMXBkai1KaGxVcjl3ak1Jazh2QWcwS3pTQnF4OG4xOTBFbW9KYXRMalNrSXhNZ0pnbjd2d1J2QUFrV1F4VVdDUQ?oc=5" target="_blank"&gt;Emergency: Delta flight DL251 to Boston turned around over Atlantic and diverted to Porto&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMGo0U3NvUjA3TlVfdTcxdTlBclhTZndxWEVMSV9wdjZHTVl6Qzh1d0ZRb2djcThUUXhqb0d6ZzBVRDctdlJkRkxuVXdKZHBlMnZaZzdzdmc4QU9FazF1WUpaRW9EenBPcjIzRlFUTEFWMnFRelEtYVJDYVplT2VudUkwYVNxOFVSZmdSeC1KMjB6eDJQM2VKZnJDMmVFSkZZRjR0a3o5cHZpeDNhRGZFVlJCbFdEYmZoMHFfRGZyYWQwNWFrNXBvRl9B0gHSAUFVX3lxTE00eDViOEpzMjBmR3Z1TnJLYkNVMjNnTU9HU2ZLRE9MTFBJdnJNbGl6UkprbkpIcGp0UjBTaEd2OG1xT0lJT1lScTlWVnNOYXplckI2ZVduNDJqU0pEREFjcmZudG8xc0tmdk5LS05YQUVSQXpfTUs3aFZnUHN1ZkRXb09lLXFEeU9zcGtNREZHYU1pMXBkai1KaGxVcjl3ak1Jazh2QWcwS3pTQnF4OG4xOTBFbW9KYXRMalNrSXhNZ0pnbjd2d1J2QUFrV1F4VVdDUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr"/>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>auto-43dfb7967c2e</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Lufthansa LH470 to Toronto declared an emergency and diverted to Manchester - airlive</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr"/>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiuAFBVV95cUxOMUNtX0diMHhvYzJLMjNPT3Jmd0lvWEg4RnpXcVAxU3lUcVRJVnRNUFYxOXVPZWp4UkZHTFp4RmhIaFJKSEhSbENabGJ3aHFyRGtsTzJKYU5pMGVnand2T1NKUzUxZkFGM2JQV1Jod2d2clFTeUd6NWJZWEZWZ0tncGJIWXJ2WXM1QXRiTE5XVV95MjI3cGhLSk5aY2JGUnFvdTNESzVzZVJ2UzJ3czMyWms2cHlKSUN40gHAAUFVX3lxTE5IOW1LZm41aFQ3WXRBZ3JLVUJhZkh6SExjUEdaT1dQdEpNSzJCTHZKaXMyeXdKRXZHNmFweHhqMmdPMGFSZzRWNUFPc2hrZEUzUVFwMExSNWktVTNuVWp1RlV6aGpaT3F5cnhtb2FOdjBRRk5oUDNxNm9VZ2lyYmxSaUEtMFZ0aVpCYU5ndE5EVGVPNko4Zjh1WlVtWmRUeTQtQVp5cnhsdzJFVUI2SDk1Nl9OSGExZ1hXeWtCNXFCZQ?oc=5" target="_blank"&gt;Lufthansa LH470 to Toronto declared an emergency and diverted to Manchester&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOMUNtX0diMHhvYzJLMjNPT3Jmd0lvWEg4RnpXcVAxU3lUcVRJVnRNUFYxOXVPZWp4UkZHTFp4RmhIaFJKSEhSbENabGJ3aHFyRGtsTzJKYU5pMGVnand2T1NKUzUxZkFGM2JQV1Jod2d2clFTeUd6NWJZWEZWZ0tncGJIWXJ2WXM1QXRiTE5XVV95MjI3cGhLSk5aY2JGUnFvdTNESzVzZVJ2UzJ3czMyWms2cHlKSUN40gHAAUFVX3lxTE5IOW1LZm41aFQ3WXRBZ3JLVUJhZkh6SExjUEdaT1dQdEpNSzJCTHZKaXMyeXdKRXZHNmFweHhqMmdPMGFSZzRWNUFPc2hrZEUzUVFwMExSNWktVTNuVWp1RlV6aGpaT3F5cnhtb2FOdjBRRk5oUDNxNm9VZ2lyYmxSaUEtMFZ0aVpCYU5ndE5EVGVPNko4Zjh1WlVtWmRUeTQtQVp5cnhsdzJFVUI2SDk1Nl9OSGExZ1hXeWtCNXFCZQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr"/>
+      <c r="L533" t="inlineStr"/>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O533"/>
+  <dimension ref="A1:O543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33317,7 +33317,6 @@
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -33348,8 +33347,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
-      <c r="L531" t="inlineStr"/>
       <c r="M531" t="inlineStr">
         <is>
           <t>review</t>
@@ -33382,7 +33379,6 @@
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -33413,8 +33409,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
-      <c r="L532" t="inlineStr"/>
       <c r="M532" t="inlineStr">
         <is>
           <t>review</t>
@@ -33447,7 +33441,6 @@
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -33478,8 +33471,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
-      <c r="L533" t="inlineStr"/>
       <c r="M533" t="inlineStr">
         <is>
           <t>review</t>
@@ -33491,6 +33482,656 @@
         </is>
       </c>
       <c r="O533" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>auto-a66d68d8ed02</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Das war der letzte Flug des Airbus A340-600 für Lufthansa</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr"/>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>Nach 23 Jahren hat Lufthansa ihren letzten regulären Flug mit einem Airbus A340-600 absolviert. Am Steuer saß Konzernvorstand Francesco Sciortino. Es war ein emotionaler Abschied von einem Flugzeug, das für viele etwas Besonderes war - aber einfach nicht mehr mit den moderneren Modellen mithalten kann.</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugzeuge/lufthansa-flug-lh419-das-war-der-letzte-einsatz-des-airbus-a340-600/0nwcfx3</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr"/>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>auto-aece6f08e322</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Swiss hält an Wiederaufnahme der Dubai-Flüge fest</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr"/>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>Swiss plant weiterhin, ihre Flüge zwischen Zürich und Dubai am 27. Oktober wieder aufzunehmen. Ab diesem Datum soll die Verbindung erneut täglich bedient werden. Angesichts der angespannten Sicherheitslage überprüft die Fluggesellschaft die Situation nach eigenen Angaben laufend gemeinsam mit den Sicherheitsfachleuten von Lufthansa Group. Noch offen ist, welche Flugroute die Flugzeuge künftig nehmen werden. «Die Routenführung ist derzeit in Planung», erklärte Swiss.</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/swiss-haelt-an-wiederaufnahme-der-dubai-fluege-fest/2fbh1se</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr"/>
+      <c r="L535" t="inlineStr"/>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>auto-afeb4eb43b50</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Lufthansa startet großen Kehraus in der Interkontflotte</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr"/>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa schließt das Kapitel A340-600. Der letzte Linienflug, LH419 aus Washington, besiegelte am Montagmorgen in Frankfurt das zuletzt hinausgezögerte Flottenaus des Vierstrahlers. Lufthansa räumt in der Interkontflotte auf - bis Ende 2027 verlassen noch vier weitere Teilflotten den Konzern.</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53965/Lufthansa-Airbus-A340-600-2.html</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr"/>
+      <c r="L536" t="inlineStr"/>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>auto-d49c5a54e675</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Aviation: How Lufthansa is Preparing for Kerosene Shortages at Frankfurt Airport - Logistik Heute</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr"/>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitgFBVV95cUxNSnZmbGJvVnBxRW1VMWhlUzBMR2s4RE5kSDd4aWxvbndQMDVsa0d6dEVFQndHRzFIbFg5aGZ1Q0dncGFMNHZnMmZuTjBoQnlMdTBGRlB2OVNQWjRJWjRNU0hwU1hZMWVBOHJZZzk5U1dsWWthZHRiQVFQN2MxYnFCa1J4aldlWlo4VHpvSUg0NnZzMUVSNVhxR0xJdlRGd1hJNEw4RVRfd0lnV3k4enBuYXRNdms1QQ?oc=5" target="_blank"&gt;Aviation: How Lufthansa is Preparing for Kerosene Shortages at Frankfurt Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Logistik Heute&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNSnZmbGJvVnBxRW1VMWhlUzBMR2s4RE5kSDd4aWxvbndQMDVsa0d6dEVFQndHRzFIbFg5aGZ1Q0dncGFMNHZnMmZuTjBoQnlMdTBGRlB2OVNQWjRJWjRNU0hwU1hZMWVBOHJZZzk5U1dsWWthZHRiQVFQN2MxYnFCa1J4aldlWlo4VHpvSUg0NnZzMUVSNVhxR0xJdlRGd1hJNEw4RVRfd0lnV3k4enBuYXRNdms1QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr"/>
+      <c r="L537" t="inlineStr"/>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>auto-2d23e179c0ff</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Tel Aviv-Vienna flight makes emergency landing after bomb threat - The Times of India</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr"/>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi1gFBVV95cUxOMm9TNlNPcTVXeG52aXp2N09sY1pKNTQ5YmR3Ry1rWi1vTDh2SE1vWk85OTlUNFhnZEUtZHdOdllfWElERW1NUzJVbEJ2aURPUnJVUXBGSFNQWlFvNUJKUWV0UmlvVWRCT3A4LU5WUjc5UmhzdURaNTlMcmZOai1NUkJsbDNBZU5uLVU4bmVWUGVVVEZMQzNkYUlucmlPeFNyLTc2VUVtYmd0TkVKZm5Yak1BaUZZdFFNY2hYQkZRaTlPOEdNckJCUGIyRlVROU1nX29FcDF30gHbAUFVX3lxTE1yZFdoeVFRaWVBLXUwa0RsM0VqYi15clk1QUF5ME9SNUJ3eldLTndtYjl6Z1d3Mm5hbXk1bUVHejBobE1jQXBpb1AwaFdvUllNbGduZ3NlQlNZbHZPX3N0WE1VaGpNQ3lpRTNSZ2FCeXRScDY1Z1Z0QVZUbDBRUm9ZSWtGUzJXeWlrQjdTVW1iQzVQUHNmN1gyLW1wemtCRUw5Sk16cW9aTnF0YXdnMUtRSGNkNnloa0haN0VpZXFqdThIYU5MTUNaaFYxSVpOdEVuSEFPRGVkLVpfMA?oc=5" target="_blank"&gt;Tel Aviv-Vienna flight makes emergency landing after bomb threat&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;The Times of India&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOMm9TNlNPcTVXeG52aXp2N09sY1pKNTQ5YmR3Ry1rWi1vTDh2SE1vWk85OTlUNFhnZEUtZHdOdllfWElERW1NUzJVbEJ2aURPUnJVUXBGSFNQWlFvNUJKUWV0UmlvVWRCT3A4LU5WUjc5UmhzdURaNTlMcmZOai1NUkJsbDNBZU5uLVU4bmVWUGVVVEZMQzNkYUlucmlPeFNyLTc2VUVtYmd0TkVKZm5Yak1BaUZZdFFNY2hYQkZRaTlPOEdNckJCUGIyRlVROU1nX29FcDF30gHbAUFVX3lxTE1yZFdoeVFRaWVBLXUwa0RsM0VqYi15clk1QUF5ME9SNUJ3eldLTndtYjl6Z1d3Mm5hbXk1bUVHejBobE1jQXBpb1AwaFdvUllNbGduZ3NlQlNZbHZPX3N0WE1VaGpNQ3lpRTNSZ2FCeXRScDY1Z1Z0QVZUbDBRUm9ZSWtGUzJXeWlrQjdTVW1iQzVQUHNmN1gyLW1wemtCRUw5Sk16cW9aTnF0YXdnMUtRSGNkNnloa0haN0VpZXFqdThIYU5MTUNaaFYxSVpOdEVuSEFPRGVkLVpfMA?oc=5</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr"/>
+      <c r="L538" t="inlineStr"/>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>auto-cbc5034bfe85</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Austrian Airlines flight makes emergency landing in Bulgaria after bomb threat - The Business Standard</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr"/>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitAFBVV95cUxQX3VCSGlUaC0taHMtN0dLQlhfWmRWOVM4ajZ4cWwySVZ0MXJqQmFsSlJqMXBKdHlrT211M25PS3lfcG9vaEZFMVdMUTRrYlZMdUwzV3d0TTNQVVFHV2tOREpwMm4ycGVEdG5uN2g2M1ZoWUNGTzNvemExQm9oS1R0Mm5fWXVkVU5qazhpck4ySWJiRUpxM0FES0V1bmlDVm00RXMzb0RoNTJMQWJwX3kxM1VyTjc?oc=5" target="_blank"&gt;Austrian Airlines flight makes emergency landing in Bulgaria after bomb threat&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;The Business Standard&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQX3VCSGlUaC0taHMtN0dLQlhfWmRWOVM4ajZ4cWwySVZ0MXJqQmFsSlJqMXBKdHlrT211M25PS3lfcG9vaEZFMVdMUTRrYlZMdUwzV3d0TTNQVVFHV2tOREpwMm4ycGVEdG5uN2g2M1ZoWUNGTzNvemExQm9oS1R0Mm5fWXVkVU5qazhpck4ySWJiRUpxM0FES0V1bmlDVm00RXMzb0RoNTJMQWJwX3kxM1VyTjc?oc=5</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr"/>
+      <c r="L539" t="inlineStr"/>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>auto-ea605ab53d95</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Bomb Threat Forces Israel-to-Europe Passenger Flight to Make Emergency Landing - news.sbs.co.kr</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr"/>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMibkFVX3lxTE15U2RQWjN5RU1hdmNReXlvbHJwQVVKQmR0LURWRkNrN0h5ZWN5STlKZlhwbFlEZDNmeUhrcTZQU1lHR3drMlBmUlhmeHd3UVNiaE9PSTZicFFEdFh2NnBOZ1g1Y3pvbmtwczNFNlBB?oc=5" target="_blank"&gt;Bomb Threat Forces Israel-to-Europe Passenger Flight to Make Emergency Landing&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;news.sbs.co.kr&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE15U2RQWjN5RU1hdmNReXlvbHJwQVVKQmR0LURWRkNrN0h5ZWN5STlKZlhwbFlEZDNmeUhrcTZQU1lHR3drMlBmUlhmeHd3UVNiaE9PSTZicFFEdFh2NnBOZ1g1Y3pvbmtwczNFNlBB?oc=5</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr"/>
+      <c r="L540" t="inlineStr"/>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>auto-27081a1fa2ce</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Israel flight makes emergency landing over bomb threat - News24</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr"/>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi7gFBVV95cUxPeGREM045eTlkX2VweUNPZ2JrTnRxYVFraWIxR0Z2cHkzRG41TzEtUnduOG1WVklWUndJRVVGZEgtem5BaGpYUmtrdWVkMm1xWHAwSFBDWnVDU1pGRVloMWVDNTBYWFZwMVFhT0NTNEgxYTNYZTRIQjJsRXpwT2hYNzg3bXFiUE1hanFDc3NsX1ZaekFvNDhQMlRFUUZsQzJLVUNxM19nR0d6TTV2ODlhMmpyLS04WWdFYWcwVUdybWl2VFVxRDJRdGNTVkF2WDQxX25UNUFKNVZQSlR6OE1rX0RZZE50c08wa3VIOWJB0gHzAUFVX3lxTE1WckNuVGQ0eko1THkzczhyb2tEYklselpYY2Q4TXVJZUFkcTJLVG1Fa1VMUVMySktNV2JTYjhWZ25uS1dMazE2c1ZrYk9QTEFNYkp1QldNLUJvRFdFU3YwNDFZaDI0cFhybEUyN3ZWdGkwMWhOVEY0ZFVrUzQtSGJHZFlpbEhlTHl6SHR6YXY1cHlxQV9tS2pXZDlRS2g1Q0J4RU9MNHYyZHlBY3ZtWEFhWEUwQmlKVEExRE1BREFxV3dXZUY4WW84X29FcXc3TlBWRzRPSDU5TUlodFJHMFJmR1pOek5WTWY5c0VKZW50R3BaZw?oc=5" target="_blank"&gt;Israel flight makes emergency landing over bomb threat&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;News24&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPeGREM045eTlkX2VweUNPZ2JrTnRxYVFraWIxR0Z2cHkzRG41TzEtUnduOG1WVklWUndJRVVGZEgtem5BaGpYUmtrdWVkMm1xWHAwSFBDWnVDU1pGRVloMWVDNTBYWFZwMVFhT0NTNEgxYTNYZTRIQjJsRXpwT2hYNzg3bXFiUE1hanFDc3NsX1ZaekFvNDhQMlRFUUZsQzJLVUNxM19nR0d6TTV2ODlhMmpyLS04WWdFYWcwVUdybWl2VFVxRDJRdGNTVkF2WDQxX25UNUFKNVZQSlR6OE1rX0RZZE50c08wa3VIOWJB0gHzAUFVX3lxTE1WckNuVGQ0eko1THkzczhyb2tEYklselpYY2Q4TXVJZUFkcTJLVG1Fa1VMUVMySktNV2JTYjhWZ25uS1dMazE2c1ZrYk9QTEFNYkp1QldNLUJvRFdFU3YwNDFZaDI0cFhybEUyN3ZWdGkwMWhOVEY0ZFVrUzQtSGJHZFlpbEhlTHl6SHR6YXY1cHlxQV9tS2pXZDlRS2g1Q0J4RU9MNHYyZHlBY3ZtWEFhWEUwQmlKVEExRE1BREFxV3dXZUY4WW84X29FcXc3TlBWRzRPSDU5TUlodFJHMFJmR1pOek5WTWY5c0VKZW50R3BaZw?oc=5</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr"/>
+      <c r="L541" t="inlineStr"/>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>auto-6ac5a0d282f9</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Austrian Airlines Flight From Tel Aviv to Vienna Makes Emergency Landing After ‘Bomb Threat’ - News.com.au</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr"/>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi-gFBVV95cUxPVlRKRkdDbGNYTHY4T1JTMmJkd3RjV2tQV3lNVmIzbHZRTElnWEpWMGI0X1FrRG5QYTFhd05USXZrYUhfVlN0VTluS01EVGtIenhSTmViZUNHRXVBTHQzZFM0Z3lvQW1Ka2ZTOEhLWUthWDBReVdCc0tjN3BhNm5kRlAzaVdsLU5WRzJjNzlGazhlQTdodFVkZ1hYamZCLXdDYmtRclJzUmN6VFNINzVHUXdMRHNNOUZlcWxUNEVOT0EwUVEyWDZJMEdYcHF0R1IyYTZ1ZnllcDdwRXhKeEpaNkZ2SzZvamJ6c0g5amM4OXlGZWZBNVJZTlhR0gH6AUFVX3lxTE9WVEpGR0NsY1hMdjhPUlMyYmR3dGNXa1BXeU1WYjNsdlFMSWdYSlYwYjRfUWtEblBhMWF3TlRJdmthSF9WU3RVOW5LTURUa0h6eFJOZWJlQ0dFdUFMdDNkUzRneW9BbUprZlM4SEtZS2FYMFF5V0JzS2M3cGE2bmRGUDNpV2wtTlZHMmM3OUZrOGVBN2h0VWRnWFhqZkItd0Nia1FyUnNSY3pUU0g3NUdRd0xEc005RmVxbFQ0RU5PQTBRUTJYNkkwR1hwcXRHUjJhNnVmeWVwN3BFeEp4Slo2RnZLNm9qYnpzSDlqYzg5eUZlZkE1UllOWFE?oc=5" target="_blank"&gt;Austrian Airlines Flight From Tel Aviv to Vienna Makes Emergency Landing After ‘Bomb Threat’&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;News.com.au&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxPVlRKRkdDbGNYTHY4T1JTMmJkd3RjV2tQV3lNVmIzbHZRTElnWEpWMGI0X1FrRG5QYTFhd05USXZrYUhfVlN0VTluS01EVGtIenhSTmViZUNHRXVBTHQzZFM0Z3lvQW1Ka2ZTOEhLWUthWDBReVdCc0tjN3BhNm5kRlAzaVdsLU5WRzJjNzlGazhlQTdodFVkZ1hYamZCLXdDYmtRclJzUmN6VFNINzVHUXdMRHNNOUZlcWxUNEVOT0EwUVEyWDZJMEdYcHF0R1IyYTZ1ZnllcDdwRXhKeEpaNkZ2SzZvamJ6c0g5amM4OXlGZWZBNVJZTlhR0gH6AUFVX3lxTE9WVEpGR0NsY1hMdjhPUlMyYmR3dGNXa1BXeU1WYjNsdlFMSWdYSlYwYjRfUWtEblBhMWF3TlRJdmthSF9WU3RVOW5LTURUa0h6eFJOZWJlQ0dFdUFMdDNkUzRneW9BbUprZlM4SEtZS2FYMFF5V0JzS2M3cGE2bmRGUDNpV2wtTlZHMmM3OUZrOGVBN2h0VWRnWFhqZkItd0Nia1FyUnNSY3pUU0g3NUdRd0xEc005RmVxbFQ0RU5PQTBRUTJYNkkwR1hwcXRHUjJhNnVmeWVwN3BFeEp4Slo2RnZLNm9qYnpzSDlqYzg5eUZlZkE1UllOWFE?oc=5</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr"/>
+      <c r="L542" t="inlineStr"/>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>auto-b8a1ca2cb411</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>easyJet U2415 declared an emergency and diverted to Liverpool following engine vibration - airlive</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr"/>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiyAFBVV95cUxObXdkbTUtWXZEWnRVN0l4S3ZsV1NqSWVVaENCTkRFRDEtVTR2Q3doQk9iRzdOT0ZWR185TDgxaFJnU2pFMXRvX0ltX2ZkSWZIcGw1SjQzbnRnMzNYOWE5c0JUQVk0V2tHXzdZRk1YUXh6NlUySDdOOGVBQU82b3ZScWJjYnVlRFh0anUtVV9LS2ZaYXc1a3R4ZDEtOWtYZU9RR0EzWjFSZ0hoX054WUtLay1ZMTRIWktaWE5sRXNKbkhvZkl4bWJGTNIB0AFBVV95cUxQb19WS1lrLS1zdzJjbUhVdXZFdTY4U0JfZ3M0Q0h1UjdYb0ljOWFKWVdqMzlZSkszc2U5U19TT0w2WGk3bHFMSnFZQkh5R3kzZXV2bU1Ka094ZHR5Y0JrekdITVZMRGVKVVFGV1NUY0Z4UkpoeTNXdXNyOVc4cVNlTXg1V0gwZk16RlhHYXQxV2ZSUTJBenFKRUdnN1k4b2FJMlduSnh4MlNfR2s0MHZqNDRzd0hWZnNJVTVJSlVPTWI1bGFTRUt4RXUxbHM1X2JH?oc=5" target="_blank"&gt;easyJet U2415 declared an emergency and diverted to Liverpool following engine vibration&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxObXdkbTUtWXZEWnRVN0l4S3ZsV1NqSWVVaENCTkRFRDEtVTR2Q3doQk9iRzdOT0ZWR185TDgxaFJnU2pFMXRvX0ltX2ZkSWZIcGw1SjQzbnRnMzNYOWE5c0JUQVk0V2tHXzdZRk1YUXh6NlUySDdOOGVBQU82b3ZScWJjYnVlRFh0anUtVV9LS2ZaYXc1a3R4ZDEtOWtYZU9RR0EzWjFSZ0hoX054WUtLay1ZMTRIWktaWE5sRXNKbkhvZkl4bWJGTNIB0AFBVV95cUxQb19WS1lrLS1zdzJjbUhVdXZFdTY4U0JfZ3M0Q0h1UjdYb0ljOWFKWVdqMzlZSkszc2U5U19TT0w2WGk3bHFMSnFZQkh5R3kzZXV2bU1Ka094ZHR5Y0JrekdITVZMRGVKVVFGV1NUY0Z4UkpoeTNXdXNyOVc4cVNlTXg1V0gwZk16RlhHYXQxV2ZSUTJBenFKRUdnN1k4b2FJMlduSnh4MlNfR2s0MHZqNDRzd0hWZnNJVTVJSlVPTWI1bGFTRUt4RXUxbHM1X2JH?oc=5</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr"/>
+      <c r="L543" t="inlineStr"/>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O543"/>
+  <dimension ref="A1:O559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33503,7 +33503,6 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
       <c r="E534" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -33534,8 +33533,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
-      <c r="L534" t="inlineStr"/>
       <c r="M534" t="inlineStr">
         <is>
           <t>review</t>
@@ -33568,7 +33565,6 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -33599,8 +33595,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
-      <c r="L535" t="inlineStr"/>
       <c r="M535" t="inlineStr">
         <is>
           <t>review</t>
@@ -33633,7 +33627,6 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -33664,8 +33657,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
-      <c r="L536" t="inlineStr"/>
       <c r="M536" t="inlineStr">
         <is>
           <t>review</t>
@@ -33698,7 +33689,6 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -33729,8 +33719,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
-      <c r="L537" t="inlineStr"/>
       <c r="M537" t="inlineStr">
         <is>
           <t>review</t>
@@ -33763,7 +33751,6 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -33794,8 +33781,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
-      <c r="L538" t="inlineStr"/>
       <c r="M538" t="inlineStr">
         <is>
           <t>review</t>
@@ -33828,7 +33813,6 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr"/>
       <c r="E539" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -33859,8 +33843,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
-      <c r="L539" t="inlineStr"/>
       <c r="M539" t="inlineStr">
         <is>
           <t>review</t>
@@ -33893,7 +33875,6 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -33924,8 +33905,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
-      <c r="L540" t="inlineStr"/>
       <c r="M540" t="inlineStr">
         <is>
           <t>review</t>
@@ -33958,7 +33937,6 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -33989,8 +33967,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
-      <c r="L541" t="inlineStr"/>
       <c r="M541" t="inlineStr">
         <is>
           <t>review</t>
@@ -34023,7 +33999,6 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -34054,8 +34029,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
-      <c r="L542" t="inlineStr"/>
       <c r="M542" t="inlineStr">
         <is>
           <t>review</t>
@@ -34088,7 +34061,6 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -34119,8 +34091,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
-      <c r="L543" t="inlineStr"/>
       <c r="M543" t="inlineStr">
         <is>
           <t>review</t>
@@ -34132,6 +34102,1046 @@
         </is>
       </c>
       <c r="O543" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>auto-526b877df637</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt bietet im Winter 2026/27 231 Ziele an</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr"/>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>Am Flughafen Frankfurt stehen im Winterflugplan 2026/27 insgesamt 231 Ziele in 92 Ländern zur Auswahl. Zwischen dem 25. Oktober und dem 27. März bedienen 80 Fluggesellschaften das Drehkreuz mit rund 3400 Abflügen und 650.000 Sitzplätzen pro Woche.</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flughafen-frankfurt-bietet-im-winter-202627-231-ziele-an/nsfylps</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr"/>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>auto-278504350c42</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Das sind die neuen Ziele von Lufthansa im Sommerflugplan 2027</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr"/>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>Lufthansa erweitert ihren Sommerflugplan 2027 um neue Langstreckenverbindungen in die USA und nach Japan. Ab dem 5. Mai fliegt die Fluggesellschaft drei Mal wöchentlich von Frankfurt nach Columbus in Ohio. Zum Einsatz kommt eine Boeing 787-9 mit Allegris-Kabine.</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/das-sind-die-neuen-ziele-von-lufthansa-im-sommerflugplan-2027/lebgyyp</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr"/>
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>auto-bf05151f87bd</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Lufthansa fliegt nach Columbus in Ohio - mit Millionen im Rücken</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr"/>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>Fast eine Million Menschen leben in Columbus. Doch eine direkte Flugverbindung nach Europa gibt es bisher nicht. Das ändert Lufthansa ab Mai 2027. Dass die deutsche Airline ausgerechnet die Hauptstadt von Ohio ins Streckennetz aufnimmt, hat nicht nur mit der Nachfrage zu tun.</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/airlines/lufthansa-fliegt-nach-columbus-in-ohio-mit-millionen-im-ruecken/bqfl7pg</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr"/>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>auto-ec2a01b7e7fb</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Das sind die neuen Ziele von Swiss im Sommerflugplan 2027</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr"/>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>Swiss erweitert ihren Flugplan für den Sommer 2027. Neu ins Streckennetz kommt Toulouse in Südfrankreich. Die Verbindung ab Zürich wird vom 25. Juni bis zum 23. August zweimal wöchentlich angeboten.</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/das-sind-die-neuen-ziele-von-swiss-im-sommerflugplan-2027/4lt03g0</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr"/>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>auto-77cc09ee79fb</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Ausbau im München: Das sind die neuen Ziele von Discover im Sommerflugplan 2027</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr"/>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>Discover Airlines erweitert ihr Langstreckennetz um zwei neue Ziele und übernimmt weitere Verbindungen von Lufthansa. Ab dem 1. Juni 2027 fliegt die Ferienfluggesellschaft dreimal wöchentlich von Frankfurt nach Edmonton in Kanada. Die Flüge finden dienstags, donnerstags und samstags statt.</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/ausbau-im-muenchen-das-sind-die-neuen-ziele-von-discover-im-sommerflugplan-2027/e23z2sg</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr"/>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>auto-b76b28588c55</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt: Geringeres Flugangebot im Winter</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr"/>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Am Frankfurter Flughafen finden Passagiere im neuen Winterflugplan ein geringeres Flugangebot als vor einem Jahr.</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53977/Flughafen-Frankfurt-Geringeres-Flugangebot-im-Winter.html</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr"/>
+      <c r="L549" t="inlineStr"/>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>auto-be303cea6ee0</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Lufthansa baut Streckennetz und Frequenzen aus</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr"/>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Zehn neue Interkontlinien, weitere Europaziele und Frequenzerhöhungen im bestehenden Netzwerk: Lufthansa baut ihren Sommerflugplan 2027 trotz anhaltend hoher Kerosinpreise massiv aus. Nur Eurowings braucht für das finale 2027er-Programm noch Zeit.</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53975/Lufthansa-baut-Streckennetz-und-Frequenzen-aus.html</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr"/>
+      <c r="L550" t="inlineStr"/>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>auto-8026d0a44739</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Zentraler Flugkorridor über Persischem Golf wieder offen</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr"/>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>KUWAIT-STADT - Im Krieg mit Israel und den USA griff der Iran mehrfach Kuwait an - für den Luftraum des Emirats galten Restriktionen. Nun gibt Kuwait Überflüge wieder frei - eine zentrale Routenoption zwischen Europa und dem Nahen Osten ist wieder verfügbar. Nicht alle Airlines machen davon Gebrauch.</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53973/Zentraler-Flugkorridor-ueber-Persischem-Golf-wieder-offen.html</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr"/>
+      <c r="L551" t="inlineStr"/>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>auto-83c291628780</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>DLR-Rover "Idefix" fliegt zu Marsmond</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr"/>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>TANEGASHIMA - Eine japanische Raumsonde mit dem deutsch-französischen Rover "Idefix" ist Richtung Mars aufgebrochen. Eine H3-Rakete hob erfolgreich mit der Sonde von Japans Weltraumbahnhof Tanegashima auf der gleichnamigen Insel im Südwesten des Landes ab.</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53970/DLR-Rover-Idefix-fliegt-zu-Marsmond-.html</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr"/>
+      <c r="L552" t="inlineStr"/>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>auto-9e4cafe98656</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Weniger Ziele von deutschen Flughäfen erreichbar</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr"/>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Seit dem Corona-Schock hinkt das Verkehrsangebot an deutschen Flughäfen im europäischen Vergleich hinterher. Der Lobbyverband BDL zeigt mit einem Atlas, was das für die einzelnen Regionen bedeutet.</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53967/Weniger-Ziele-von-deutschen-Flughaefen-erreichbar-.html</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr"/>
+      <c r="L553" t="inlineStr"/>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>auto-1a27ed4eed95</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>EU-Kommission will "Project Bromo" durchwinken</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr"/>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>BRÜSSEL - Airbus, Leonardo und Thales legen ihre Satellitensparten zusammen: "Project Bromo" soll Europa zu einem schlagkräftigen Hersteller für Weltraum-Infrastruktur verhelfen - und eine Alternative zum Starlink-Netzwerk von SpaceX hervorbringen. Die EU-Kommission wird das Vorhaben durchwinken.</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53966/EU-Kommission-will-Project-Bromo-durchwinken.html</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr"/>
+      <c r="L554" t="inlineStr"/>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>auto-d3f0652f252b</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Discover Airlines übernimmt Lufthansa-Langstrecke – und stellt sie wieder ein - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr"/>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMipgFBVV95cUxPcVV0TjV1MEswLTYyZHJ1NUlvOE9fV0xfakVmVEcxYzlCV183dHhkQS13aTRRY2JNT0NCTGc3NFZHdlFFRnh0eUFkNjRtNG5tTE1pWDNXSjU3dGhwbkRZaVBnZmlaRUVNZ3ZRNzlYNXN4V1BGRWtmWE5pOTBfXzZxLXZqbEJjcjRxWXpKMmxDS2xtRmJ2N2xLdlZkbi1BWE5fNnRiMXF3?oc=5" target="_blank"&gt;Discover Airlines übernimmt Lufthansa-Langstrecke – und stellt sie wieder ein&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPcVV0TjV1MEswLTYyZHJ1NUlvOE9fV0xfakVmVEcxYzlCV183dHhkQS13aTRRY2JNT0NCTGc3NFZHdlFFRnh0eUFkNjRtNG5tTE1pWDNXSjU3dGhwbkRZaVBnZmlaRUVNZ3ZRNzlYNXN4V1BGRWtmWE5pOTBfXzZxLXZqbEJjcjRxWXpKMmxDS2xtRmJ2N2xLdlZkbi1BWE5fNnRiMXF3?oc=5</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr"/>
+      <c r="L555" t="inlineStr"/>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>auto-2808f2ebf344</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Austrian Airlines flight from Tel Aviv makes emergency landing after bomb threat - DW.com</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr"/>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiswFBVV95cUxNUjNZSW5XelNyLUN0cnd0NktqZk5YczlfZnlPQW5mWERWOFdmRE12dHFtcm1URmE3NXhWb21RekFhTXRSR3V2UEQyRFotTXBRSkJiTGtXTGxOTUVwWHBhSFpFS2FlUTdJcmNiMHRfZC1TdE52MEUwMm0zVzNtNlZtYkNLWjVZY2ZtVVRuZk5OS3QzSVJOaWxBNmVyN19FSWRwYjRmZDlQMllkVUdleWlxUHFTQdIBswFBVV95cUxOLXB3aUZfSUppYThCdG1oMDZPdjMyUnhZNk91UUcyaVdzV3FzOWRSMVhURXprVmRHczdrQVRvWExQam9TUDV0VWhIcWlDaVV3SGJOVG5uMmZhVDRXVHZHZ2ZqMnBZV01qZ0ZveGRGWHZMN3NxQzhLRm4yZXhfMUpYN011UzJrUENJUjBzOVY1WXhxYlV0Z2dpSWsxLWl6M05CUmFUMXJpTWxYT25PMWR4aDl4Zw?oc=5" target="_blank"&gt;Austrian Airlines flight from Tel Aviv makes emergency landing after bomb threat&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;DW.com&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNUjNZSW5XelNyLUN0cnd0NktqZk5YczlfZnlPQW5mWERWOFdmRE12dHFtcm1URmE3NXhWb21RekFhTXRSR3V2UEQyRFotTXBRSkJiTGtXTGxOTUVwWHBhSFpFS2FlUTdJcmNiMHRfZC1TdE52MEUwMm0zVzNtNlZtYkNLWjVZY2ZtVVRuZk5OS3QzSVJOaWxBNmVyN19FSWRwYjRmZDlQMllkVUdleWlxUHFTQdIBswFBVV95cUxOLXB3aUZfSUppYThCdG1oMDZPdjMyUnhZNk91UUcyaVdzV3FzOWRSMVhURXprVmRHczdrQVRvWExQam9TUDV0VWhIcWlDaVV3SGJOVG5uMmZhVDRXVHZHZ2ZqMnBZV01qZ0ZveGRGWHZMN3NxQzhLRm4yZXhfMUpYN011UzJrUENJUjBzOVY1WXhxYlV0Z2dpSWsxLWl6M05CUmFUMXJpTWxYT25PMWR4aDl4Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr"/>
+      <c r="L556" t="inlineStr"/>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>auto-b431e419143c</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>easyJet flight U28105 declared an emergency over France following technical issue with the aircraft - airlive</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr"/>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi2AFBVV95cUxPdlZ6T3ViUDFFWHpGSy1DYl9oZDROZWx5cnZqTVR4LWlncHM0OUp5WURMRlFQeHUwR3JReGJ2NlZWbVpuYzZabjRlSHlpbjhqOVF2NUk0VS1JZGpaXzUzTUQzeGtRbmZkSWw2aTliVXgwY205Tm1FaVpBUk9FWk9IcHdrUEVyWDd5a2JQVnpMc04ycm81bkRNNW9hZlpHT3lxUzBLRm81ZTc1ZGRkUHZ2cS11NHdkQ2E3OUprRWtTd2RacEhNN2J5b29scl9Ra2tDVXYtMTRqSDfSAeABQVVfeXFMTXFvY3NCRkh3bkpsN084SW1HZmU2WUZHMnJPNy1pZjBnYWc4cW9rVzVsN004QWx1aWlWNE54ck5KbUJsMTJPWmVCUVBJa2RYMFJDSi1vRWZ1ai1WV1RhQ1l1TXV1dGdsZTFSWTFzZnRlSkpmOFZRRUYyYjJvVFdmLTZiOS1lMHdhYk43Ym9POWFBbEJZUjJNcXd3S2dTa1VKQzBQSTloM0pXOVZVNEN3TlBkYnNHYnRkY2kzUDhmVTNlZ0V4RVdqM0gzSklwUnBRZ3V0elo3YkFic1RKTElVUVg?oc=5" target="_blank"&gt;easyJet flight U28105 declared an emergency over France following technical issue with the aircraft&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPdlZ6T3ViUDFFWHpGSy1DYl9oZDROZWx5cnZqTVR4LWlncHM0OUp5WURMRlFQeHUwR3JReGJ2NlZWbVpuYzZabjRlSHlpbjhqOVF2NUk0VS1JZGpaXzUzTUQzeGtRbmZkSWw2aTliVXgwY205Tm1FaVpBUk9FWk9IcHdrUEVyWDd5a2JQVnpMc04ycm81bkRNNW9hZlpHT3lxUzBLRm81ZTc1ZGRkUHZ2cS11NHdkQ2E3OUprRWtTd2RacEhNN2J5b29scl9Ra2tDVXYtMTRqSDfSAeABQVVfeXFMTXFvY3NCRkh3bkpsN084SW1HZmU2WUZHMnJPNy1pZjBnYWc4cW9rVzVsN004QWx1aWlWNE54ck5KbUJsMTJPWmVCUVBJa2RYMFJDSi1vRWZ1ai1WV1RhQ1l1TXV1dGdsZTFSWTFzZnRlSkpmOFZRRUYyYjJvVFdmLTZiOS1lMHdhYk43Ym9POWFBbEJZUjJNcXd3S2dTa1VKQzBQSTloM0pXOVZVNEN3TlBkYnNHYnRkY2kzUDhmVTNlZ0V4RVdqM0gzSklwUnBRZ3V0elo3YkFic1RKTElVUVg?oc=5</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr"/>
+      <c r="L557" t="inlineStr"/>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>auto-4976ab8c44f6</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Turkish Airlines TK6 declared an emergency over The Netherlands and just diverted to Amsterdam - airlive</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr"/>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi0gFBVV95cUxQZlNDWjdoZjNOSVNLdGhRRGZydnNxaWw5NEJPLUl4eEU1VHRzR1hjb1l2OW1LbGZ3QmwxODY3ZTBHdnJaMmE5c3JGWEgzWjUzcmZQcVY1Z0RuM1RoNUtLXy1oR19mWjJKX1pWcS14TkpyU1J6dnFBc3UwZTkwc0g5VXZodVp4Zk5kcjJIRFdwNzZtVHV5UlhrR0VtR3p5a3VBRE9aZl8tZ3FvR1RGamJkZGZFRlR4T21EVTFwV0pPQkZLenMtRkY2em5xTmtwWFZKT1HSAdoBQVVfeXFMT1JMbHFBX21QR0l3aTVFUms0UDFocDFncldPZEtxVF9iTjVIOUdzZzY0TjJtZTN4bXJxX2NsTVJQLW1CMGlUWTRROWl3U0ktVFVESWMyc01HRUR5N2J6NXlRV0FfWEpMSGJFUDNjcmtDenhUUFRsUzJ2YWQtV2xBdTdGOEJ6VlJ6Rk42bVZadVZFaU1hS2cxdzdqVmFNeW1wYzhPanloX2MzZWZqbEppek50RHlEYldHYnBkT09ZNl9hVVhMMmpsQXhjOWtFTjllcGllUUhlYmI3SVE?oc=5" target="_blank"&gt;Turkish Airlines TK6 declared an emergency over The Netherlands and just diverted to Amsterdam&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQZlNDWjdoZjNOSVNLdGhRRGZydnNxaWw5NEJPLUl4eEU1VHRzR1hjb1l2OW1LbGZ3QmwxODY3ZTBHdnJaMmE5c3JGWEgzWjUzcmZQcVY1Z0RuM1RoNUtLXy1oR19mWjJKX1pWcS14TkpyU1J6dnFBc3UwZTkwc0g5VXZodVp4Zk5kcjJIRFdwNzZtVHV5UlhrR0VtR3p5a3VBRE9aZl8tZ3FvR1RGamJkZGZFRlR4T21EVTFwV0pPQkZLenMtRkY2em5xTmtwWFZKT1HSAdoBQVVfeXFMT1JMbHFBX21QR0l3aTVFUms0UDFocDFncldPZEtxVF9iTjVIOUdzZzY0TjJtZTN4bXJxX2NsTVJQLW1CMGlUWTRROWl3U0ktVFVESWMyc01HRUR5N2J6NXlRV0FfWEpMSGJFUDNjcmtDenhUUFRsUzJ2YWQtV2xBdTdGOEJ6VlJ6Rk42bVZadVZFaU1hS2cxdzdqVmFNeW1wYzhPanloX2MzZWZqbEppek50RHlEYldHYnBkT09ZNl9hVVhMMmpsQXhjOWtFTjllcGllUUhlYmI3SVE?oc=5</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr"/>
+      <c r="L558" t="inlineStr"/>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>auto-834ac9738313</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Ryanair flight FR4017 to Milan declared an emergency over South of France - airlive</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr"/>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitgFBVV95cUxNWkdYelFrSFg1VE9BTGRQb1RaakVtbktRWTlIMllBbHl3TTNuWVcyZzU2OWpSekxGYzRZclpqLVFOb1RqYXZxUVI4dTc1ek1hXzZRTnl4dzJvd01qTk1vTXBxUmtsUVpHOHRyV1NGcmM3aFNlU1BBcEtHRHA1RVVEZHYzNml1Smt6bUVyREJXeUZNMnZLUTNldXdhb3VWcm1OYlQycmhLdF9PSnM3UTh5RFlHUzlBQdIBvgFBVV95cUxQbmQwRjRlbWdnUXExZlVZMVZkODg2YzF1Z2lISFF1d2dGQmhQTWlFNjVfRmlHNk42Z0tYUHVEMU9Cb2xaLWhyMzhnZ19FTk5Ba2ZPS3J1RVJfX0JQZFNSVkdycnhFSHVYS3FQM29iRWJtcDM5U2ZOdkhzZnBhYjhZMGFkSWFUZERZMnljNGpWN0IwQi02QXp6Ry1Ba05JOGJEOE44TDdBMWRsd3ZNWTU0WXUyMThiTi1GNjFydEdn?oc=5" target="_blank"&gt;Ryanair flight FR4017 to Milan declared an emergency over South of France&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNWkdYelFrSFg1VE9BTGRQb1RaakVtbktRWTlIMllBbHl3TTNuWVcyZzU2OWpSekxGYzRZclpqLVFOb1RqYXZxUVI4dTc1ek1hXzZRTnl4dzJvd01qTk1vTXBxUmtsUVpHOHRyV1NGcmM3aFNlU1BBcEtHRHA1RVVEZHYzNml1Smt6bUVyREJXeUZNMnZLUTNldXdhb3VWcm1OYlQycmhLdF9PSnM3UTh5RFlHUzlBQdIBvgFBVV95cUxQbmQwRjRlbWdnUXExZlVZMVZkODg2YzF1Z2lISFF1d2dGQmhQTWlFNjVfRmlHNk42Z0tYUHVEMU9Cb2xaLWhyMzhnZ19FTk5Ba2ZPS3J1RVJfX0JQZFNSVkdycnhFSHVYS3FQM29iRWJtcDM5U2ZOdkhzZnBhYjhZMGFkSWFUZERZMnljNGpWN0IwQi02QXp6Ry1Ba05JOGJEOE44TDdBMWRsd3ZNWTU0WXUyMThiTi1GNjFydEdn?oc=5</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr"/>
+      <c r="L559" t="inlineStr"/>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O559"/>
+  <dimension ref="A1:O564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34123,7 +34123,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -34154,8 +34153,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
-      <c r="L544" t="inlineStr"/>
       <c r="M544" t="inlineStr">
         <is>
           <t>review</t>
@@ -34188,7 +34185,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -34219,8 +34215,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
-      <c r="L545" t="inlineStr"/>
       <c r="M545" t="inlineStr">
         <is>
           <t>review</t>
@@ -34253,7 +34247,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -34284,8 +34277,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
-      <c r="L546" t="inlineStr"/>
       <c r="M546" t="inlineStr">
         <is>
           <t>review</t>
@@ -34318,7 +34309,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -34349,8 +34339,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
-      <c r="L547" t="inlineStr"/>
       <c r="M547" t="inlineStr">
         <is>
           <t>review</t>
@@ -34383,7 +34371,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -34414,8 +34401,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
-      <c r="L548" t="inlineStr"/>
       <c r="M548" t="inlineStr">
         <is>
           <t>review</t>
@@ -34448,7 +34433,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr"/>
       <c r="E549" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -34479,8 +34463,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
-      <c r="L549" t="inlineStr"/>
       <c r="M549" t="inlineStr">
         <is>
           <t>review</t>
@@ -34513,7 +34495,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -34544,8 +34525,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
-      <c r="L550" t="inlineStr"/>
       <c r="M550" t="inlineStr">
         <is>
           <t>review</t>
@@ -34578,7 +34557,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr"/>
       <c r="E551" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -34609,8 +34587,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
-      <c r="L551" t="inlineStr"/>
       <c r="M551" t="inlineStr">
         <is>
           <t>review</t>
@@ -34643,7 +34619,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -34674,8 +34649,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
-      <c r="L552" t="inlineStr"/>
       <c r="M552" t="inlineStr">
         <is>
           <t>review</t>
@@ -34708,7 +34681,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -34739,8 +34711,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
-      <c r="L553" t="inlineStr"/>
       <c r="M553" t="inlineStr">
         <is>
           <t>review</t>
@@ -34773,7 +34743,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -34804,8 +34773,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
-      <c r="L554" t="inlineStr"/>
       <c r="M554" t="inlineStr">
         <is>
           <t>review</t>
@@ -34838,7 +34805,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D555" t="inlineStr"/>
       <c r="E555" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -34869,8 +34835,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
-      <c r="L555" t="inlineStr"/>
       <c r="M555" t="inlineStr">
         <is>
           <t>review</t>
@@ -34903,7 +34867,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr"/>
       <c r="E556" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -34934,8 +34897,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
-      <c r="L556" t="inlineStr"/>
       <c r="M556" t="inlineStr">
         <is>
           <t>review</t>
@@ -34968,7 +34929,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
       <c r="E557" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -34999,8 +34959,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
-      <c r="L557" t="inlineStr"/>
       <c r="M557" t="inlineStr">
         <is>
           <t>review</t>
@@ -35033,7 +34991,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
       <c r="E558" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -35064,8 +35021,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
-      <c r="L558" t="inlineStr"/>
       <c r="M558" t="inlineStr">
         <is>
           <t>review</t>
@@ -35098,7 +35053,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D559" t="inlineStr"/>
       <c r="E559" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35129,8 +35083,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
-      <c r="L559" t="inlineStr"/>
       <c r="M559" t="inlineStr">
         <is>
           <t>review</t>
@@ -35142,6 +35094,331 @@
         </is>
       </c>
       <c r="O559" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>auto-6b5e87f37c57</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Tap-Chef erwartet schwierige Prüfung des Lufthansa-Einstiegs</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr"/>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>Tap-Chef Luís Rodrigues begrüßt den geplanten Einstieg der Lufthansa Group bei der portugiesischen Fluggesellschaft. Zugleich warnt er vor einem langwierigen Genehmigungsverfahren. Die Transaktion muss noch von den zuständigen Behörden in der Europäischen Union, Brasilien und den USA genehmigt werden, wie das Portal AViation week berichtet.</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/tap-chef-erwartet-schwierige-pruefung-des-lufthansa-einstiegs/3n73gbz</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr"/>
+      <c r="L560" t="inlineStr"/>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>auto-7e599fcee626</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Die wichtigsten Fragen und Antworten zur Boeing 737 Max 10</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr"/>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>Boeing hat die Zulassung für das größte Mitglied der 737-Max-Familie erhalten. Die wichtigsten Fragen und Antworten zur Boeing 737 Max 10.</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugzeuge/die-wichtigsten-fragen-und-antworten-zur-boeing-737-max-10/p1ee9p3</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr"/>
+      <c r="L561" t="inlineStr"/>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>auto-c110fd587579</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Amac Aerospace meldet mehr Wartungsaufträge und neue Zulassungen</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr"/>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>Amac Aerospace verzeichnet am Standort Basel eine steigende Nachfrage nach Wartungs- und Umrüstungsarbeiten an Geschäftsflugzeugen. Die Zahl der Bombardier-Wartungsprojekte liegt nach Unternehmensangaben 25 Prozent über dem Vorjahresniveau. Noch 2026 soll die dritte umfangreiche 8C-Inspektion an einer Bombardier Global Express abgeschlossen werden.</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/amac-aerospace-meldet-mehr-wartungsauftraege-und-neue-zulassungen/se9v7km</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr"/>
+      <c r="L562" t="inlineStr"/>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>auto-fa22e5012de9</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Mirage in Ostfrankreich abgestürzt</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr"/>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>NANCY - Der Absturzort liegt rund 100 Kilometer vom Saarland entfernt. Die Maschine war auf einem Übungsflug unterwegs; was über die Besatzung und den Unfallhergang bekannt ist.</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53986/Mirage-in-Ostfrankreich-abgestuerzt.html</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr"/>
+      <c r="L563" t="inlineStr"/>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>auto-47f232b1a0c9</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Frankfurt startet mit 80 Airlines und 231 Zielen in den Winterflugplan 2026/2027 - Austrian Wings</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr"/>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMivAFBVV95cUxQa1psVkl6WHFYOTd5eVlVVzBHNTF6WW5FX0plTHMyd2I2anZHamJZOWo2aFFqbHdIOVNqbzdUeXRaVGJrTEUwU0lzdXdjT3h0dnZVVnc2TElPbUNPbllhU3NZci15UTZJb1BFQXBZTUJMWEl6R01udmlFbFRjX1hTeWpQbWVaUTFNajY4ekRGVDEwTlRhb0VRUkVVUmZFTGdzbFQ5V0trNHF1NXJlVDVfeEdxcExiOUNQVVRtTg?oc=5" target="_blank"&gt;Frankfurt startet mit 80 Airlines und 231 Zielen in den Winterflugplan 2026/2027&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Austrian Wings&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQa1psVkl6WHFYOTd5eVlVVzBHNTF6WW5FX0plTHMyd2I2anZHamJZOWo2aFFqbHdIOVNqbzdUeXRaVGJrTEUwU0lzdXdjT3h0dnZVVnc2TElPbUNPbllhU3NZci15UTZJb1BFQXBZTUJMWEl6R01udmlFbFRjX1hTeWpQbWVaUTFNajY4ekRGVDEwTlRhb0VRUkVVUmZFTGdzbFQ5V0trNHF1NXJlVDVfeEdxcExiOUNQVVRtTg?oc=5</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr"/>
+      <c r="L564" t="inlineStr"/>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O564"/>
+  <dimension ref="A1:O575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35115,7 +35115,6 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35146,8 +35145,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
-      <c r="L560" t="inlineStr"/>
       <c r="M560" t="inlineStr">
         <is>
           <t>review</t>
@@ -35180,7 +35177,6 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35211,8 +35207,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
-      <c r="L561" t="inlineStr"/>
       <c r="M561" t="inlineStr">
         <is>
           <t>review</t>
@@ -35245,7 +35239,6 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35276,8 +35269,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
-      <c r="L562" t="inlineStr"/>
       <c r="M562" t="inlineStr">
         <is>
           <t>review</t>
@@ -35310,7 +35301,6 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35341,8 +35331,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
-      <c r="L563" t="inlineStr"/>
       <c r="M563" t="inlineStr">
         <is>
           <t>review</t>
@@ -35375,7 +35363,6 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr"/>
       <c r="E564" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35406,8 +35393,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
-      <c r="L564" t="inlineStr"/>
       <c r="M564" t="inlineStr">
         <is>
           <t>review</t>
@@ -35419,6 +35404,721 @@
         </is>
       </c>
       <c r="O564" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>auto-e2b6487dda74</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>United Airlines verteilt 3000 Hygienetaschen an Bedürftige in Frankfurt</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr"/>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>Mitarbeitende von United Airlines haben am Flughafen Frankfurt 3000 Taschen mit Hygiene- und Pflegeartikeln für Menschen in schwierigen Lebenssituationen gepackt. An der Aktion beteiligten sich auch Passagiere, die zufällig vorbeikamen und spontan mithalfen.</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/united-airlines-verteilt-3000-hygienetaschen-an-beduerftige-in-frankfurt/jpv1fn4</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr"/>
+      <c r="L565" t="inlineStr"/>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>auto-43017a604d16</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Einigung bei Lufthansa City Airlines: Beschäftigte können zwischen Altersvorsorge und mehr Gehalt wählen</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr"/>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>Die Gewerkschaft Verdi und Lufthansa City Airlines haben sich auf einen Tarifvertrag zur betrieblichen Altersvorsorge für das Cockpit- und Kabinenpersonal geeinigt. Die Vereinbarung sieht erstmals innerhalb der Lufthansa Group eine Wahlmöglichkeit zwischen einer arbeitgeberfinanzierten Altersvorsorge und einer zusätzlichen Gehaltszahlung vor.</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/einigung-bei-lufthansa-city-airlines-beschaeftigte-koennen-zwischen-altersvorsorge/n8q6efx</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr"/>
+      <c r="L566" t="inlineStr"/>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>auto-e12c1fd848da</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Airbus erwartet Bedarf an 2670 Frachtflugzeugen bis 2045</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr"/>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>Die weltweite Flotte reiner Frachtflugzeuge wird bis 2045 um 46 Prozent wachsen. Das prognostiziert Airbus in seinem neuen Cargo Global Market Forecast, den der Hersteller am Cargo Facts Symposium vorgestellt hat. Demnach steigt die Zahl der Frachter von derzeit 2360 auf 3460 Flugzeuge.</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/airbus-erwartet-bedarf-an-2670-frachtflugzeugen-bis-2045/fmzzc2t</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr"/>
+      <c r="L567" t="inlineStr"/>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>auto-3b0452bc8b52</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Russische Boeing 737 steht seit 2022 in Köln/Bonn und niemand zahlt dafür</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr"/>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>Seit Februar 2022 steht eine Boeing 737-400 F der russischen Frachtfluglinie Atran am Flughafen Köln/Bonn. Die aufgelaufenen Gebühren hat bislang niemand bezahlt. Aber anders als in Genf kümmert sich jemand um das Flugzeug.</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugzeuge/russische-boeing-737-von-atran-seit-2022-in-koelnbonn-gestrandet/wrbkz3j</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr"/>
+      <c r="L568" t="inlineStr"/>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>auto-2345c7963b5f</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Air France und Air Côte d’Ivoire vereinbaren Codeshare auf Strecke nach Abidjan</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr"/>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>Air France und Air Côte d’Ivoire haben eine Codeshare-Vereinbarung für die Verbindung zwischen Paris und Abidjan geschlossen. Das Abkommen ermöglicht es Air France, ihre Flugnummer auch auf Flügen der ivorischen Fluggesellschaft anzubieten. Durch die gemeinsame Vermarktung können beide Airlines ihr Angebot auf der Strecke erweitern, ohne zusätzliche Flüge durchzuführen. Die Zusammenarbeit erhöht damit den Wettbewerbsdruck auf Corsair, die als einzige weitere Fluggesellschaft Direktflüge zwischen Paris und Abidjan anbietet.</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/air-france-und-air-cote-divoire-vereinbaren-codeshare-auf-strecke-nach-abidjan/nr4r21h</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr"/>
+      <c r="L569" t="inlineStr"/>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>auto-8067ecb350b4</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Azul übernimmt vierten Airbus A321 P2F</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr"/>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>Die brasilianische Fluggesellschaft Azul hat am 19. Oktober ihren vierten Airbus A321 P2F für die Frachtsparte Azul Logística übernommen. Das Flugzeug mit dem Kennzeichen PS-AJH traf am Flughafen Belo Horizonte-Confins ein und kann rund 25 Tonnen Fracht pro Flug transportieren.</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/azul-uebernimmt-vierten-airbus-a321-p2f/7emhn1g</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr"/>
+      <c r="L570" t="inlineStr"/>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>auto-9eaac54f5d46</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Betriebliche Altersvorsorge – oder mehr Gehalt</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr"/>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>MÜNCHEN - Flugpersonal von Lufthansa City Airlines erhält eine betriebliche Altersvorsorge - oder einen Gehaltsaufschlag. Verdi hat mit dem Lufthansa-Hubvernetzer eine entsprechende Wahlmöglichkeit in einer neuen Tarifregelung verankert. Das sind die Details des aus Gewerkschaftssicht "innovativen" Modells.</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53993/Betriebliche-Altersvorsorge--oder-mehr-Gehalt.html</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr"/>
+      <c r="L571" t="inlineStr"/>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>auto-3ae63e65c651</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Kreise: Schlichtung bei Lufthansa "weitgehend ergebnislos"</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr"/>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Harte Tarifthemen zwischen Lufthansa und Vereinigung Cockpit bleiben vorerst ungelöst. Nach Information von aero.de hat ein über mehrere Wochen geführtes Schlichtungsverfahren bei Lufthansa keinen Durchbruch erzielt. Das erhöht den Druck auf die parallel stattfindende Mediation.</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53989/Schlichtung-bei-Lufthansa-endet-ergebnislos.html</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr"/>
+      <c r="L572" t="inlineStr"/>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>auto-a211f1fe5947</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Diese Lounges findet Ihr am Flughafen Frankfurt - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr"/>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMif0FVX3lxTFBoMVEwN1hRME52V2k4X1p2RHFoajFuaG1YRGd6MGs2aFRVOVk1TFhFaXhScEhZZ2lHOFdwWG9nRVl5ZGp6Ti05LXEyRVBPSHBRTlQwUEJfSDRQTXVISHJPYzF3ZEUzOWF1alpDLUlrQkdpVUJyM2lLRTkxekc0b28?oc=5" target="_blank"&gt;Diese Lounges findet Ihr am Flughafen Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBoMVEwN1hRME52V2k4X1p2RHFoajFuaG1YRGd6MGs2aFRVOVk1TFhFaXhScEhZZ2lHOFdwWG9nRVl5ZGp6Ti05LXEyRVBPSHBRTlQwUEJfSDRQTXVISHJPYzF3ZEUzOWF1alpDLUlrQkdpVUJyM2lLRTkxekc0b28?oc=5</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr"/>
+      <c r="L573" t="inlineStr"/>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>auto-7f10d08712db</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Flight from Israel makes emergency landing in Bulgaria after bomb threat - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr"/>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitAFBVV95cUxQZ19xM0UxTl9TNGVlbUhHYlFlZjdJbzd0V1FmZWVGTnpfdDJvWTdHckw4Y1lhVFNoUW1HSmdUeXVPN3dibkE1WjJYLVR6cUQ2YlBibnpoc2ZrbmtJblZjM0Z4QU1LeTJVT0JjWHhUakk1T3A4WVdiUjlfUmNiYTBVSU16ZThLMFpvTzdoUTRyUUxJeERKdHBhZzBKZWlUcTVGcGdfYm5MQVA5MlJVYXFreXZ4bnXSAboBQVVfeXFMUDUzbFhadE5rWXkwMEkwajRvX0lnWUlIczFQMUMzSFpLbnFEM3pEb0xoQXZ2eklOS2UyN19Hc2Jzb2pTWWdFY1BJUnk1bXR3UzRhR3hZckNHVTM2UTlLSmlQaXZ0M0R6dl9wU1lfVUdjSXd6WS1rXzc0QmZyZ1gzNTd0dEQ4WFI0ZWo3Y1RiSmxYUk9qN2xfTUJmRUl3cm0zQzFBUV82NDJPSU1BV05sNllMaklGMmxRUUl3?oc=5" target="_blank"&gt;Flight from Israel makes emergency landing in Bulgaria after bomb threat&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Al Jazeera&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQZ19xM0UxTl9TNGVlbUhHYlFlZjdJbzd0V1FmZWVGTnpfdDJvWTdHckw4Y1lhVFNoUW1HSmdUeXVPN3dibkE1WjJYLVR6cUQ2YlBibnpoc2ZrbmtJblZjM0Z4QU1LeTJVT0JjWHhUakk1T3A4WVdiUjlfUmNiYTBVSU16ZThLMFpvTzdoUTRyUUxJeERKdHBhZzBKZWlUcTVGcGdfYm5MQVA5MlJVYXFreXZ4bnXSAboBQVVfeXFMUDUzbFhadE5rWXkwMEkwajRvX0lnWUlIczFQMUMzSFpLbnFEM3pEb0xoQXZ2eklOS2UyN19Hc2Jzb2pTWWdFY1BJUnk1bXR3UzRhR3hZckNHVTM2UTlLSmlQaXZ0M0R6dl9wU1lfVUdjSXd6WS1rXzc0QmZyZ1gzNTd0dEQ4WFI0ZWo3Y1RiSmxYUk9qN2xfTUJmRUl3cm0zQzFBUV82NDJPSU1BV05sNllMaklGMmxRUUl3?oc=5</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr"/>
+      <c r="L574" t="inlineStr"/>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>auto-11f5fa76c275</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Air France flight AF99 to Paris declared an emergency and just diverted to Dublin - airlive</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr"/>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiwAFBVV95cUxQUW1UamhKQXhlZXVBMy1LZ1dPUEJiRksza0I4R2t6RzgyaEVid3EtRVdrMWRjMW5fckQ2SmtVVVQ5c1pOMGk2ZHlEdXcwbTNEUXdwc3FLd0w4T2l4bXpnNXF1clp2UmZYWUhlWlVrRnlxaTBxLWM1S1E4QnlXekdzMjZ3M2EzbGlvWWNyaFFZajQ5WDdieFBFVlpqalhqVDRxSDhUaDhDRG5FSDdLc0VmcWFSbjVZZnV6bEQ5d21Bdk7SAcgBQVVfeXFMTjVWaVFCWTdzQmcxa3Z2OWFIV19LbFh0amRITEJIUzR2b2Zjem1YaEwtNk9hZW1majBpTmxJQ094NTNwa2w2dG9ZampzQnd3VEIyRlhRX0I1bDlWY091amVzOERJQXhtUnpHbkh4SFB0YzZPRUwwQ1R1empjUmYtbW54eHVET0xybmJBUktEWU1rZXl6N0hJc0VHRjV2aDJNUTlmODlyOUp3TXpWZ2FCRGdOX2xkUXNPdlhuUVBpS2VTT0ZSZWp1Vm0?oc=5" target="_blank"&gt;Air France flight AF99 to Paris declared an emergency and just diverted to Dublin&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQUW1UamhKQXhlZXVBMy1LZ1dPUEJiRksza0I4R2t6RzgyaEVid3EtRVdrMWRjMW5fckQ2SmtVVVQ5c1pOMGk2ZHlEdXcwbTNEUXdwc3FLd0w4T2l4bXpnNXF1clp2UmZYWUhlWlVrRnlxaTBxLWM1S1E4QnlXekdzMjZ3M2EzbGlvWWNyaFFZajQ5WDdieFBFVlpqalhqVDRxSDhUaDhDRG5FSDdLc0VmcWFSbjVZZnV6bEQ5d21Bdk7SAcgBQVVfeXFMTjVWaVFCWTdzQmcxa3Z2OWFIV19LbFh0amRITEJIUzR2b2Zjem1YaEwtNk9hZW1majBpTmxJQ094NTNwa2w2dG9ZampzQnd3VEIyRlhRX0I1bDlWY091amVzOERJQXhtUnpHbkh4SFB0YzZPRUwwQ1R1empjUmYtbW54eHVET0xybmJBUktEWU1rZXl6N0hJc0VHRjV2aDJNUTlmODlyOUp3TXpWZ2FCRGdOX2xkUXNPdlhuUVBpS2VTT0ZSZWp1Vm0?oc=5</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr"/>
+      <c r="L575" t="inlineStr"/>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O575"/>
+  <dimension ref="A1:O580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35425,7 +35425,6 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="D565" t="inlineStr"/>
       <c r="E565" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35456,8 +35455,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
-      <c r="L565" t="inlineStr"/>
       <c r="M565" t="inlineStr">
         <is>
           <t>review</t>
@@ -35490,7 +35487,6 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35521,8 +35517,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
-      <c r="L566" t="inlineStr"/>
       <c r="M566" t="inlineStr">
         <is>
           <t>review</t>
@@ -35555,7 +35549,6 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35586,8 +35579,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
-      <c r="L567" t="inlineStr"/>
       <c r="M567" t="inlineStr">
         <is>
           <t>review</t>
@@ -35620,7 +35611,6 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr"/>
       <c r="E568" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35651,8 +35641,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
-      <c r="L568" t="inlineStr"/>
       <c r="M568" t="inlineStr">
         <is>
           <t>review</t>
@@ -35685,7 +35673,6 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="D569" t="inlineStr"/>
       <c r="E569" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35716,8 +35703,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
-      <c r="L569" t="inlineStr"/>
       <c r="M569" t="inlineStr">
         <is>
           <t>review</t>
@@ -35750,7 +35735,6 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="D570" t="inlineStr"/>
       <c r="E570" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35781,8 +35765,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
-      <c r="L570" t="inlineStr"/>
       <c r="M570" t="inlineStr">
         <is>
           <t>review</t>
@@ -35815,7 +35797,6 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="D571" t="inlineStr"/>
       <c r="E571" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35846,8 +35827,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
-      <c r="L571" t="inlineStr"/>
       <c r="M571" t="inlineStr">
         <is>
           <t>review</t>
@@ -35880,7 +35859,6 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr"/>
       <c r="E572" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35911,8 +35889,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
-      <c r="L572" t="inlineStr"/>
       <c r="M572" t="inlineStr">
         <is>
           <t>review</t>
@@ -35945,7 +35921,6 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -35976,8 +35951,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
-      <c r="L573" t="inlineStr"/>
       <c r="M573" t="inlineStr">
         <is>
           <t>review</t>
@@ -36010,7 +35983,6 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -36041,8 +36013,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
-      <c r="L574" t="inlineStr"/>
       <c r="M574" t="inlineStr">
         <is>
           <t>review</t>
@@ -36075,7 +36045,6 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="D575" t="inlineStr"/>
       <c r="E575" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -36106,8 +36075,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
-      <c r="L575" t="inlineStr"/>
       <c r="M575" t="inlineStr">
         <is>
           <t>review</t>
@@ -36119,6 +36086,331 @@
         </is>
       </c>
       <c r="O575" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>auto-cd8b721133c2</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Boeing liefert 200. Boeing 737-800 BCF aus</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr"/>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>Boeing hat die 200. 737-800 BCF ausgeliefert. Das aus einem Passagierflugzeug zum Frachter umgebaute Flugzeug wurde Anfang Oktober bei einer Feier in Auckland in Neuseeland vorgestellt. Es trägt eine Sonderlackierung zum Produktionsjubiläum.</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/boeing-liefert-200-boeing-737-800-bcf-aus/y6e5l2y</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr"/>
+      <c r="L576" t="inlineStr"/>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>auto-0c5d00056383</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Atlas Air könnte bis zu 60 Airbus A350F übernehmen</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr"/>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>Die US-amerikanische Frachtfluggesellschaft Atlas Air hat ihre Vereinbarung mit Airbus über den neuen Frachter A350F erweitert. Das Unternehmen sicherte sich zusätzliche Kaufrechte für 20 Flugzeuge. Damit könnte die künftige Flotte auf bis zu 60 Exemplare anwachsen. Das erklärte Strategie- und Transformationschef Martin Drew bei einer Konferenz, wie das Portal Aviation Week berichtet. Die neuen Kaufrechte ergänzen die bereits bestehenden Bestellungen und Optionen.</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/atlas-air-koennte-bis-zu-60-airbus-a350f-uebernehmen/5n1vsjs</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr"/>
+      <c r="L577" t="inlineStr"/>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>auto-32dd848c611c</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Ungesicherte 2,6-Tonnen-Palette legt Airbus A330 Neo von Azul seit einem halben Jahr lahm</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr"/>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Bei der Landung in Lissabon rutschte im Frachtraum eines Airbus A330 Neo von Azul eine fast 2,6 Tonnen schwere Palette nach vorne. Die Schäden halten den Großraumjet seit einem halben Jahr am Boden. Das ist auch für eine andere Fluggesellschaft ärgerlich.</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugzeuge/airbus-a330-neo-von-azul-ist-seit-april-in-lissabon-gestrandet-wegen-ungesicherter/xtcv9m4</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr"/>
+      <c r="L578" t="inlineStr"/>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>auto-04c34a3cfbd1</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Discover Airlines fliegt nach Seattle, Lufthansa nach Columbus</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr"/>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa baut ihren Nordamerika-Flugplan 2027 an einem markanten Netzpunkt um - die Verbindungen von Frankfurt und München nach Seattle gehen an Discover Airlines über. Zwei neue USA-Linien zieht Lufthansa mit eigenen Boeing 787-9 und Airbus A350-900 hoch.</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54002/Discover-Airlines-fliegt-nach-Seattle-Lufthansa-nach-Columbus.html</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr"/>
+      <c r="L579" t="inlineStr"/>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>auto-41fbcf9cdce1</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Honeywell Tech hebt Prognose an</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr"/>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>CHARLOTTE - Honeywell Technologies hat im dritten Quartal von einer breit angelegten Nachfrage in seinen wichtigsten Absatzmärkten profitiert und hebt seine Ziele für das Jahr an.</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53997/Honeywell-Tech-hebt-Prognose-an.html</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr"/>
+      <c r="L580" t="inlineStr"/>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O580"/>
+  <dimension ref="A1:O600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36107,7 +36107,6 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -36138,8 +36137,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
-      <c r="L576" t="inlineStr"/>
       <c r="M576" t="inlineStr">
         <is>
           <t>review</t>
@@ -36172,7 +36169,6 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="D577" t="inlineStr"/>
       <c r="E577" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -36203,8 +36199,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
-      <c r="L577" t="inlineStr"/>
       <c r="M577" t="inlineStr">
         <is>
           <t>review</t>
@@ -36237,7 +36231,6 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="D578" t="inlineStr"/>
       <c r="E578" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -36268,8 +36261,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
-      <c r="L578" t="inlineStr"/>
       <c r="M578" t="inlineStr">
         <is>
           <t>review</t>
@@ -36302,7 +36293,6 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="D579" t="inlineStr"/>
       <c r="E579" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -36333,8 +36323,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
-      <c r="L579" t="inlineStr"/>
       <c r="M579" t="inlineStr">
         <is>
           <t>review</t>
@@ -36367,7 +36355,6 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr"/>
       <c r="E580" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -36398,8 +36385,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
-      <c r="L580" t="inlineStr"/>
       <c r="M580" t="inlineStr">
         <is>
           <t>review</t>
@@ -36411,6 +36396,1306 @@
         </is>
       </c>
       <c r="O580" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>auto-beff156bca33</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Fahrwerk von Boeing 747-8 F von Cargolux in Luxemburg eingeknickt</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr"/>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Bei einer Boeing 747-8 F von Cargolux ist am Freitagmorgen (23. Oktober) am Flughafen Luxemburg das linke Tragflächenfahrwerk eingeknickt. Das Frachtflugzeug mit der Registrierung LX-VCF befand sich zum Zeitpunkt des Vorfalls auf seiner Parkposition. Verletzt wurde niemand. Die Bergung des Flugzeugs läuft in Abstimmung mit den zuständigen Behörden.</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/fahrwerk-von-boeing-747-8-f-von-cargolux-in-luxemburg-eingeknickt/93sqm13</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr"/>
+      <c r="L581" t="inlineStr"/>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>auto-1894ce011ef1</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Hynaero und Helibravo kooperieren bei neuem Löschflugzeug</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr"/>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>Der französische Flugzeugentwickler Hynaero und das portugiesische Luftfahrtunternehmen Helibravo Aviação haben eine Absichtserklärung zur Zusammenarbeit beim Löschflugzeug Fregate-F100 unterzeichnet. Helibravo soll seine operative Erfahrung und Marktkenntnisse in Portugal und auf der Iberischen Halbinsel einbringen. Gemeinsam wollen die Unternehmen die Entwicklung und Vermarktung des neuen amphibischen Löschflugzeugs vorantreiben. Die Fregate-F100 soll bis zu zehn Tonnen Wasser aufnehmen können und eine Reisegeschwindigkeit von 250 Knoten erreichen. Sie ist als Nachfolger für alternde Löschflugzeugflotten konzipiert. Das Programm soll zudem mehr als 2500 Arbeitsplätze in der Endmontage und der Zulieferindustrie schaffen.</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/hynaero-und-helibravo-kooperieren-bei-neuem-loeschflugzeug/718ewz7</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr"/>
+      <c r="L582" t="inlineStr"/>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>auto-62855da77b0a</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Das bietet der Winterflugplan 2026/27 am Flughafen Leipzig/Halle</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr"/>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>Am 25. Oktober beginnt an den Flughäfen Leipzig/Halle und Dresden der Winterflugplan, der bis zum 27. März 2027 gilt. Ab Leipzig/Halle werden bis zu elf Ziele in sechs Ländern von elf Fluggesellschaften bedient. Neu ist eine wöchentliche Verbindung von Freebird Europe nach Assuan in Ägypten, die vom 26. Oktober bis zum 30. November angeboten wird. Lufthansa fliegt bis zu 21-mal wöchentlich nach Frankfurt, Austrian Airlines bis zu sechsmal nach Wien. Ab Dresden stehen bis zu neun Ziele in sieben Ländern im Flugplan. Neu ist Chișinău in Moldau, das FLYONE ab dem 17. Dezember zweimal wöchentlich anfliegt. Lufthansa bietet bis zu 21 Flüge nach Frankfurt und 17 nach München pro Woche an. Swiss verbindet Dresden bis zu sechsmal wöchentlich mit Zürich. Hinzu kommen unter anderem Verbindungen nach Düsseldorf, Bozen und zu Urlaubszielen am Mittelmeer.</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/das-bietet-der-winterflugplan-202627-am-flughafen-leipzighalle/qwwtpxg</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr"/>
+      <c r="L583" t="inlineStr"/>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>auto-2fd93afb1180</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Drohnen, Cyberangriffe und Flugtaxis: Wo das Luftfahrtrecht an seine Grenzen stößt</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr"/>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>Eine einzige Drohne kann Tausende Passagiere stranden lassen, ein Cyberangriff den Flugverkehr lahmlegen. Doch wer trägt die Kosten? Im Interview geht ein Luftrechtsexperte den juristischen Fragen hinter aktuellen Entwicklungen nach - von den neuen EU-Fluggastrechten bis zur Haftung bei autonomen Flugzeugen. Sechs Fragen, sechs Antworten.</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/kolumnen/drohnen-cyberangriffe-und-flugtaxis-wo-das-luftfahrtrecht-an-seine-grenzen-stoesst/31qn7yq</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr"/>
+      <c r="L584" t="inlineStr"/>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>auto-213416a6e05b</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Lufthansa Group verschiebt Rückkehr nach Dubai um einen Monat</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr"/>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>Die Lufthansa Group verschiebt die geplante Wiederaufnahme ihrer Flüge nach Dubai auf den 25. November 2026. Grund sind die aktuelle Lage im Nahen Osten und die Einschätzung der weiteren Entwicklung. Ursprünglich sollten Lufthansa und Swiss ihre Verbindungen in die Vereinigten Arabischen Emirate am 25. Oktober wieder aufnehmen. Eurowings hatte einen Neustart für den 1. November vorgesehen. Damit verlängert der Konzern die Flugpause um rund einen Monat. Betroffene Passagiere werden von den jeweiligen Fluggesellschaften direkt informiert. Sie können ihre Flüge flexibel umbuchen oder sich den Ticketpreis vollständig erstatten lassen.</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lufthansa-group-verschiebt-rueckkehr-nach-dubai-um-einen-monat/fzxn9pk</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr"/>
+      <c r="L585" t="inlineStr"/>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>auto-dfc8bcf033b1</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Lufthansa setzt Verbindung Frankfurt - Turin im Sommer 2027 aus</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr"/>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>Nach 55 Jahren wird die Flugverbindung zwischen Frankfurt und Turin im Sommerflugplan 2027 ausgesetzt. Wie die Zeitung La Stampa berichtet, streicht Lufthansa die Strecke vom 28. März bis zum 30. Oktober. Der Flughafenbetreiber Sagat bestätigte die Entscheidung und verwies auf eine strategische Überprüfung des Streckennetzes der Lufthansa-Gruppe. Als Gründe werden die geopolitische Lage, gestiegene Treibstoffkosten und Kapazitätsengpässe genannt.</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lufthansa-setzt-verbindung-frankfurt-turin-im-sommer-2027-aus/6pdlt7r</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr"/>
+      <c r="L586" t="inlineStr"/>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>auto-073853cc822f</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Piloten von Pegasus Airlines wollen in Frankfurt in die falsche Richtung starten</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr"/>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>Ein Airbus A321 Neo von Pegasus Airlines sollte von Frankfurt nach Istanbul fliegen. Doch obwohl die Crew eine Startfreigabe Richtung Süden hatte, beschleunigte sie in die entgegengesetzte Richtung. Erst ein Funkspruch der Fluglotsen stoppte den Startversuch.</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/sicherheit/airbus-a321-neo-von-pegasus-startet-am-flughafen-frankfurt-in-die-falsche-richtung/8rmjb60</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr"/>
+      <c r="L587" t="inlineStr"/>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>auto-2428ca5d8d24</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Emirates fliegt vorerst nicht vom BER</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr"/>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Emirates-Flüge vom BER schienen ausgemachte Sache. Nun droht der Deal zu platzen - Emirates verzichtet bis auf Weiteres auf Flüge aus Berlin nach Dubai. Die staatliche Fluggesellschaft sieht Klärungsbedarf bei der Auslegung eines Zusatzes zum Luftverkehrsabekommen zwischen den VAE und Deutschland.</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54010/Emirates-fliegt-vorerst-nicht-vom-BER.html</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr"/>
+      <c r="L588" t="inlineStr"/>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>auto-371ec48044fa</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Lufthansa verschiebt Wiederaufnahme von Flügen nach Dubai</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr"/>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Im Nahen Osten zeichnet sich kaum Entspannung ab. Lufthansa stellt die Wiederaufnahme ihrer Dubai-Linien kurzfristig einige Wochen zurück.</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54008/Lufthansa-verschiebt-Wiederaufnahme-von-Fluegen-nach-Dubai.html</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr"/>
+      <c r="L589" t="inlineStr"/>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>auto-ce7bf8d5c9ec</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Alles oder nichts</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr"/>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Drei Schlichtungen bei Lufthansa verlaufen im Sand. Alle Augen richten sich jetzt auf die Mediation. Scheitert auch dieses Verfahren, droht dem Konzern 2027 eine neuerliche Eskalation mit den Piloten bei Lufthansa Classic und Lufthansa Cargo - denn in einem wesentlichen Tarifvertrag tickt die Uhr.</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54005/Alles-oder-nichts.html</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr"/>
+      <c r="L590" t="inlineStr"/>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>auto-2c84fddd49ec</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Safran kann Triebwerksauslieferungen steigern</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr"/>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>PARIS - Der Triebwerksbauer und Luftfahrt-Zulieferer Safran hat auch im Sommer stärker zugelegt als gedacht.</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54007/Safran-kann-Triebwerksauslieferungen-steigern.html</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr"/>
+      <c r="L591" t="inlineStr"/>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>auto-07e50e901803</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Airbus A321neo rollt in falscher Richtung auf Startbahn ein</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr"/>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Ein Airbus A321neo von Pegasus Airlines positioniert sich auf der Westbahn am Flughafen Frankfurt in falscher Startrichtung - und rollt an. Die Flugsicherung unterbindet die Geisterfahrt rechtzeitig, meldet den Zwischenfall an Bundesstelle für Flugunfalluntersuchung (BFU).</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54006/Airbus-A321neo-setzt-in-falscher-Richtung-zum-Start-an.html</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr"/>
+      <c r="L592" t="inlineStr"/>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>auto-52645ea7c129</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt: Diese Airlines starten ab dem 19. Mai vom neuen Terminal 3 - Main-Post</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr"/>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMivwFBVV95cUxNN0FNYk01c25kTTJLakowNDZKVkpXRUVGWWk1V2lwZ1dSZl9PU052Z1NjcDdVYkdldDVwamo1WHJjTkdlRHFBZXlOZUtoVmk4N1d2MFVINHY1ZUZjLWc0ejVQb1ZUbWVfRmhfaHVkRlVjMnFhMkpZYjBOVjV4d3Y2Tk9JV25xN0FKQXBDTlpJMXJxUG11RFJlZHFqUUdQVWtaejE0M0NFZWxaWmNaQWg0eTI4dW1OV1RGVkp4akQ5dw?oc=5" target="_blank"&gt;Flughafen Frankfurt: Diese Airlines starten ab dem 19. Mai vom neuen Terminal 3&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Main-Post&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNN0FNYk01c25kTTJLakowNDZKVkpXRUVGWWk1V2lwZ1dSZl9PU052Z1NjcDdVYkdldDVwamo1WHJjTkdlRHFBZXlOZUtoVmk4N1d2MFVINHY1ZUZjLWc0ejVQb1ZUbWVfRmhfaHVkRlVjMnFhMkpZYjBOVjV4d3Y2Tk9JV25xN0FKQXBDTlpJMXJxUG11RFJlZHFqUUdQVWtaejE0M0NFZWxaWmNaQWg0eTI4dW1OV1RGVkp4akQ5dw?oc=5</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr"/>
+      <c r="L593" t="inlineStr"/>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>auto-10da1d1847d8</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt: AiRail-Terminal wird dauerhaft geschlossen - Travel-Dealz</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr"/>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMic0FVX3lxTE54NktWTmN1cHVPVzlMQWR2OXRtM0gxdDN2dTRMcW5La0JEaUpuYklrbEZzdFFOb0QxdVcybDBMc1BhbkttaGNFV2RQb0VfcFFvakZZQlpRZ29CdU9DbkZIZ09RUlJISVZXM1J2WjFBRGYwMzg?oc=5" target="_blank"&gt;Flughafen Frankfurt: AiRail-Terminal wird dauerhaft geschlossen&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Travel-Dealz&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE54NktWTmN1cHVPVzlMQWR2OXRtM0gxdDN2dTRMcW5La0JEaUpuYklrbEZzdFFOb0QxdVcybDBMc1BhbkttaGNFV2RQb0VfcFFvakZZQlpRZ29CdU9DbkZIZ09RUlJISVZXM1J2WjFBRGYwMzg?oc=5</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr"/>
+      <c r="L594" t="inlineStr"/>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>auto-06e09718152a</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Winterflugplan 2026/27: Frankfurt erweitert Angebot auf vier Kontinenten - Osthessen|News</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr"/>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMisgFBVV95cUxOYjhhd3Y3QTZaZ3FwdGlJbFJVZjJtSG5JbzdldEhQZGFYVVhTNFZvRk51dVU1UklENm0wWFlFd1RieFMzandIeFRuTVQ4WDlSZmRsZjZlVFBlRjFFa1JScUFEWTd0S0RfSmJKZlFPWUtiNVZKY2hNZ3hTRlhEcW9YVnpLQnlaWkpKb1U0YUQ1ZmJ3Mk5vdnBWWEF6WW9lZjBNOXpJOG9pOG1LNHNSbHVDeldn?oc=5" target="_blank"&gt;Winterflugplan 2026/27: Frankfurt erweitert Angebot auf vier Kontinenten&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Osthessen|News&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOYjhhd3Y3QTZaZ3FwdGlJbFJVZjJtSG5JbzdldEhQZGFYVVhTNFZvRk51dVU1UklENm0wWFlFd1RieFMzandIeFRuTVQ4WDlSZmRsZjZlVFBlRjFFa1JScUFEWTd0S0RfSmJKZlFPWUtiNVZKY2hNZ3hTRlhEcW9YVnpLQnlaWkpKb1U0YUQ1ZmJ3Mk5vdnBWWEF6WW9lZjBNOXpJOG9pOG1LNHNSbHVDeldn?oc=5</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr"/>
+      <c r="L595" t="inlineStr"/>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>auto-99943df6b4ff</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt: An diesem Tag wird das neue Terminal eröffnet - hessenschau.de</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr"/>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMizgFBVV95cUxOWERseVNMajhpZTV2Y3VOSUZqSFRXbnVSWFg3aVVjTHJsazRnUVpUcVJfZExhNGl5eVViS21lNHhXeXJIUE1RbDd1akE5VEhIN3NMUTFxVkRRT1d0czFWQ3N3bld6S0xncUlETEVqUi1laElVbnBQUUgydmZwRGVEcVpjUldSdG9fVFpqTFpPTnl4SEljOXRGOEx3UEkyUEtCYkR6SzdudkRvNDF6TDFQbWFiU0lGYktCdm9Ec2Q3bGU1eDBCdFFTNTRhTGloQQ?oc=5" target="_blank"&gt;Flughafen Frankfurt: An diesem Tag wird das neue Terminal eröffnet&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;hessenschau.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOWERseVNMajhpZTV2Y3VOSUZqSFRXbnVSWFg3aVVjTHJsazRnUVpUcVJfZExhNGl5eVViS21lNHhXeXJIUE1RbDd1akE5VEhIN3NMUTFxVkRRT1d0czFWQ3N3bld6S0xncUlETEVqUi1laElVbnBQUUgydmZwRGVEcVpjUldSdG9fVFpqTFpPTnl4SEljOXRGOEx3UEkyUEtCYkR6SzdudkRvNDF6TDFQbWFiU0lGYktCdm9Ec2Q3bGU1eDBCdFFTNTRhTGloQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr"/>
+      <c r="L596" t="inlineStr"/>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>auto-da1f53d53e33</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Lufthansa möchte Terminal 2 in Frankfurt gemeinsam mit Fraport betreiben - meilenoptimieren</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr"/>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMibEFVX3lxTE5UdGJJVFJ0YlprdFZPbDgzTW0xODdERi0xU0ZjUThqTGhnZkF1YmN2Z1RzTS03aDFaWDhOVjN6Y3Vob0tybV9Jd2N3QVRJRHZXbFFYdzNWOTZrZ09MZVhNUUtKY1dHUUNDaXltLQ?oc=5" target="_blank"&gt;Lufthansa möchte Terminal 2 in Frankfurt gemeinsam mit Fraport betreiben&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;meilenoptimieren&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5UdGJJVFJ0YlprdFZPbDgzTW0xODdERi0xU0ZjUThqTGhnZkF1YmN2Z1RzTS03aDFaWDhOVjN6Y3Vob0tybV9Jd2N3QVRJRHZXbFFYdzNWOTZrZ09MZVhNUUtKY1dHUUNDaXltLQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr"/>
+      <c r="L597" t="inlineStr"/>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>auto-60e2eb5be7f4</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Frankfurt: Fraport stoppt Terminal-1-Projekt und plant Generalsanierung von Terminal 2 - Aviation.Direct</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr"/>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirgFBVV95cUxNbzJKSWpnYklGSlBqTjJJakZUSEtXcGpQNWV1cnR1LU9mVzZCNVZibTBiSllDdUVQdW9vaTJFeHRxR3NqZHVycVNTZ1VBYWRJTGNTUF9Hd3hualJxc2dBYWxyN29TLVh1a0g1NHFROFJyNVJ2Z2NNLUM2dExidFdOc3lsZjJRWVU2NjVFT2hNMmozMVBVNVZaeTZSWkhWWDFDaVNRcmJtd1k2ZHZSaWc?oc=5" target="_blank"&gt;Frankfurt: Fraport stoppt Terminal-1-Projekt und plant Generalsanierung von Terminal 2&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Aviation.Direct&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNbzJKSWpnYklGSlBqTjJJakZUSEtXcGpQNWV1cnR1LU9mVzZCNVZibTBiSllDdUVQdW9vaTJFeHRxR3NqZHVycVNTZ1VBYWRJTGNTUF9Hd3hualJxc2dBYWxyN29TLVh1a0g1NHFROFJyNVJ2Z2NNLUM2dExidFdOc3lsZjJRWVU2NjVFT2hNMmozMVBVNVZaeTZSWkhWWDFDaVNRcmJtd1k2ZHZSaWc?oc=5</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr"/>
+      <c r="L598" t="inlineStr"/>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>auto-9ab344af1359</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Flughafenentgelte - Fraport AG</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr"/>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMif0FVX3lxTE5Rb2R1VF9jMUQ3OGdDTlRvV1lPLURhVFJxbFMzWDFieklZRmZWb1dSb1JjX1NfNDVpVjlqRC1RbGJGbzhicjlwbll4T3p4UWhrdjhtNWhEaXdMMkgyLVNtalF3Z0xaOFBFMlIzMDIteVBXLTI3eVgwOEw3bmdUVEk?oc=5" target="_blank"&gt;Flughafenentgelte&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Fraport AG&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5Rb2R1VF9jMUQ3OGdDTlRvV1lPLURhVFJxbFMzWDFieklZRmZWb1dSb1JjX1NfNDVpVjlqRC1RbGJGbzhicjlwbll4T3p4UWhrdjhtNWhEaXdMMkgyLVNtalF3Z0xaOFBFMlIzMDIteVBXLTI3eVgwOEw3bmdUVEk?oc=5</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr"/>
+      <c r="L599" t="inlineStr"/>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>auto-f6257ac4ffa7</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Flughafen Graz: Vier neue Airlines im Sommer 2027 – mehr Frankfurt und München im Winter - airportzentrale.de</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr"/>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWTJScm9za1V0RHczZUw2ZlpVbDA3S2V1SUJoaGstLWx5cFVZejhRZ191YlFxcmN3emQ5TmxDZU9LWXdwY2dwSjBITjdvSkh3R1B4WmRtVmwtOV91eUZrMm45ZDdZU1V1MjdJZzRNVVJYbXBDbV82QTRLQ0VvOFhHc0tKTEMxWGVDSDVvYjNKSmk0SWhOelNMcFI0ZWVwVVA5VnhqRW0ydGlscGFjcjRrR3FHbDRqbmdFRDRIc3FIc0lpUQ?oc=5" target="_blank"&gt;Flughafen Graz: Vier neue Airlines im Sommer 2027 – mehr Frankfurt und München im Winter&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airportzentrale.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWTJScm9za1V0RHczZUw2ZlpVbDA3S2V1SUJoaGstLWx5cFVZejhRZ191YlFxcmN3emQ5TmxDZU9LWXdwY2dwSjBITjdvSkh3R1B4WmRtVmwtOV91eUZrMm45ZDdZU1V1MjdJZzRNVVJYbXBDbV82QTRLQ0VvOFhHc0tKTEMxWGVDSDVvYjNKSmk0SWhOelNMcFI0ZWVwVVA5VnhqRW0ydGlscGFjcjRrR3FHbDRqbmdFRDRIc3FIc0lpUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr"/>
+      <c r="L600" t="inlineStr"/>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O600" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O600"/>
+  <dimension ref="A1:O603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36417,7 +36417,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -36448,8 +36447,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
-      <c r="L581" t="inlineStr"/>
       <c r="M581" t="inlineStr">
         <is>
           <t>review</t>
@@ -36482,7 +36479,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr"/>
       <c r="E582" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -36513,8 +36509,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
-      <c r="L582" t="inlineStr"/>
       <c r="M582" t="inlineStr">
         <is>
           <t>review</t>
@@ -36547,7 +36541,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D583" t="inlineStr"/>
       <c r="E583" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -36578,8 +36571,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
-      <c r="L583" t="inlineStr"/>
       <c r="M583" t="inlineStr">
         <is>
           <t>review</t>
@@ -36612,7 +36603,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D584" t="inlineStr"/>
       <c r="E584" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -36643,8 +36633,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
-      <c r="L584" t="inlineStr"/>
       <c r="M584" t="inlineStr">
         <is>
           <t>review</t>
@@ -36677,7 +36665,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D585" t="inlineStr"/>
       <c r="E585" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -36708,8 +36695,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
-      <c r="L585" t="inlineStr"/>
       <c r="M585" t="inlineStr">
         <is>
           <t>review</t>
@@ -36742,7 +36727,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D586" t="inlineStr"/>
       <c r="E586" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -36773,8 +36757,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
-      <c r="L586" t="inlineStr"/>
       <c r="M586" t="inlineStr">
         <is>
           <t>review</t>
@@ -36807,7 +36789,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -36838,8 +36819,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
-      <c r="L587" t="inlineStr"/>
       <c r="M587" t="inlineStr">
         <is>
           <t>review</t>
@@ -36872,7 +36851,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -36903,8 +36881,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
-      <c r="L588" t="inlineStr"/>
       <c r="M588" t="inlineStr">
         <is>
           <t>review</t>
@@ -36937,7 +36913,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -36968,8 +36943,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
-      <c r="L589" t="inlineStr"/>
       <c r="M589" t="inlineStr">
         <is>
           <t>review</t>
@@ -37002,7 +36975,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D590" t="inlineStr"/>
       <c r="E590" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -37033,8 +37005,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
-      <c r="L590" t="inlineStr"/>
       <c r="M590" t="inlineStr">
         <is>
           <t>review</t>
@@ -37067,7 +37037,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D591" t="inlineStr"/>
       <c r="E591" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -37098,8 +37067,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
-      <c r="L591" t="inlineStr"/>
       <c r="M591" t="inlineStr">
         <is>
           <t>review</t>
@@ -37132,7 +37099,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr"/>
       <c r="E592" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -37163,8 +37129,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
-      <c r="L592" t="inlineStr"/>
       <c r="M592" t="inlineStr">
         <is>
           <t>review</t>
@@ -37197,7 +37161,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D593" t="inlineStr"/>
       <c r="E593" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -37228,8 +37191,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
-      <c r="L593" t="inlineStr"/>
       <c r="M593" t="inlineStr">
         <is>
           <t>review</t>
@@ -37262,7 +37223,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D594" t="inlineStr"/>
       <c r="E594" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -37293,8 +37253,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
-      <c r="L594" t="inlineStr"/>
       <c r="M594" t="inlineStr">
         <is>
           <t>review</t>
@@ -37327,7 +37285,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D595" t="inlineStr"/>
       <c r="E595" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -37358,8 +37315,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
-      <c r="L595" t="inlineStr"/>
       <c r="M595" t="inlineStr">
         <is>
           <t>review</t>
@@ -37392,7 +37347,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D596" t="inlineStr"/>
       <c r="E596" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -37423,8 +37377,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
-      <c r="L596" t="inlineStr"/>
       <c r="M596" t="inlineStr">
         <is>
           <t>review</t>
@@ -37457,7 +37409,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D597" t="inlineStr"/>
       <c r="E597" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -37488,8 +37439,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
-      <c r="L597" t="inlineStr"/>
       <c r="M597" t="inlineStr">
         <is>
           <t>review</t>
@@ -37522,7 +37471,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -37553,8 +37501,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
-      <c r="L598" t="inlineStr"/>
       <c r="M598" t="inlineStr">
         <is>
           <t>review</t>
@@ -37587,7 +37533,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -37618,8 +37563,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
-      <c r="L599" t="inlineStr"/>
       <c r="M599" t="inlineStr">
         <is>
           <t>review</t>
@@ -37652,7 +37595,6 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -37683,8 +37625,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
-      <c r="L600" t="inlineStr"/>
       <c r="M600" t="inlineStr">
         <is>
           <t>review</t>
@@ -37696,6 +37636,201 @@
         </is>
       </c>
       <c r="O600" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>auto-a22573c2e8cf</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Zulieferer Ontic startet Austauschprogramm für Vorflügelklappen der Boeing 747</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr"/>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>Der britische Luftfahrtzulieferer Ontic führt unter dem Namen Cargo Care ein neues Wartungsprogramm für Frachtflugzeuge ein. Das Unternehmen übernimmt häufig Produktlinien etablierter Hersteller, um die Versorgung mit Ersatzteilen und deren Wartung langfristig sicherzustellen. Als erstes Cargo-Care-Angebot umfasst das Programm den Austausch und die Überholung von Antrieben für die Vorflügelklappen der Boeing 747.</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/zulieferer-ontic-startet-austauschprogramm-fuer-vorfluegelklappen-der-boeing-747/f01zr74</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr"/>
+      <c r="L601" t="inlineStr"/>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>auto-3c36c742456d</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>"Mit GCAP hätten wir eher einen Bomber"</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr"/>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Der deutsch-französische Kampfjet FCAS - gescheitert. Nun steht die Bundesregierung vor der Wahl: Spurwechsel ins GCAP-Konsortium - oder doch ein eigenes Fighter-Programm. Airbus-Defence-Chef Michael Schöllhorn lässt in einem Interview mit dem "Handelsblatt" eine klare Präferenz durchblicken.</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53987/Mit-GCAP-haetten-wir-eher-einen-Bomber.html</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr"/>
+      <c r="L602" t="inlineStr"/>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>auto-9e86d7d34561</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Air France flight makes emergency landing in Germany after technical issue - Anadolu Ajansı</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr"/>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirwFBVV95cUxOY2IwdnRzSEFBUmhrOXlKQXhuYTNlU0JIaHc1ZXNvYUFuV2dzQ0JzUUloNFpYXzdPTlF2QVJ5TjhfZ3UxbHNnYThkU2ZZOXV5UUU1SE1UU1Y4a3JnTmhPaE81RkN0SC14YkhhazR5UDRxM0txcVlFZDcyUEVaeko1SGVrcldzWGhjRDNlQ0p0ME05VUkwc1pKZ2U3SFl1VHR3UGhFMjFwNkI3dkJTZkNN?oc=5" target="_blank"&gt;Air France flight makes emergency landing in Germany after technical issue&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Anadolu Ajansı&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOY2IwdnRzSEFBUmhrOXlKQXhuYTNlU0JIaHc1ZXNvYUFuV2dzQ0JzUUloNFpYXzdPTlF2QVJ5TjhfZ3UxbHNnYThkU2ZZOXV5UUU1SE1UU1Y4a3JnTmhPaE81RkN0SC14YkhhazR5UDRxM0txcVlFZDcyUEVaeko1SGVrcldzWGhjRDNlQ0p0ME05VUkwc1pKZ2U3SFl1VHR3UGhFMjFwNkI3dkJTZkNN?oc=5</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr"/>
+      <c r="L603" t="inlineStr"/>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O603"/>
+  <dimension ref="A1:O614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37657,7 +37657,6 @@
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -37688,8 +37687,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
-      <c r="L601" t="inlineStr"/>
       <c r="M601" t="inlineStr">
         <is>
           <t>review</t>
@@ -37722,7 +37719,6 @@
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -37753,8 +37749,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
-      <c r="L602" t="inlineStr"/>
       <c r="M602" t="inlineStr">
         <is>
           <t>review</t>
@@ -37787,7 +37781,6 @@
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="D603" t="inlineStr"/>
       <c r="E603" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -37818,8 +37811,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
-      <c r="L603" t="inlineStr"/>
       <c r="M603" t="inlineStr">
         <is>
           <t>review</t>
@@ -37831,6 +37822,721 @@
         </is>
       </c>
       <c r="O603" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>auto-9adfdeda4560</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Condor macht Airbus A320 Neo zum neuen Eintracht-Frankfurt-Flieger</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr"/>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>Seit einem Jahr &lt;a href="https://www.aerotelegraph.com/flugzeuge/ein-blick-auf-und-in-den-eintracht-frankfurt-flieger-von-condor/wjn4f19" id="b9b636da-9a12-41bf-879a-b02b3b2dfaff"&gt;betreibt Condor einen Airbus A320 Ceo im Eintracht-Frankfurt-Design&lt;/a&gt;. Doch im Frühjahr 2027 kommt die Ablösung für den Jet mit dem Kennzeichen D-ASGE: Ein neuer A320 Neo wird dann die schwarz-weißen Streifen und dem Eintracht-Adler auf dem Heck tragen. Die Lackierung werde «nahezu unverändert» aussehen, so die deutsche Fluggesellschaft. «Auch die Gestaltung des Innenraums soll so weit wie technisch möglich übernommen werden und lediglich um ein paar optimierte Details erweitert werden.»</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/condor-macht-airbus-a320-neo-zum-neuen-eintracht-frankfurt-flieger/xpx9c0w</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr"/>
+      <c r="L604" t="inlineStr"/>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>auto-2d3619516bcf</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Das bietet ITA Airways in der Premium Economy im Airbus A321 LR</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr"/>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>Als einzige Fluggesellschaft innerhalb von Lufthansa Group fliegt ITA Airways mit Airbus A321 LR - und das mit drei Reiseklassen. Was bietet die italienische Fluglinie dort? aeroTELEGRAPH hat die Premium Economy getestet.</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugtests/ita-airways-im-flugtest-das-bietet-die-premium-economy-im-airbus-a321-lr/2y849b4</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr"/>
+      <c r="L605" t="inlineStr"/>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>auto-ae900244d689</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Powerbank überhitzt auf Flug von HK Express - Passagierin verletzt</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr"/>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>Auf einem Flug von HK Express von Hongkong nach Jeju in Südkorea ist am Sonntag eine Powerbank überhitzt und hat Rauch entwickelt. Der Vorfall ereignete sich auf Flug UO676 mit 236 Passagieren und sieben Besatzungsmitgliedern kurz vor der Landung. Das Gerät befand sich in einer Tasche unter einem Sitz. Eine etwa 50-jährige Passagierin erlitt beim Herausnehmen der Powerbank eine Verbrennung am linken Daumen. Die Kabinenbesatzung verstaute das Gerät in einer hitzebeständigen Sicherheitstasche und kühlte es mit Wasser. Das Flugzeug landete gegen 6 Uhr Ortszeit planmäßig in Jeju. Die verletzte Frau wurde nach der Landung medizinisch versorgt. Weitere Verletzte gab es nicht. HK Express verbietet die Nutzung von Powerbanks während des Fluges sowie deren Aufbewahrung in den Gepäckfächern über den Sitzen.</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/powerbank-ueberhitzt-auf-flug-von-hk-express-passagierin-verletzt/6psrv9f</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr"/>
+      <c r="L606" t="inlineStr"/>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>auto-6ed65c58fb30</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Lot streicht vier Europastrecken wegen hoher Treibstoffkosten vier Europatsrecken</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr"/>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>Lot Polish Airlines setzt im Winterflugplan vier europäische Verbindungen aus. Betroffen sind die Strecken von Warschau nach Bologna sowie von Krakau nach Madrid, Barcelona und Rom. Im April 2027 sollen alle vier Verbindungen wieder aufgenommen werden. Als einen der Gründe nennt die polnische Fluggesellschaft die stark gestiegenen Treibstoffkosten. Nach Angaben der Airline ist der Anteil des Kerosins an den Gesamtkosten seit Februar von 25 auf 40 Prozent gestiegen. Preiserhöhungen seien angesichts des starken Wettbewerbs auf den betroffenen Strecken kaum durchsetzbar, ohne Passagiere zu verlieren. Deshalb verzichtet Lot während der nachfrageschwächeren Wintermonate auf die Verbindungen.</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lot-streicht-vier-europastrecken-wegen-hoher-treibstoffkosten-vier-europatsrecken/fztsyp5</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr"/>
+      <c r="L607" t="inlineStr"/>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>auto-07f66aed5a38</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Tui will Frachtgeschäft zusammen mit TCE ausbauen</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr"/>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>Die Fluggesellschaften der TUI-Gruppe nutzen freie Frachtraumkapazitäten ihrer Passagierflugzeuge für den Transport von Luftfracht. Bei der Vermarktung und Abwicklung arbeitet TUI Airline seit Januar 2019 mit dem Luftfrachtdienstleister TCE zusammen.</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/tui-will-frachtgeschaeft-zusammen-mit-tce-ausbauen/fqm0lkf</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr"/>
+      <c r="L608" t="inlineStr"/>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>auto-764afa7644ff</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Azul Conecta startet Flüge nach Angra dos Reis</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr"/>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>Die brasilianische Regionalfluggesellschaft Azul Conecta nimmt zur Sommersaison neue Verbindungen nach Angra dos Reis auf. Ab dem 22. Oktober sind Flüge von São Paulo-Campo de Marte, Belo Horizonte-Confins und Rio de Janeiro-Jacarepaguá buchbar. Erstmals bietet Azul damit kommerzielle Flüge ab dem Flughafen Campo de Marte an, der im Norden von São Paulo liegt und bisher vor allem als Hub für Hubschrauber dient. Eingesetzt werden Cessna Grand Caravan mit Platz für neun Passagiere. Die saisonalen Verbindungen sollen insbesondere die Nachfrage während der brasilianischen Sommerferien, über Neujahr und zum Karneval bedienen.</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/azul-conecta-startet-fluege-nach-angra-dos-reis/779fk1j</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr"/>
+      <c r="L609" t="inlineStr"/>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>auto-b9584d132b48</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Fraport erwartet 2027 effizienteren T1-Betrieb</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr"/>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Condor wechselt in Frankfurt 2027 vom T1 ins T3. Für Lufthansa und die Star Alliance entspannt sich durch den Condor-Umzug die Lage an den Gates und auf dem Vorfeld deutlich. Flughafenbetreiber Fraport rechnet für den Flugsommer 2027 mit wesentlich effizienteren Abläufen am Drehkreuz.</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54004/Fraport-erwartet-2027-effizienteren-T1-Betrieb.html</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr"/>
+      <c r="L610" t="inlineStr"/>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>auto-fae42e93b303</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>GlobeCross: Supporting Air Freight – New Headquarters in Frankfurt - TRANSPORT - die Zeitung für den Güterverkehr</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr"/>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirAFBVV95cUxOTFRiaHhJREZMVG5DVlVCb3FCajFjeE0yTWJrdGRLV1gtYWFEeHB6U3UwbXk1T0o3VDNxNFh1ejBna09Ia29OSVRwbENXLXBrNVkzekphOVdxWTdtTVFOdGpVeVI2NjlwcDY3czlsTDY2NkJTdTZyVVd4b0FYU2pUcHQ5dWJYeVlvcW9VVkM0dzhrTWE4anlCSWEzcWlCc1RPLVhhaFNGc0VQOFVE?oc=5" target="_blank"&gt;GlobeCross: Supporting Air Freight – New Headquarters in Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;TRANSPORT - die Zeitung für den Güterverkehr&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOTFRiaHhJREZMVG5DVlVCb3FCajFjeE0yTWJrdGRLV1gtYWFEeHB6U3UwbXk1T0o3VDNxNFh1ejBna09Ia29OSVRwbENXLXBrNVkzekphOVdxWTdtTVFOdGpVeVI2NjlwcDY3czlsTDY2NkJTdTZyVVd4b0FYU2pUcHQ5dWJYeVlvcW9VVkM0dzhrTWE4anlCSWEzcWlCc1RPLVhhaFNGc0VQOFVE?oc=5</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr"/>
+      <c r="L611" t="inlineStr"/>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>auto-b78b1f1ee7ee</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Neue Priority Pass Lounge im Terminal 3 am Flughafen Frankfurt eröffnet - reisetopia</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr"/>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMijAFBVV95cUxPV0UxMXRrN3pQZEQ0b0xIa0tsWldpUzVVVElZMEk5N1BMcE9QcXJxNDBqUFc2a01XMXNYNU5KbW94NUp6RlFkQ2xCRU53aFAtbjZod0pVV3Mxcjd3NVVfc1o4LUNTZjlQSG5QOF8tVjJsTE10bmEzTzhVYk1seHhwdkE0Zk1ub2o5WEdneA?oc=5" target="_blank"&gt;Neue Priority Pass Lounge im Terminal 3 am Flughafen Frankfurt eröffnet&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;reisetopia&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPV0UxMXRrN3pQZEQ0b0xIa0tsWldpUzVVVElZMEk5N1BMcE9QcXJxNDBqUFc2a01XMXNYNU5KbW94NUp6RlFkQ2xCRU53aFAtbjZod0pVV3Mxcjd3NVVfc1o4LUNTZjlQSG5QOF8tVjJsTE10bmEzTzhVYk1seHhwdkE0Zk1ub2o5WEdneA?oc=5</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr"/>
+      <c r="L612" t="inlineStr"/>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>auto-d1adb81d90ff</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Neue Airline &amp; neue Langstrecke: So startet der Flughafen Frankfurt in den Winter - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr"/>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiqAFBVV95cUxOdGdqVTRpeHJwZzBaQ3FkdnlDTkI5UVhnQkdzRUZqeEVmNnRXUHNMSjVhc2ZzTE5iOS1sVkhtQ0JRMnFybzVXRVUtZVlUY29IaWljcWNxLVFKejZEZ2NJWXpSejdHZE4yLVBfWnV1ZDg4TXlIZjhHTncxQzJPaFNuQUFPVDNjdVFFYWxMdC1RRzczaW0xOEt6ZnpLZXdwYjRxX2tpOFRjQjI?oc=5" target="_blank"&gt;Neue Airline &amp; neue Langstrecke: So startet der Flughafen Frankfurt in den Winter&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOdGdqVTRpeHJwZzBaQ3FkdnlDTkI5UVhnQkdzRUZqeEVmNnRXUHNMSjVhc2ZzTE5iOS1sVkhtQ0JRMnFybzVXRVUtZVlUY29IaWljcWNxLVFKejZEZ2NJWXpSejdHZE4yLVBfWnV1ZDg4TXlIZjhHTncxQzJPaFNuQUFPVDNjdVFFYWxMdC1RRzczaW0xOEt6ZnpLZXdwYjRxX2tpOFRjQjI?oc=5</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr"/>
+      <c r="L613" t="inlineStr"/>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>auto-a6229f949962</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>British Airways flight BA16 to Singapore just returned to Sydney for emergency landing - airlive</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr"/>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMixgFBVV95cUxNQmlzTHJ2VTQwRW9OTlFtMTdIVUxnTW1WODNuU3IzbEpiZDR3NlJtclJTQVh0dFdKOUhmS1ZZUkNUZ09paXl3RmcySmdfZFdCSTM3T2gwUUJPeHo5ZndxVm9vUFhTMWZKX1FfOWdmOHEtZFFta0FpNUdWczVvWFI5ZkpMRHNaRFNsUC1udzBIUjVtU05VREFTdlhsMUpIb3UxQk9Jbk9fNGIwVEJRNG4zcWVwMzRzSjRQQXVsSkRMcTJDeWZweWfSAc4BQVVfeXFMTU5zN1VHbTFvUXRMRDM4Nng2Q01jX3RzMHNrRFNVSTczcUJkaDVPTVlxU2pfdFIzVk1IbEtRbDFNay0xZzhEaDRDQllVQ2hIeWduNmhucXJLbnBjZjBMaWRTSzhldkE1UWtkaGVRa1lPaXhKLWxzQTFKY19DV3VORlVrRzFqeXJQa2l2WkRCQk9QTjhGOXJlOVhUdDdEX0t3dmZtUW1vYWZVS1NjLTVrc080cU1VQzV1VzFOSW04LU1WdHZPal9oemVpQ1M0VHc?oc=5" target="_blank"&gt;British Airways flight BA16 to Singapore just returned to Sydney for emergency landing&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNQmlzTHJ2VTQwRW9OTlFtMTdIVUxnTW1WODNuU3IzbEpiZDR3NlJtclJTQVh0dFdKOUhmS1ZZUkNUZ09paXl3RmcySmdfZFdCSTM3T2gwUUJPeHo5ZndxVm9vUFhTMWZKX1FfOWdmOHEtZFFta0FpNUdWczVvWFI5ZkpMRHNaRFNsUC1udzBIUjVtU05VREFTdlhsMUpIb3UxQk9Jbk9fNGIwVEJRNG4zcWVwMzRzSjRQQXVsSkRMcTJDeWZweWfSAc4BQVVfeXFMTU5zN1VHbTFvUXRMRDM4Nng2Q01jX3RzMHNrRFNVSTczcUJkaDVPTVlxU2pfdFIzVk1IbEtRbDFNay0xZzhEaDRDQllVQ2hIeWduNmhucXJLbnBjZjBMaWRTSzhldkE1UWtkaGVRa1lPaXhKLWxzQTFKY19DV3VORlVrRzFqeXJQa2l2WkRCQk9QTjhGOXJlOVhUdDdEX0t3dmZtUW1vYWZVS1NjLTVrc080cU1VQzV1VzFOSW04LU1WdHZPal9oemVpQ1M0VHc?oc=5</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr"/>
+      <c r="L614" t="inlineStr"/>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O614"/>
+  <dimension ref="A1:O623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37843,7 +37843,6 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -37874,8 +37873,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
-      <c r="L604" t="inlineStr"/>
       <c r="M604" t="inlineStr">
         <is>
           <t>review</t>
@@ -37908,7 +37905,6 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D605" t="inlineStr"/>
       <c r="E605" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -37939,8 +37935,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
-      <c r="L605" t="inlineStr"/>
       <c r="M605" t="inlineStr">
         <is>
           <t>review</t>
@@ -37973,7 +37967,6 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -38004,8 +37997,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
-      <c r="L606" t="inlineStr"/>
       <c r="M606" t="inlineStr">
         <is>
           <t>review</t>
@@ -38038,7 +38029,6 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -38069,8 +38059,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
-      <c r="L607" t="inlineStr"/>
       <c r="M607" t="inlineStr">
         <is>
           <t>review</t>
@@ -38103,7 +38091,6 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -38134,8 +38121,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
-      <c r="L608" t="inlineStr"/>
       <c r="M608" t="inlineStr">
         <is>
           <t>review</t>
@@ -38168,7 +38153,6 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -38199,8 +38183,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
-      <c r="L609" t="inlineStr"/>
       <c r="M609" t="inlineStr">
         <is>
           <t>review</t>
@@ -38233,7 +38215,6 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -38264,8 +38245,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
-      <c r="L610" t="inlineStr"/>
       <c r="M610" t="inlineStr">
         <is>
           <t>review</t>
@@ -38298,7 +38277,6 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -38329,8 +38307,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
-      <c r="L611" t="inlineStr"/>
       <c r="M611" t="inlineStr">
         <is>
           <t>review</t>
@@ -38363,7 +38339,6 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -38394,8 +38369,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
-      <c r="L612" t="inlineStr"/>
       <c r="M612" t="inlineStr">
         <is>
           <t>review</t>
@@ -38428,7 +38401,6 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -38459,8 +38431,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
-      <c r="L613" t="inlineStr"/>
       <c r="M613" t="inlineStr">
         <is>
           <t>review</t>
@@ -38493,7 +38463,6 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -38524,8 +38493,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
-      <c r="L614" t="inlineStr"/>
       <c r="M614" t="inlineStr">
         <is>
           <t>review</t>
@@ -38537,6 +38504,591 @@
         </is>
       </c>
       <c r="O614" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>auto-106e3c045a0f</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Lufthansas Einstieg bei Tap: Bundeskanzler rief mehrmals in Lissabon an</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr"/>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>Lufthansa Group erhielt beim Werben um Tap laut Konzernchef Carsten Spohr wichtige Hilfe von Bundeskanzler Friedrich Merz, der selber mehrmals zum Telefon griff. Den Einstieg bei der portugiesischen Fluglinie rechnet Spohr in Langstreckenjets auf.</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/airlines/einstieg-von-lufthansa-bei-tap-gelang-auch-weil-bundeskanzler-merz-mehrfach-in/s2gt0ch</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr"/>
+      <c r="L615" t="inlineStr"/>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>auto-c7bd100b439f</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Das sind die Frachtstrecken von Flydubai</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr"/>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>Flydubai Cargo erweitert zum Beginn des Winterflugplans 2026/27 ihr Streckennetz für reine Frachtflüge. Ab dem 25. Oktober sind zahlreiche Verbindungen mit Boeing 737-800 F ab dem Flughafen Dubai-Al Maktoum geplant. Das geht aus den veröffentlichten Flugplandaten der Fluggesellschaft hervor, so das Portal Aero Routes.</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/das-sind-die-frachtstrecken-von-flydubai/41b0zzy</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr"/>
+      <c r="L616" t="inlineStr"/>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>auto-7b5e66fac572</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Turkish Cargo startet Frachtflüge nach Moskau-Sheremetyevo</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr"/>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>Turkish Cargo nimmt am 31. Oktober 2026 eine neue Frachtverbindung zwischen Istanbul und dem Moskauer Flughafen Sheremetyevo auf. Die Frachttochter von Turkish Airlines wird die Strecke ein Mal wöchentlich nonstop bedienen.</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/turkish-cargo-startet-frachtfluege-nach-moskau-sheremetyevo/prxgqz0</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr"/>
+      <c r="L617" t="inlineStr"/>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>auto-370ce6c7c756</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>"Die Reformfähigkeit ist einfach unterentwickelt"</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr"/>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa und Vereinigung Cockpit verheddern sich im Tarifgeflecht - wieder einmal. Eine auf Geldfragen begrenzte Schlichtung ist gerade geplatzt. Reformen sind im Lufthansa-Kern "schwerer" umsetzbar "als überall sonst im Konzern", meint Lufthansa-Chef Carsten Spohr. Typisch deutsch?</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54024/Die-Reformfaehigkeit-ist-einfach-unterentwickelt.html</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr"/>
+      <c r="L618" t="inlineStr"/>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>auto-7234b921e6b4</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>SAF-Tarif von Lufthansa darf nicht "grün" rüberkommen</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr"/>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa benennt die "Green Fare" in "Impact Fare" um. Der Lufthansa-Tarif mit SAF-Anteil darf unter strengeren EU-Vorgaben nicht mehr "grün" rüberkommen. Das Angebot ist vor allem bei Firmenkunden gefragt - Lufthansa kann mehr als fünf Millionen Flugbuchungen vorweisen.</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54018/SAF-Tarif-von-Lufthansa-darf-nicht-mehr-gruen-rueberkommen.html</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr"/>
+      <c r="L619" t="inlineStr"/>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>auto-c66d2853f732</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Piloten: Riskanter Umgang mit Schlafmangel</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr"/>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Sekundenschlaf im Cockpit - und Angst vor Konsequenzen: Übermüdete Pilotinnen und Piloten sind nach Einschätzung der Vereinigung Cockpit (VC) ein erhebliches Sicherheitsrisiko in der europäischen Luftfahrt. Die Pilotengewerkschaft fordert auch von behördlicher Seite mehr Problembewusstsein.</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54022/Piloten-Riskanter-Umgang-mit-Schlafmangel.html</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr"/>
+      <c r="L620" t="inlineStr"/>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>auto-b8cb74d3f907</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Fraport-Gewinn steigt durch Anteilsverkauf</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr"/>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Fraport hat seine Hälfte am Dienstleister Medical Airport Service verkauft und damit den Quartalsgewinn aufgepolstert.</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54021/Fraport-Gewinn-steigt-durch-Anteilsverkauf.html</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr"/>
+      <c r="L621" t="inlineStr"/>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>auto-f9896bc80513</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Ryanair flight from Dublin to Bristol diverted to… Spain - airlive</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr"/>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMinAFBVV95cUxNMXhCT3pOWVVGLUZSZ2RwVldCTnJtNHJZWDlZaG43V0p0UjRya0tyNzl5TmhoOWRUZmhIQmRuME9LZHFBMy04R1pKbFJ2OWoxcXhaUTF4VW92dGJ1X1E4akhZUWtqcWhQQTJjT3d6WjFPclFlSjZKbmREREhGRVdDV09ITklseVMzMEg3amdSWjJ4UHp4NkZnRHZ6b2nSAaQBQVVfeXFMT1hqQURJSkpoT0xpcU9kTFgtc25jUVljUmhjWFBIaVZQSENsZU55SHpRdlJDSHlNejloUG9RelZSTXc3UmpSWmZWWE5xeU9BUk1YUmRxSy1zYzZvR0JGSnRYZV9vR0FpRFdYWEo5NkZHaEs0N0cyUkJUMGNDLWJuazgyNWxONkp4Y1VwRlFqcVdQSy1HMF9KaWJLeVpxZnBrdFR2VjM?oc=5" target="_blank"&gt;Ryanair flight from Dublin to Bristol diverted to… Spain&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNMXhCT3pOWVVGLUZSZ2RwVldCTnJtNHJZWDlZaG43V0p0UjRya0tyNzl5TmhoOWRUZmhIQmRuME9LZHFBMy04R1pKbFJ2OWoxcXhaUTF4VW92dGJ1X1E4akhZUWtqcWhQQTJjT3d6WjFPclFlSjZKbmREREhGRVdDV09ITklseVMzMEg3amdSWjJ4UHp4NkZnRHZ6b2nSAaQBQVVfeXFMT1hqQURJSkpoT0xpcU9kTFgtc25jUVljUmhjWFBIaVZQSENsZU55SHpRdlJDSHlNejloUG9RelZSTXc3UmpSWmZWWE5xeU9BUk1YUmRxSy1zYzZvR0JGSnRYZV9vR0FpRFdYWEo5NkZHaEs0N0cyUkJUMGNDLWJuazgyNWxONkp4Y1VwRlFqcVdQSy1HMF9KaWJLeVpxZnBrdFR2VjM?oc=5</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr"/>
+      <c r="L622" t="inlineStr"/>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>auto-4c712002e524</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Delta flight DL22 to Munich has declared an emergency during the night and diverted to Ireland - airlive</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr"/>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi0gFBVV95cUxOQVJvYTRVT0xwaVg3YVM4UGh4RmU3SXdKckxYMUFycmpkd20zY0UxOHRwbmdmdWhOamhRYjFIcndEandZRUR5TDRnUnZPS21ERXdURFpRQ3g1NFRFTFlNMHI2aUVmbnEzV1BZdFN2Sjl1dmtQUG1mRWVwTnVqYmoyZjJsOHBSN2xCLXRZUkpVNXk5Sm9iWUpaSkNiNEN5S2lwV2dBa2gzVjI3YmMxVHB2X096dC1ORGlzMG9KaTktUjNiUUhnRmc0UkJ0eVBuaTJUbkHSAdoBQVVfeXFMTlZIN3BFdFM0bHBCSFZvUklUcUkyaExkVXpDbkk5T2tleDJVWnRRa1pWN255R3ZnWmlYOXVjQ3BqeC1LRzFPbXVscU1BUFQyWGxMUUp3QlJFWkFjYS1rd0lFVmtuVGNMTGdJVTh6bGpZQldCQUotUU1oN3daWGE1dkpVeW9OUEJ2SlBTLVJWX2pLRkxTUG1zamF0TG5tTFVqbE5ual9DSHNqNDR3YkxBekhrclVVZDJaZThGTEJiSWxFSG1veHl5Ym9jdnZ5ZGhNRF9RNXBwUENLZ2c?oc=5" target="_blank"&gt;Delta flight DL22 to Munich has declared an emergency during the night and diverted to Ireland&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOQVJvYTRVT0xwaVg3YVM4UGh4RmU3SXdKckxYMUFycmpkd20zY0UxOHRwbmdmdWhOamhRYjFIcndEandZRUR5TDRnUnZPS21ERXdURFpRQ3g1NFRFTFlNMHI2aUVmbnEzV1BZdFN2Sjl1dmtQUG1mRWVwTnVqYmoyZjJsOHBSN2xCLXRZUkpVNXk5Sm9iWUpaSkNiNEN5S2lwV2dBa2gzVjI3YmMxVHB2X096dC1ORGlzMG9KaTktUjNiUUhnRmc0UkJ0eVBuaTJUbkHSAdoBQVVfeXFMTlZIN3BFdFM0bHBCSFZvUklUcUkyaExkVXpDbkk5T2tleDJVWnRRa1pWN255R3ZnWmlYOXVjQ3BqeC1LRzFPbXVscU1BUFQyWGxMUUp3QlJFWkFjYS1rd0lFVmtuVGNMTGdJVTh6bGpZQldCQUotUU1oN3daWGE1dkpVeW9OUEJ2SlBTLVJWX2pLRkxTUG1zamF0TG5tTFVqbE5ual9DSHNqNDR3YkxBekhrclVVZDJaZThGTEJiSWxFSG1veHl5Ym9jdnZ5ZGhNRF9RNXBwUENLZ2c?oc=5</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr"/>
+      <c r="L623" t="inlineStr"/>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O623"/>
+  <dimension ref="A1:O636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38525,7 +38525,6 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -38556,8 +38555,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
-      <c r="L615" t="inlineStr"/>
       <c r="M615" t="inlineStr">
         <is>
           <t>review</t>
@@ -38590,7 +38587,6 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -38621,8 +38617,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
-      <c r="L616" t="inlineStr"/>
       <c r="M616" t="inlineStr">
         <is>
           <t>review</t>
@@ -38655,7 +38649,6 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -38686,8 +38679,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
-      <c r="L617" t="inlineStr"/>
       <c r="M617" t="inlineStr">
         <is>
           <t>review</t>
@@ -38720,7 +38711,6 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="D618" t="inlineStr"/>
       <c r="E618" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -38751,8 +38741,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
-      <c r="L618" t="inlineStr"/>
       <c r="M618" t="inlineStr">
         <is>
           <t>review</t>
@@ -38785,7 +38773,6 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -38816,8 +38803,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
-      <c r="L619" t="inlineStr"/>
       <c r="M619" t="inlineStr">
         <is>
           <t>review</t>
@@ -38850,7 +38835,6 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="D620" t="inlineStr"/>
       <c r="E620" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -38881,8 +38865,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
-      <c r="L620" t="inlineStr"/>
       <c r="M620" t="inlineStr">
         <is>
           <t>review</t>
@@ -38915,7 +38897,6 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="D621" t="inlineStr"/>
       <c r="E621" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -38946,8 +38927,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
-      <c r="L621" t="inlineStr"/>
       <c r="M621" t="inlineStr">
         <is>
           <t>review</t>
@@ -38980,7 +38959,6 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="D622" t="inlineStr"/>
       <c r="E622" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -39011,8 +38989,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
-      <c r="L622" t="inlineStr"/>
       <c r="M622" t="inlineStr">
         <is>
           <t>review</t>
@@ -39045,7 +39021,6 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr"/>
       <c r="E623" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -39076,8 +39051,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
-      <c r="L623" t="inlineStr"/>
       <c r="M623" t="inlineStr">
         <is>
           <t>review</t>
@@ -39089,6 +39062,851 @@
         </is>
       </c>
       <c r="O623" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>auto-c937ba471518</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Condor benennt Fracht-Produkte um</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr"/>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>Condor führt zum Start des Winterflugplans am 1. November eine neue Struktur für ihre Cargo-Produkte ein. Die einheitliche Namenslogik soll Spediteuren und Versendern die Orientierung erleichtern. Standardfracht wird künftig unter «Just move» angeboten. Für Spezialtransporte gibt es «Move cool» für Pharma- und Healthcare-Sendungen sowie «Move Fresh» für verderbliche Waren. Das bisherige Express-Angebot erhält den Namen «Move Fast». Mit der neuen Produktarchitektur schaffe Condor eine Grundlage, um das Cargo-Portfolio systematisch auszubauen, sagt Thilo Schäfer, Cargo-Chef der Fluggesellschaft.</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/condor-benennt-fracht-produkte-um/lmjm6pd</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr"/>
+      <c r="L624" t="inlineStr"/>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>auto-738b1ebe48e8</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Airbus und Air France-KLM bündeln A350-Ersatzteilversorgung</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr"/>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>Airbus und Air France-KLM haben gemeinsam die Kontrolle über das Unternehmen Alpha Component Solutions übernommen, wie Airbus am Mittwoch (28. Oktober) mitteilt. Es ist auf Ersatzteilversorgung und Wartung von A350 spezialisiert. Das Gemeinschaftsunternehmen wird zu gleichen Teilen von Airbus und Air France gehalten und bündelt die Kompetenzen von Airbus Flight Hours Services und Air France Industries KLM Engineering &amp;amp; Maintenance.</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/airbus-und-air-france-klm-buendeln-a350-ersatzteilversorgung/ss6hs4c</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr"/>
+      <c r="L625" t="inlineStr"/>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>auto-135c7c901889</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Rumänien erhält mobile Radarsysteme von Thales</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr"/>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>Thales liefert der rumänischen Luftwaffe vier mobile Radarsysteme für die Luftraumüberwachung sowie Anflug und Landung. Das teilte der französische Rüstungskonzern am Mittwoch (28. Oktober) mit.</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker-verteidigung/rumaenien-erhaelt-mobile-radarsysteme-von-thales/h7px5j1</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr"/>
+      <c r="L626" t="inlineStr"/>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>auto-f8cb718137b4</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Zu Besuch an Lufthansas Gate der Zukunft am Flughafen Frankfurt</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr"/>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>Lufthansa und der Flughafen Frankfurt testen im Terminal 1, wie ein Gate effizienter funktionieren kann und zugleich komfortabler für die Gäste wird. Dabei geht es sowohl um Lounge-Elemente, als auch darum, Bewegungen zu analysieren und einem Software-Wirrwarr Herr zu werden.</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugerlebnis/lufthansa-testet-neues-boarding-mit-sensoren-am-flughafen-frankfurt/rn50xhc</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr"/>
+      <c r="L627" t="inlineStr"/>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>auto-95d5a4ef96db</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Atlas Air lässt drei Boeing 747 einen Schnurrbart wachsen</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr"/>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>Im Oktober tragen Flugzeuge Pink, im November bekommen sie einen Schnurrbart. Zumindest bei Atlas Air. Die amerikanische Frachtfluggesellschaft versieht gleich drei Boeing 747 mit riesigen Schnurrbärten.</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugzeuge/atlas-air-laesst-drei-boeing-747-einen-schnurrbart-wachsen/rfg4y17</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr"/>
+      <c r="L628" t="inlineStr"/>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>auto-06537355da3c</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Der Airbus A330-200 ist bei Discover Airlines raus</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr"/>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Der Airbus A340-600 ist bei Lufthansa gerade aus der Tür, schon verlässt eine weitere Teilflotte den Konzern: Discover Airlines schließt nach einem letzten USA-Umlauf das Kapitel A330-200. Die betagten Flugzeuge waren ein Überbleibsel aus den Anfangstagen des Lufthansa-Ferienfliegers.</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54032/Der-Airbus-A330-200-ist-bei-Discover-Airlines-raus.html</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr"/>
+      <c r="L629" t="inlineStr"/>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>auto-97b4028ce7e4</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>"Der Counter ist auf einen Arbeitsplatz reduziert"</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr"/>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa hat das Terminal 1 zusammen mit ihren Star-Alliance-Partnern 2027 für sich - an A16 testet Lufthansa komplett neu gestaltetes Abflug-Gate. Das Boarding-Personal bezieht vor dem Abflug nicht mehr hinter dem Counter Stellung.</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54029/Der-Counter-ist-auf-einen-Arbeitsplatz-reduziert.html</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr"/>
+      <c r="L630" t="inlineStr"/>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>auto-8a72504eed3d</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>„Geisterfahrer“ am Frankfurter Flughafen: Airbus fährt falsch auf Startbahn auf - RP Online</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr"/>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirwFBVV95cUxQQkxnOFhOc0dPV1ppX0Ewbk1CcWJvRThpNjJyRjJESUM4T2p4YTJpQUp2VEZDbEhNMFZMTWhhSWN5bnNGMUk0MmVjb0RRdVl5R0YxQW5aM2xoT1dzeHM4d1hQWmNlNXFQS3FCX0pYMmVKcWRPOE9ZSG1RdVNaeEhoY1haV3lOTExVaTcxNXZuVDZ3Ny1tSmY2dUxBWTR4NG56N1NWVnlldHhZQ2VkUGo4?oc=5" target="_blank"&gt;„Geisterfahrer“ am Frankfurter Flughafen: Airbus fährt falsch auf Startbahn auf&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;RP Online&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQQkxnOFhOc0dPV1ppX0Ewbk1CcWJvRThpNjJyRjJESUM4T2p4YTJpQUp2VEZDbEhNMFZMTWhhSWN5bnNGMUk0MmVjb0RRdVl5R0YxQW5aM2xoT1dzeHM4d1hQWmNlNXFQS3FCX0pYMmVKcWRPOE9ZSG1RdVNaeEhoY1haV3lOTExVaTcxNXZuVDZ3Ny1tSmY2dUxBWTR4NG56N1NWVnlldHhZQ2VkUGo4?oc=5</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr"/>
+      <c r="L631" t="inlineStr"/>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>auto-b839344e53d8</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Passengers from diverted Air Europa flight recount turbulence ordeal - Reuters</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr"/>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitAFBVV95cUxNT2tUVXFIT1BTeDBlTFZJRVNKWnFfdDgzcVg2cHNxOFFkMnRYekNiVzktYXo4QXI0cndTOEVob1h5MXJOUmlRYk53U3AxNHY5R3l4aWZOTHVOalpIWVdzLWxId1NaTmU2Uy1yNlF0QUhPTVBDU2ZCYWJzX2h5STA4aWFfZFVONmgwLVVPeExaWUY1MnU3dzM1SDRBQ3M1SGNZLURyZ1ViQURscFpaNTA4bkZocVg?oc=5" target="_blank"&gt;Passengers from diverted Air Europa flight recount turbulence ordeal&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Reuters&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNT2tUVXFIT1BTeDBlTFZJRVNKWnFfdDgzcVg2cHNxOFFkMnRYekNiVzktYXo4QXI0cndTOEVob1h5MXJOUmlRYk53U3AxNHY5R3l4aWZOTHVOalpIWVdzLWxId1NaTmU2Uy1yNlF0QUhPTVBDU2ZCYWJzX2h5STA4aWFfZFVONmgwLVVPeExaWUY1MnU3dzM1SDRBQ3M1SGNZLURyZ1ViQURscFpaNTA4bkZocVg?oc=5</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr"/>
+      <c r="L632" t="inlineStr"/>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N632" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>auto-aef6cd689c6a</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>New York-Bound Flight From Europe Forced To Make Emergency Landing Due To Extreme Turbulence - NDTV</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr"/>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMizAFBVV95cUxQQ2l2N2JDYVkydGpJVlgxRENaQkx6Wm1vSnhpVHFxb2F2cnZrVnVURU5ZWVBQX1ZIYW9fTjlQSnkyVU9Ia1dld0N5Vmh6aHZLRnU1b2dJSjFjWHpPT0FySGtnMFR1czZBQkpYeG1qXzhfNEZDLTFzNXIwWnZLb2I3QlVkLVRfeW9BcGdwM1llT2luNkdTVHg3WnZ1MG5hVGY1eExDTF9FdmdXRjJXUm1QM2cyRG9YMFdBTXdOWkZ2dHlmanJENmxWSkdMQmzSAdQBQVVfeXFMTS1PZjZ4cHU5RHBxQTBfUnhlUnMxam1lLVpXU21DNjFlOHF4ZlZubmNobnRWalY1ZTJWQWZQcUt4bzVzc2E4am96SzZJNmh2Q3NWMlZjT0p5ZmRfV2pvdVFYeXJuSGdSRjk4RWlleV9EQ1Fqd0N4alk4NVIwZTlmT1ltTThnVEliZ21EcjRLLU5WSW5fMkV3djgxbVlqSl9EQW9mZVl6ekdVSHBJSDR6TndOR0E2cUdyVkNfM3ZaWnVaS0RDTllFeHAzVTJLaEVfLU9PenE?oc=5" target="_blank"&gt;New York-Bound Flight From Europe Forced To Make Emergency Landing Due To Extreme Turbulence&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;NDTV&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQQ2l2N2JDYVkydGpJVlgxRENaQkx6Wm1vSnhpVHFxb2F2cnZrVnVURU5ZWVBQX1ZIYW9fTjlQSnkyVU9Ia1dld0N5Vmh6aHZLRnU1b2dJSjFjWHpPT0FySGtnMFR1czZBQkpYeG1qXzhfNEZDLTFzNXIwWnZLb2I3QlVkLVRfeW9BcGdwM1llT2luNkdTVHg3WnZ1MG5hVGY1eExDTF9FdmdXRjJXUm1QM2cyRG9YMFdBTXdOWkZ2dHlmanJENmxWSkdMQmzSAdQBQVVfeXFMTS1PZjZ4cHU5RHBxQTBfUnhlUnMxam1lLVpXU21DNjFlOHF4ZlZubmNobnRWalY1ZTJWQWZQcUt4bzVzc2E4am96SzZJNmh2Q3NWMlZjT0p5ZmRfV2pvdVFYeXJuSGdSRjk4RWlleV9EQ1Fqd0N4alk4NVIwZTlmT1ltTThnVEliZ21EcjRLLU5WSW5fMkV3djgxbVlqSl9EQW9mZVl6ekdVSHBJSDR6TndOR0E2cUdyVkNfM3ZaWnVaS0RDTllFeHAzVTJLaEVfLU9PenE?oc=5</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr"/>
+      <c r="L633" t="inlineStr"/>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N633" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>auto-91abe80a173e</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Pilots of AA5078 requested urgent diversion due to flight attendant’s medical situation - airlive</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr"/>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMixwFBVV95cUxQYTJrcGJaMGYta3B6UjR4NF9MNGx3emQtSHZvTWQxbmRGZERQbklhQllyN1d3bFczTkRyeG56UzVNN2xoTW1CTnJibGZZekhZRzN1Yk93VlF6R1Bqdk5YT0tIQ0xza0J2dVpHVWhvUTFocjVLdEdraUlBU1c2ei1yOFB1bjc5Q3Rod2w4MW00bGNpd0ZhSXBxcTEwSnk5eU5ob1A1T1ByczNxSHdISEFZcG1FT2VQR25kNko1cVRIa3p3QWhjckUw0gHPAUFVX3lxTE1mR1Fic3JObllxeXpHSlh2X3hubXRONnU2akRLY25qaXI4SlJ2UkJpSnFVdEJQSWI3ZXlRNVNuWjRyX0hfeS1tMkVYYmhObDF3bVhLbXpqdGF3RDYzRng1dEc3RDZjb21RaGF0UXJtN245NHJyMkVYM2p6djR2bjlxOW5BY3N6ZUw2ZGJISzVOZnRPdHR0b19PRzRZakNxNWo3cW14SnlzNjdkNTZUY1ZYN1NhdUZCT1FLdEp5bk1icWp0YzlsaHpxSlRJRVllMA?oc=5" target="_blank"&gt;Pilots of AA5078 requested urgent diversion due to flight attendant’s medical situation&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQYTJrcGJaMGYta3B6UjR4NF9MNGx3emQtSHZvTWQxbmRGZERQbklhQllyN1d3bFczTkRyeG56UzVNN2xoTW1CTnJibGZZekhZRzN1Yk93VlF6R1Bqdk5YT0tIQ0xza0J2dVpHVWhvUTFocjVLdEdraUlBU1c2ei1yOFB1bjc5Q3Rod2w4MW00bGNpd0ZhSXBxcTEwSnk5eU5ob1A1T1ByczNxSHdISEFZcG1FT2VQR25kNko1cVRIa3p3QWhjckUw0gHPAUFVX3lxTE1mR1Fic3JObllxeXpHSlh2X3hubXRONnU2akRLY25qaXI4SlJ2UkJpSnFVdEJQSWI3ZXlRNVNuWjRyX0hfeS1tMkVYYmhObDF3bVhLbXpqdGF3RDYzRng1dEc3RDZjb21RaGF0UXJtN245NHJyMkVYM2p6djR2bjlxOW5BY3N6ZUw2ZGJISzVOZnRPdHR0b19PRzRZakNxNWo3cW14SnlzNjdkNTZUY1ZYN1NhdUZCT1FLdEp5bk1icWp0YzlsaHpxSlRJRVllMA?oc=5</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr"/>
+      <c r="L634" t="inlineStr"/>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N634" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>auto-402d12670b0b</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Swiss flight makes emergency landing in Austria after smoke detection - The Times of India</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr"/>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi3AFBVV95cUxOTGpwWTVTNV92NUMxUXpPNDJSWWJVbmdYOERXUFEzQ1VCN29aUERWZl9rLS1zTklYeDl5MF8tVW0xZFRBTk9NbEtKSzhyUE9tTV9CN1RBTkZwdWc4VFFwQ1k2ZFR4dkpBTUNKd09NenZ2VG9ER3VBaXFSX2ZjQUc0XzRHemxrclpPdE5zZlJnZmZ3RHNyN3I1U3JZUFhaUnAxWmlhT3B5cVJOYlMxYXBtMlpBQ2w5R0c1SUtpNmtmbDhuXzBqcjNUOE9UdTYxSnJWdUd1aDdqai0xMHBK0gHiAUFVX3lxTE9FWEFqQmdMS3c2YWVmTU11T3M0MjZ3S194akJWTFNobWFMTFV6ODQ5dUkxajhsbHdWS0dCckZBOUZHeUdkU0VnSEhLM0t6eFJiN21LUk1wQk56czBvbThmaUQtUTctOGYwRTlFdV91bnB4V25XdnI0RFNqaGFqa0VkMUVnZ1Y3X3hqb2pnWkVtbjh6THlaNFhXYWI1VXJ1elRKekVsMlViUkU3SW42d19RMks4c2Z3c2Jvd3J1dHhkTUI2X2phNEx3UklZRHlIV1dGZHBvUm9YTEk4TEY4dHVtQ3c?oc=5" target="_blank"&gt;Swiss flight makes emergency landing in Austria after smoke detection&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;The Times of India&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOTGpwWTVTNV92NUMxUXpPNDJSWWJVbmdYOERXUFEzQ1VCN29aUERWZl9rLS1zTklYeDl5MF8tVW0xZFRBTk9NbEtKSzhyUE9tTV9CN1RBTkZwdWc4VFFwQ1k2ZFR4dkpBTUNKd09NenZ2VG9ER3VBaXFSX2ZjQUc0XzRHemxrclpPdE5zZlJnZmZ3RHNyN3I1U3JZUFhaUnAxWmlhT3B5cVJOYlMxYXBtMlpBQ2w5R0c1SUtpNmtmbDhuXzBqcjNUOE9UdTYxSnJWdUd1aDdqai0xMHBK0gHiAUFVX3lxTE9FWEFqQmdMS3c2YWVmTU11T3M0MjZ3S194akJWTFNobWFMTFV6ODQ5dUkxajhsbHdWS0dCckZBOUZHeUdkU0VnSEhLM0t6eFJiN21LUk1wQk56czBvbThmaUQtUTctOGYwRTlFdV91bnB4V25XdnI0RFNqaGFqa0VkMUVnZ1Y3X3hqb2pnWkVtbjh6THlaNFhXYWI1VXJ1elRKekVsMlViUkU3SW42d19RMks4c2Z3c2Jvd3J1dHhkTUI2X2phNEx3UklZRHlIV1dGZHBvUm9YTEk4TEY4dHVtQ3c?oc=5</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr"/>
+      <c r="L635" t="inlineStr"/>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>auto-5cb042bffe86</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>TUI emergency landing in Bari sparks widespread flight disruptions during Europe’s peak travel season - Aviation24.be</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr"/>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi7AFBVV95cUxNcjhsay1nQlMtWTdsbW1rblc4eHBKSDNMUUVCSE9raEdFZTFCVDNFNnRkMWNweFJpLVZ0bFIwbUZEcURacFhNX2Q3YjFQZFV5ZjIxSGFoUXg4TUtLYVNVNFljSlkyVDljTzFqcXpjd1Q5Z0ZycXZjRF9WTHE3U0VRYktYTUFtVWhnUjFBQzRvS3JfVHdhTFdKT2tabGYxeVNVZ0N5U1JOY1ZuTTloVW5HdllKZURJTEcwZ3FTa2dnUzd3aTBQWXpKMDBGckdMdVNKVm5MU3JZelBiLXR1OG5FQ0UyRC1weElvYjZsRNIB8gFBVV95cUxOLU5GMHc4RUs5MkFiVjVRWVpNaWE4MGxDVFNWbU1qcFlROFFfS3FQR0dOeFlXQ1dUdGdkVkwybE55XzJJRDlBdlFBRUlMb21HWFRSWlA3UHdQbm5HdFpBa2pPMVZ2T3FjMFQtMTZXa1lJbnZNckZXMmo2c3JFS2NUWU03TUhwWWtWVW9DcTdNaC1uU0tnQ1k0dlM2YjZHV2hBQ0VNanJNNHQ2MEhzc1N2Q1RLcVJaODNyQW5zaWZoeXlLTDFGbmp5U3VJbHM0cHU5ZC16MEtPZF93M1NLaUo1YWlKSGx4Q2YxbHEzVU0tQzg4dw?oc=5" target="_blank"&gt;TUI emergency landing in Bari sparks widespread flight disruptions during Europe’s peak travel season&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Aviation24.be&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNcjhsay1nQlMtWTdsbW1rblc4eHBKSDNMUUVCSE9raEdFZTFCVDNFNnRkMWNweFJpLVZ0bFIwbUZEcURacFhNX2Q3YjFQZFV5ZjIxSGFoUXg4TUtLYVNVNFljSlkyVDljTzFqcXpjd1Q5Z0ZycXZjRF9WTHE3U0VRYktYTUFtVWhnUjFBQzRvS3JfVHdhTFdKT2tabGYxeVNVZ0N5U1JOY1ZuTTloVW5HdllKZURJTEcwZ3FTa2dnUzd3aTBQWXpKMDBGckdMdVNKVm5MU3JZelBiLXR1OG5FQ0UyRC1weElvYjZsRNIB8gFBVV95cUxOLU5GMHc4RUs5MkFiVjVRWVpNaWE4MGxDVFNWbU1qcFlROFFfS3FQR0dOeFlXQ1dUdGdkVkwybE55XzJJRDlBdlFBRUlMb21HWFRSWlA3UHdQbm5HdFpBa2pPMVZ2T3FjMFQtMTZXa1lJbnZNckZXMmo2c3JFS2NUWU03TUhwWWtWVW9DcTdNaC1uU0tnQ1k0dlM2YjZHV2hBQ0VNanJNNHQ2MEhzc1N2Q1RLcVJaODNyQW5zaWZoeXlLTDFGbmp5U3VJbHM0cHU5ZC16MEtPZF93M1NLaUo1YWlKSGx4Q2YxbHEzVU0tQzg4dw?oc=5</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr"/>
+      <c r="L636" t="inlineStr"/>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O636" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O636"/>
+  <dimension ref="A1:O645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39083,7 +39083,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="D624" t="inlineStr"/>
       <c r="E624" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -39114,8 +39113,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
-      <c r="L624" t="inlineStr"/>
       <c r="M624" t="inlineStr">
         <is>
           <t>review</t>
@@ -39148,7 +39145,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="D625" t="inlineStr"/>
       <c r="E625" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -39179,8 +39175,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
-      <c r="L625" t="inlineStr"/>
       <c r="M625" t="inlineStr">
         <is>
           <t>review</t>
@@ -39213,7 +39207,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="D626" t="inlineStr"/>
       <c r="E626" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -39244,8 +39237,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
-      <c r="L626" t="inlineStr"/>
       <c r="M626" t="inlineStr">
         <is>
           <t>review</t>
@@ -39278,7 +39269,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="D627" t="inlineStr"/>
       <c r="E627" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -39309,8 +39299,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
-      <c r="L627" t="inlineStr"/>
       <c r="M627" t="inlineStr">
         <is>
           <t>review</t>
@@ -39343,7 +39331,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="D628" t="inlineStr"/>
       <c r="E628" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -39374,8 +39361,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
-      <c r="L628" t="inlineStr"/>
       <c r="M628" t="inlineStr">
         <is>
           <t>review</t>
@@ -39408,7 +39393,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="D629" t="inlineStr"/>
       <c r="E629" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -39439,8 +39423,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
-      <c r="L629" t="inlineStr"/>
       <c r="M629" t="inlineStr">
         <is>
           <t>review</t>
@@ -39473,7 +39455,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="D630" t="inlineStr"/>
       <c r="E630" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -39504,8 +39485,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
-      <c r="L630" t="inlineStr"/>
       <c r="M630" t="inlineStr">
         <is>
           <t>review</t>
@@ -39538,7 +39517,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="D631" t="inlineStr"/>
       <c r="E631" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -39569,8 +39547,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
-      <c r="L631" t="inlineStr"/>
       <c r="M631" t="inlineStr">
         <is>
           <t>review</t>
@@ -39603,7 +39579,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="D632" t="inlineStr"/>
       <c r="E632" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -39634,8 +39609,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
-      <c r="L632" t="inlineStr"/>
       <c r="M632" t="inlineStr">
         <is>
           <t>review</t>
@@ -39668,7 +39641,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -39699,8 +39671,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
-      <c r="L633" t="inlineStr"/>
       <c r="M633" t="inlineStr">
         <is>
           <t>review</t>
@@ -39733,7 +39703,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -39764,8 +39733,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
-      <c r="L634" t="inlineStr"/>
       <c r="M634" t="inlineStr">
         <is>
           <t>review</t>
@@ -39798,7 +39765,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -39829,8 +39795,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
-      <c r="L635" t="inlineStr"/>
       <c r="M635" t="inlineStr">
         <is>
           <t>review</t>
@@ -39863,7 +39827,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="D636" t="inlineStr"/>
       <c r="E636" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -39894,8 +39857,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
-      <c r="L636" t="inlineStr"/>
       <c r="M636" t="inlineStr">
         <is>
           <t>review</t>
@@ -39907,6 +39868,591 @@
         </is>
       </c>
       <c r="O636" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>auto-42a19f6ade82</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Boeing prognostiziert mehr als 4000 Frachtflugzeuge bis 2045</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr"/>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>Die weltweite Flotte reiner Frachtflugzeuge wird bis 2045 auf mehr als 4000 Exemplare wachsen - das prognostiziert Boeing in seiner neuen Frachtmarktstudie. Der Flugzeugbauer erwartet, dass sich der Luftfrachtverkehr in den kommenden 20 Jahren verdoppelt und jährlich um durchschnittlich 3,5 Prozent wächst. Treiber seien unter anderem der Onlinehandel, veränderte Lieferketten sowie die Nachfrage nach zeitkritischen und hochwertigen Gütern, etwa für die KI-Industrie.</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/boeing-prognostiziert-mehr-als-4000-frachtflugzeuge-bis-2045/ry37egl</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr"/>
+      <c r="L637" t="inlineStr"/>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>auto-e60e01644d1f</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Wie Lufthansa die Boeing 747-400 auf welchen Routen ersetzt</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr"/>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>Mit dem Ende des Sommerflugplans 2027 soll auch das Kapitel Boeing 747-400 bei &lt;a href="https://www.aerotelegraph.com/tags/lufthansa" id="747050d6-c5ec-417e-aa79-38f3070fde1b"&gt;Lufthansa&lt;/a&gt; enden. Änderungen im Winterflugplan 2027/28 zeigen nun, wie die Flugzeuge auf verschiedenen Routen ersetzt werden, wie das Portal &lt;a href="https://www.aeroroutes.com/eng/261028-lhnw27inc" id="e2b62a41-b92e-4ac8-ae0a-4cfa49a4ced4"&gt;Aero Routes&lt;/a&gt; berichtet. Auf der Strecke Frankfurt - Bengaluru ist demnach ab Ende Oktober 2027 die Boeing 787-9 statt der Boeing 747-400 vorgesehen. Auch nach Shanghai soll der Airbus A350-900 statt einer Boeing 747 fliegen. Auf der Verbindung nach Singapur soll die Boeing 747-8 die 747-400 ablösen, auf der Strecke nach Houston soll der A350-900 die 747-400 beziehungsweise die 787-9 ersetzen.</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/wie-lufthansa-die-boeing-747-400-auf-welchen-routen-ersetzt/epjvhrb</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr"/>
+      <c r="L638" t="inlineStr"/>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>auto-66634194a192</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Boeing 777 F verdrängt den Jumbo-Jet als Frachter-Königin</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr"/>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>Mehr als 50 Jahre war der Jumbo das Rückgrat der Luftfracht. Jetzt hat die Boeing 777 F ihn als meistgeflogenen Frachter abgelöst. Ein Blick auf die Zahlen zeigt, wie deutlich.</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/fracht/boeing-777-f-ueberholt-boeing-747-als-meistgenutztes-frachtflugzeug/hmbvsj0</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr"/>
+      <c r="L639" t="inlineStr"/>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>auto-de8100df2926</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Norwegen sucht mehr Flugzeuge für emissionsarme Regionalflüge</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr"/>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>Der norwegische Flughafenbetreiber Avinor und die norwegische Luftfahrtbehörde starten zwei neue Ausschreibungen für emissionsarme Flugzeuge, wie er am Mittwoch (28. Oktober) mittteilt. Gesucht werden zum einen Regionalflugzeuge mit mindestens neun Sitzplätzen für Strecken unter 1000 Kilometern, zum anderen neue, pilotengesteuerte Vtol-Flugzeuge, die senkrecht starten und landen können. Die Konzepte sollen mit Batterien, Wasserstoff oder Hybridantrieben fliegen und für Passagier- oder Frachttransporte geeignet sein.</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/norwegen-sucht-mehr-flugzeuge-fuer-emissionsarme-regionalfluege/q2dzz9d</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr"/>
+      <c r="L640" t="inlineStr"/>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>auto-ef0ec17880c1</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Leipzig hat weitere Anfragen von Rüstungsunternehmen</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr"/>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>LEIPZIG - In den Diskussionen um die Ansiedlung von Verteidigungswirtschaft hat die Stadt Leipzig die Anfragen weiterer Rüstungsunternehmen offengelegt.</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54041/Leipzig-hat-weitere-Anfragen-von-Ruestungsunternehmen.html</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr"/>
+      <c r="L641" t="inlineStr"/>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>auto-4f73ad5be321</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Reifenplatzer im Startlauf</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr"/>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Im fortgeschrittenen Startlauf platzt ein Reifen einer Lufthansa-Maschine. Es geht glimpflich aus - mit an Bord ist ein ehemaliger Formel-1-Rennfahrer.</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54040/Reifenplatzer-im-Startlauf.html</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr"/>
+      <c r="L642" t="inlineStr"/>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N642" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>auto-0a6428b21b09</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Lufthansa stellt "Inbound Tankering" in Frankfurt wieder ein</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr"/>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Der Frankfurter Flughafen ist wieder flüssig: Lufthansa stellt Tankering-Maßnahmen am Drehkreuz ein. Der Konzern hatte wegen einer zwischenzeitlich angespannten Versorgungslage Piloten im Oktober 2026 angehalten, für Flüge nach Frankfurt zusätzliche Kerosinmengen zu tanken.</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54035/Lufthansa-stellt-Inbound-Tankering-in-Frankfurt-wieder-ein.html</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr"/>
+      <c r="L643" t="inlineStr"/>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N643" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>auto-b90c3fec935c</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>TAP flight TP780 is declaring an emergency and diverting to France - airlive</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr"/>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirAFBVV95cUxOMEktWVZvNnh6VHhMWGpyRmsyWjVvOGJJMzRFQnlMTGJVMVA3dmI5TS01ZUphNGwxNjZJUzEyOG50a05KY0xwaF9sRnd2b0Q0SGpWSkcxMEJ4Y0pIUzBkMXpQSUkyNHJDQnRwR3RodzMxNDk3cE1CaUYzR2JaRUg4eDZNbzZLSzVyakU1TllMQ2hWN0JHUFNsS0VFNHVUUEpKM1UxcU1JU2JDTC150gG0AUFVX3lxTE9ZdW5pN0VlaFdQNTRlQ090LWtvSXR2UkxDdXRIZUFCdFl0azRQejg3MlNzV3UxcnZUZV9jWGRJQjZBOTVUaVkzMTBYbXViOFV6MHVkOFRZakktalZkZ2xiQTM2dFpXWVE1MmpoeWM0a0tqMkJmamhwd2U2VHM2UHpJR2tPVTdRZmZaT2UxRm9SRngwUUhUanlMNnVXbG95dEhzdzZmc2NZN0J3eUVsREQwcDlqbg?oc=5" target="_blank"&gt;TAP flight TP780 is declaring an emergency and diverting to France&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOMEktWVZvNnh6VHhMWGpyRmsyWjVvOGJJMzRFQnlMTGJVMVA3dmI5TS01ZUphNGwxNjZJUzEyOG50a05KY0xwaF9sRnd2b0Q0SGpWSkcxMEJ4Y0pIUzBkMXpQSUkyNHJDQnRwR3RodzMxNDk3cE1CaUYzR2JaRUg4eDZNbzZLSzVyakU1TllMQ2hWN0JHUFNsS0VFNHVUUEpKM1UxcU1JU2JDTC150gG0AUFVX3lxTE9ZdW5pN0VlaFdQNTRlQ090LWtvSXR2UkxDdXRIZUFCdFl0azRQejg3MlNzV3UxcnZUZV9jWGRJQjZBOTVUaVkzMTBYbXViOFV6MHVkOFRZakktalZkZ2xiQTM2dFpXWVE1MmpoeWM0a0tqMkJmamhwd2U2VHM2UHpJR2tPVTdRZmZaT2UxRm9SRngwUUhUanlMNnVXbG95dEhzdzZmc2NZN0J3eUVsREQwcDlqbg?oc=5</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr"/>
+      <c r="L644" t="inlineStr"/>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N644" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>auto-62dff046bd22</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Air Europa flight from Panama to Madrid makes emergency landing in Tenerife for a sick passenger - Aviation24.be</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr"/>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi2wFBVV95cUxNVWRsUG84bzdMRzR2ZDFZdU5mRnZjM2E4ZjBsdnIzYmN1WmpDVm1ELWdlb0VHWFYtMVViS3ZBSzNIZUtueXZ1NXVHRUhmcTI1bTJpX21Zd0NoTDJ6bGdYTmxpVmZYQXhraVZhWWV0MFJZdWExRjVMeTN1T0dMbXRKZlZXRXUtdGhGTUZsb0ZFbklsSG53UU96UXJONkFtX3dJSlVSbms0dVR5aHBDRU5sWEtzTC05TnZiUG5xQUNjTC0zOVVRTU81TTVSTjFPSVp5LTNQMW5pNGxJbmvSAeABQVVfeXFMTjF3dkVudWpGcjNwN2NvdjJDWkNoVWNTYUl4OUFOYURlWFUxVmZfVEdxRXg0TEF4NWJWQkZUendvNUhfTjJqb0JLd3lTUndJVHAxaktXWGl5QVBqd2NYdFgzYUU5anU5UzdybUFMbkE1b0xzMzhYd3kxd2NkcjVSa0dubWFNTDE1VTl1NFVtLUpIaTg3NTlQaWw1SUJfMlVjYUpSRW15d1VqMVJEWDNwWHRyOVhKVjl2Nkl3Vm1pTU9xR3hPdEQtZENmLUZJdE1SNEJpa09QNFpBSmhmanVQNWs?oc=5" target="_blank"&gt;Air Europa flight from Panama to Madrid makes emergency landing in Tenerife for a sick passenger&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Aviation24.be&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNVWRsUG84bzdMRzR2ZDFZdU5mRnZjM2E4ZjBsdnIzYmN1WmpDVm1ELWdlb0VHWFYtMVViS3ZBSzNIZUtueXZ1NXVHRUhmcTI1bTJpX21Zd0NoTDJ6bGdYTmxpVmZYQXhraVZhWWV0MFJZdWExRjVMeTN1T0dMbXRKZlZXRXUtdGhGTUZsb0ZFbklsSG53UU96UXJONkFtX3dJSlVSbms0dVR5aHBDRU5sWEtzTC05TnZiUG5xQUNjTC0zOVVRTU81TTVSTjFPSVp5LTNQMW5pNGxJbmvSAeABQVVfeXFMTjF3dkVudWpGcjNwN2NvdjJDWkNoVWNTYUl4OUFOYURlWFUxVmZfVEdxRXg0TEF4NWJWQkZUendvNUhfTjJqb0JLd3lTUndJVHAxaktXWGl5QVBqd2NYdFgzYUU5anU5UzdybUFMbkE1b0xzMzhYd3kxd2NkcjVSa0dubWFNTDE1VTl1NFVtLUpIaTg3NTlQaWw1SUJfMlVjYUpSRW15d1VqMVJEWDNwWHRyOVhKVjl2Nkl3Vm1pTU9xR3hPdEQtZENmLUZJdE1SNEJpa09QNFpBSmhmanVQNWs?oc=5</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr"/>
+      <c r="L645" t="inlineStr"/>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N645" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O645" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O645"/>
+  <dimension ref="A1:O655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39889,7 +39889,6 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="D637" t="inlineStr"/>
       <c r="E637" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -39920,8 +39919,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
-      <c r="L637" t="inlineStr"/>
       <c r="M637" t="inlineStr">
         <is>
           <t>review</t>
@@ -39954,7 +39951,6 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="D638" t="inlineStr"/>
       <c r="E638" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -39985,8 +39981,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
-      <c r="L638" t="inlineStr"/>
       <c r="M638" t="inlineStr">
         <is>
           <t>review</t>
@@ -40019,7 +40013,6 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40050,8 +40043,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
-      <c r="L639" t="inlineStr"/>
       <c r="M639" t="inlineStr">
         <is>
           <t>review</t>
@@ -40084,7 +40075,6 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40115,8 +40105,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
-      <c r="L640" t="inlineStr"/>
       <c r="M640" t="inlineStr">
         <is>
           <t>review</t>
@@ -40149,7 +40137,6 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40180,8 +40167,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
-      <c r="L641" t="inlineStr"/>
       <c r="M641" t="inlineStr">
         <is>
           <t>review</t>
@@ -40214,7 +40199,6 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40245,8 +40229,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
-      <c r="L642" t="inlineStr"/>
       <c r="M642" t="inlineStr">
         <is>
           <t>review</t>
@@ -40279,7 +40261,6 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40310,8 +40291,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
-      <c r="L643" t="inlineStr"/>
       <c r="M643" t="inlineStr">
         <is>
           <t>review</t>
@@ -40344,7 +40323,6 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr"/>
       <c r="E644" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40375,8 +40353,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
-      <c r="L644" t="inlineStr"/>
       <c r="M644" t="inlineStr">
         <is>
           <t>review</t>
@@ -40409,7 +40385,6 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="D645" t="inlineStr"/>
       <c r="E645" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -40440,8 +40415,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
-      <c r="L645" t="inlineStr"/>
       <c r="M645" t="inlineStr">
         <is>
           <t>review</t>
@@ -40453,6 +40426,656 @@
         </is>
       </c>
       <c r="O645" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>auto-7e2173ce19f6</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Bis zu 20.000 Mahlzeiten täglich: GIC International Catering eröffnet neuen Standort beim Flughafen München</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr"/>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>GIC International Catering eröffnet am 15. November einen neuen Produktionsstandort nahe dem Flughafen München. Wie das Unternehmen, das in der Nähe von Frankfurt am Main beheimatetet ist, mitteilt, soll die rund 2500 Quadratmeter große Anlage noch im November mit 80 Beschäftigten die Produktion aufnehmen. Die Kapazität liegt bei bis zu 20.000 Mahlzeiten täglich. Zudem verlängerte GIC die Verträge mit Air Astana und Ethiopian Airlines um jeweils drei Jahre. In China beliefert das Unternehmen seit diesem Frühjahr Air China auf Flügen von Frankfurt nach Peking-Daxing und seit Juni auch China Eastern Airlines. Die Zahl der Beschäftigten stieg nach Unternehmensangaben von 140 Ende 2025 auf inzwischen 270.</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/bis-zu-20000-mahlzeiten-taeglich-gic-international-catering-eroeffnet-neuen-standort/fhxwe6p</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr"/>
+      <c r="L646" t="inlineStr"/>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>auto-275465eb24df</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Virgin Atlantic erbost, dass Partnerin Delta Air Lines in London-Heathrow das Terminal wechseln soll</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr"/>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>Virgin Atlantic kritisiert Pläne, ihre Joint-Venture-Partnerin Delta Air Lines ab 2028 vom Terminal 3 ins Terminal 4 des Flughafens London-Heathrow zu verlegen. Wie der britische Sender &lt;a href="https://news.sky.com/story/virgin-atlantic-fury-as-heathrow-forces-delta-terminal-move-13604337" id="febf3eac-127b-41bc-baef-54cc17eb577c"&gt;Sky News&lt;/a&gt; berichtet, soll Delta dort näher bei den Skyteam-Partnern Air France und KLM angesiedelt werden. Virgin Atlantic würde dagegen im Terminal 3 bleiben. Virgin-Chef Corneel Koster warnte, die Trennung der beiden Airlines werde Umsteigeverbindungen erschweren, den Wettbewerb schwächen und die Auswahl für Reisende einschränken. Der Flughafen Heathrow begründet die Neuverteilung mit einer effizienteren Nutzung der Terminals, besseren Passagierströmen und mehr betrieblicher Stabilität. Laut Sky News unterstützen Airlines, auf die 81 Prozent des Passagieraufkommens entfallen, die Pläne.</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/virgin-atlantic-erbost-dass-partnerin-delta-air-lines-in-london-heathrow-das-terminal/g61r019</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr"/>
+      <c r="L647" t="inlineStr"/>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N647" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>auto-8e2b60ddc368</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Steht hier ein neues chinesisches Regionalflugzeug mit Elektroantrieb?</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr"/>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>Bilder sollen ein neues chinesisches Regionalflugzeug mit Elektroantrieb zeigen - die Comac CE-25A. Doch viele Fragen sind noch offen.</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugzeuge/steht-hier-ein-neues-chinesisches-regionalflugzeug-mit-elektroantrieb/7v2tg0c</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr"/>
+      <c r="L648" t="inlineStr"/>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N648" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>auto-09f905ec4e32</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Boeing stellt Airlines 2027 bis zu 15 777-9 in Aussicht</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr"/>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa plant auch den Flugsommer 2027 ohne die Boeing 777-9. Am Drehkreuz Frankfurt absolvieren stattdessen Airbus A340-300 eine weitere Nachspielzeit. Trotz neuer Verzögerungen will Boeing im nächsten Jahr bis zu 15 777-9 an frühe Betreiber wie Lufthansa ausliefern.</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54052/Boeing-stellt-Airlines-2027-bis-zu-15-777-9-in-Aussicht.html</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr"/>
+      <c r="L649" t="inlineStr"/>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N649" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>auto-64029f90cb7e</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Discover Airlines steckt erste A350-Ziele ab</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr"/>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Der erste Airbus A350-900 stößt nach aktueller Planung im Juni 2027 zur Flotte von Discover Airlines. Der Lufthansa-Ferienflieger will den Neuzugang auf einer eingespielten Transatlantiklinie einspulen.</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54048/Discover-Airlines-steckt-erste-A350-Ziele-ab.html</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr"/>
+      <c r="L650" t="inlineStr"/>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N650" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>auto-01b496e9f734</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Condor einigt sich bis 2029 mit Piloten</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr"/>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Anders als ihre große Konkurrentin Lufthansa hat die Fluggesellschaft Condor mit ihren Piloten einen langfristigen Tariffrieden geschlossen - der Gewerkschaft Vereinigung Cockpit (VC) zufolge hat man sich auf einen Tarifvertrag bis Ende September 2029 geeinigt. Bis dahin gilt ein Kündigungsschutz für die rund 1.000 Beschäftigten.</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54046/Condor-einigt-sich-bis-2029-mit-Piloten.html</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr"/>
+      <c r="L651" t="inlineStr"/>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N651" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>auto-3b3ac51c0d36</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport: Lufthansa reagiert auf drohenden Kerosinmangel - Manager Magazin</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr"/>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi7gFBVV95cUxOdktGOUxWR090WlpRMkw1RVItYVptT0xiRXNIbHU0N01UQjBKZ2s5S3ZZM1dsLWk4SkVtUVNtWHc5dmhsbVQ2TU05YXVua2lMZTNva2FxTElKZnhhdnNjT2pEWGVnVUNPRWlLa3ozamVjMFY0RVdsMDBfbEZpcmRidXJYZy1TaDl5OE9UV1FCWFhHTVpWRFFlX0F1YnVKZVVoRWxCZ284d0NWTjE0N29DSmtBUGJkQWRaLTRENGE5SThqd2FJeG5KTjMyT1JBNjVkMHNoYXJCLVJ6MlhZVUNENERLUjJwQkttQ0wzcGd3?oc=5" target="_blank"&gt;Frankfurt Airport: Lufthansa reagiert auf drohenden Kerosinmangel&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Manager Magazin&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOdktGOUxWR090WlpRMkw1RVItYVptT0xiRXNIbHU0N01UQjBKZ2s5S3ZZM1dsLWk4SkVtUVNtWHc5dmhsbVQ2TU05YXVua2lMZTNva2FxTElKZnhhdnNjT2pEWGVnVUNPRWlLa3ozamVjMFY0RVdsMDBfbEZpcmRidXJYZy1TaDl5OE9UV1FCWFhHTVpWRFFlX0F1YnVKZVVoRWxCZ284d0NWTjE0N29DSmtBUGJkQWRaLTRENGE5SThqd2FJeG5KTjMyT1JBNjVkMHNoYXJCLVJ6MlhZVUNENERLUjJwQkttQ0wzcGd3?oc=5</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr"/>
+      <c r="L652" t="inlineStr"/>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N652" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>auto-084a02b29282</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Ausflugsziel Airport - Fraport AG</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr"/>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMinwFBVV95cUxQandmaEhEQVBJUEtTbEYxWm9NcnItLVNmeF9hZFN6RDhOYWcwXzNwdEdsa2ZyX2NVNzNsUXp5RDhaZk5fVXhoNW41cUlSajQ0aDRmMGJSeGVZY0VzUWltb0Nhai1yeWQ5M3h5MEtub2Q5Y0NZRVRJZm9UNGZvazRuVDgtR3k2U0t5UlVUWDZYZlQzT2lrVjdmQTh2d3RWNUE?oc=5" target="_blank"&gt;Ausflugsziel Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Fraport AG&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQandmaEhEQVBJUEtTbEYxWm9NcnItLVNmeF9hZFN6RDhOYWcwXzNwdEdsa2ZyX2NVNzNsUXp5RDhaZk5fVXhoNW41cUlSajQ0aDRmMGJSeGVZY0VzUWltb0Nhai1yeWQ5M3h5MEtub2Q5Y0NZRVRJZm9UNGZvazRuVDgtR3k2U0t5UlVUWDZYZlQzT2lrVjdmQTh2d3RWNUE?oc=5</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr"/>
+      <c r="L653" t="inlineStr"/>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N653" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>auto-93999b83bfe9</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Party-Sommer am Flughafen - Fraport AG</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr"/>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMimAFBVV95cUxOSDJGbzVNRGZkWDNTOTdjZzNxMXdjWTlCd08zNEFPS1NZTFg1N0dBT2hWMF83Mk1iZkR0eUhxS3Y4NGNmRWZnclZOdXhEV0ZPN0hJbkdFTWp1enpGR19aYkdYOUFpVHE2WVFDYWJKUnJhQmNxRUszZjg1U1NScVFycEhPc2hKU3BBODJVOC0zaTllOE9qUG9TRQ?oc=5" target="_blank"&gt;Party-Sommer am Flughafen&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Fraport AG&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOSDJGbzVNRGZkWDNTOTdjZzNxMXdjWTlCd08zNEFPS1NZTFg1N0dBT2hWMF83Mk1iZkR0eUhxS3Y4NGNmRWZnclZOdXhEV0ZPN0hJbkdFTWp1enpGR19aYkdYOUFpVHE2WVFDYWJKUnJhQmNxRUszZjg1U1NScVFycEhPc2hKU3BBODJVOC0zaTllOE9qUG9TRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr"/>
+      <c r="L654" t="inlineStr"/>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N654" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>auto-07501cbb948e</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Oman Air: Oneway-Tickets von Kuala Lumpur nach Frankfurt ab 183€ (209€ inkl. Gepäck) - Travel-Dealz</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr"/>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMibkFVX3lxTE1CSkpVWEktc3FuM0xhX1prZlNGRjU1azl2N2pwbm5xTlVjalptc1ZCemJaSkYxcHY0U3VWRVJ2bDh1bnhzQnVXS1RwWDZLaDZYUzcxblB4OUxaamJmYU1xa3JlbHJhWDlNTnFrY2t3?oc=5" target="_blank"&gt;Oman Air: Oneway-Tickets von Kuala Lumpur nach Frankfurt ab 183€ (209€ inkl. Gepäck)&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Travel-Dealz&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1CSkpVWEktc3FuM0xhX1prZlNGRjU1azl2N2pwbm5xTlVjalptc1ZCemJaSkYxcHY0U3VWRVJ2bDh1bnhzQnVXS1RwWDZLaDZYUzcxblB4OUxaamJmYU1xa3JlbHJhWDlNTnFrY2t3?oc=5</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr"/>
+      <c r="L655" t="inlineStr"/>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N655" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O655" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O655"/>
+  <dimension ref="A1:O663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40447,7 +40447,6 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="D646" t="inlineStr"/>
       <c r="E646" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40478,8 +40477,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
-      <c r="L646" t="inlineStr"/>
       <c r="M646" t="inlineStr">
         <is>
           <t>review</t>
@@ -40512,7 +40509,6 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="D647" t="inlineStr"/>
       <c r="E647" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40543,8 +40539,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
-      <c r="L647" t="inlineStr"/>
       <c r="M647" t="inlineStr">
         <is>
           <t>review</t>
@@ -40577,7 +40571,6 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="D648" t="inlineStr"/>
       <c r="E648" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40608,8 +40601,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
-      <c r="L648" t="inlineStr"/>
       <c r="M648" t="inlineStr">
         <is>
           <t>review</t>
@@ -40642,7 +40633,6 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="D649" t="inlineStr"/>
       <c r="E649" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40673,8 +40663,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
-      <c r="L649" t="inlineStr"/>
       <c r="M649" t="inlineStr">
         <is>
           <t>review</t>
@@ -40707,7 +40695,6 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="D650" t="inlineStr"/>
       <c r="E650" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40738,8 +40725,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
-      <c r="L650" t="inlineStr"/>
       <c r="M650" t="inlineStr">
         <is>
           <t>review</t>
@@ -40772,7 +40757,6 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="D651" t="inlineStr"/>
       <c r="E651" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40803,8 +40787,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
-      <c r="L651" t="inlineStr"/>
       <c r="M651" t="inlineStr">
         <is>
           <t>review</t>
@@ -40837,7 +40819,6 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40868,8 +40849,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
-      <c r="L652" t="inlineStr"/>
       <c r="M652" t="inlineStr">
         <is>
           <t>review</t>
@@ -40902,7 +40881,6 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40933,8 +40911,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
-      <c r="L653" t="inlineStr"/>
       <c r="M653" t="inlineStr">
         <is>
           <t>review</t>
@@ -40967,7 +40943,6 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="D654" t="inlineStr"/>
       <c r="E654" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -40998,8 +40973,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
-      <c r="L654" t="inlineStr"/>
       <c r="M654" t="inlineStr">
         <is>
           <t>review</t>
@@ -41032,7 +41005,6 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="D655" t="inlineStr"/>
       <c r="E655" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -41063,8 +41035,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
-      <c r="L655" t="inlineStr"/>
       <c r="M655" t="inlineStr">
         <is>
           <t>review</t>
@@ -41076,6 +41046,526 @@
         </is>
       </c>
       <c r="O655" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>auto-b90bea66056d</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Icao will Luftrecht an neue Technologien anpassen - auch zu Luftfahrzeugen ohne Piloten</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr"/>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>Die Internationale Zivilluftfahrtorganisation Icao will das internationale Luftrecht an neue Entwicklungen in der Luftfahrt anpassen. Der Rechtsausschuss der Organisation hat dazu bei seiner 40. Sitzung Empfehlungen verabschiedet. Ein Schwerpunkt ist die Frage, wie bestehende internationale Regeln für Luftfahrzeuge ohne Piloten an Bord gelten.</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/icao-will-luftrecht-an-neue-technologien-anpassen-auch-zu-luftfahrzeugen-ohne-piloten/y1xnlmd</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr"/>
+      <c r="L656" t="inlineStr"/>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N656" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>auto-f1c2845ec215</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Philippine Airlines setzt Airbus A350-1000 täglich nach San Francisco ein</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr"/>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>Philippine Airlines setzt ihren Airbus A350-1000 vorübergehend täglich auf der Strecke Manila - San Francisco ein, auf der sonst zweitweise auch eine Boeing 777-300 ER unterwegs ist.</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/philippine-airlines-setzt-airbus-a350-1000-taeglich-nach-san-francisco-ein/m7ddegj</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr"/>
+      <c r="L657" t="inlineStr"/>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N657" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>auto-73e585c7026a</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Frankreich erprobt erstes Aufklärungsflugzeug Dassault Falcon 8X Archange</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr"/>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>Frankreich hat mit der technischen und operationellen Erprobung seines ersten Aufklärungsflugzeugs Dassault Falcon 8X Archange begonnen. Wie das Verteidigungsministerium am 27. Oktober mitteilte, landete das Flugzeug am 7. Oktober auf dem Luftwaffenstützpunkt Évreux in der Normandie. Dort testet das militärische Erprobungszentrum gemeinsam mit der Beschaffungsbehörde DGA sowie den Herstellern Dassault Aviation und Thales das Flugzeug und seine Ausrüstung. Das System soll gegnerische elektromagnetische Signale erfassen und auswerten. Es ersetzt die 2022 ausgemusterten Aufklärungsflugzeuge vom Typ Transall C-160G Gabriel. Frankreich plant insgesamt drei Archange-Flugzeuge; die Auslieferung ist für 2028 bis 2029 vorgesehen.</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker-verteidigung/frankreich-erprobt-erstes-aufklaerungsflugzeug-dassault-falcon-8x-archange/e7ep72y</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr"/>
+      <c r="L658" t="inlineStr"/>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N658" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>auto-582082519ac6</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Zulieferprobleme treffen auch Cessna und Beechcraft</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr"/>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>Die Nachfrage nach Cessna Citation und Beechcraft King Air ist so hoch wie lange nicht. Doch Textron Aviation kommt mit der Produktion nicht hinterher. Denn es fehlen Triebwerke, Flügelholme und andere Bauteile.</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/business-aviation/zulieferprobleme-bremsen-produktion-von-cessna-und-beechcraft/hd6k51n</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr"/>
+      <c r="L659" t="inlineStr"/>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N659" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>auto-9a6e93e2c120</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Binter stockt Flüge zwischen Kanareninseln auf</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr"/>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>Binter bietet zum verlängerten Allerheiligen-Wochenende mehr Flüge zwischen den Kanarischen Inseln an. Vom 30. Oktober bis zum 2. November plant die Fluggesellschaft insgesamt 942 Verbindungen mit 69.562 Sitzplätzen. Das sind an den drei besonders nachfragestarken Tagen 30. und 31. Oktober sowie 2. November zusammen 4010 Plätze mehr als im regulären Flugplan. Die größten zusätzlichen Kapazitäten entfallen auf die Strecken zwischen Gran Canaria und La Palma mit 576 Plätzen sowie zwischen Lanzarote und Teneriffa Nord mit 566 zusätzlichen Sitzen. Auch die Verbindungen von Gran Canaria nach El Hierro und Teneriffa Süd werden jeweils um 292 Plätze erweitert.</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/binter-stockt-fluege-zwischen-kanareninseln-auf/zmb57be</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr"/>
+      <c r="L660" t="inlineStr"/>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N660" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>auto-f2ce4dda2fc0</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Neue Flugverbindung von Emden nach Dänemark</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr"/>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>EMDEN - Dreimal pro Woche können Passagiere jetzt zwischen Emden und Esbjerg mit dem Flugzeug reisen. An wen sich das Angebot richtet und welche Nachfrage die Airline erwartet.</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54057/Neue-Flugverbindung-von-Emden-nach-Daenemark.html</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K661" t="inlineStr"/>
+      <c r="L661" t="inlineStr"/>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N661" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>auto-3067e5e6f5b7</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Lufthansa greift tief in die Erinnerungskiste</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr"/>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Schon seit einigen Monaten ist ein Airbus A321neo für Lufthansa mit einem außergewöhnlichen Design unterwegs. Nach jüngsten Ergänzungen ist die Jubiläumsbeklebung auf der D-AIEM vollständig. Zwölf Motive erzählen persönliche Geschichten von Lufthansa-Mitarbeitern und -Wegbegleitern.</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-54054/Lufthansa-D-AIEM-A321neo.html</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr"/>
+      <c r="L662" t="inlineStr"/>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N662" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>auto-b596bd552e23</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>The week in pictures: Disaster averted on Flydubai flight, French school protests and Bangkok floods - France 24</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr"/>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi3AFBVV95cUxQNWM5alk1UG84UURzX0RGWHJGcmJBcGZuX1lUdVZudUFfNjJNUDlNSkd3MzRCczJUTUhfOWNScmV3U3d6VkVpdTJ0bTJpaE9mYXVlZTFsRXVBcjVwemVmUEhEdlIxM1pJQnQ2XzFxSy1ESWsxUjYybFJ6UDVqZkZibUhsQnJOU3JpRVZIRW5KSU9xU3BRbjhKcUVEWXd3bUM5alZLemZIdFREc0tzWVpLb09HTDV2R2Q1VFpaV3ZFQWE3VmRtYzVTOFlqbTNaeVJqb1I3VHQydnZJVHRl?oc=5" target="_blank"&gt;The week in pictures: Disaster averted on Flydubai flight, French school protests and Bangkok floods&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;France 24&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQNWM5alk1UG84UURzX0RGWHJGcmJBcGZuX1lUdVZudUFfNjJNUDlNSkd3MzRCczJUTUhfOWNScmV3U3d6VkVpdTJ0bTJpaE9mYXVlZTFsRXVBcjVwemVmUEhEdlIxM1pJQnQ2XzFxSy1ESWsxUjYybFJ6UDVqZkZibUhsQnJOU3JpRVZIRW5KSU9xU3BRbjhKcUVEWXd3bUM5alZLemZIdFREc0tzWVpLb09HTDV2R2Q1VFpaV3ZFQWE3VmRtYzVTOFlqbTNaeVJqb1I3VHQydnZJVHRl?oc=5</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr"/>
+      <c r="L663" t="inlineStr"/>
+      <c r="M663" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N663" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O663" t="inlineStr">
         <is>
           <t>no</t>
         </is>
